--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L172"/>
+  <dimension ref="A1:L173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.8）
+          <t>俄洛伊附加包（league_illaoi v0.2.9）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -4929,49 +4929,114 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>斯卡纳</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Skarner</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>league_skarner</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>毒刺扎击。战栗：普攻、巨石、毒刺打中英雄叠层，满3层4秒内每秒掉最大生命1%。震地壁垒：冲锋停下时得40 + 20% 攻击力护盾3秒，震伤周围20 + 30% 攻击力、减速30%。
+（攻击间隔 1.33 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>撼地：掘起巨石6秒，攻速+20%；3次普攻溅射10 + 20% 攻击力，第3次加最大生命3%、减速40%。举满3秒就扔出擎天：50 + 80% 攻击力+最大生命3%。
+（冷却 1 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>以绪塔尔冲击：冲向敌方英雄，撞上后拖着走，停下时造成60 + 80% 攻击力物理伤害并晕眩0.67秒。
+（冷却 1 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>毒刺贯体：三根毒刺往前扎：直线上的敌方英雄受到60 + 50% 攻击力物理伤害，被压制0.75秒并拖到身边跟着走；扎中后移速+30%2.5秒。
+（冷却 80 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>斯卡纳附加包（league_skarner v0.1.0）
+战栗：层数叠在每个英雄身上（按这个斯卡纳起名），满 p_n 层开始战栗：每 p_p 拍最大生命 p_pct% 的魔法伤害，战栗中不再叠层
+以绪塔尔冲击：拖的路上碰到墙才砸、才晕（伤害 e_wall_dmg + e_ratio% 攻击力 + 最大生命 e_wall_hp%），没墙就只是拖走
+毒刺贯体：只压最先碰到的 r_n 个英雄：魔法伤害、压制 r_sup 拍，压制期间每拍摆在他身边（保持被打中时的方向，离他最多 R_GAP），他走到哪拖到哪</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_skarner.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>特朗德尔</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Trundle</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>league_trundle</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>抡冰棒。国王的贡品：打死单位回复12 + 8% 攻击力生命，冰面上双倍。冰封领域：利齿撕咬咬中英雄时冻住地面8秒（每12秒一次），其间攻速+50%、移速+15%。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>利齿撕咬：咬一口造成40 + 130% 攻击力物理伤害并减速60%；4秒内对方攻击力-15%，自己+20%。
 （冷却 1 秒 · 施放距离 25000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>寒冰之柱：在敌方英雄处立起寒冰之柱4秒，周围敌人减速25%。
 （冷却 1 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>强权至上：吸取敌方英雄：立刻造成最大生命10%真实伤害，4秒内每秒再3%，每次回复20 + 10% 攻击力生命；偷走25%护甲和魔抗8秒。
 （冷却 80 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>特朗德尔附加包（league_trundle v0.1.0）
 国王的贡品：他身边 p_r 内任何敌方单位倒下（谁打死的都算）都回它最大生命 p_pct% 的血，冰面上翻倍
@@ -4981,185 +5046,185 @@
 强权至上：偷走目标自己护甲、魔抗的 r_steal%（r_t + r_keep 拍），伤害是魔法伤害（立刻 r_pct0%、之后每 r_p 拍 r_pct% 最大生命），打掉多少血就回多少…</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="3" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_trundle.md</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>乌迪尔</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Udyr</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>league_udyr</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>拳击目标。众灵纽带：放技能后两次攻击攻速+30%。坚铁甲胄：每12秒首个技能附带70 + 40% 攻击力护盾，之后两次攻击各回复15 + 20% 攻击力生命。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>狂暴爪击：熊姿态：攻速+30%持续4秒，下两次攻击额外造成15 + 35% 攻击力+目标4%最大生命值。觉醒（熊姿态再放）：攻速+60%，两次攻击引来闪电，造成25 + 35% 攻击力魔法伤害。
 （冷却 6 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>踏火蛮冲：公羊姿态：移速+35%，冲向敌方英雄，撞击造成25 + 100% 攻击力物理伤害并晕眩0.75秒。觉醒（公羊姿态再放）：移速+60%，1.5秒免疫控制。
 （冷却 10 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>极凌飓风：凤凰姿态：冰风暴环绕自身4秒，每0.5秒对周围敌人造成18 + 22% 攻击力魔法伤害并减速25%；结束时风暴飞向一名敌方英雄，造成60 + 60% 攻击力魔法伤害并减速40%。
 （冷却 40 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>乌迪尔附加包（league_udyr v0.1.0）
 Native add-on for Udyr in *League of Legends Heroes* (league). It replaces the main pack's Udyr with a copy (override/league_udyr.data_champion, made by make_override.py from tool…</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="3" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_udyr.md</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>蔚</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Vi</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>league_vi</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力物理伤害。爆弹重拳：每第3次普攻额外造成20物理伤害（对英雄再加5%最大生命），减护甲20%，自身攻速+30%，均4秒。爆裂护盾：技能命中敌人获得100+60% 攻击力护盾3秒，冷却12秒，第3次普攻减3秒。
 （攻击间隔 1 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>强能冲拳：蓄力0.5秒（开始蓄力时锁定方向）后向前冲刺，对路上的敌人造成60+100% 攻击力物理伤害；撞到第一个英雄时停下并击退他，叠1层爆弹重拳，之后1.5秒内施放透体之劲会立刻出拳。
 （冷却 8 秒 · 施放距离 45000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>透体之劲：2层充能（每层8秒）。下一次普攻变为透体之劲，对目标和其身后扇形内的敌人造成30+110% 攻击力物理伤害。
 （冷却 16 秒 · 可存 2 次 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>天霸横空烈轰：锁定一名敌方英雄冲过去，期间免疫控制；撞开路上的敌人，造成75+60% 攻击力物理伤害并眩晕0.75秒；到达后将目标击飞1.25秒并造成150+120% 攻击力物理伤害，下一拳自带透体之劲。
 （冷却 50 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="3" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_vi.md</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>佛耶戈</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Viego</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>league_viego</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>君命已决：他伤过的敌方英雄3秒内阵亡则附身其灵魂10秒：1秒无敌，回复60 + 50% 攻击力，攻击+20%、攻速+30%、移速+15%，Q、W冷却减半。普攻附加英雄最大生命2%。
 （攻击间隔 1.07 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>破败王剑：向前刺出，造成50 + 70% 攻击力伤害。刺中的英雄被标记4秒，下次普攻对其斩两下：再造成20 + 60% 攻击力伤害并回复30 + 30% 攻击力。
 （冷却 5.5 秒 · 施放距离 36000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>千载幽咽：茫茫焦土：黑雾升起，5秒内移速+30%、攻速+40%，站在黑雾里（留2.5秒）时隐身。随后冲刺并吐出亡魂，第一个被击中的敌人受到90 + 70% 攻击力伤害并眩晕1.1秒。
 （冷却 10 秒 · 施放距离 46000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>痛贯天灵：跃向队伍正在交手的敌方英雄并减速99%，落地刺穿它，造成120 + 120% 攻击力+其最大生命12%伤害，击退周围其他敌人。结束附身。
 （冷却 50 秒 · 施放距离 42000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.3）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
@@ -5170,317 +5235,317 @@
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="3" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_viego.md</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>沃里克</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Warwick</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>league_warwick</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>挥爪。血之饥渴：普攻附带20魔法伤害并回复8生命。鲜血追猎：打中英雄后2秒内攻速+30%、移速+12%。
 （攻击间隔 1 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>野兽之口：扑向目标撕咬，造成30 + 110% 攻击力+5%目标最大生命值物理伤害，回复30 + 40% 攻击力生命。
 （冷却 6 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>远祖嗥叫：2.5秒内受到的伤害减少40%，结束时仰天嚎叫，让周围的敌人恐惧1秒。
 （冷却 12 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>无尽束缚：朝前扑出，压制撞到的第一个敌方英雄1.5秒，期间连抓三下，每下50 + 55% 攻击力物理伤害并回复40生命。
 （冷却 60 秒 · 施放距离 90000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>沃里克附加包（league_warwick v0.1.1）
 主包 league 保持纯数据。用户选了「做附加包」，又要求「有连招要做连招」。主包的数据读不到当前生命，英雄联盟里沃里克最核心的两件事——残血吸血和鲜血追猎——都看生命，所以放在这个附加包里用原生代码做，外加连招： - 血之饥渴：英雄联盟里沃里克的普攻附带魔法伤害；他生命低于 50% 时回复同样多的生命，低于 25% 时回三倍。主包只能每下固定回一点；副…</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="3" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_warwick.md</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>孙悟空</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Wukong</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>league_wukong</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>金箍棒横扫。金刚不坏：打中英雄叠1层（最多5层）：每层护甲+4、每秒回复2生命。粉碎打击：每4秒下一次普攻伸长棒子，多造成30 + 50% 攻击力物理伤害，目标护甲-20%，持续3秒。
 （攻击间隔 1 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>腾云突击：腾云冲向目标，分身打中目标和附近最多2个敌人，各造成40 + 70% 攻击力物理伤害；之后攻击速度+40%，持续5秒。
 （冷却 8 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>真假猴王：隐身1秒冲到敌方英雄身后，原地留下分身4秒：每秒打身边一个敌人（英雄优先），造成50% 攻击力物理伤害；他放大招时分身也跟着转。
 （冷却 20 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>大闹天宫：伸长金箍棒旋转2秒，每0.25秒造成10 + 35% 攻击力外加英雄2%最大生命的物理伤害，第一下击飞0.6秒；8秒内可再转一次。身边有敌方英雄时才放。
 （冷却 60 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>悟空附加包（league_wukong v0.1.0）
 金刚不坏的回血：每 5 秒回复最大生命的 0.35%，每层再多 0.35%（叠满 5 层 2.1%，英雄联盟）</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="3" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_wukong.md</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>赵信</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Xin Zhao</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>league_xinzhao</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>长枪攻击。被动果决：每第三次攻击额外造成40% 攻击力物理伤害，并回复15 + 15% 攻击力生命。
 （攻击间隔 1 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>无畏冲锋：冲向目标，对周围敌人造成40 + 50% 攻击力物理伤害并减速30%，攻击速度+40%，持续5秒。随后三重爪击：接下来3次攻击各额外造成20 + 30% 攻击力，第三次击飞0.75秒。
 （冷却 9 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>风斩电刺：先横扫面前，造成20 + 40% 攻击力物理伤害；再向前直刺，造成40 + 65% 攻击力物理伤害并减速50%，持续1.5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>新月护卫：横扫周围，造成100 + 100% 攻击力加目标最大生命值10%的物理伤害，除被挑战的目标（施放对象）外全部击退。之后3秒内受到的伤害降低40%。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>赵信大招远程免伤附加包（league_xinzhao_guard v0.1.0）
 主包 league 保持纯数据。英雄联盟里赵信的 R「新月护卫」之后，他免疫 450 码外敌人的伤害；数据读不到伤害来自多远， 所以主包里改成 R 之后 3 秒受到的伤害降低 40%（用户选的）。用户：「读不到多远就改rust源代码 看看能不能」—— 这个附加包用原生代码读攻击者的位置，做成英雄联盟的样子： - 远处的伤害挡掉：主包的护卫 buff lea…</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="3" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_xinzhao.md</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>扎克</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Zac</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>league_zac</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>拳击。不稳定物质：冷却好时普攻炸开，周围敌人受25 + 30% 法强魔法伤害，英雄再受最大生命4%真实伤害（冷却5秒）。细胞分裂：技能打中英雄掉下黏液，吃掉回复55 + 15% 法强生命（复活需扩展包）。
 （攻击间隔 1.17 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>延伸打击：伸长手臂抓向目标，造成55 + 30% 法强 + 自身最大生命2%魔法伤害并减速40%；抓住的英雄0.4秒后被甩到身边砸地，再受同样伤害，周围敌人击飞0.5秒。
 （冷却 1 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>橡筋弹弓：蓄力0.6秒后把自己弹向目标，落地造成85 + 60% 法强 + 自身最大生命3%魔法伤害并击飞周围敌人0.5秒。
 （冷却 15 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>动感弹球：不可阻挡地连跳4次，每次落地造成90 + 50% 法强魔法伤害（之后每次50%）并减速25%；第一跳越过目标把敌人击退回自己那边，之后每跳击飞0.33秒。
 （冷却 1.5 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>扎克附加包（league_zac v0.1.1）
 细胞分裂·复活：受到致命伤害时不倒下，化成一滩 split_t tick（6 秒）：生命设成最大生命的 split_hp%（40%）当作这一滩的生命，定身、禁普攻、禁技能，双抗 −20；这一滩被…
 细胞分裂·黏液：一样</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="3" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zac.md</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>阿狸</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Ahri</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>league_ahri</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>普攻发射妖力球，造成100% 攻击力的物理伤害。被动 摄魂夺魄：普攻每打死1个小兵或野怪积攒1层，满9层回复80 + 20% 法术强度的生命值；她3秒内伤害过的敌方英雄阵亡时，回复160 + 30% 法术强度的生命值。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>欺诈宝珠：掷出宝珠再收回，往返各对路径上的敌人造成70 + 55% 法术强度的魔法伤害，回程无视魔法抗性。同时施放 妖异狐火（冷却9秒）：3团狐火追击附近敌人，优先被魅惑的英雄，每团造成45 + 30% 法术强度的魔法伤害，并移动速度提高40%，2秒内递减。
 （冷却 6 秒 · 施放距离 65000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>魅惑妖术：献出飞吻，对命中的第一个敌方英雄造成75 + 75% 法术强度的魔法伤害并魅惑其1.25秒，使其走向阿狸，期间减速65%。
 （冷却 10 秒 · 施放距离 70000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>灵魄突袭：向前冲刺（离敌方英雄太近时向后冲），再向附近敌人射出3枚精魄弹，优先英雄，每枚造成55 + 35% 法术强度的魔法伤害。施放后15秒内可再施放2次；期间参与击杀英雄再给1次，并至少再开10秒。
 （冷却 60 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>阿狸附加包（league_ahri v0.1.0）
 精魄（9 层回血）：她补到的每一个小兵、野怪，用什么打死的都算
@@ -5488,127 +5553,127 @@
 灵魄突袭多给 1 次：同上（窗口开着时）</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="3" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ahri.md</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>阿卡丽</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Akali</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>league_akali</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 我流忍法！潜龙印：技能命中敌方英雄后4秒内，下一次普攻射程翻倍并额外造成54 + 70% 法术强度的魔法伤害，期间移动速度提高30%。
 （攻击间隔 0.92 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>我流奥义！寒影：向前方扇形掷出苦无，造成65 + 76% 法术强度的魔法伤害和30% 攻击力的物理伤害，末端敌人减速50%。连招 E Q A：隼舞二段落到英雄身上后2秒内施放，苦无出手后立刻甩出潜龙印的强化镰刀。
 （冷却 3 秒 · 施放距离 38000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>我流奥义！隼舞：向后翻身并掷出手里剑，对首个命中的敌人造成54 + 54% 法术强度的魔法伤害并标记它，0.5秒后冲到它身边，造成97 + 97% 法术强度的魔法伤害。附近有敌方英雄时落地施放 我流奥义！霞阵（冷却18秒）：放出烟雾，隐身2秒，移动速度提高40%并递减。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>我流秘奥义！表里杀缭乱：穿过目标英雄，路径上的敌人受到140 + 70% 法术强度的魔法伤害；2.5秒后再穿过它（死了或跑远就换附近的英雄），86 + 43% 法强，两段之间每命中英雄一次 +25%（最多200%）。连招 R E E R：两段之间隼舞二段落到英雄身上，立刻放第二段。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>斩杀附加包：伊芙琳、阿卡丽、锐雯（league_executes v0.2.0）
 阿卡丽 R2：86 + 43% 法强，按目标已损失生命最多 +200%（损失 70% 时加满）</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="3" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_akali.md</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>艾尼维亚</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Anivia</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>league_anivia</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>冰弹。寒霜涅槃（需安装扩展包）：受到致命伤害时变成冰蛋6秒，蛋没被打碎就复活；冷却240秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>寒冰闪耀：射出冰球，穿过的敌人受到55 + 32% 法强并减速30%；碰到英雄或到达落点时引爆：95 + 65% 法强魔法伤害并眩晕1.1秒。寒冰屏障：晕到英雄时在原地竖起冰墙5秒，敌人过不去。
 （冷却 7 秒 · 施放距离 95000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>霜寒刺骨：冰锥造成75 + 65% 法强魔法伤害；目标被控制时，或冰川风暴成形后，伤害翻倍。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>冰川风暴：在敌方英雄处召唤暴风雪6秒，逐渐变大；每0.5秒造成32 + 13% 法强魔法伤害并减速，成形后伤害×3。有被控制的敌方英雄或2名敌方英雄在身边时才放。
 （冷却 40 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>艾尼维亚附加包（league_anivia v0.1.4）
 寒霜涅槃：受到致命伤害时不倒下，变成冰蛋 egg_t tick（6 秒）：生命回满当作蛋的生命，禁普攻、禁技能，双抗降低；蛋被打碎才阵亡（击杀算打碎蛋的人），撑过去就带着蛋剩下的生命孵化。…
@@ -5616,64 +5681,64 @@
 霜寒刺骨翻倍：目标身上有冰冻标记（被寒冰闪耀穿过或引爆、被成形的风暴打中后 3 秒，数据挂在每个目标身上，头顶一枚雪花）就翻倍，按每个目标判断</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="3" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_anivia.md</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>安妮</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Annie</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>league_annie</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>普攻扔出小火球，造成100% 攻击力的物理伤害。被动 嗜火：每施放4次技能（焚烧、熔岩护盾各算一次）后，下一个伤害技能眩晕命中的英雄0.75秒，小兵和野怪不会消耗它。出生和复活时自带眩晕。
 （攻击间隔 1.5 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>碎裂之火：扔出火球，造成70 + 65% 法术强度的魔法伤害。
 （冷却 4 秒 · 施放距离 62500 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>焚烧：向前方喷出扇形火焰，造成60 + 65% 法术强度的魔法伤害。同时施放 熔岩护盾：获得60 + 40% 法术强度的护盾，持续3秒，护盾存在时反弹20%所受伤害，并移动速度提高30%，持续1.5秒。
 （冷却 7 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>提伯斯之怒：召唤提伯斯砸向敌方英雄，对周围敌人造成130 + 70% 法术强度的魔法伤害。提伯斯紧跟该英雄6秒，每秒灼烧其周围敌人，造成14 + 8% 法术强度的魔法伤害；该英雄阵亡时提伯斯随之离场。
 （冷却 60 秒 · 施放距离 62500 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>安妮附加包：Q 返还、提伯斯换目标（league_annie_q v0.2.0）
 Q 击杀：返还一半冷却（120 tick；小兵、野怪、英雄都算）
@@ -5681,191 +5746,191 @@
 提伯斯（v0.2.0）：目标阵亡（或不能选中）就转向 50000 内最近的敌方英雄，6 秒满或附近没人才离场；挥爪、火圈、每秒 14 + 8% 法强的灼烧照主包</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="3" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_annie.md</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>奥瑞利安·索尔</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Aurelion Sol</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>league_aurelionsol</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>甩出一颗星星。星海焕然：技能命中英雄收集星尘（每层法强+3%，最多15层），每6层下一次大招变为天瀑。星穹流丽：击杀英雄后起飞4秒，移速+60%、法强+20%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>星河冲荡：引导龙息1.5秒，每0.17秒对一线上的敌人造成26 + 17% 法强魔法伤害，喷同一目标1秒后每次额外30；被控制打断。飞行中无冷却、引导更久。
 （冷却 1 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>星芒凝汇：在目标处召唤黑洞（5秒），每0.25秒造成16 + 9% 法强魔法伤害，把敌人拉向中心并减速25%；中心每秒造成英雄最大生命值4%的真实伤害。
 （冷却 1 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>星天落瀑：星落：星星坠落在目标处，造成270 + 85% 法强魔法伤害并眩晕1秒。天瀑：范围更大，350 + 105% 法强并击飞0.83秒，外圈冲击波再造成80 + 30% 法强并减速50%。
 （冷却 35 秒 · 施放距离 125000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>奥瑞利安·索尔附加包（league_aurelionsol v0.1.0）
 星海焕然（星尘）：活着时记下每一层，死亡清掉后原样补回（最多 d_max 层）
 星芒凝汇（黑洞中心）：同样的伤害，另外英雄生命低于 e_low% + 每层星尘 e_low_d%（默认 5% + 1%/层，最多 20%）就直接处决</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="3" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_aurelionsol.md</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>阿萝拉</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Aurora</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>league_aurora</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>魔杖点出灵光。驱灵奇术：命中英雄叠层，第三层抽出灵物，造成40 + 30% 法强+2%最大生命值的伤害，回复45 + 15% 法强生命并加速。灵纱洞开：被敌方英雄贴身时后跳，隐身1.25秒、加速30%（20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>飞去来咒：放出咒弹穿过敌人，造成100 + 55% 法强魔法伤害并留下诅咒；0.67秒后把诅咒抽回，回程再造成100 + 55% 法强魔法伤害。
 （冷却 7.5 秒 · 施放距离 85000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>怪奇喷涌：向前喷出灵魂冲击，造成150 + 80% 法强魔法伤害并减速60%（逐渐减弱），随后向后跳开。
 （冷却 13 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>双界合一：跳到敌方英雄身上，冲击波造成260 + 80% 法强魔法伤害并减速40%；张开领域3.5秒，减速其中敌人30%，目标走开时她穿过领域追上去。
 （冷却 35 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>阿萝拉附加包（league_aurora v0.2.0）
 灵纱洞开（并入被动）：同样的跳法，但还要她生命低于 w_low%（默认 35%），英雄联盟「残血时跳开」</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="3" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_aurora.md</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>阿兹尔</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Azir</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>league_azir</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>沙兵现身：普攻每2.5秒在目标处召出一个黄沙士兵（最多3个，存在8秒），士兵代他刺击，造成75 + 100% 法强魔法伤害；士兵都够不着时他自己射出沙光。
 （攻击间隔 1.33 秒 · 攻击距离 52500）</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>狂沙猛攻：所有黄沙士兵冲向目标，沿途造成110 + 65% 法强魔法伤害并减速25%，落地马上刺击；没有士兵时在目标处召出一个。
 （冷却 8 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>流沙移形：身边有士兵才能施放：获得80 + 60% 法强护盾，大招就绪时冲向敌方英雄，造成90 + 55% 法强魔法伤害并召出一个士兵；被敌方英雄贴身时改为后跳。
 （冷却 1 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>禁军之墙：一排禁军举盾冲锋，造成260 + 90% 法强魔法伤害并击退敌人；刚用流沙移形冲到英雄身上时，先绕到他身后，再把他推回己方。
 （冷却 30 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>阿兹尔附加包（league_azir v0.1.2）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
@@ -5873,375 +5938,375 @@
 沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="3" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_azir.md</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>布兰德</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>league_brand</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>被动炽热之焰：技能命中使敌人烈焰焚身4秒，每秒受到6 + 4% 法强魔法伤害。技能命中英雄叠层，第3层时该英雄2秒后爆炸，对周围造成50 + 30% 法强+4%最大生命值伤害。
 （攻击间隔 1.5 秒 · 攻击距离 52000）</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>烈焰之柱：短暂延迟后在目标处升起烈焰之柱，对范围内敌人造成70 + 55% 法强魔法伤害并点燃；有英雄在燃烧时伤害提高25%。
 （冷却 8 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>烈火燃烧：点燃敌方英雄并蔓延到周围，造成45 + 35% 法强。随后火焰烙印：火球命中首个敌人造成60 + 45% 法强魔法伤害并晕眩0.83秒。命中英雄且烈焰之柱就绪时，再对他施放烈焰之柱。
 （冷却 11 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>烈焰风暴：火种在敌人间弹射5次，优先英雄，每次造成60 + 20% 法强魔法伤害、点燃并减速35%。目标附近没有其他敌人时不施放。
 （冷却 45 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>布兰德被动层数附加包（league_brand v0.1.1）
 主包 league 保持纯数据。数据只读得到施法者自己身上的 buff，所以主包布兰德的被动「炽热之焰」把层数记在布兰德身上： 技能连中不同的英雄也会叠到第 3 层，第 3 下打中的那个英雄爆炸。这个附加包用原生代码做成英雄联盟的样子： - 层数记在每个敌人身上：原生效果 league_brand:blaze 代替主包里的叠层。技能（W、E 的蔓延、Q、R…</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="3" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_brand.md</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>卡西奥佩娅</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Cassiopeia</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>league_cassiopeia</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>双生毒牙：甩出毒牙，造成18 + 14% 法强魔法伤害；Q、W毒到敌人后3秒内，多造成14 + 24% 法强并回复10% 法强生命。优雅蛇行：移速成长更高。
 （攻击间隔 0.75 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>瘟毒爆炸：0.4秒后在目标处炸开，敌人中毒3秒，共受75 + 60% 法强魔法伤害；毒到英雄时她移速+45%，3秒内渐退。
 （冷却 4 秒 · 施放距离 80000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>剧毒迷雾：放出持续5秒的毒雾：每秒24 + 12% 法强魔法伤害，减速50%、禁锢（不能用位移技能）。
 （冷却 15 秒 · 施放距离 65000 · 施放：地点 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>石化凝视：朝面前扇形石化凝视，造成160 + 70% 法强魔法伤害：近处交战的敌人石化2秒，远处的减速40%。前方有2个以上敌方英雄或被突进时才放。
 （冷却 50 秒 · 施放距离 72000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>卡西奥佩娅附加包（league_cassiopeia v0.1.0）
 双生毒牙的加伤和回血：只有这个目标本人中毒时才加伤、回血（英雄联盟）
 石化凝视：面朝她的石化，背对她的减速（英雄联盟）</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="3" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_cassiopeia.md</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>库奇</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Corki</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>league_corki</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>海克斯科技军备：普攻20%伤害转为真实伤害。特别快递：开局、复活后及每45秒，下次瓦尔基里俯冲变成弹药包：起飞时击退附近英雄并造成40 + 30% 法强魔法伤害，飞得更远、火焰更宽更久，加速30%。
 （攻击间隔 1.03 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>磷光炸弹：向目标位置扔出磷光炸弹，范围内敌人受到95 + 70% 法强魔法伤害和55% 攻击力物理伤害。
 （冷却 7.5 秒 · 施放距离 58000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>格林机枪：4秒内向前方锥形扫射，每次造成9 + 16% 攻击力物理和9% 法强魔法伤害，叠加降低护甲和魔抗。冷却中被英雄贴近时改为瓦尔基里俯冲：向后俯冲，沿途留下火焰，每0.5秒造成15 + 12% 法强魔法伤害。
 （冷却 2 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>火箭轰击：储存4发火箭（每10秒补一发），命中第一个敌人后爆炸，范围内造成75 + 42% 法强魔法伤害和52% 攻击力物理伤害；每第3发是大火箭：范围更大，伤害200%。
 （冷却 40 秒 · 可存 4 次 · 施放距离 84000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>库奇智能火箭 + 脱身方向附加包（league_corki v0.1.0）
 主包 league 保持纯数据、全平台可用；数据读不到敌人站在哪、血量多少，主包的火箭朝 AI 选的英雄直线飞（Q 炸到人时改打「刚被打过的 英雄」），瓦尔基里俯冲只能「背对身边那个英雄往后跳」，不看墙、塔和队友。英雄联盟里高手把火箭打向能炸到最多人的地方、大火箭留给残血， 俯冲往安全的地方飞——要读每个单位的位置和血量，只能用原生代码，所以放在这个附加包…</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="3" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_corki.md</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>菲兹</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Fizz</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>league_fizz</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害，并让目标流血3秒，共18 + 18% 法术强度的魔法伤害（可叠加）。被动 伶俐斗士：受到的普攻伤害降低12%。连招 Q E / R E：淘气打击穿过英雄后1秒内，或鱼粘在英雄身上时施放古灵精怪，不等直接跳起砸下。
 （攻击间隔 0.92 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>淘气打击：穿过目标冲刺，造成100% 攻击力的物理伤害和40 + 65% 法术强度的魔法伤害，附带流血。海石三叉戟（每6秒）：下一次普攻或淘气打击额外造成50 + 60% 法术强度的魔法伤害，击杀目标则冷却缩短为1秒。
 （冷却 5 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>古灵精怪：跳上三叉戟0.63秒（受到的伤害只有1点、免疫控制），再砸向最近的敌人，对周围造成80 + 80% 法术强度的魔法伤害并减速40%2秒。附近有敌方英雄时先蓄着，挨打就跳起躲开后面的技能（最多等1秒）。
 （冷却 9 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>巨鲨强袭：扔出一条鱼粘在第一个敌方英雄身上并减速，2秒后鲨鱼从它脚下冲出，击飞周围敌人1秒并造成魔法伤害。鱼飞得越远鲨鱼越大：150/220/300 + 70/90/110% 法术强度，减速40/60/80%。落空则在落点冲出大鲨鱼。
 （冷却 50 秒 · 施放距离 85000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_fizz.md</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>加里奥</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Galio</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>league_galio</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>巨像重击：每4秒下一次普攻对周围敌人造成80 + 70% 法强魔法伤害。杜朗护盾被动：普攻时获得90 + 30% 法强护盾，每12秒一次。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>战争罡风：射出两道风刃，落点造成120 + 80% 法强魔法伤害，并留下2秒龙卷风，每0.5秒造成30 + 18% 法强魔法伤害。
 （冷却 7 秒 · 施放距离 55000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>正义冲拳：冲向敌方英雄，撞到第一个英雄造成130 + 90% 法强魔法伤害并击飞0.75秒。杜朗护盾：蓄力0.83秒，伤害降低40%，随后嘲讽1.17秒周围敌人，造成90 + 70% 法强魔法伤害。
 （冷却 1 秒 · 施放距离 43000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>英雄登场：给陷入苦战的友方英雄150 + 50% 法强护盾，引导2秒后飞到其身边，落地造成220 + 90% 法强魔法伤害并击飞0.75秒，周围友方英雄也获得护盾。
 （冷却 70 秒 · 施放距离 960000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>加里奥附加包（league_galio v0.1.1）
 主包 league 保持纯数据。用户选了「主包数据 + 附加包」。这个附加包用原生代码做主包数据做不到的三件事： - 杜朗护盾的被动护盾按「多久没挨打」给：主包里加里奥普攻时给护盾（每 12 秒最多一次），因为数据读不到「多久没受伤」。 附加包的被动 league_galio:colossus 记下他最后一次受伤的 tick，12 秒没受伤就给 90 + …</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="3" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_galio.md</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>黑默丁格</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Heimerdinger</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>league_heimerdinger</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>射出一道海克斯电光。海克斯科技微型导弹：每第3次普攻额外射出5枚导弹，每枚造成10 + 7% 法强魔法伤害。
 （攻击间隔 1.47 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>H-28 G 进化炮台：放下一座炮台（最多3座）10秒，每0.83秒攻击一个敌人，造成6 + 4% 法强魔法伤害；对受控制的英雄发射光束，造成18 + 14% 法强。海克斯科技亲和：在炮台旁移速+20%。
 （冷却 4 秒 · 施放距离 60000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>CH-2电子风暴手雷：掷出手雷，造成60 + 45% 法强魔法伤害并减速35%，正中的敌人被眩晕1秒。
 （冷却 11 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>升级！！！：升级！刷新Q、E，10秒内强化下一个对英雄的技能：Q放下巨型炮台8秒，每0.5秒造成22 + 12% 法强并减速25%；E连掷3颗手雷，每颗80 + 40% 法强并眩晕1秒；普攻射出12枚导弹。
 （冷却 40 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
         <is>
           <t>黑默丁格附加包（league_heimerdinger v0.2.0）
 炮台的样子：侧面、炮口朝目标那边（用户：「炮台改成侧面朝敌人」）：英雄联盟模型的侧面，PPU 1.75（用户：「灵活利用PPU 炮也可以调的清晰」，PPU 3 时又「炮太高清了 降低点像素」…
@@ -6251,248 +6316,248 @@
 R 的升级给谁：敌方英雄扎堆就按 E（CH-3X 砸人堆），不然按 Q（巨型炮台），Q 没好再按 E</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="3" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_heimerdinger.md</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>彗</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Hwei</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>league_hwei</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>挥笔甩出一团墨。落款：技能命中英雄后4秒内再命中则引爆，造成45 + 35% 法强魔法伤害。主题：靖：画灾时加速25%，画悚时为自己和附近队友加护盾60 + 35% 法强。
 （攻击间隔 1.53 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>主题：灾：依局势作画：被控制的英雄头上落攒聚雷60 + 45% 法强，再加90 + 60% 法强；否则向英雄掷没骨火75 + 50% 法强加3%最大生命；没有英雄时画连皴山，熔岩灼烧并减速35%。均为魔法伤害。
 （冷却 1 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>主题：悚：依局势作画：贴身的英雄被阴沉变意恐惧1秒；否则轮流画滞涩幽瞳（睁眼后禁锢1.3秒）与双钩血喉（咬住并减速45%）。均造成80 + 50% 法强魔法伤害。
 （冷却 12 秒 · 施放距离 85000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>焚心绚华绘：向英雄甩出颜料，命中后在其脚下展开画卷3秒，持续造成魔法伤害并减速25%，最后爆炸造成110 + 55% 法强魔法伤害。
 （冷却 35 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="3" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_hwei.md</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>卡尔萨斯</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Karthus</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>league_karthus</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>痛苦之墙：每12秒，身边有敌方英雄时，攻击在那名英雄脚下立起一道墙（5秒），墙里的敌人减速40%，魔抗-20%（4秒）。
 （攻击间隔 1.53 秒 · 攻击距离 50000）</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>荒芜：目标处0.53秒后爆炸，造成45 + 30% 法强魔法伤害；只炸到一个敌人时伤害翻倍。
 （冷却 2.5 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>亵渎：5秒内灵魂环绕自身，每0.25秒对身边敌人造成10 + 5% 法强魔法伤害。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>安魂曲：引导3秒（被控制会打断），然后对全图所有敌方英雄造成200 + 75% 法强魔法伤害。
 （冷却 70 秒 · 施放距离 960000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>卡尔萨斯附加包（league_karthus v0.2.0）
 主包 league 保持纯数据。用户选了「被动做附加包」。这个附加包用原生代码做主包数据做不到的死亡契约： - 英雄联盟里卡尔萨斯死后化成灵体，7 秒内照样放技能，然后才倒下。数据读不到血量，主包做不了。 附加包的被动 league_karthus:death_defied 每 10 tick 给他挂一个 30 tick 的不死 buff league_k…</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J94" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="3" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_karthus.md</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>卡萨丁</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Kassadin</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>league_kassadin</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>虚空之石：受到的魔法伤害降低约10%。虚空之刃：普攻附带15 + 10% 法强魔法伤害；每7秒强化一次普攻，额外造成70 + 70% 法强魔法伤害。
 （攻击间隔 0.92 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>虚无法球：向目标发射虚无法球，造成90 + 70% 法强魔法伤害，打断英雄的动作。自身获得50 + 40% 法强护盾1.5秒。
 （冷却 6 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>能量脉冲：向前方锥形释放能量脉冲，造成90 + 70% 法强魔法伤害并减速50%1秒。每次施放虚无法球或虚空行走都会缩短它的冷却。
 （冷却 15 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>虚空行走：闪现到附近一名敌方英雄身边，对周围敌人造成100 + 50% 法强魔法伤害。15秒内再次施放叠加一层（最多3层），每层额外40 + 10% 法强魔法伤害。
 （冷却 8 秒 · 施放距离 48000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>卡萨丁附加包（league_kassadin v0.1.2）
 主包 league 保持纯数据。用户问被动「看看rust能做吗」，附加包做哪几项「你看着办吧」——这个附加包用原生代码做主包数据做不到的三件事： - 虚空之石正好减 10% 魔法伤害：主包用一个固定的魔抗 buff 近似（他自己的魔抗下约 10–11%）。附加包的被动 league_kassadin:void_stone 每 15 tick 读他现在的魔抗…</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>2.42</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="3" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_kassadin.md</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>卡特琳娜</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Katarina</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>league_katarina</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>贪婪：被她伤害过的敌方英雄3秒内阵亡时，Q、W冷却刷新，瞬步就绪。落地的匕首留4秒，捡起时旋斩周围敌人，造成138+100% 法强魔法伤害，瞬步冷却降为2秒。
 （攻击间隔 0.92 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>弹射之刃：掷出弹射之刃，造成150+62% 法强魔法伤害，再弹向附近2个敌人；匕首落在第一个目标身后。瞬步就绪且匕首旁有敌方英雄时，瞬步到匕首处。
 （冷却 8 秒 · 施放距离 62500 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>伺机待发：瞬步就绪时先瞬步到敌方英雄身边，造成75+38% 法强魔法伤害（冷却10秒）；再把匕首抛向空中，1.25秒后落地，获得逐渐衰减的移速+60%。
 （冷却 11 秒 · 施放距离 55000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>死亡莲华：原地旋转引导2.5秒，向周围的敌方英雄连续掷出匕首，共造成650+350% 法强魔法伤害并使其治疗效果-60%。受到控制时中断。
 （冷却 60 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>卡特琳娜附加包（league_katarina v0.1.0）
 瞬步：另外瞬步一好就自己判断：射程内哪把匕首旁有敌方英雄就跳过去（那里生命比例最低的英雄优先），落地捡刀旋斩、冷却缩短，接着跳下一把——匕首循环；生命低于 30% 而身边有敌方英雄时，…
@@ -6502,379 +6567,379 @@
 卡特琳娜 R：她生命 ≥ 30%、自己不在敌方塔下（目标残血除外）；25000 内的敌方英雄，身边 50000 内有两个以上，或目标生命不到一半</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="3" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_katarina.md</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>乐芙兰</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>LeBlanc</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>league_leblanc</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>魔法飞弹。被动 镜花水月：两名以上敌方英雄贴近时隐身1秒并后闪，原地留下幻像（40秒一次）。幻影锁链：每10秒对英雄的下一击改为甩出锁链，造成80 + 50% 法强魔法伤害，1.5秒内都在附近则禁锢1.5秒并再受110 + 100% 法强。
 （攻击间隔 1.5 秒 · 攻击距离 52500）</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>恶意魔印：投出魔印，造成90 + 70% 法强的魔法伤害并标记3.5秒；她的下一个技能命中时魔印引爆，再造成90 + 70% 法强。命中英雄时若魔影迷踪就绪，立刻接上（连招）。
 （冷却 5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>魔影迷踪：冲到一名敌人（英雄、小兵或野怪）身边，对周围敌人造成120 + 100% 法强的魔法伤害，0.93秒后闪回出发点（被控制时留在原地）。
 （冷却 8 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>故技重施：重放上一个施放的技能，伤害更高：魔印160 + 110% 法强（引爆同样）；迷踪220 + 150% 法强；锁链130 + 90% 法强，禁锢时再200 + 150% 法强。
 （冷却 45 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.0）
 乐芙兰 镜花水月：生命不高于 40%</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="3" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_leblanc.md</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>丽桑卓</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Lissandra</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>league_lissandra</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>发射冰弹攻击。被动冰脉驱役：她击杀的敌方英雄化为冰仆，1.5秒后碎裂，对周围敌人造成150 + 70% 法强魔法伤害并减速。
 （攻击间隔 1.42 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>寒冰碎片：射出冰锥，沿途每个敌人受到120 + 100% 法强魔法伤害并减速25%。出手时方向已锁定，可以躲开。
 （冷却 4 秒 · 施放距离 70000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>冰霜之环：周围敌人受到100 + 80% 法强魔法伤害并定身1.25秒。身边没敌人时放冰川之径：冰爪造成80 + 60% 法强，追上正在交战的敌方英雄后再放冰环。
 （冷却 7 秒 · 施放距离 85000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>冰封陵墓：冰封敌方英雄：眩晕1.5秒，受到200 + 100% 法强魔法伤害。被两名以上敌方英雄围住时改为冰封自己2.5秒：免疫伤害和控制，回复200 + 80% 法强生命。冰块周围留下减速冰地。
 （冷却 60 秒 · 施放距离 90000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.0）
 丽桑卓 大招冰封自己：生命不高于 35%</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="3" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_lissandra.md</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>拉克丝</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Lux</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>league_lux</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>普攻从法杖射出光弹，造成100% 攻击力的物理伤害。被动 光芒四射：技能命中敌人后5秒内，下一次普攻引爆光芒，额外造成50 + 35% 法术强度的魔法伤害。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>光之束缚：向前方射出一颗光球，对路径上的每个敌人造成80 + 75% 法术强度的魔法伤害并禁锢1.5秒。同时施放 曲光屏障：拉克丝和身边的友方英雄获得55 + 40% 法术强度的护盾，持续2.5秒。
 （冷却 6 秒 · 施放距离 130000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>透光奇点：向目标位置抛出光球，落地后形成光圈，使圈内敌人减速20%。1秒后光圈引爆，对圈内敌人造成70 + 80% 法术强度的魔法伤害。
 （冷却 8 秒 · 施放距离 110000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>终极闪光：拉克丝跃起蓄力，0.5秒后向目标方向发射一道极长的激光，对直线上所有敌人造成250 + 115% 法术强度的魔法伤害。
 （冷却 60 秒 · 施放距离 120000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>目标标记附加包（league_marks v0.1.0）
 拉克丝 光芒四射：光芒留在被技能打中的敌人身上（5 秒），普攻打中带光芒的人才引爆 50 + 35% 法强的魔法伤害</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="3" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_lux.md</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>玛尔扎哈</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Malzahar</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>league_malzahar</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>射出虚空弹。被动虚空穿越：获得90 + 40% 法强护盾，护盾存在时免疫控制；护盾被打破后12秒重新获得。
 （攻击间隔 1.5 秒 · 攻击距离 52000）</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>煞星幻象 / 虚空虫群：煞星幻象：4秒内造成170 + 80% 法强魔法伤害，目标死亡时跳到附近的敌人身上。虚空虫群随之撕咬目标，每0.5秒造成14 + 8% 法强魔法伤害。
 （冷却 9 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>虚空召唤：在目标两侧打开虚空裂隙，裂隙合拢时对范围内的敌人造成70 + 45% 法强魔法伤害并沉默1.5秒。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>冥府之握：压制一名敌方英雄（优先煞星幻象的目标）：引导期间使其眩晕，2.5秒内造成220 + 80% 法强魔法伤害，脚下留下持续伤害的虚空区域。玛尔扎哈被控制时引导中断。
 （冷却 70 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>玛尔扎哈附加包（league_malzahar v0.1.0）
 主包 league 保持纯数据。用户选了「做：E 跳转 + 被动精确」。这个附加包用原生代码做主包数据做不准的两件事： - 虚空穿越（被动）：英雄联盟里玛尔扎哈身上有一层法术护盾：受到的伤害大幅减少、免疫控制；被非小兵的伤害打中后很快消失， 一段时间没受到英雄伤害才回来。主包数据读不到「被谁打了」「多久没挨打」，只能做成墨菲特那样的护盾（打破后过一会儿回来…</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="3" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_malzahar.md</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>妮蔻</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Neeko</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>league_neeko</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>发射一颗魔法弹。两生花影：每第三次攻击额外造成45 + 50% 法强魔法伤害，并提高30%移动速度1秒。
 （攻击间隔 1.53 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>盛开花种：扔出一颗种子，落地炸开造成95 + 65% 法强魔法伤害。炸到英雄时会再次盛开，最多两次，每次40 + 25% 法强魔法伤害。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>缠结倒刺：投出一团贯穿的倒刺，路径上的敌人受到90 + 60% 法强魔法伤害并被禁锢1秒。穿过英雄后，后面的英雄多被禁锢0.75秒。
 （冷却 11 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>怒放：蓄力0.75秒，获得护盾（附近每个敌方英雄额外40），然后跃起击飞周围敌人，落地造成260 + 115% 法强魔法伤害并晕眩0.83秒。
 （冷却 35 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>妮蔻附加包（league_neeko v0.1.0）
 天生幻魅：脱战 2 秒后整个身体画成最近的友方英雄（站、跑、出招、挨打都用他的图）；放技能、被控（击飞、晕眩、禁锢、嘲讽、恐惧、魅惑、强制位移）、假扮以来挨了她 35% 最大生命的伤害、或…</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="3" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_neeko.md</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>奥莉安娜</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Orianna</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>league_orianna</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>发射发条弹。发条协奏：普攻附带18 + 15% 法强魔法伤害，4秒内连续普攻再叠加，最多2层。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>指令：攻击：把球扔到敌方英雄脚下并停留，造成85 + 65% 法强魔法伤害。指令：杂音：球附近有敌人时自动放电，造成85 + 85% 法强魔法伤害，减速30%，队友加速30%。
 （冷却 5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>指令：防卫：把球送给离敌人最近的队友（被贴身时给自己），提供60 + 45% 法强护盾，路过的敌人受到60 + 30% 法强魔法伤害。带球者+12护甲和魔抗。
 （冷却 9 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>指令：冲击波：待命6秒，球附近有敌方英雄时放出冲击波：造成250 + 100% 法强魔法伤害并把敌人甩向球。
 （冷却 70 秒 · 施放距离 90000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>奥莉安娜附加包（league_orianna v0.2.0）
 Q / E 的球从哪飞出：从球所在的位置飞出：地上、队友身上、飞回来的半路都行；E 路过的敌人按球到队友这条线算
@@ -6886,127 +6951,127 @@
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_orianna.md</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>瑞兹</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Ryze</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>league_ryze</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>发射符文法球攻击。被动奥术专精：所有技能伤害额外加上2% 最大生命值（本作没有法力值，以生命值代替法力）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>超负荷：向前释放魔爆，对命中的第一个敌人造成55 + 50% 法强的魔法伤害。若有敌人带着涌动，命中时它们全部受到35 + 35% 法强的弹射伤害，涌动随之消耗。
 （冷却 3.5 秒 · 施放距离 80000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>符文禁锢：连招 E→W→Q→E→Q：法术涌动造成45 + 45% 法强伤害，给目标和附近敌人挂上涌动4秒；符文禁锢造成70 + 55% 法强伤害，有涌动时禁锢1.25秒，否则减速；超负荷引爆涌动，再一发法术涌动和超负荷，符文让他移速+30%。
 （冷却 14 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>曲境折跃：被敌方英雄贴身时开门逃到远处安全的队友身边（没有就往反方向逃）；身边没敌人、队友在远处交战时开门追过去。引导1秒后传送，门里的友军一起过去，落地补一发法术涌动。被控会打断。被动：施放后本条命内涌动弹射伤害提高到50 + 55% 法强。
 （冷却 70 秒 · 施放距离 360000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 瑞兹 R（备好式）：逃命：生命不到 35% 而 60000 内有敌方英雄；去打架：照崔斯特的规则（身边没敌人、远处队友在打）。传到哪里由主包判断</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="3" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ryze.md</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>斯维因</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Swain</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>league_swain</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>恶魔手射出乌鸦弹。狂食鸦群：帝国视界、永不复行抓到英雄或他打过的英雄阵亡时得到魂屑，回复80 + 30% 法强生命，最大生命+15（死后清空）。帝国视界：每16秒在远处交战的敌方英雄脚下睁眼，1.5秒后炸开造成90 + 60% 法强魔法伤害并减速。
 （攻击间隔 1.5 秒 · 攻击距离 52000）</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>解脱之触：恶魔手射出五道扇形散开的闪电，造成120 + 80% 法强魔法伤害；近处的敌人被更多闪电打中，另受60 + 45% 法强魔法伤害。
 （冷却 4 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>永不复行：恶魔之手飞出再飞回，回程打中的敌人受到110 + 80% 法强魔法伤害并禁锢1.5秒；被禁锢的英雄随后被拉近，留下一片魂屑。
 （冷却 10 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>恶魔升华：化身恶魔，吸取周围敌人的生命：每0.5秒造成25 + 8% 法强魔法伤害，每名英雄回复40 + 15% 法强；吸到英雄时形态延续。2秒后放出恶魔耀光：170 + 70% 法强魔法伤害并减速。2名敌方英雄在身边，或有敌方英雄且队友在旁时才放。
 （冷却 60 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>斯维因附加包（league_swain v0.1.1）
 魂屑：永久保留：死了、复活后一块不少（英雄联盟的规则）
@@ -7014,127 +7079,127 @@
 开大时机：不变，照主包（用户：「是乌鸦看情况开大吧」），日志里记下每次变身时身边几个敌方英雄</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_swain.md</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>塞拉斯</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Sylas</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>league_sylas</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>甩链。破敌禁法：每放一个技能存一层（最多2层），有层时攻速+40%，下次普攻挥链横扫周围，20 + 35% 法强魔法伤害。弑君突刺：每9秒对英雄的普攻变成突刺，80 + 70% 法强魔法伤害，回复40 + 35% 法强生命。
 （攻击间隔 0.97 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>锁链鞭击：甩出两条锁链交叉于目标处，沿途敌人受到50 + 35% 法强魔法伤害并减速25%；0.6秒后交叉点爆炸，造成90 + 65% 法强魔法伤害。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>潜掠/强掳：朝敌方英雄突进，再甩出锁链：命中的第一个敌方英雄受到80 + 70% 法强魔法伤害、被击飞0.5秒，塞拉斯把自己拉过去。
 （冷却 11 秒 · 施放距离 70000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>其人之道：锁链命中敌方英雄，眩晕0.5秒并夺走大招；10秒内再放，在目标处爆发，200 + 80% 法强魔法伤害并击飞周围敌人。
 （冷却 45 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>塞拉斯附加包（league_sylas v0.2.8）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="3" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_sylas.md</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>辛德拉</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Syndra</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>league_syndra</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>被动卓尔不凡：3级Q对英雄伤害+25%，5级W附带20%真实伤害，7级E范围更大，9级R的法球无视魔抗。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>暗黑法球：召唤暗黑法球，对周围敌人造成62 + 52% 法强魔法伤害。法球留在原地6秒。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>弱者退散：先用驱使念力把法球掷向敌方英雄，造成55 + 55% 法强魔法伤害并减速30%。再锥形击退敌人，造成45 + 45% 法强魔法伤害，被推开的法球使附近敌人晕眩1.25秒。
 （冷却 11 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>能量倾泻：向一名敌方英雄发射3颗+场上法球数（最多7颗），每颗造成52 + 18% 法强魔法伤害。
 （冷却 70 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>辛德拉举小兵附加包（league_syndra v0.1.1）
 这个附加包把主包的辛德拉换成 override/ 里的副本（make_override.py 用 tools/kit/build_syndra.py 的 --native 生成：技能 一样，W 施放时在她身上挂 league_syndra_w_grab、在投掷目标身上挂 league_syndra_w_at；她身上有 league_syndra_w_uni…
@@ -7142,128 +7207,128 @@
 辛德拉 R：75000 内的敌方英雄生命不到 60%、被控住，或射程内有两个以上；主包再按法球数和控制决定立刻放还是待命 8 秒（没用上退还冷却）</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="3" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_syndra.md</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>塔莉垭</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Taliyah</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>league_taliyah</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>甩出一块石子。浮石冲：脱战时移速+10%；放出墙幔后踩石冲浪，移速+40%（5秒）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>石穿：朝目标方向一颗接一颗扔出5颗石头（扔出第一颗后可以移动），第一颗46 + 24% 法强魔法伤害，之后每颗23 + 12% 法强；脚下留下掘石场（8秒），站在上面施放改为一颗大石头：110 + 60% 法强并减速40%。
 （冷却 6 秒 · 施放距离 90000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>岩突：在身前地上撒下石雷（减速20%，4秒），目标脚下裂开后隆起，造成50 + 30% 法强魔法伤害并把敌人掀向自己；飞过石雷时石雷爆炸，造成38 + 24% 法强魔法伤害并眩晕0.4秒。
 （冷却 1 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>墙幔：敌人在附近或已在交战：在目标处竖起长石墙（5秒），墙上的敌人被拖到她这一侧；敌人较远：从脚下拉出一道横墙，踩着石头沿墙冲刺，靠近敌人时跳下。碰到墙的敌人减速42%。
 （冷却 70 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>塔莉垭附加包（league_taliyah v0.1.0）
 竖墙（敌人近、或她已在打架）：同一块地方是真的墙：英雄、小兵、野怪、召唤物（两边都算，她自己也算）都过不去；立起时压在上面的单位推到她那一侧
 横墙（敌人远：骑墙）：每一段都是真的墙；她骑墙时站在墙顶上不受挡，跳下来那一 tick 推到近的一侧</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="3" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_taliyah.md</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>泰隆</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Talon</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>league_talon</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>腕刃攻击。刀锋之末：技能命中英雄叠一层伤口，叠满3层后下次普攻使其流血，2秒内受到40 + 120% 攻击力伤害。刺客之道（自动，10秒）：收刀或Q击杀时身边有2名敌方英雄，就翻身跃开并加速。
 （攻击间隔 0.92 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>斩草除根：扇形掷出飞刀造成30 + 40% 攻击力伤害，随后飞刀收回，造成40 + 70% 攻击力伤害并减速40%。
 （冷却 9 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>诺克萨斯式外交：跃向目标造成48 + 100% 攻击力伤害；目标就在身边时改为原地捅刺，造成150%暴击伤害。击杀目标回复60生命并返还冷却。
 （冷却 5 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>暗影突袭：向四周甩出一圈飞刀造成55 + 75% 攻击力伤害，随后隐身2.5秒、移速+40%；隐身结束或攻击时飞刀收回，再次造成同样伤害。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>泰隆「刺客之道」翻墙附加包（league_talon_vault v0.1.2）
 什么时候翻：照旧，另外：残血（低于 35%）而身边有敌方英雄，或被围（身边敌方英雄 ≥ 2、比身边友方多、生命低于 70%）时；残血敌方英雄（≤ 60%）躲在墙后、他自己生命 ≥ 40% 时
@@ -7271,190 +7336,190 @@
 冷却：同一个冷却（主包的 league_talon_e_cd），两种翻越不会连着出</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="3" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_talon.md</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>崔斯特</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Twisted Fate</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>league_twistedfate</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>扔牌攻击。被动灌铅骰子：普攻或万能牌击杀单位时掷骰子，按点数获得少量法强，死亡清空。卡牌骗术：每第4次攻击额外造成80 + 60% 法强魔法伤害。
 （攻击间隔 1.1 秒 · 攻击距离 57500）</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>万能牌：扔出三张牌，沿途每个敌人受到120 + 100% 法强魔法伤害。出手前方向就已锁定，可以躲开。
 （冷却 4 秒 · 施放距离 95000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>选牌：头顶蓝、红、金牌轮换，转到想要的就锁定，下次普攻扔出（另加100% 攻击力）：蓝牌60 + 100% 法强，技能冷却减半；红牌目标周围50 + 70% 法强并减速；金牌30 + 60% 法强并眩晕1.67秒。
 （冷却 5 秒 · 施放距离 75000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>命运：所有敌方英雄头顶出现标记。传送之门：引导1.5秒（被控打断）后传到远处队友正在打的敌方英雄身边，落地锁定金牌。身边没有敌人时才会用。
 （冷却 90 秒 · 施放距离 960000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 崔斯特 R：只在主包会传送的局面按：他身边 75000 内没有敌方英雄、生命不低于 40%，而且离他 100000–340000 有队友 50000 内贴着敌方英雄（在打架）。之后揭示、引导…</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="3" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_twistedfate.md</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>维迦</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Veigar</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>league_veigar</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>普攻射出暗能量弹，造成100% 攻击力的物理伤害。被动 超凡邪力：技能每命中一名敌方英雄，永久获得1 点法术强度；黑暗祭祀每击杀一个单位 +1，击杀敌方英雄 +5。死亡时清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>黑暗祭祀：射出一束黑暗能量，对最先命中的两个敌人造成70 + 60% 法术强度的魔法伤害。
 （冷却 4 秒 · 施放距离 75000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>扭曲空间：在敌方英雄处扭曲空间，0.4秒后形成持续3秒的牢笼，碰到它的敌人眩晕1秒（每人一次）。随后 黑暗物质 砸向牢笼中心，造成90 + 80% 法术强度的魔法伤害。
 （冷却 13 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>能量爆裂：向敌方英雄发射原始魔法，造成160 + 70% 法术强度的魔法伤害。此前技能每连续命中英雄一次（间隔不超过4秒），伤害提高25%，最多100%。
 （冷却 50 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>维迦法强常驻附加包（league_veigar_power v0.1.0）
 这个附加包把主包的维迦换成 override/ 里的副本（make_override.py 生成：技能一字不改，只加被动 league_veigar_power:keep， 普攻说明里的「死亡时清空」换成「【扩展包】死后保留」），被动每 tick 看一次： - 活着时把身上每一层 league_veigar_p_stack 原样记下来（记在被动里，被动在玩…</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_veigar.md</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>维克兹</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Vel'Koz</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>league_velkoz</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>发射虚空能量。每第3次普攻打开虚空裂隙，造成35 + 20% 法强魔法伤害，随后爆炸再造成55 + 25% 法强。有机体解构：技能命中英雄叠层，3层时造成45 + 45% 法强真实伤害。
 （攻击间隔 1.43 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>等离子裂变：发射一束等离子，造成85 + 65% 法强魔法伤害并减速50%，持续1.25秒。命中后一分为二，对周围敌人造成45 + 35% 法强魔法伤害和减速。
 （冷却 7 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>构造分解：让目标区域爆炸，造成75 + 40% 法强魔法伤害并击飞敌人0.75秒。
 （冷却 11 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>生命形态瓦解射线：引导一束射线2.5秒，共造成320 + 105% 法强魔法伤害。对被有机体解构研究过的英雄改为真实伤害。
 （冷却 35 秒 · 施放距离 95000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>维克兹附加包（league_velkoz v0.1.1）
 有机体解构：层数记在每个敌方英雄身上（每层 7 秒，再中一下全部刷新），第 3 层对那个英雄造成真实伤害；每叠一层都「研究」他 7 秒
@@ -7463,64 +7528,64 @@
 连招：AI 钩子按顺序：E -&gt; Q（AI 要 Q 英雄时先 E）、击飞后马上 Q、窗口里的普攻打英雄（裂隙打在他身上）、两层的英雄在射程里就放 R、R 先射被研究的英雄</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="3" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_velkoz.md</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>薇古丝</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Vex</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>league_vex</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>射出暗影弹。终焉暮气：每15秒下一个技能恐惧命中的敌人0.75秒。生人勿近：敌方英雄靠近时改为获得60 + 60% 法强护盾并震伤周围70 + 40% 法强（每12秒）。
 （攻击间隔 1.43 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>寒心波云：射出一道暗风，穿过路径上的所有敌人，造成105 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>溟濛渐染：影子飞到目标处扩散，造成80 + 60% 法强魔法伤害、减速35%2秒，并施加暮气：她下一次技能打中带暮气的英雄额外造成60 + 30% 法强魔法伤害。
 （冷却 10 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>愁煞：射出飞弹标记一名敌方英雄，造成80 + 20% 法强魔法伤害，随后冲到他身边再造成225 + 70% 法强魔法伤害。
 （冷却 35 秒 · 施放距离 110000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>薇古丝附加包（league_vex v0.1.0）
 暮气：照英雄联盟：暮气挂在每个被 E 打中的敌人身上（小兵、野怪也算），她身边突进的敌方英雄也被挂上；她之后打中带暮气的敌人（普攻也算）就引爆：补暮气伤害，终焉的等待缩短 25%
@@ -7528,248 +7593,248 @@
 愁煞：被愁煞打中的英雄 6 秒内阵亡就刷新愁煞（谁杀的都算）</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="3" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_vex.md</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>维克托</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Viktor</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>league_viktor</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>被动光荣进化：3级E附带余波，5级Q护盾更强并加速30%，7级技能命中减速20%，9级风暴变大、转移后持续更久。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>虹吸能量：能量弹造成60 + 45% 法强魔法伤害，获得40 + 20% 法强护盾；4秒内下次普攻额外造成30 + 45% 法强魔法伤害。
 （冷却 8 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>海克斯射线：先在敌方英雄脚下放重力场：减速35%，1.25秒后场内敌人晕眩1.25秒。再从目标处向后方射出海克斯射线，造成45 + 40% 法强魔法伤害。
 （冷却 10 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>奥术风暴：风暴落在敌方英雄身上，造成80 + 40% 法强魔法伤害，之后6秒每秒对周围敌人造成25 + 15% 法强魔法伤害，目标阵亡就转移到附近英雄。
 （冷却 70 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="3" t="inlineStr">
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_viktor.md</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>泽拉斯</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Xerath</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>league_xerath</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>发射奥术法球攻击。被动法力澎湃：每14秒下一次攻击额外造成40 + 40% 法强魔法伤害，并使小技能冷却缩短23%；他每击杀一个单位，等待缩短3.5秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>奥能脉冲：蓄力后射出贯穿光束，对直线上的敌人造成110 + 85% 法强魔法伤害。附近有敌方英雄时蓄满，射得更远；只打小兵时快速蓄力，伤害65%。
 （冷却 5 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>冲击法球：命中第一个敌人造成60 + 45% 法强并晕眩0.75~2秒（飞得越远越久）。随后毁灭之眼落在敌方英雄头上，造成60 + 50% 法强并减速，中心伤害+67%。
 （冷却 10 秒 · 施放距离 95000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>奥术仪式：飞升并原地引导，向远处的敌方英雄连发4次魔法炮击，落点预警后爆炸，每发造成120 + 45% 法强魔法伤害；每次命中英雄，之后的炮击伤害+20%。被控制会打断。
 （冷却 50 秒 · 施放距离 220000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J114" s="2" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="3" t="inlineStr">
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_xerath.md</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>亚索</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Yasuo</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>league_yasuo</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 浪客之道：20%暴击几率，暴击造成双倍伤害。剑意每15秒充满一次，充满后下一次出手获得40 + 40% 攻击力的护盾，持续2秒。
 （攻击间隔 0.92 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>斩钢闪：向前突刺，对直线上的敌人造成30 + 100% 攻击力的物理伤害，视为普攻，可以暴击。命中后获得一层旋风烈斩，满2层时下一次改为放出旋风，击飞直线上的敌人1秒。在踏前斩突进中施放时改为环状出剑。
 （冷却 4 秒 · 施放距离 45000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>踏前斩：冲刺穿过一名敌人，造成40 + 60% 攻击力的物理伤害。6秒内再次施放，伤害提高25%，最多提高50%。连招 Q3 E Q：旋风击飞英雄后2.5秒内施放，冲刺途中自动环状出剑。
 （冷却 5 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>狂风绝息斩：闪到一名被控制（击飞、眩晕、禁锢等）的敌方英雄身边，对附近所有被控制的敌方英雄造成150 + 150% 攻击力的物理伤害并再击飞1秒。之后10秒内无视目标30%护甲，剑意立即充满。连招 R Q：斩击后接一记较轻的环状出剑（15 + 50% 攻击力）。
 （冷却 40 秒 · 施放距离 100000 · 施放：指定目标 · 被控制的敌方英雄）</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>亚索风之障壁附加包（league_yasuo_wall v0.1.0）
 主包没有 W：游戏里没有能挡掉飞行物的效果，只画一面墙显得奇怪，当时用户决定删掉。亚索也没有空的技能格，所以风墙全由原生代码做（被动 league_yasuo_wall:wall，不占技能格、没有施法动作）。</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="3" t="inlineStr">
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_yasuo.md</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>永恩</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Yone</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>league_yone</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 狩人之道：20%暴击几率，暴击造成双倍伤害；每第二次普攻换用恶魔刀，造成50% 攻击力的物理伤害和40% 攻击力的真实伤害。
 （攻击间隔 0.92 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>错玉切：向前出剑，对直线上的敌人造成25 + 100% 攻击力的物理伤害，视为普攻，可以暴击。命中后获得一层风暴聚集，满2层时下一次改为向前冲刺，带着旋风击飞路径上的敌人1秒。
 （冷却 4 秒 · 施放距离 45000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>凛神斩：向前顺劈，造成15 + 25% 攻击力的物理伤害和10 + 15% 攻击力的真实伤害（英雄另受5% 最大生命值），每命中一名英雄得35 + 35% 攻击力护盾。每15秒先施放破障之锋：灵体冲向英雄，4秒后归位，以真实伤害重现期间对英雄伤害的25%。
 （冷却 7 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>封尘绝念斩：对一条直线上的所有敌人造成70 + 50% 攻击力的物理伤害和50 + 35% 攻击力的真实伤害并击飞0.75秒，永恩冲到目标身后。连招 Q3 R：Q3 击飞英雄后1.5秒内施放，不蓄力直接斩出；斩中英雄叠一层错玉切（R Q3）。
 （冷却 50 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>永恩 R 附加包（league_yone_r v0.1.0）
 落在哪里：直线上离他最远的那个被斩中的英雄身后 6000（一个都没斩中就照主包，落在 90000 内最近的敌方英雄身后）
@@ -7777,64 +7842,64 @@
 伤害、击飞、画面、Q3 连 R：一样</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J116" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="3" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_yone.md</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>劫</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Zed</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>league_zed</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>影忍法！灭魂劫：技能命中英雄后，下次攻击英雄附加其6%最大生命真实伤害（10秒）。影奥义！鬼斩（自动，4秒）：旋斩周围，造成65 + 75% 攻击力伤害，减速25%。
 （攻击间隔 0.92 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>影奥义！分身：影子落到敌方英雄脚下（5秒），接着鬼斩和诸刃；影子在时模仿他的每次诸刃和鬼斩。影子旁只有一名敌人时，和影子互换位置追击。
 （冷却 12 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>影奥义！诸刃：掷出手里剑，贯穿一条直线：首个敌人受到75 + 100% 攻击力伤害，之后的受到60%。
 （冷却 4 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>禁奥义！瞬狱影杀阵：对交战中的英雄发动：无法选中，突进穿过并留下影子（模仿诸刃和鬼斩）与印记，3秒后爆发110 + 100% 攻击力，期间每次命中+35（最多3次）。击杀、被包围或被控时，和影子互换位置。
 （冷却 50 秒 · 施放距离 60000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>劫读血附加包（league_zed_mark v0.1.3）
 主包 league 保持纯数据。数据读不到生命也读不到伤害，所以主包里劫的两处是替代做法： - 被动「影忍法！灭魂劫」：英雄联盟里是攻击生命低于 50% 的英雄时附加其最大生命的伤害；主包改成「技能刚打中过英雄」后的下一次普攻（league_zed_cw_ready），附加 6% 最大生命真实伤害，10 秒一次。 - 大招「禁奥义！瞬狱影杀阵」：英雄联盟里…
@@ -7842,128 +7907,128 @@
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="3" t="inlineStr">
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zed.md</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>吉格斯</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Ziggs</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>league_ziggs</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>扔小炸弹。一触即发：每12秒下次普攻多造成40 + 60% 法强魔法伤害，每放一个技能冷却-4秒。定点爆破：3级起，敌方英雄贴身时在脚下引爆，造成80 + 50% 法强魔法伤害并击退，自己也被炸开。
 （攻击间隔 1.47 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>弹跳炸弹：扔出炸弹沿直线弹跳，最多落地3次，落地时附近有敌人就爆炸：周围敌人受到105 + 85% 法强魔法伤害。
 （冷却 4.5 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>海克斯爆破雷区：撒下雷区5秒：敌人第一次踩雷受到65 + 45% 法强魔法伤害，之后每0.5秒受到其40%；每次踩雷减速30%。
 （冷却 12 秒 · 施放距离 75000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>科学的地狱火炮：把超大炸弹扔向远处的敌方英雄，落点先出现预警：范围内敌人受到250 + 85% 法强魔法伤害，中心共受到385 + 130% 法强。优先扔向被控制的敌方英雄。
 （冷却 60 秒 · 施放距离 220000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>吉格斯附加包（league_ziggs v0.1.1）
 定点爆破（W）：同上；另外 W 不在冷却时，身边 w_hex_r 以内有血量低于 w_ex% 的敌方防御塔，就在塔上炸开、直接把塔炸掉（算他的击杀），W 进入冷却（英雄联盟：W 能炸掉 25–3…
 一触即发（被动）：强化弹打中防御塔的那一下 ×p_tower%（1.75 倍，英雄联盟对建筑的加成）</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J118" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="3" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ziggs.md</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>佐伊</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Zoe</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>league_zoe</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>射出一颗小星星。烟火四射！：每放一个技能，下一次普攻多造成40 + 50% 法强魔法伤害。
 （攻击间隔 1.47 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>飞星乱入！：掷出一颗飞星，打中第一个敌人造成105 + 60% 法强魔法伤害；飞得越远伤害越高，最远250%。
 （冷却 6 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>催眠气泡：踢出气泡，打中敌方英雄造成60 + 40% 法强魔法伤害，困倦（减速30%）1.4秒后昏睡2秒；没打中就留在原地。昏睡中第一次被飞星打中伤害翻倍。
 （冷却 15 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>折返跃迁：跳进传送门闪向敌方英雄，掷出飞星造成200 + 90% 法强魔法伤害；窃法巧手：再射3颗飞弹，每颗45 + 15% 法强，加速40%。1.2秒后跳回原地。
 （冷却 30 秒 · 施放距离 110000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>佐伊附加包（league_zoe v0.3.0）
 催眠气泡的昏睡：照英雄联盟：困倦后昏睡 2.25 秒，受到任何伤害就醒（谁打的都算），那一下再来一遍真实伤害，最多 100 + 60% 法强
@@ -7972,64 +8037,64 @@
 召唤师技能（0.2.0）：用户：「可以改成召唤师技能那种效果吗 随机的」「能做成智能释放吗」：窃法巧手每次发动（大招射飞弹的那一刻、捡起碎片时）先放一个召唤师技能，按局面挑：被控 → 净化；残血、敌方英雄…</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="3" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zoe.md</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>婕拉</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Zyra</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>league_zyra</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>甩出一颗荆棘种子。荆棘花园：她每次放Q、E都先种下一颗种子，长成植物作战5秒，每1秒攻击一个敌人，造成20 + 12% 法强魔法伤害。
 （攻击间隔 1.43 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>致命棘刺：地面炸出棘刺，范围内的敌人受到80 + 55% 法强魔法伤害。种子长成荆棘喷射者，远距离攻击。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>缠绕之根：放出贯穿地面的藤蔓，路径上的敌人受到70 + 45% 法强魔法伤害并被禁锢1.25秒。种子长成藤蔓鞭击者，近距离攻击并减速30%。
 （冷却 11 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>绞杀之藤：召唤扭曲的密林，造成180 + 70% 法强魔法伤害，2秒后击飞仍在其中的敌人1秒。植物被激怒5秒，伤害提高50%。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t>婕拉附加包（league_zyra v0.1.1）
 荆棘花园 / 狂野生长：主包的照旧；另外种子掉在她身边的地上：每 10 秒一颗（有敌方英雄在附近就掉在朝他的方向），在地上留 30 秒、最多 4 颗；她参与击杀敌方英雄时马上掉一颗（英雄联盟：击杀缩短狂…
@@ -8039,64 +8104,64 @@
 R 绞杀之藤：主包的照旧；密林范围里种子长的植物 5 秒内出手间隔减半（英雄联盟：密林里的植物攻速提高）</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zyra.md</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>阿克尚</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Akshan</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>league_akshan</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>每次普攻开两枪，第二枪对英雄只有50%伤害。无所不用：普攻和技能每打中3下，多造成20 + 30% 攻击力物理伤害，打中英雄还获得40 + 35% 攻击力护盾2秒。赴险夺人：被2个以上敌方英雄围住时伪装2秒并加速40%。
 （攻击间隔 1.07 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>去而复还：朝敌人扔出回旋镖（先瞄准再出手，能躲开），去程和回程各造成45 + 90% 攻击力物理伤害；打中英雄加速20%，持续1秒。
 （冷却 7 秒 · 施放距离 95000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>骄行荡寇：甩出钩索朝敌方英雄荡过去，1.4秒内每0.23秒朝最近的敌人开一枪，造成25 + 60% 攻击力物理伤害，最后翻滚离开再开一枪。
 （冷却 15 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>恩怨相抵：锁定受伤的敌方英雄蓄力0.5秒，最多存5发子弹，被控制会中断；然后连射，每发打中路上第一个敌人，造成35 + 25% 攻击力物理伤害，前面每打中一发，后面的子弹多30%。
 （冷却 50 秒 · 施放距离 160000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>阿克尚扩展包（league_akshan v0.2.2）
 无所不用（第 3 下）：每个目标分别数 3 下（英雄联盟）
@@ -8108,64 +8173,64 @@
 赴险夺人：另外：杀了队友的敌方英雄成为恶徒 60 秒（头上有标记）；阿克尚在恶徒附近加速；阿克尚参与击杀恶徒时，被这个恶徒杀死、还在等复活的队友 1 秒后在泉水复活，阿克尚得 100 金</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="3" t="inlineStr">
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_akshan.md</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>厄斐琉斯</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Aphelios</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>league_aphelios</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>用主手武器开火，每把20发，打空换下一把：通碧射程更远，断魄吸血10%、攻速+20%，坠明减速25%，荧焰溅射，折镜每次命中攻击+5%（4秒，可叠加）。传知者与真知者：随等级额外成长。
 （攻击间隔 0.97 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>武器技能：主手武器的技能，各自冷却：通碧狙击造成110 + 100% 攻击力物理伤害并追射；断魄加速连射回血；坠明定身被它减速的敌人1秒；荧焰扇形波后副手追击；折镜放下哨塔5秒。
 （冷却 1 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>月相轮转：交换主手和副手武器：主手技能在冷却、副手技能已就绪且附近有敌方英雄时才交换。
 （冷却 1.5 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>清辉夜凝：爆点附近有2个以上敌方英雄或目标被控制时，射出月光，在第一个英雄处爆炸，造成160 + 120% 攻击力物理伤害，再按主手：通碧追射、断魄回血、坠明减速90%、荧焰加伤、折镜叠3层。
 （冷却 25 秒 · 施放距离 90000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>厄斐琉斯附加包（league_aphelios v0.2.1）
 武器在手里：整身换武器：主手是断魄 / 坠明 / 荧焰 / 折镜时，站着、跑着、挨打、出手的第一刻都画成那把武器在手里（只在游戏 0.6.4 上）
@@ -8175,301 +8240,301 @@
 厄斐琉斯 R（备好式，v0.4.0）：90000 内有敌方英雄就按：主包待命 6 秒，正被我方打的敌方英雄身边还有别人、或被控住才放，没用上缩短冷却</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="3" t="inlineStr">
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_aphelios.md</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>艾希</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Ashe</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>league_ashe</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>普攻射出冰霜箭，造成100% 攻击力的物理伤害。被动 冰霜射击：普攻使目标减速20%，持续1秒。
 （攻击间隔 1 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>射手的专注：艾希获得30% 攻击速度，持续4秒。期间普攻变为连射，造成130% 攻击力的物理伤害，并使目标减速30%。
 （冷却 7 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>万箭齐发：向前方扇形射出13支冰霜箭，对扇形内每个敌人造成40 + 100% 攻击力的物理伤害（每个敌人只会被命中一次），并使其减速25%，持续1.5秒。
 （冷却 8 秒 · 施放距离 70000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>魔法水晶箭：向目标方向射出一支飞得很远的水晶箭，命中第一个敌方英雄，造成150 + 100% 攻击力的物理伤害并眩晕1.75秒。水晶箭在命中处炸开，对周围敌人造成60 + 50% 攻击力的物理伤害并减速50%，持续2秒。
 （冷却 50 秒 · 施放距离 100000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="3" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ashe.md</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>凯特琳</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Caitlyn</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>league_caitlyn</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 爆头：每第6枪造成180% 攻击力；被夹住的英雄在1.5倍射程内优先爆头，再加40 + 40% 攻击力。90口径绳网：英雄贴身时改射网，造成60 + 60% 攻击力并减速50%，向后跳开，下一枪爆头（冷却12秒）。
 （攻击间隔 1 秒 · 攻击距离 65000）</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>和平使者：瞄准后朝锁定的位置射出穿透子弹（优先瞄敌方英雄，开枪前走开可躲），对第一个命中的敌人造成60 + 110% 攻击力的物理伤害，之后的敌人受到60%。
 （冷却 8 秒 · 施放距离 120000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>约德尔诱捕器：朝敌方英雄扔出夹子（3层充能，每层12秒），第一个落在他脚下，其余错开放在两人之间，存在8秒；第一个踩中的敌方英雄被禁锢1.5秒，凯特琳会对他爆头。
 （冷却 36 秒 · 可存 3 次 · 施放距离 80000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>让子弹飞：瞄准一名敌方英雄1秒（被控制会中断），然后开枪，对路上第一个敌方英雄造成250 + 150% 攻击力的物理伤害。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>凯特琳附加包（league_caitlyn v0.1.0）
 经典引擎模拟（下路对 4 个原版射手、3 套阵容、两边、8 个种子）：她前 5 分钟击杀差 +0.38（金克丝 +1.29、艾希 +0.95、 厄运小姐 +0.90），10 分钟 +1.65，前期伤害只有别的射手的六七成。加攻击、加 Q 伤害、加爆头、出手加快、Q 只能对英雄放等 9 个数值方案，前期最多 +0.6 左右，能拉高前期的也让后期太强。跟踪一局…</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_caitlyn.md</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>德莱文</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Draven</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>league_draven</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>德莱文联盟：每接住一把斧头+1层崇拜（最多6层，每层攻击+4），用斧头击杀英雄时兑现：每层回复25生命，攻速+30%4秒。血性冲刺（自动，12秒）：对英雄出手时移速+40%、攻速+35%，接住斧头即刷新。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>旋转飞斧：手中转起一把飞斧（最多2把），下次攻击额外造成40 + 55% 攻击力伤害。斧头弹回空中，0.4秒后落在他身边随机一处，他会跑进落点圈接住，继续旋转。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>开道利斧：掷出一对贯穿的斧刃，造成70 + 50% 攻击力伤害，击退敌人并减速30%2秒。
 （冷却 15 秒 · 施放距离 95000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>冷血追命：向远处交战中的英雄掷出两把宽大的巨斧，飞得很远，贯穿路上的敌人造成110 + 80% 攻击力伤害；碰到第一个英雄（或飞到尽头）后折返，回程再造成一次伤害。
 （冷却 45 秒 · 施放距离 250000 · 施放：方向 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="3" t="inlineStr">
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_draven.md</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>伊泽瑞尔</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Ezreal</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>league_ezreal</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动咒能高涨：技能每打中一个目标，攻击速度提高12%，持续6秒，最多叠加5层，再次打中时刷新。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>秘术射击：能量箭对命中的第一个敌人造成40 + 140% 攻击力的物理伤害（视为普攻，可暴击），命中后各技能冷却最多剩2/3。精华跃动（冷却6秒）：先向附近敌方英雄射出精华，粘住4秒，下次普攻或技能命中英雄时引爆，造成90 + 90% 攻击力的物理伤害。
 （冷却 5 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>奥术跃迁：交战中：有敌方英雄贴近时朝远离他的方向闪现，目标在普攻射程外时朝他闪现，然后射出追踪魔法箭，造成50 + 50% 攻击力的物理伤害，也会引爆精华跃动。
 （冷却 14 秒 · 施放距离 90000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>精准弹幕：蓄力1秒后射出飞得很远的能量波，对路径上的敌方英雄造成250 + 130% 攻击力的物理伤害，对小兵和野怪伤害减半。
 （冷却 60 秒 · 施放距离 120000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="3" t="inlineStr">
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ezreal.md</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>烬</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Jhin</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>league_jhin</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>被动 低语：四发一轮，第四发必定暴击并附加目标10%最大生命值的伤害，然后装弹2.17秒（可走动、放技能）并加速25%。烬击杀的英雄会在倒下处绽放莲花。
 （攻击间隔 1.2 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>曼舞手雷：掷出手雷，炸到目标后弹向其身后的敌人，最多命中4次，每次造成60 + 70% 攻击力物理伤害；每击杀一个单位，之后每次+35%。
 （冷却 6 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>致命华彩：若万众倾倒就绪，先在敌方英雄脚下种莲花：踩中后减速35%，2秒后炸开造成60 + 120% 攻击力。随后超远射击第一个敌方英雄造成90 + 90% 攻击力；他近期受过我方伤害则禁锢1.67秒。
 （冷却 10 秒 · 施放距离 160000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>完美谢幕：架枪引导，开4枪锁定后射出的超远子弹（被控制会中断），各打中路上第一个敌方英雄造成90 + 55% 攻击力并减速80%；每中一枪后续+30%，第四枪伤害翻倍。
 （冷却 50 秒 · 施放距离 180000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr">
         <is>
           <t>烬低语附加包（league_jhin_whisper v0.1.0）
 额外攻速：不变快；每 1% 换成 0.25% 攻击力（+40% 攻速 = +10% 攻击力）
@@ -8479,190 +8544,190 @@
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="3" t="inlineStr">
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_jhin.md</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>金克丝</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Jinx</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>league_jinx</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>枪炮交响曲！：近处有敌人时用砰砰，造成100% 攻击力的物理伤害，每发加15% 攻击速度（至多3层）；否则换鱼骨头，射程更远，对目标及周围敌人造成110% 攻击力的伤害。罪恶快感：亲手击杀英雄后6秒内25% 攻击速度，100% 移动速度（逐渐回落）。
 （攻击间隔 1 秒 · 攻击距离 64500）</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>震荡电磁波！：蓄力0.4秒后射出电磁波，对命中的第一个敌人造成75 + 120% 攻击力的物理伤害并减速25%，持续2秒。
 （冷却 6 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>嚼火者手雷！：向敌方英雄脚下扔出3只嚼火者手雷，0.5秒后布好，最多留5秒。敌方英雄踩上时手雷爆炸，禁锢范围内的敌方英雄1.5秒并造成80 + 100% 攻击力的物理伤害，随后手雷消失。
 （冷却 10 秒 · 施放距离 80000 · 施放：地点 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>超究极死神飞弹！：发射一枚飞得很远的飞弹，穿过小兵和野怪，命中第一个敌方英雄后爆炸，对周围敌人造成175 + 90% 攻击力 + 10% 目标最大生命值的物理伤害。
 （冷却 50 秒 · 施放距离 250000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
 金克丝：每一次英雄击杀和助攻（几个人同时阵亡也各算一次）</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="3" t="inlineStr">
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_jinx.md</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>卡莎</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Kai'Sa</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>league_kaisa</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力物理伤害。体表活肤：普攻命中英雄叠电浆（被控制的英雄2层），每次命中附加18+9×层数魔法伤害；满5层引爆，造成80+60% 攻击力+8%最大生命真实伤害。极限超载：每8秒首次命中英雄时加速，随后4秒攻速+90%，9级起隐身0.5秒。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>艾卡西亚暴雨：朝周围敌人发射6枚导弹：第一枚射向目标，造成30+50% 攻击力物理伤害，其余每枚10+17% 攻击力。活体武器：攻击力达到200后变为12枚，每枚20+34% 攻击力。
 （冷却 8 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>虚空索敌：锁定后朝敌方英雄射出长距离虚空光束（开火前走开可躲），穿过小兵，命中的第一个英雄受到60+150% 攻击力物理伤害并叠2层电浆。活体武器：12级起叠3层并返还75%冷却。
 （冷却 12 秒 · 施放距离 150000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>猎手本能：冲向一名近期受伤的敌方英雄，落地获得220+180% 攻击力的护盾，持续2秒。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr">
         <is>
           <t>目标标记附加包（league_marks v0.1.0）
 卡莎 体表活肤：每个英雄各记各的（4 秒）：普攻每次附加 18 + 9 × 层数 + 20% 法强的魔法伤害，同一个人第五层引爆 80 + 60% 攻击力 + 8% 最大生命的真实伤害</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr">
+      <c r="J129" s="2" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="3" t="inlineStr">
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_kaisa.md</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>卡莉丝塔</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Kalista</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>league_kalista</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>投矛，命中的敌人身上插一支矛（4秒）。武术姿态：每次投矛后向后跳开。哨兵：有队友在目标身边时，额外造成目标14%最大生命值的真实伤害（5秒一次）。
 （攻击间隔 0.77 秒 · 攻击距离 52500）</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>穿刺：掷出长矛，对第一个敌人造成120 + 105% 攻击力物理伤害并插上一支矛；若将其击杀，长矛穿过去命中下一个。
 （冷却 7 秒 · 施放距离 100000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>撕裂：拔出所有敌人身上的矛：每支造成20 + 50% 攻击力物理伤害并减速8%。击杀英雄时刷新冷却。插满3支时自动拔出。
 （冷却 1.5 秒 · 施放距离 100000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>命运的召唤：把身边一名队友拉进身体保护0.5秒，然后甩向目标，落地击飞周围敌人1.25秒，造成80 + 60% 攻击力物理伤害。
 （冷却 80 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>卡莉丝塔附加包（league_kalista v0.1.1）
 武术姿态：每次投矛后自己判断往前还是往后：最近的敌方英雄残血（40% 以下），或者它在逃（越跑越远）而且快跑出射程（超过攻击距离 80%），就往前追；其余都往后跳开；身边没有敌方英雄时照主…
@@ -8673,311 +8738,311 @@
 卡莉丝塔 E：主包「矛够了」的标记（league_kalista_e_ok）在、撕裂不在冷却（league_kalista_e_cd）：按下就是撕裂，不会空按</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="3" t="inlineStr">
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_kalista.md</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>克格莫</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Kog'Maw</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>league_kogmaw</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>生化弹幕（自动，12秒）：攻击时开启8秒，射程+180，攻击附带目标5%最大生命值伤害。来自艾卡西亚的惊喜：死后虚空之力化身追向附近敌方英雄，爆炸造成80 + 100% 攻击力真实伤害。
 （攻击间隔 0.9 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>腐蚀唾液：吐出腐蚀唾液，命中首个敌人造成80 + 70% 攻击力伤害，护甲和魔抗-20%4秒。被动：攻速+35%。连招：生化弹幕开启时自动补一发Q。
 （冷却 8 秒 · 施放距离 95000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>虚空淤泥：吐出贯穿的虚空淤泥，造成70 + 60% 攻击力伤害并减速35%，留下4秒的减速淤泥带。连招：淤泥命中英雄后补一发活体大炮。
 （冷却 12 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>活体大炮：炮击远处交战中的英雄，0.67秒后落地造成90 + 65% 攻击力伤害；被炸后剩余生命不足50 + 35% 攻击力的英雄直接被击杀。一轮最多3发，冷却20秒。
 （冷却 20 秒 · 施放距离 130000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 克格莫 R：R 好了、射程（130000）内有引擎接受的敌方英雄（主包 R 只打最近被我方打过的）就按，先挑生命比例最低的（大招打残血更痛）。一轮三发、之后锁 20 秒都是主包的数据。不限时…</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="3" t="inlineStr">
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_kogmaw.md</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>卢锡安</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Lucian</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>league_lucian</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动圣光银弹：每放一个技能，下次普攻连开两枪，第二枪50% 攻击力（对小兵、野怪100%）。警惕：附近敌方英雄被定身后，接下来两次普攻额外造成20 + 25% 攻击力的真实伤害。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>透体圣光：射出穿透目标的光束，对直线上的敌人造成65 + 130% 攻击力的物理伤害。
 （冷却 6 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>冷酷追击：冲刺：敌方英雄贴近时后撤，射程内有敌人时后跳，否则追到射程内。接着射出热诚烈弹，爆炸造成60 + 60% 攻击力的真实伤害并标记6秒，期间每次命中移动速度+25%，持续1秒。之后两次普攻都连开两枪。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>圣枪洗礼：原地引导3秒，连射20发子弹，每发射向最近的敌方英雄（穿过小兵），造成12 + 30% 攻击力的物理伤害。受到眩晕、禁锢、击飞等控制或阵亡时中断。
 （冷却 60 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="3" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_lucian.md</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>梅尔</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Mel</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>league_mel</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>射出金色光弹。灼灼之光：每放一个技能，下次普攻多射3枚光弹（最多9枚），每枚12 + 5% 法强魔法伤害；打中英雄叠一层夺命残影。灵魂折镜：每25秒第一次打中英雄时张开屏障1.25秒，受到的伤害减少50%并反弹40%，移速+25%。
 （攻击间隔 1.17 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>耀光齐射：耀光飞弹落在目标处，连续爆炸6次，每次对范围内的敌人造成22 + 15% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>阳炎涡旋：射出阳炎法球，中心的敌人受到60 + 50% 法强魔法伤害并被禁锢1秒；周围的敌人减速30%，1.5秒内受到10 + 6% 法强×4魔法伤害。
 （冷却 10 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>鎏金蚀日：无视距离打击所有带夺命残影的敌方英雄，每层残影造成15 + 8% 法强魔法伤害。
 （冷却 35 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>梅尔附加包（league_mel v0.1.3）
 主包 league 保持纯数据。用户选了「做附加包」，又要求「有连招要做连招」。主包的数据做不到英雄联盟里梅尔的两件事——夺命残影的处决（数据读不到生命，也数不了目标身上的层数）和灵魂折镜的反弹（没有效果能挡住或拐弯一个弹体）——所以放在这个附加包里用原生代码做，外加连招： - 夺命残影的处决：英雄联盟里梅尔每次打中都叠一层残影，残影的伤害够了，下一次打中…</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="3" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_mel.md</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>厄运小姐</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Miss Fortune</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>league_missfortune</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>双枪射击，造成100% 攻击力的物理伤害。被动厄运的眷顾：对新目标的第一枪（她击杀上一个目标后，或1.25秒没开枪后）额外造成40% 攻击力的物理伤害。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>一箭双雕：射出一发子弹，对命中的第一个敌人造成20 + 100% 攻击力的物理伤害，子弹继续飞，对其身后的下一个敌人造成20 + 140% 攻击力的物理伤害（含厄运的眷顾）。第一发击杀目标时，第二发暴击，伤害翻倍。
 （冷却 6 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>枪林弹雨：向目标区域倾泻2秒弹雨，每0.25秒对区域内的敌人造成10 + 15% 攻击力的物理伤害（共80 + 120% 攻击力）并减速40%。随后大步流星：4秒内获得40% 攻击速度和20% 移动速度。
 （冷却 10 秒 · 施放距离 70000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>弹幕时间：原地引导3秒，向前方锥形区域连射12波子弹，每波对其中的敌人造成15 + 45% 攻击力的物理伤害，可以暴击。她受到眩晕、禁锢、击飞等控制或阵亡时引导中断。
 （冷却 50 秒 · 施放距离 75000 · 施放：地点 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>目标标记附加包（league_marks v0.1.0）
 厄运小姐 爱心一击：和上一枪打的不是同一个人就算新目标</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="3" t="inlineStr">
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_missfortune.md</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>尼菈</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Nilah</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>league_nilah</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>喜色川流：鞭刃近战攻击。游刃万变后4秒内，射程+125，攻击扇形顺劈，额外造成25% 攻击力物理伤害，并回复伤害10%的生命。
 （攻击间隔 0.93 秒 · 攻击距离 30000）</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>游刃万变：朝目标方向甩出鞭刃，对直线上的所有敌人造成40+100% 攻击力物理伤害，并强化之后4秒的攻击。
 （冷却 1 秒 · 施放距离 60000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>纵情逐流 / 轻纱飞漾：纵情逐流：穿过敌方英雄冲刺，落地对周围造成60+45% 攻击力物理伤害，2层充能。用完时放轻纱飞漾：2.25秒内闪避所有攻击，技能伤害-25%，移速+20%，附近友方英雄同样获得1.5秒。
 （冷却 1 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>神恩激荡：旋转鞭刃1秒，每段造成12+20% 攻击力物理伤害，最后造成100+110% 攻击力物理伤害并把周围敌人拉到身边；附近友方英雄回复40+30% 攻击力生命并获得40+30% 攻击力护盾。
 （冷却 40 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr">
         <is>
           <t>尼菈附加包（league_nilah v0.1.1）
 喜色川流（被动）：另外她和附近友方英雄每次回血、得到护盾都多 15%（英雄联盟的「乐无止境」：她给的、给她的治疗和护盾都更强）
@@ -8986,64 +9051,64 @@
 神恩激荡什么时候放：圈里有 2 个以上敌方英雄才放；只有 1 个时，他血量不到一半、她自己血量不到 40%、或者附近没有别的敌方英雄会赶来，也放；最多等 1.5 秒</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="3" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_nilah.md</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>莎弥拉</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Samira</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>league_samira</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>远处开枪，近身挥刀并附加15 + 20% 攻击力魔法伤害。被动悍勇本色：用和上一次不同的招式命中英雄，评价E→S升一级，每级移速+3%，9秒没打到英雄清零。攻击被控制的英雄时冲上去击飞0.5秒。
 （攻击间隔 0.97 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>交火：身边有敌人时挥刀斩击前方，否则开枪打中第一个敌人，造成30 + 130% 攻击力物理伤害。
 （冷却 5 秒 · 施放距离 90000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>狂飙：冲到敌方英雄身后，对周围敌人造成70 + 40% 攻击力魔法伤害，攻速+30%。随即锋旋：旋转0.75秒砍两次，每次25 + 70% 攻击力，期间受到的攻击伤害-60%。击杀英雄刷新冷却。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>炼狱扳机：评价到S时才会施放：原地旋转连射2秒，每0.2秒向周围所有敌人各开一枪，造成10 + 40% 攻击力物理伤害，期间生命偷取40%。放完评价清零。
 （冷却 5 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>莎弥拉边走边射附加包（league_samira_r v0.1.0）
 R 期间：旋转连射，同时走向 90000 内生命 + 护盾最少的敌方英雄，走到 30000 内站住；被硬控时不走
@@ -9053,127 +9118,127 @@
 莎弥拉 E、Q（攒评价）：S 要连着换五种出手打中英雄（枪 / 剑普攻、Q、E 冲刺、落地的 W 旋转），一下打不中 9 秒就掉。R 不按时：60000 内有敌方英雄、她生命不低于 50%、目标身边的敌方…</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>2.84</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="3" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_samira.md</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>希维尔</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Sivir</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>league_sivir</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>被动 敏锐疾行：攻击或技能命中英雄时移速+25%，2秒内递减。弹射：每10秒下一次攻击开启4秒弹射：攻速+45%，攻击再弹向目标身后最多3个敌人，各造成60% 攻击力物理伤害（可暴击）。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>回旋之刃：掷出十字刃，飞到尽头再飞回手中，往返都对路上所有敌人造成60 + 80% 攻击力物理伤害。附近有英雄时朝他所在的位置掷出（出手前锁定，可以躲开）。
 （冷却 8 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>法术护盾：张开法术护盾，最多3秒：免疫技能伤害和控制。第一次被击中时回复60 + 40% 攻击力生命并触发敏锐疾行，护盾再撑1秒后破碎。
 （冷却 12 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>狩猎：附近友方英雄（含自己）移速+30%，持续8秒。狩猎期间希维尔的攻击命中英雄会缩短回旋之刃和法术护盾的冷却，弹射冷却减半；她的攻击击杀英雄时刷新狩猎。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 希维尔 E：60000 内的敌方英雄刚放了技能（20 tick 内技能冷却开始走），或她生命不到 40% 而 40000 内有敌方英雄</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="3" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_sivir.md</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>斯莫德</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Smolder</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>league_smolder</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>喷出小火球。被动龙之研习：技能命中英雄、龙息击杀单位各获得1层（阵亡清空），每层使龙息、喷嚏、扑棱火球各+0.75/1.65/0.25魔法伤害。龙息在10/25/40层时依次获得爆炸、反冲火球、灼烧。
 （攻击间隔 0.93 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>超级灼热龙息：喷吐火球，造成60+120% 攻击力物理伤害。10层：爆炸波及周围敌人；25层：向目标身后喷出反冲火球（50%伤害）；40层：灼烧3秒，每秒造成10+10% 攻击力+1%最大生命真实伤害。
 （冷却 5 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>阿嚏！ / 扑棱，扑棱，扑棱！：打喷嚏喷出火焰，造成40+40% 攻击力物理伤害并减速35%，命中英雄时爆炸，再造成40+40% 攻击力物理伤害。被近身或追击残血时改用扑棱，扑棱，扑棱！：飞起并加速40%，向残血敌人连发5枚火球，各10+30% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>妈----！：呼唤妈妈沿直线喷火，造成110+80% 攻击力物理伤害，中心的敌人多受50%伤害并减速40%（2秒）。斯莫德站在中心线上时回复80+30% 攻击力生命。
 （冷却 50 秒 · 施放距离 90000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>斯莫德附加包（league_smolder v0.1.1）
 龙之研习的层数：死后保留（层数、计数器、三档全部原样补回）
@@ -9181,190 +9246,190 @@
 扑棱，扑棱，扑棱！：自己的冷却（20 秒），好了就每 3 tick 看一次：撤——生命低于 40% 而 40000 内有敌方英雄、30000 内有敌方英雄、或 40000 内敌方英雄 2 名以上且比…</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="3" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_smolder.md</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>崔丝塔娜</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Tristana</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>league_tristana</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>普攻发射炮弹，造成100% 攻击力的物理伤害。被动 瞄准：3/6/9/12级时射程各提高4.5%。爆炸火花：普攻击杀的敌人会爆炸，对周围敌人造成30 + 30% 攻击力的物理伤害。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>爆炸火花：向目标投掷炸弹，4秒后爆炸，对周围敌人造成70 + 80% 攻击力的物理伤害；她每命中一次伤害 +25%，第4次立即引爆。同时急速射击：攻速+80%，持续7秒。
 （冷却 8 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>火箭跳跃：炮弹打中炸弹已叠2层以上的敌方英雄时跳到他身边；开炮时有敌方英雄贴身则向后跳开。落地对周围敌人造成50 + 60% 攻击力的物理伤害并减速40%，持续2秒。冷却18秒；她击杀敌方英雄或满层引爆英雄身上的炸弹时刷新。
 （冷却 10 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>毁灭射击：对敌方英雄发射巨型炮弹（优先贴身的），对目标及周围敌人造成200 + 120% 攻击力的物理伤害，将他们击退，落地后眩晕0.5秒。
 （冷却 50 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
 崔丝塔娜：每一次英雄击杀和助攻都刷新（满层引爆照旧）</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="3" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_tristana.md</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>图奇</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Twitch</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>league_twitch</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>弩箭攻击。被动死亡毒液：普攻、毒桶和大招的箭每次挂一层毒，每层6秒内每秒造成1 + 2% 攻击力真实伤害。
 （攻击间隔 0.9 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>埋伏：伪装隐身最多5秒并加速20%，出手即现形，之后6秒攻速+35%。击杀敌方英雄时刷新冷却。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>剧毒之桶：扔出毒桶：范围内敌人挂一层毒并减速30%，毒池持续3秒。随后接毒性爆发：每层毒造成6 + 16% 攻击力物理伤害。
 （冷却 11 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>火力全开：6秒内射程+300、攻击力+15，弩箭穿透一条直线，每多穿一个少10%（最低60%）。两名敌方英雄在附近时施放。
 （冷却 60 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
 图奇：埋伏助攻也刷新；E 等到有人满 6 层毒、或这一爆能毒死人才引爆（v0.3.0），条件一满足下一箭就爆（v0.3.1）</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="3" t="inlineStr">
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_twitch.md</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>韦鲁斯</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Varus</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>league_varus</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>射箭攻击，附带20魔法伤害，命中英雄叠一层枯萎（最多3层）。被动复仇之欲：击杀英雄后攻速+60%，击杀小兵野怪+20%，持续5秒。
 （攻击间隔 0.93 秒 · 攻击距离 57500）</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>穿刺之箭：拉弓射出穿透箭：射程内有敌方英雄时蓄满力，造成110 + 130% 攻击力物理伤害，否则快速出手、伤害较低；之后每个敌人伤害递减。命中英雄时引爆枯萎：每层3%最大生命值真实伤害并缩短技能冷却。每40秒一次蓄满的箭再加6%。
 （冷却 6.67 秒 · 施放距离 95000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>恶灵箭雨：向目标区域射下箭雨，造成70 + 90% 攻击力物理伤害并引爆枯萎；地面腐化4秒，其中的敌人减速30%、受到的治疗降低40%。
 （冷却 8 秒 · 施放距离 90000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>腐败锁链：射出腐败锁链，命中第一个敌方英雄：150 + 80% 攻击力物理伤害、禁锢2秒、叠满3层枯萎；锁链随后扩散到附近的敌方英雄，禁锢1.5秒。
 （冷却 60 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>韦鲁斯枯萎附加包（league_varus_blight v0.1.0）
 枯萎记在哪里：每个敌方英雄自己身上（各最多 3 层，6 秒）
@@ -9373,191 +9438,191 @@
 R：一样（叠在被锁住的人身上）</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="3" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_varus.md</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>薇恩</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Vayne</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>league_vayne</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 暗夜猎手：附近有敌方英雄时移动速度+8%。圣银弩箭：3.5秒内连续第3次命中（普攻、技能都算）额外造成50的真实伤害，对英雄再加7%最大生命值。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>闪避突袭：翻滚：敌方英雄贴近时往后滚，射程内有敌人时后跳，否则滚进射程。7秒内的下一次普攻额外造成25 + 80% 攻击力的物理伤害。
 （冷却 5 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>恶魔审判：用大弩射出重箭，对敌方英雄造成60 + 70% 攻击力的物理伤害并击退，落地时再受到30 + 35% 攻击力的物理伤害并眩晕1秒。
 （冷却 10 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>终极时刻：8秒内攻击力+25%，技能冷却缩短50%，闪避突袭附带1秒隐身，暗夜猎手的移速变为3倍。期间她亲手击杀英雄时，终极时刻刷新为8秒。
 （冷却 50 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>薇恩圣银弩箭附加包（league_vayne_bolts v0.1.0）
 主包 league 保持纯数据。数据分不清一次攻击打中的是谁，所以主包里圣银弩箭的两层记在薇恩自己身上：她轮流打两个人也会凑满 3 下，在第三个被打中的人身上爆。这个附加包用原生代码做成英雄联盟的样子：同一个目标连续挨 3 下才爆。</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="3" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_vayne.md</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>霞</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Xayah</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>league_xayah</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>甩出羽刃攻击。被动锐切：每放一个技能，之后3次普攻（最多存5次）穿透直线，其他目标受到50%伤害，并在目标身后留下一根羽毛（6秒）。
 （攻击间隔 0.83 秒 · 攻击距离 57500）</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>双刃·倒钩：扔出两把穿透匕首，各造成60 + 80% 攻击力物理伤害（后续目标50%），各留一根羽毛；随后倒钩收回所有羽毛，每根对路过的敌人造成50 + 60% 攻击力伤害，一次收回命中英雄第3次起禁锢1.25秒。
 （冷却 7 秒 · 施放距离 75000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>致死羽衣：攻速+50%，持续4秒；期间每次普攻再甩出一片25%伤害的羽刃，命中英雄时移速+30%。洛在附近时，他也获得这些效果。
 （冷却 8 秒 · 施放距离 57500 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>暴风羽刃：跃向空中，1.1秒内不受伤害和控制，再向前方降下匕首雨，造成160 + 100% 攻击力物理伤害，留下一排羽毛并随即收回。
 （冷却 60 秒 · 施放距离 60000 · 施放：方向 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>霞羽毛附加包（league_xayah_feathers v0.1.0）
 定身条件：同一个英雄被 3 根羽毛打中（60 tick 内）
 定身时长、画面、伤害：一样</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="3" t="inlineStr">
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_xayah.md</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>芸阿娜</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Yunara</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>league_yunara</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>念珠普攻附带18 + 20% 法强魔法伤害。初生之誓：这段伤害也会暴击（基础暴击10%）。灵蕴拳：普攻攒灵蕴，满了自动开启5秒：攻速+40%，多附带18 + 20% 法强魔法伤害，并溅射周围敌人30% 攻击力物理伤害。
 （攻击间隔 0.83 秒 · 攻击距离 57500）</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>善恶轮：掷出旋转念珠，对路径上的敌人造成70 + 85% 攻击力物理伤害和衰减减速，终点再旋转1秒。超凡形态：改为射线，造成160 + 120% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>明踪步：附近有敌方英雄时，移速+40%（追击时+60%），持续1.5秒。超凡形态：敌方英雄贴近时改为向后冲刺。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>定圣诀：附近有2个以上敌方英雄或目标被控制时，进入超凡形态15秒：灵蕴拳持续开启，善恶轮变为射线，明踪步变为冲刺，两者冷却立刻减少80%。
 （冷却 70 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>芸阿娜附加包（league_yunara v0.1.1）
 夜影翻（超凡形态的 E）：按情况选方向：最近的敌方英雄残血（35% 以下）又快出射程就往前冲把它拉进射程；它贴身、或她自己残血（40% 以下）就往后冲
@@ -9566,185 +9631,185 @@
 超凡形态的样子：另外站着、跑着都画成带金边和头后光环的她（游戏 0.6.4）</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="3" t="inlineStr">
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_yunara.md</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>泽丽</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Zeri</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>league_zeri</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>普攻电火迸射：7发连射打第一个敌人。被动内能迁转：每5次攻击充满电，下一击为电击弹，额外造成40 + 100% 法强魔法伤害并减速，命中英雄再造成4%最大生命真实伤害，自己获得护盾和移速。
 （攻击间隔 0.93 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>强穿激光：发射电脉冲，对第一个敌人造成60 + 110% 攻击力物理伤害并减速35%。先打中小兵或野怪时，从那里化为长激光，伤害并减速身后所有敌人。
 （冷却 10 秒 · 施放距离 90000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>灿丽花火：短距冲刺（被贴身时后撤），之后5秒普攻贯穿：后面的敌人受到80%伤害，并额外造成20 + 30% 法强魔法伤害。命中英雄缩短冷却。
 （冷却 20 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>超限爆闪：电新星对周围敌人造成150 + 100% 法强魔法伤害，超载5秒：攻速+30%、移速+20%，命中英雄叠加移速并延长；普攻变为三连发，在敌人间连锁闪电。
 （冷却 60 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>泽丽附加包：W 撞墙激光 + 被动偷盾（league_zeri v0.1.1）
 - W「强穿激光」的脉冲先打中小兵或野怪时才在那里化为长激光（小兵代替墙）； - 被动「内能迁转」的电击弹打中英雄时给自己一个小护盾（代替偷盾）。</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="3" t="inlineStr">
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zeri.md</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>阿利斯塔</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Alistar</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>league_alistar</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>用双拳重击。被动凯旋怒吼：控制命中敌方英雄3次后怒吼，回复自己40 + 20% 法强、周围友方英雄50 + 30% 法强生命。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>大地粉碎：践踏接大地粉碎：先践踏3秒（每脚12 + 9% 法强），再砸地，周围敌人受到80 + 80% 法强魔法伤害并击飞1秒。踩中英雄5次后，下次普攻眩晕1秒。
 （冷却 10 秒 · 施放距离 24000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>野蛮冲撞：野蛮冲撞接大地粉碎：冲向敌方英雄，撞退并造成100 + 110% 法强魔法伤害，随即砸地击飞周围敌人，同时开始践踏。（和大地粉碎共用：6秒内只砸一次）
 （冷却 12 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>坚定意志：交战时怒吼：免疫控制1秒，7秒内受到的伤害降低50%。
 （冷却 60 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="3" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_alistar.md</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>巴德</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Bard</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>league_bard</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>射出星光。被动旅者的召唤：每3秒一只米普随攻击飞出，对目标周围的敌人造成45 + 50% 法强魔法伤害并减速25%（1秒）。
 （攻击间隔 1.5 秒 · 攻击距离 52000）</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>星界束缚：射出星界能量，命中的第一个敌人受到100 + 75% 法强魔法伤害并减速60%；若其身后还有敌人，两者都受到伤害并眩晕1.5秒。
 （冷却 7 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>游神圣坛 / 神奇旅程：游神圣坛：向交战中的友方英雄（或自己）投出圣坛，治疗140 + 60% 法强，移速+30%。神奇旅程：被敌人近身时开门，带身边的友方英雄远离，移速+40%（16秒一次）。
 （冷却 7 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>调和命运：向聚在一起的敌方英雄（或被控制的友方英雄）投出金色法球，范围内所有单位（含友军、自己和防御塔）时停2.5秒：无法行动、无法被选中、不受伤害。
 （冷却 60 秒 · 施放距离 90000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>巴德「神奇旅程」穿墙门附加包（league_bard v0.6.1）
 什么时候开门：冷却（16 秒）一好就每 3 tick 看一次：撤——生命低于 45% 而 30000 内有敌方英雄、15000 内有敌方英雄、或 30000 内敌方英雄 2 名以上且比身边友方…
@@ -9753,190 +9818,190 @@
 争大小龙（命运之轮）：用户：「给巴德加上争大小龙时主动对龙放大招拖时间」。大龙、小龙在大招射程 80000 内、生命低于 95%（已经有人在打）、35000 内有敌方英雄、命运之轮的圈（36000）里…</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="3" t="inlineStr">
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_bard.md</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>布里茨</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Blitzcrank</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>league_blitzcrank</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害；大招没在冷却时，1秒后再落一道闪电，造成20 + 15% 法术强度的魔法伤害。被动 法力屏障：被围攻或被控制时获得120 + 80% 法术强度的护盾（冷却60秒）。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>机械飞爪：射出机械手，抓住直线上第一个敌方英雄（穿过小兵），造成70 + 50% 法术强度的魔法伤害，眩晕并把它拉到身前。
 （冷却 10 秒 · 施放距离 70000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>能量铁拳：一记上勾拳，造成20 + 100% 攻击力的物理伤害并击飞1秒。过载运转（每15秒）：敌方英雄靠近时自动开启，4秒内移速+40%（逐渐降低）、攻速+25%，结束后减速25%1.5秒。
 （冷却 7 秒 · 施放距离 25000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>静电力场：释放静电，对身边敌人造成150 + 80% 法术强度的魔法伤害，并沉默敌方英雄1秒。打起来才放；放出后普攻的闪电停用，直到大招冷却结束。
 （冷却 50 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.0）
 布里茨 法力屏障：生命不高于 30%</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="3" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_blitzcrank.md</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>布隆</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Braum</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>league_braum</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>震荡猛击：普攻和寒冬之咬命中英雄叠一层，第4层眩晕1.25秒并造成85 + 60% 法强魔法伤害；之后8秒不再叠层，普攻额外造成12 + 10% 法强魔法伤害。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>寒冬之咬：从盾中甩出寒冰，造成105 + 60% 法强+最大生命2%魔法伤害，减速70%，2秒内渐弱到35%。
 （冷却 8 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>坚不可摧：举盾3.5秒：受到伤害降低50%，获得60 + 40% 法强护盾，身边友方英雄伤害降低20%。挺身而出：冲到友方英雄身边，两人护甲和魔抗+30，持续3秒。
 （冷却 1 秒 · 施放距离 45000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>冰川裂隙：猛砸地面，冰川裂隙冲向目标，造成180 + 70% 法强魔法伤害并击飞0.6秒（第一个英雄1.25秒），留下4秒的裂隙，减速40%。
 （冷却 60 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>布隆附加包（league_braum v0.1.1）
 Test build of Braum as in League (needs League of Legends Heroes): replaces the main pack's Braum so Concussive Blows stacks on each champion and his allies' attacks add stacks to…</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="3" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_braum.md</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>迦娜</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Janna</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>league_janna</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>普攻吹出一道风弹，造成100% 攻击力的物理伤害。被动 顺风而行：战斗中，她和身边的友方英雄移动速度提高8%。
 （攻击间隔 1.5 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>飓风呼啸：放出一道龙卷风，对直线上的敌人造成80 + 60% 法术强度的魔法伤害，并击飞0.75秒。
 （冷却 9 秒 · 施放距离 75000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>风暴之眼：对一名敌方英雄放出和风守护，造成60 + 40% 法术强度的魔法伤害并减速30%，持续2秒。同时以风暴之眼为身边一名友方英雄提供150 + 75% 法术强度的护盾，持续4秒，护盾存在时攻击力提高15%；身边没有队友时护住自己。
 （冷却 5 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>复苏季风：击退身边的敌人，然后引导3秒，每秒为身边的友方英雄（包括自己）回复130 + 50% 法术强度的生命值，共4次。受到控制或阵亡时中断。
 （冷却 50 秒 · 施放距离 40000 · 施放：指定目标 · 友方英雄）</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 迦娜 E 风暴之眼（50000 内）：有危险的队友（生命不高于 50%，或身边 25000 内有 2 个以上敌方英雄）里生命比例最低的；都没危险就给离敌方英雄最近的（正在打的那个）
@@ -9944,248 +10009,248 @@
 迦娜 R：她或身边 40000 内的队友生命不到 35% 而 50000 内有敌方英雄，或两人以上生命不到 60% 而她身边有敌方英雄。对生命最低的那位放（治疗是她身边一圈，对谁放都一样）</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="3" t="inlineStr">
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_janna.md</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>卡尔玛</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Karma</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>league_karma</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>射出灵能飞弹。聚能之炎：技能命中英雄，梵咒冷却最多缩短60%。鼓舞（自动，9秒）：给被控或交战中的队友（或自己）110 + 50% 法强护盾，移速+35%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>心灵烈焰：射出灵火，命中首个敌人爆炸，周围敌人受到100 + 70% 法强魔法伤害并减速35%。灵光闪耀（梵咒）：额外50 + 30% 法强伤害并留下火环，1.5秒后爆发造成70 + 50% 法强伤害、减速50%。
 （冷却 6 秒 · 施放距离 62000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>坚定不移：连住敌方英雄，造成60 + 40% 法强魔法伤害；1.33秒未挣脱则再次受伤并禁锢1.67秒。焕发（梵咒，被围攻时）：回复110 + 40% 法强生命，禁锢2.33秒。连招：禁锢时梵咒Q随即跟上。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>梵咒：强化6秒内的下一个技能：队友危险时立即蔑视（附近队友都获得60 + 30% 法强护盾和加速），否则强化Q或被围攻时的W。未使用则返还冷却。
 （冷却 35 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="3" t="inlineStr">
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_karma.md</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>蕾欧娜</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Leona</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>league_leona</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 日光：被蕾欧娜技能命中的敌人1.5秒内受到的伤害提高10%，每个技能各挂一层。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>破晓之盾：用盾猛击身边的一个敌人，造成100% 攻击力的物理伤害和40 + 40% 法术强度的魔法伤害，眩晕1秒。
 （冷却 5 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>天顶之刃：掷出剑光，对直线上的敌人造成60 + 40% 法术强度的魔法伤害，禁锢命中的第一个敌方英雄0.5秒并冲到它身边。日蚀：出手时举盾，3秒内受到的伤害降低25%，随后盾牌爆发，对周围敌人造成60 + 40% 法术强度的魔法伤害；命中敌人则减伤再持续3秒。
 （冷却 8 秒 · 施放距离 60000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>日炎耀斑：召唤一道阳光，0.6秒后落在敌方英雄所在处，对范围内的敌人造成150 + 80% 法术强度的魔法伤害并减速80%，中心的敌人改为眩晕，持续1.75秒。
 （冷却 60 秒 · 施放距离 80000 · 施放：地点 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="3" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_leona.md</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>璐璐</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Lulu</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>league_lulu</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>射出魔弹。被动皮克斯，仙灵伙伴：皮克斯朝同一目标射出3颗飞弹，每颗造成12 + 8% 法强魔法伤害。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>闪耀长枪：璐璐和皮克斯各射出一道贯穿魔弹，直线上的敌人受到80 + 60% 法强魔法伤害并减速80%，1.5秒内逐渐减弱。
 （冷却 6 秒 · 施放距离 60000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>奇思妙想：把敌方英雄变形1.75秒（无法攻击和施法、减速），造成70 + 40% 法强魔法伤害；帮忙，皮克斯！：附近友方英雄获得110 + 50% 法强护盾和25%移速、攻速（3.5秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>狂野生长：交战时让被控制或被敌人贴身的友方英雄（或自己）变大：生命+350，周围敌人击飞1秒，7秒内身边敌人减速30%。
 （冷却 60 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 璐璐 E 帮忙，皮克斯！（先 30000，再 60000 内）：同迦娜</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="3" t="inlineStr">
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_lulu.md</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>茂凯</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Maokai</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>league_maokai</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>巨臂砸击。吸元秘术：技能命中后下一次普攻额外造成2%最大生命魔法伤害，回复40 + 60% 法强生命（4秒一次）。树苗投掷：每10秒自动向敌方英雄扔树苗，敌人靠近就爆炸：100 + 50% 法强魔法伤害，减速35%。
 （攻击间隔 1.25 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>荆棘重击：巨拳砸地，推开身边的敌人，冲击波对前方敌人造成100 + 40% 法强魔法伤害外加目标2%最大生命伤害，并减速95%（很快减弱）。
 （冷却 6 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>扭曲突刺：化作树根冲向敌方英雄（途中免伤免控），到达后禁锢1.3秒，造成100 + 40% 法强魔法伤害。身边有友方英雄或正在交战时才放。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>自然之握：召唤荆棘墙缓缓向前推进，碰到的敌人受到180 + 75% 法强魔法伤害并被禁锢0.8~2.4秒（推得越远越久），撞到英雄后他加速。有2名敌方英雄或交战时才放。
 （冷却 60 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>茂凯附加包（league_maokai v0.1.0）
 吸元秘术回血：按等级回复最大生命的 4.5%–12%（英雄联盟）
@@ -10193,64 +10258,64 @@
 草丛里的树苗：读地图的草丛格子；立在草丛里的树苗爆炸半径更大（34000）、伤害 ×1.6、减速 45%（英雄联盟草丛里的树苗更强）</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="K153" s="2" t="inlineStr"/>
-      <c r="L153" s="3" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_maokai.md</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>米利欧</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Milio</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>league_milio</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>射出小火球。被动热情洋溢！：技能触及的友方获得30%攻击力和法术强度（5秒），米利欧获得15%移速。
 （攻击间隔 1.5 秒 · 攻击距离 53000）</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>火爆飞踢：踢出火球，击退命中的第一个敌人，随后火球落下，对周围敌人造成120 + 70% 法强魔法伤害并减速40%（1.5秒）。
 （冷却 7 秒 · 施放距离 75000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>融融情谊 / 依依不舍：融融情谊（2次）：友方英雄获得80 + 40% 法强护盾和16%移速（2.5秒）。依依不舍：在其身上点燃营火6秒，每1秒治疗周围友方22 + 4% 法强并增加攻击距离。
 （冷却 18 秒 · 可存 2 次 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>生生不息：友方被控制或被敌人贴身时，为周围友方英雄恢复150 + 50% 法强生命，免疫控制1秒并获得65%韧性（3秒）。
 （冷却 60 秒 · 施放距离 75000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>米利欧附加包（league_milio v0.1.2）
 热情洋溢！：E、R 触及的友方（营火每一跳也算）身上挂记号（画面不变，攻击力、法强 +20%）；他下一次打中敌人（普攻或技能，不算防御塔）就把那个敌人点燃：1.5 秒内 20-100 魔法伤…
@@ -10258,243 +10323,243 @@
 解控：R 生效时圈里身上有控制的友方英雄真的被解控（再加主包的 1 秒免控和韧性）</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="3" t="inlineStr">
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_milio.md</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>莫甘娜</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Morgana</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>league_morgana</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>普攻射出一团暗影，造成100% 攻击力的物理伤害。被动 灵魂吸取：技能对英雄造成伤害时，为自己回复约为伤害15%的生命值。
 （攻击间隔 1.5 秒 · 攻击距离 50000）</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>暗之禁锢：射出暗之禁锢，穿过小兵和野怪，对沿途敌人造成80 + 60% 法术强度的魔法伤害，停在第一个敌方英雄身上并将其禁锢2秒。每12秒同时在其脚下留下折磨之影，4秒内共造成80 + 40% 法术强度的魔法伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>黑暗之盾：对敌方英雄施法，为身边一名友方英雄套上150 + 70% 法术强度的护盾，持续5秒，护盾存在时免疫控制。身边没有队友时护住自己。
 （冷却 8 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>灵魂镣铐：锁住身边所有敌方英雄，造成170 + 80% 法术强度的魔法伤害并减速20%，自身移动速度提高20%。跑出锁链范围的敌人会挣断锁链；3秒后仍被锁住的敌方英雄再受到一次伤害并被眩晕1.5秒。
 （冷却 50 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="3" t="inlineStr">
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_morgana.md</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>娜美</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Nami</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>league_nami</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>普攻射出一颗水弹，造成100% 攻击力的物理伤害。被动 踏浪之行：技能命中友方英雄时，使其移动速度提高20%，持续1.5秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>冲击之潮：水流冲击敌人，造成65 + 45% 法术强度的魔法伤害，弹向附近友方英雄回复70 + 35% 法术强度的生命值，再弹向另一名敌方英雄造成60 + 40% 法术强度伤害。唤潮之佑：被治疗者4秒内攻击力和法术强度提高15%，被击中者减速25%。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>碧波之牢：向敌人（优先敌方英雄）扔出水泡，落地时对范围内的敌人造成80 + 60% 法术强度的魔法伤害，并将其困在水泡中击飞1.25秒。
 （冷却 10 秒 · 施放距离 70000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>怒涛之啸：召唤一道巨浪朝敌方英雄推进，对沿途敌人造成150 + 70% 法术强度的魔法伤害，击飞0.5秒并减速60%，巨浪走得越远减速越久（2至3秒）。经过的友方英雄获得双倍踏浪之行加速。
 （冷却 50 秒 · 施放距离 90000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="3" t="inlineStr">
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_nami.md</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>诺提勒斯</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Nautilus</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>league_nautilus</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>排山倒海：普攻敌方英雄时将其禁锢0.83秒，并额外造成20 + 30% 法强魔法伤害，之后6秒内不再触发。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>疏通航道：抛出铁锚，钩中第一个敌方英雄，造成75 + 60% 法强魔法伤害，并把双方拉向彼此。
 （冷却 10 秒 · 施放距离 75000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>泰坦之怒：获得110 + 60% 法强护盾，6秒内普攻还会伤及目标周围的敌人15 + 20% 法强。暗流涌动：地面震荡三波，周围敌人受到70 + 50% 法强魔法伤害并减速40%1.25秒。
 （冷却 8 秒 · 施放距离 25000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>深海冲击：对射程内一名敌方英雄发出深海冲击波：沿途敌人被击飞并受到60 + 30% 法强伤害；目标受到150 + 80% 法强魔法伤害，击飞1秒后眩晕0.75秒。
 （冷却 50 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>诺提勒斯钩墙附加包（league_nautilus v0.1.2）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个附加包里（合集 league_addons 也带着它）。 装上后，诺提勒斯的 Q「疏通航道」：锚沿路线先碰到野区的墙（引擎的碰撞墙，5v5 地图 90 格）时，把他拉到墙边，并返还一半冷却—— 和英雄联盟一样；先碰到敌方英雄时照主包钩人（两人拉向彼此）。</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="3" t="inlineStr">
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_nautilus.md</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>波比</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Poppy</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>league_poppy</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>钢铁大使：每8秒普攻远远扔出圆盾，多造成60 + 30% 法强魔法伤害；盾落在地上，捡起得120 + 60% 攻击力护盾。坚定风采：双抗+16%；敌方英雄靠近时移速+40%，2秒内身边敌人不能位移。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>圣锤猛击：锤击地面，造成60 + 70% 攻击力物理伤害（英雄另受6%最大生命），地面减速25%，1秒后再炸一次。
 （冷却 7 秒 · 施放距离 30000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>英勇冲锋：冲向敌方英雄，造成70 + 80% 攻击力物理伤害并推着他走，结束时眩晕0.75秒。
 （冷却 11 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>持卫的裁决：身边有2个以上敌方英雄时砸地：80 + 40% 攻击力物理伤害并击飞1秒；否则蓄力抡锤推出冲击波，打中的英雄受150 + 70% 攻击力物理伤害并被打飞到远处。
 （冷却 60 秒 · 施放距离 55000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>波比附加包（league_poppy v0.1.0）
 坚定风采的光环：光环里正在突进的敌方英雄被挡下：击飞 0.5 秒、受魔法伤害，然后缚地并减速 2 秒（每次光环每人一次）
@@ -10504,185 +10569,185 @@
 钢铁大使的护盾：最大生命的 11%（1 级）到 21%（18 级）</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="3" t="inlineStr">
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_poppy.md</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>派克</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Pyke</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>league_pyke</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>鱼叉挥砍。被动溺水之幸：挨打积攒灰血（最多5层），潜行或3秒没挨打时每层回复15 + 8% 攻击力生命。无法靠生命成长，攻击力成长更高。
 （攻击间隔 0.92 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>透骨尖钉：英雄贴身时戳刺，否则蓄力扔出鱼叉，命中第一个敌人：35 + 60% 攻击力物理伤害，减速90%，鱼叉命中的会被拉回。
 （冷却 7 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>魅影浪洄：幽潭潜行：潜行并加速，回复灰血。随即魅影浪洄：冲过敌方英雄，魅影随后飞回他身边，途经的英雄受到50 + 60% 攻击力物理伤害并晕眩1秒。
 （冷却 11 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>涌泉之恨：X形打击：英雄受到180 + 60% 攻击力真实伤害，低于此值被处决，否则只受一半；其他敌人受一半物理伤害。有英雄死在X里时派克闪到其身上并刷新大招。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>派克精确斩杀附加包（league_pyke v0.1.1）
 主包 league 保持纯数据。数据读不到当前生命，主包里派克的 R 由 AI 对「队伍刚打过的敌方英雄」放出，满血的也会被砍 （用户：「大招逻辑也有点问题 总是满血砍人」）；X 里的英雄先吃斩杀线的真实伤害、下一 tick 活下来的回一半，近似「低于斩杀线处决」。 这个附加包用原生代码读生命，做成 League 的样子： - 只砍斩得死的人：AI 钩子 …</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="3" t="inlineStr">
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_pyke.md</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>洛</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Rakan</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>league_rakan</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>掷出羽毛攻击。被动异色羽裳：获得70 + 70% 法强的护盾，破掉12秒后再生；攻击和技能每命中一名敌方英雄，再生快1秒。
 （攻击间隔 1.42 秒 · 攻击距离 40000）</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>微光飞翎：掷出羽毛，第一个敌人受到100 + 80% 法强的魔法伤害。命中英雄后，3秒后或碰到友方英雄时，为自己和身边的友方英雄回复70 + 50% 法强生命值。
 （冷却 5.5 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>盛大登场·轻舞成双：盛大登场：冲向一名敌方英雄，旋上空中，击飞周围敌人0.8秒并造成100 + 70% 法强的魔法伤害；随后轻舞成双：飞到最近的友方英雄身边，给他90 + 70% 法强的护盾（3秒）。霞在附近时飞得更远。
 （冷却 7.5 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>惊鸿过隙：4秒内疾速穿梭于敌人之间：碰到的每个敌人受到140 + 70% 法强的魔法伤害并被魅惑1.25秒（每个敌人一次）；碰到第一个英雄后更快。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="3" t="inlineStr">
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_rakan.md</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>芮尔</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Rell</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>league_rell</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>骑枪突刺，附带6+最大生命1%魔法伤害。溃敌沉力：普攻和技能命中英雄，5秒内削减其3%护甲和魔抗，自己获得3点护甲和魔抗（可叠加）。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>裂阵：前冲一刺，对直线上的敌人造成80 + 60% 法强魔法伤害并晕眩0.65秒。全速冲锋：与身边一名队友加速15%→30%，下次普攻或裂阵爆炸，额外造成英雄最大生命5%真实伤害。
 （冷却 10 秒 · 施放距离 38000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>驭铁术：轰落：跃向敌方英雄砸下，造成80 + 60% 法强魔法伤害并击飞0.83秒，获得90 + 40% 法强护盾，下马作战15秒（双抗、攻速提升）。驾临：上马冲锋，晕眩0.6秒并掀飞目标。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>极涌：把附近敌人猛地拉到身边，2秒内持续拖拽并共造成280 + 112% 法强魔法伤害。等到身边有2个敌方英雄或有被控住的敌人时才放。
 （冷却 60 秒 · 施放距离 64000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>芮尔附加包（league_rell v0.1.2）
 下马作战：整个身体换成披甲步行的她：站着、走着、挨打、普攻、放裂阵、阵亡都是步行的样子（游戏 0.6.4），上马换回骑马
@@ -10691,64 +10756,64 @@
 全速冲锋：一直 15%，她或那名队友朝最近的敌方英雄、或朝对方跑时再加 15%（英雄联盟：朝敌人或彼此时翻倍）</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="3" t="inlineStr">
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_rell.md</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>烈娜塔</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Renata</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>league_renata</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>手枪普攻。物尽其用：命中英雄时额外造成最大生命2%真实伤害并标记；队友在旁攻击时引爆，造成30 + 20% 法强魔法伤害。及时救难：队友被控或团战时自动施放，攻速+40%、移速+20%，5秒内不会阵亡，结束时回复200 + 60% 法强生命。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>忠诚激励：发射一对飞弹，命中敌人或飞到尽头时爆炸，造成85 + 60% 法强魔法伤害并减速30%；途经的友方英雄获得90 + 50% 法强护盾，持续3秒。
 （冷却 10 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>铁腕竞合：射出机械手，抓住第一个敌人，造成95 + 85% 法强魔法伤害并禁锢0.83秒，随后把它甩向身后；落点周围的敌人受到75 + 50% 法强魔法伤害，甩出的是英雄时还会被眩晕0.5秒。
 （冷却 15 秒 · 施放距离 85000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>恶意收购：附近有2个以上敌方英雄，或敌方英雄被控制时，放出化学波：命中的敌方英雄狂暴1.75秒，不能攻击我方、不能施法，每0.5秒攻击身边的队友，造成70 + 40% 法强魔法伤害。
 （冷却 80 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>烈娜塔附加包（league_renata v0.1.2）
 物尽其用：队友真的打中它才引爆（普攻或技能）：魔法伤害 + 最大生命 3% 的真实伤害
@@ -10756,185 +10821,185 @@
 恶意收购的狂暴：真的转身打自己人：走向最近的队友（英雄优先），按他自己的攻击间隔、用他自己的攻击力打；打死队友的击杀和助攻算烈娜塔的（和英雄联盟一样）</t>
         </is>
       </c>
-      <c r="J162" s="2" t="inlineStr">
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="3" t="inlineStr">
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_renata.md</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>赛娜</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Senna</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>league_senna</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>赦除：技能和普攻标记敌方英雄，下次普攻吸走：额外3%最大生命伤害+1层黑雾；每6秒一次普攻和击杀英雄也+1层。每层攻击+1、射程略增，每2层暴击+1%（死亡清空）。黑雾咒附（自动）：英雄贴近时，她和身边队友隐身4秒、移速+20%。
 （攻击间隔 1.6 秒 · 攻击距离 62000）</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>黑暗洞灭：遗物炮射出穿透目标的暗影光束：直线上的敌人受到60 + 50% 攻击力物理伤害并减速20%1.25秒，队友英雄回复70 + 35% 攻击力生命。
 （冷却 9 秒 · 施放距离 62000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>无尽厮守：射出黑雾，附着在首个命中的敌人身上并造成70 + 60% 攻击力物理伤害；1秒后黑雾扩散，禁锢它和周围的敌人1.5秒。
 （冷却 11 秒 · 施放距离 90000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>暗影燎原：蓄力后朝远方交战中的英雄射出横贯战场的光束：中心对敌方英雄造成150 + 75% 攻击力物理伤害，两侧宽阔的光芒给她和沿途队友英雄120 + 40% 攻击力护盾3秒。
 （冷却 50 秒 · 施放距离 250000 · 施放：方向 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>赛娜黑雾常驻附加包（league_senna_mist v0.1.0）
 这个附加包把主包的赛娜换成 override/ 里的副本（make_override.py 用 tools/kit/build_senna.py 的 --native 生成：技能 一字不改，只加被动 league_senna_mist:keep，普攻说明里的「（死亡清空）」换成「（扩展包保留）」），被动每 tick 看一次： - 活着时把身上每一层 lea…</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="3" t="inlineStr">
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_senna.md</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>萨勒芬妮</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Seraphine</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>league_seraphine</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>被动星光漫射：每第3个技能回音再放一次。放技能时得到一个音符，身边每个友方英雄再给一个（最多4个），下次普攻每个音符额外造成8 + 8% 法强魔法伤害，有音符时射程更远。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>清籁穿云：在目标处落下高音，对范围内敌人造成55 + 40% 法强魔法伤害；被控制的敌方英雄多受50%。
 （冷却 9 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>增幅节拍：声波对直线上的敌人造成45 + 35% 法强魔法伤害并减速30%；回音的声波定身被减速的英雄、晕眩被控制的英雄。接着聚和心声：身边友方英雄获得50 + 25% 法强护盾和移速+20%，2.5秒后按身边友方英雄数各回复8 + 6% 法强生命。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>炫音返场：放出一道音波，碰到友方英雄后传得更远，对敌方英雄造成120 + 50% 法强魔法伤害并魅惑1.5秒。附近有两名敌方英雄时施放。
 （冷却 55 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="3" t="inlineStr">
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_seraphine.md</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>娑娜</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Sona</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>league_sona</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>弹出音符攻击。被动能量和弦：每放3次技能，下次普攻额外造成50 + 50% 法强的魔法伤害，并按最后一首歌：断奏 伤害翻倍；渐弱 目标伤害降低25%（3秒）；节奏 减速40%（2秒）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>英勇赞美诗：对附近两个敌人（英雄优先）各造成95 + 60% 法强的魔法伤害。旋律：3秒内来到她身边的友方英雄3秒内获得15% 攻击力和15% 法强。
 （冷却 7 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>坚毅咏叹调：为自己和一名附近的友方英雄回复100 + 40% 法强生命值。旋律：身边的友方英雄获得70 + 40% 法强的护盾1.5秒。每14秒同时弹迅捷奏鸣曲：身边友方英雄移速+20%（自己+30%）3秒。
 （冷却 8 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>狂舞终乐章：朝敌方英雄弹出一道音波，途经的敌方英雄受到150 + 60% 法强的魔法伤害并被晕眩1.5秒。被动：每条命放出大招后，技能冷却缩短20%。
 （冷却 50 秒 · 施放距离 75000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 娑娜 W 回血（60000 内）：损失生命最多的队友
@@ -10942,122 +11007,122 @@
 娑娜 W：她或 60000 内的队友生命不到 70%，射程内有敌方英雄</t>
         </is>
       </c>
-      <c r="J165" s="2" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K165" s="2" t="inlineStr"/>
-      <c r="L165" s="3" t="inlineStr">
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_sona.md</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>索拉卡</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Soraka</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>league_soraka</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>普攻用法杖射出星光弹，造成100% 攻击力的物理伤害。
 （攻击间隔 1.5 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>流星坠落：造成70+50%法术强度的魔法伤害并减速30%，命中敌方英雄时获得活力焕发：2.5秒内回复75+30%法术强度的生命值并加速20%。每16秒一次附带星体结界：沉默圈内敌人，1.5秒后仍在圈内的禁锢1秒并受到40+30%法术强度的魔法伤害。
 （冷却 8 秒 · 施放距离 70000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>星之灌注：消耗自身6%最大生命值（不会致死），为一名其他友方英雄回复200+50%法术强度的生命值。带活力焕发时不消耗生命值，目标也获得活力焕发。被动拯救：施放后2秒内移动速度提高30%。
 （冷却 4 秒 · 施放距离 90000 · 施放：指定目标 · 友方（不含自己））</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>祈愿：为全图所有友方英雄（包括自己）回复220 + 60% 法术强度的生命值。
 （冷却 50 秒 · 施放距离 960000 · 施放：指定目标 · 友方英雄）</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="3" t="inlineStr">
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_soraka.md</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>塔姆</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Tahm Kench</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>league_tahmkench</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>培养品味：普攻额外造成30 + 2%最大生命魔法伤害，普攻、Q、W命中英雄叠一层，最多3层。厚实表皮：受到伤害降低15%，被两名敌方英雄围住时获得160 + 80% 法强护盾。
 （攻击间隔 1.33 秒 · 攻击距离 28000）</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>巨舌鞭笞：舌头鞭打第一个单位，造成170 + 60% 法强 + 2%最大生命魔法伤害，减速40%1.5秒；命中英雄回复40 + 30% 法强生命并叠一层，3层时眩晕1.25秒。
 （冷却 6 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>深渊潜航：潜入地下1秒（不可选中），在目标处冒出，造成160 + 70% 法强 + 2%最大生命魔法伤害并击飞1秒。
 （冷却 1 秒 · 施放距离 70000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>大快朵颐：吞下被控制、身陷敌群的队友2.5秒，吐出时给予150 + 100% 法强护盾；或吞下3层的敌方英雄2.5秒，造成220 + 50% 法强 + 3%最大生命魔法伤害和其最大生命6%真实伤害。
 （冷却 60 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>塔姆附加包（league_tahmkench v0.1.2）
 培养品味的层数：每个敌方英雄各自记层（最多 3 层，5 秒），鱼标记按那个人自己的层数画
@@ -11068,122 +11133,122 @@
 深渊潜航：同样的条件，再加上落点附近的敌方英雄不多于身边队友加一、他自己生命不低于 30%；不放时改成普攻或回到队友身边</t>
         </is>
       </c>
-      <c r="J167" s="2" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="3" t="inlineStr">
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_tahmkench.md</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>塔里克</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Taric</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>league_taric</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 正气凌人：施放技能后4秒内的下2次普攻攻速+100%，额外造成30 + 20% 法强 + 3% 最大生命值的魔法伤害，缩短基础技能冷却，并为星光之触充能1层。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>炫光：朝敌人投射一道星光，0.75秒后沿直线爆裂，造成95 + 60% 法强 + 2% 最大生命值的魔法伤害并晕眩1.25秒。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>星光之触：消耗全部层数（最多3层），每层为自己和附近友方英雄回复40 + 12% 法强的生命值。坚毅壁垒（12秒）：给身边队友80 + 40% 法强的护盾和15护甲并相连，技能也会在他身边施放。
 （冷却 6 秒 · 施放距离 30000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>宇宙之辉：团战开始时召唤星光，2.5秒后自己和附近的友方英雄（相连的队友身边也算）免疫伤害2.5秒。
 （冷却 60 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="3" t="inlineStr">
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_taric.md</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>锤石</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Thresh</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>league_thresh</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>普攻甩出锁链，造成100% 攻击力的物理伤害。被动 厄运钟摆：超过2秒没有普攻时，下一次普攻额外造成40 + 50% 法术强度的魔法伤害。地狱诅咒：收割的灵魂化为每级成长的护甲与法术强度。
 （攻击间隔 1.5 秒 · 攻击距离 48000）</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>死亡判决：掷出镰刀，钩住直线上第一个敌方英雄（穿过小兵），造成80 + 60% 法术强度的魔法伤害，眩晕1秒并把它拉到身前。魂引之灯：每14秒同时掷出灯笼，为自己和身边一名友方英雄提供60 + 40% 法术强度的护盾，持续2.5秒。
 （冷却 8 秒 · 施放距离 65000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>厄运钟摆：挥动锁链横扫身边，对敌人造成60 + 40% 法术强度的魔法伤害并减速40%，持续1秒。刚钩中英雄或没有敌方英雄贴身时，把敌人拉向并越过锤石；有敌方英雄贴身时把敌人推开。
 （冷却 6 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>幽冥监牢：在脚下立起幽冥监牢，持续5秒。第一个碰到监牢的敌方英雄受到150 + 80% 法术强度的魔法伤害并被减速99%，持续2秒；之后碰到的敌方英雄不受伤害，减速时间减半。
 （冷却 60 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>锤石灯笼附加包（league_thresh_lantern v0.1.0）
 灯笼给谁：50000 内有危险的友方英雄（生命不高于 45%，或身边 25000 内有 2 个以上敌方英雄），几个时挑生命比例最低的；都没危险就给最近的
@@ -11191,64 +11256,64 @@
 拉回来：有危险的队友离锤石超过 15000、没被硬控时，拉到锤石身边（每 tick 3000）</t>
         </is>
       </c>
-      <c r="J169" s="2" t="inlineStr">
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="3" t="inlineStr">
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_thresh.md</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>悠米</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Yuumi</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>league_yuumi</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>射出书页光弹。猫的博爱：每6秒普攻命中英雄时多造成50 + 25% 法强魔法伤害，回复自己60 + 20% 法强生命，下次附身时队友也回复同样多。
 （攻击间隔 1.5 秒 · 攻击距离 50000）</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>摸鱼飞弹：发射飞弹，打中第一个敌人造成110 + 50% 法强魔法伤害并减速20%；飞了0.33秒以上改为170 + 70% 法强，减速50%。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>悠米出动！：附身在交战中的队友身上4秒（不可选取、跟着他走，照样能放摸鱼飞弹和魔典终章），他每秒回复45 + 15% 法强生命。旺盛精力：给他130 + 60% 法强护盾，攻速+20%、移速+10%。
 （冷却 6 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>魔典终章：翻开魔典连发5道波纹，每道造成110 + 35% 法强魔法伤害并减速，沿途友军回复60 + 10% 法强生命；第3道定身1.25秒。
 （冷却 45 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>悠米附加包（league_yuumi v0.1.1）
 附身多久：不限时，队友死了才跳下来
@@ -11258,64 +11323,64 @@
 猫的博爱：普攻或摸鱼飞弹命中英雄（附身时她不普攻）</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="3" t="inlineStr">
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_yuumi.md</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>基兰</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Zilean</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>league_zilean</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>发射时光法球。被动瓶中时光：每90秒攒满一瓶，下次时光发条加速友方英雄时送给他：他和基兰各获得10攻击力、10法强和80生命值，直到阵亡。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>定时炸弹：向目标脚下扔出炸弹（出手时锁定落点，可躲开），粘在附近第一个敌人身上（英雄优先），3秒后爆炸，造成80 + 70% 法强的魔法伤害。穿梭未来（每12秒）：炸弹粘上英雄时倒转时间再扔一颗，两颗立即爆炸并晕眩1.25秒，技能冷却缩短。
 （冷却 7 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>时光发条：使一名敌方英雄减速35%，同时让身边一名友方英雄（没有则自己）移速+35%，持续2.5秒。
 （冷却 10 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>时光倒流：附近的友方英雄被控制、或基兰被两名以上敌方英雄贴身时，为其挂上时光符文：5秒内不会阵亡，结束时时光回溯，回复400 + 150% 法强生命值。
 （冷却 60 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>基兰复活附加包（league_zilean_rewind v0.2.0）
 主包 league 保持纯数据。主包里基兰的 R 由 AI 在敌方英雄 60000 内时放出、待命 900 tick（没用上就退还冷却）； 待命期间他每次出手查一次：附近有被控制的友方英雄、或自己被两名以上敌方英雄贴身，才给那个人挂 5 秒的时光符文 （league_zilean_r_rune，带「不死」，生命最低停在 1），到第 299 tick 不管有…
@@ -11323,78 +11388,78 @@
 奥莉安娜 E、基兰 E：在打架：她 / 他或射程内的队友 40000 内有敌方英雄（基兰也追射程内生命不到 40% 的）</t>
         </is>
       </c>
-      <c r="J171" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="3" t="inlineStr">
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zilean.md</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="3" t="inlineStr">
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L172"/>
+  <autoFilter ref="A1:L173"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -11567,6 +11632,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L172"/>
+  <dimension ref="A1:L173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.8）
+          <t>俄洛伊附加包（league_illaoi v0.2.10）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -6643,238 +6643,306 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>洛克</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Locke</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>league_locke</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>中单</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>圣银穿心：攻击附带15 + 15% 法强魔法伤害。灵焰仪式：灰猎无影落到敌方英雄身边时点燃（每16秒一次）：4秒内攻速+35%、移速+40%（递减），每秒受到最大生命2%真实伤害，结束时回复20 + 10% 法强生命。
+（攻击间隔 0.92 秒 · 攻击距离 23000）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>伏魔三钉：接连掷出三枚咒钉，每枚造成35 + 20% 法强魔法伤害并减速15%1.5秒（可叠加）。钉中英雄后4秒内，他的攻击引爆钉子：每枚25 + 12% 法强魔法伤害，两枚+25%，三枚+50%。
+（冷却 1 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>灰猎无影：瞬移到敌方英雄身边，对周围敌人造成50 + 25% 法强魔法伤害；3秒内下一次攻击冲穿目标，造成55 + 30% 法强魔法伤害。被他打过的英雄3秒内阵亡时冷却刷新。
+（冷却 1 秒 · 施放距离 45000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>万魔狱：法器箱砸向敌方英雄：周围敌人受到200 + 80% 法强魔法伤害并减速50%（递减）；英雄被标记4秒，生命低于100 + 40% 法强即被处决。标记期间参与击杀得一层封印（最多3层，阵亡清空）：处决线+40，大招冷却最多剩50%。
+（冷却 60 秒 · 施放距离 50000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>洛克附加包（league_locke v0.1.0）
+圣银穿心（被动）：再加目标已损失生命 p_miss% 的魔法伤害
+灵焰仪式（W，并入被动）：每秒烧当前生命 w_cost%（不会把自己烧死），结束时补回烧掉的 w_back%
+万魔狱（R）的处决：被标记的英雄当前生命低于最大生命 r_exec%（每层封印 +r_exec_step%）就处决
+封印和法器：处决的地方掉下法器（r_drop 拍），洛克走到 pick_r 以内捡起来：封印 +1（最多 3 层，整局都在），大招剩下的冷却少 r_cap%
+参与击杀刷新 E：被他打过（p_win 拍内）的敌方英雄倒下，谁打死的都算，E 立刻好
+W 的样子：灵焰仪式期间整身换成 W 的配色（第 0 步 B：深蓝 / 靛紫皮肤、白西装、发白光的眼镜、蓝水晶法器箱；用户：「洛克会变成蓝色吧？」）</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_locke.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
           <t>拉克丝</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Lux</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>league_lux</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>普攻从法杖射出光弹，造成100% 攻击力的物理伤害。被动 光芒四射：技能命中敌人后5秒内，下一次普攻引爆光芒，额外造成50 + 35% 法术强度的魔法伤害。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>光之束缚：向前方射出一颗光球，对路径上的每个敌人造成80 + 75% 法术强度的魔法伤害并禁锢1.5秒。同时施放 曲光屏障：拉克丝和身边的友方英雄获得55 + 40% 法术强度的护盾，持续2.5秒。
 （冷却 6 秒 · 施放距离 130000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>透光奇点：向目标位置抛出光球，落地后形成光圈，使圈内敌人减速20%。1秒后光圈引爆，对圈内敌人造成70 + 80% 法术强度的魔法伤害。
 （冷却 8 秒 · 施放距离 110000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>终极闪光：拉克丝跃起蓄力，0.5秒后向目标方向发射一道极长的激光，对直线上所有敌人造成250 + 115% 法术强度的魔法伤害。
 （冷却 60 秒 · 施放距离 120000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>目标标记附加包（league_marks v0.1.0）
 拉克丝 光芒四射：光芒留在被技能打中的敌人身上（5 秒），普攻打中带光芒的人才引爆 50 + 35% 法强的魔法伤害</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="3" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_lux.md</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>玛尔扎哈</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Malzahar</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>league_malzahar</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>射出虚空弹。被动虚空穿越：获得90 + 40% 法强护盾，护盾存在时免疫控制；护盾被打破后12秒重新获得。
 （攻击间隔 1.5 秒 · 攻击距离 52000）</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>煞星幻象 / 虚空虫群：煞星幻象：4秒内造成170 + 80% 法强魔法伤害，目标死亡时跳到附近的敌人身上。虚空虫群随之撕咬目标，每0.5秒造成14 + 8% 法强魔法伤害。
 （冷却 9 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>虚空召唤：在目标两侧打开虚空裂隙，裂隙合拢时对范围内的敌人造成70 + 45% 法强魔法伤害并沉默1.5秒。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>冥府之握：压制一名敌方英雄（优先煞星幻象的目标）：引导期间使其眩晕，2.5秒内造成220 + 80% 法强魔法伤害，脚下留下持续伤害的虚空区域。玛尔扎哈被控制时引导中断。
 （冷却 70 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>玛尔扎哈附加包（league_malzahar v0.1.0）
 主包 league 保持纯数据。用户选了「做：E 跳转 + 被动精确」。这个附加包用原生代码做主包数据做不准的两件事： - 虚空穿越（被动）：英雄联盟里玛尔扎哈身上有一层法术护盾：受到的伤害大幅减少、免疫控制；被非小兵的伤害打中后很快消失， 一段时间没受到英雄伤害才回来。主包数据读不到「被谁打了」「多久没挨打」，只能做成墨菲特那样的护盾（打破后过一会儿回来…</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="3" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_malzahar.md</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>妮蔻</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Neeko</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>league_neeko</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>发射一颗魔法弹。两生花影：每第三次攻击额外造成45 + 50% 法强魔法伤害，并提高30%移动速度1秒。
 （攻击间隔 1.53 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>盛开花种：扔出一颗种子，落地炸开造成95 + 65% 法强魔法伤害。炸到英雄时会再次盛开，最多两次，每次40 + 25% 法强魔法伤害。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>缠结倒刺：投出一团贯穿的倒刺，路径上的敌人受到90 + 60% 法强魔法伤害并被禁锢1秒。穿过英雄后，后面的英雄多被禁锢0.75秒。
 （冷却 11 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>怒放：蓄力0.75秒，获得护盾（附近每个敌方英雄额外40），然后跃起击飞周围敌人，落地造成260 + 115% 法强魔法伤害并晕眩0.83秒。
 （冷却 35 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>妮蔻附加包（league_neeko v0.1.0）
 天生幻魅：脱战 2 秒后整个身体画成最近的友方英雄（站、跑、出招、挨打都用他的图）；放技能、被控（击飞、晕眩、禁锢、嘲讽、恐惧、魅惑、强制位移）、假扮以来挨了她 35% 最大生命的伤害、或…</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="3" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_neeko.md</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>奥莉安娜</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Orianna</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>league_orianna</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>发射发条弹。发条协奏：普攻附带18 + 15% 法强魔法伤害，4秒内连续普攻再叠加，最多2层。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>指令：攻击：把球扔到敌方英雄脚下并停留，造成85 + 65% 法强魔法伤害。指令：杂音：球附近有敌人时自动放电，造成85 + 85% 法强魔法伤害，减速30%，队友加速30%。
 （冷却 5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>指令：防卫：把球送给离敌人最近的队友（被贴身时给自己），提供60 + 45% 法强护盾，路过的敌人受到60 + 30% 法强魔法伤害。带球者+12护甲和魔抗。
 （冷却 9 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>指令：冲击波：待命6秒，球附近有敌方英雄时放出冲击波：造成250 + 100% 法强魔法伤害并把敌人甩向球。
 （冷却 70 秒 · 施放距离 90000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>奥莉安娜附加包（league_orianna v0.2.0）
 Q / E 的球从哪飞出：从球所在的位置飞出：地上、队友身上、飞回来的半路都行；E 路过的敌人按球到队友这条线算
@@ -6886,127 +6954,127 @@
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_orianna.md</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>瑞兹</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Ryze</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>league_ryze</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>发射符文法球攻击。被动奥术专精：所有技能伤害额外加上2% 最大生命值（本作没有法力值，以生命值代替法力）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>超负荷：向前释放魔爆，对命中的第一个敌人造成55 + 50% 法强的魔法伤害。若有敌人带着涌动，命中时它们全部受到35 + 35% 法强的弹射伤害，涌动随之消耗。
 （冷却 3.5 秒 · 施放距离 80000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>符文禁锢：连招 E→W→Q→E→Q：法术涌动造成45 + 45% 法强伤害，给目标和附近敌人挂上涌动4秒；符文禁锢造成70 + 55% 法强伤害，有涌动时禁锢1.25秒，否则减速；超负荷引爆涌动，再一发法术涌动和超负荷，符文让他移速+30%。
 （冷却 14 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>曲境折跃：被敌方英雄贴身时开门逃到远处安全的队友身边（没有就往反方向逃）；身边没敌人、队友在远处交战时开门追过去。引导1秒后传送，门里的友军一起过去，落地补一发法术涌动。被控会打断。被动：施放后本条命内涌动弹射伤害提高到50 + 55% 法强。
 （冷却 70 秒 · 施放距离 360000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 瑞兹 R（备好式）：逃命：生命不到 35% 而 60000 内有敌方英雄；去打架：照崔斯特的规则（身边没敌人、远处队友在打）。传到哪里由主包判断</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="3" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ryze.md</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>斯维因</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Swain</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>league_swain</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>恶魔手射出乌鸦弹。狂食鸦群：帝国视界、永不复行抓到英雄或他打过的英雄阵亡时得到魂屑，回复80 + 30% 法强生命，最大生命+15（死后清空）。帝国视界：每16秒在远处交战的敌方英雄脚下睁眼，1.5秒后炸开造成90 + 60% 法强魔法伤害并减速。
 （攻击间隔 1.5 秒 · 攻击距离 52000）</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>解脱之触：恶魔手射出五道扇形散开的闪电，造成120 + 80% 法强魔法伤害；近处的敌人被更多闪电打中，另受60 + 45% 法强魔法伤害。
 （冷却 4 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>永不复行：恶魔之手飞出再飞回，回程打中的敌人受到110 + 80% 法强魔法伤害并禁锢1.5秒；被禁锢的英雄随后被拉近，留下一片魂屑。
 （冷却 10 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>恶魔升华：化身恶魔，吸取周围敌人的生命：每0.5秒造成25 + 8% 法强魔法伤害，每名英雄回复40 + 15% 法强；吸到英雄时形态延续。2秒后放出恶魔耀光：170 + 70% 法强魔法伤害并减速。2名敌方英雄在身边，或有敌方英雄且队友在旁时才放。
 （冷却 60 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>斯维因附加包（league_swain v0.1.1）
 魂屑：永久保留：死了、复活后一块不少（英雄联盟的规则）
@@ -7014,127 +7082,127 @@
 开大时机：不变，照主包（用户：「是乌鸦看情况开大吧」），日志里记下每次变身时身边几个敌方英雄</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_swain.md</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>塞拉斯</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Sylas</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>league_sylas</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>甩链。破敌禁法：每放一个技能存一层（最多2层），有层时攻速+40%，下次普攻挥链横扫周围，20 + 35% 法强魔法伤害。弑君突刺：每9秒对英雄的普攻变成突刺，80 + 70% 法强魔法伤害，回复40 + 35% 法强生命。
 （攻击间隔 0.97 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>锁链鞭击：甩出两条锁链交叉于目标处，沿途敌人受到50 + 35% 法强魔法伤害并减速25%；0.6秒后交叉点爆炸，造成90 + 65% 法强魔法伤害。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>潜掠/强掳：朝敌方英雄突进，再甩出锁链：命中的第一个敌方英雄受到80 + 70% 法强魔法伤害、被击飞0.5秒，塞拉斯把自己拉过去。
 （冷却 11 秒 · 施放距离 70000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>其人之道：锁链命中敌方英雄，眩晕0.5秒并夺走大招；10秒内再放，在目标处爆发，200 + 80% 法强魔法伤害并击飞周围敌人。
 （冷却 45 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>塞拉斯附加包（league_sylas v0.2.8）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="3" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_sylas.md</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>辛德拉</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Syndra</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>league_syndra</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>被动卓尔不凡：3级Q对英雄伤害+25%，5级W附带20%真实伤害，7级E范围更大，9级R的法球无视魔抗。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>暗黑法球：召唤暗黑法球，对周围敌人造成62 + 52% 法强魔法伤害。法球留在原地6秒。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>弱者退散：先用驱使念力把法球掷向敌方英雄，造成55 + 55% 法强魔法伤害并减速30%。再锥形击退敌人，造成45 + 45% 法强魔法伤害，被推开的法球使附近敌人晕眩1.25秒。
 （冷却 11 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>能量倾泻：向一名敌方英雄发射3颗+场上法球数（最多7颗），每颗造成52 + 18% 法强魔法伤害。
 （冷却 70 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>辛德拉举小兵附加包（league_syndra v0.1.1）
 这个附加包把主包的辛德拉换成 override/ 里的副本（make_override.py 用 tools/kit/build_syndra.py 的 --native 生成：技能 一样，W 施放时在她身上挂 league_syndra_w_grab、在投掷目标身上挂 league_syndra_w_at；她身上有 league_syndra_w_uni…
@@ -7142,128 +7210,128 @@
 辛德拉 R：75000 内的敌方英雄生命不到 60%、被控住，或射程内有两个以上；主包再按法球数和控制决定立刻放还是待命 8 秒（没用上退还冷却）</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="3" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_syndra.md</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>塔莉垭</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Taliyah</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>league_taliyah</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>甩出一块石子。浮石冲：脱战时移速+10%；放出墙幔后踩石冲浪，移速+40%（5秒）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>石穿：朝目标方向一颗接一颗扔出5颗石头（扔出第一颗后可以移动），第一颗46 + 24% 法强魔法伤害，之后每颗23 + 12% 法强；脚下留下掘石场（8秒），站在上面施放改为一颗大石头：110 + 60% 法强并减速40%。
 （冷却 6 秒 · 施放距离 90000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>岩突：在身前地上撒下石雷（减速20%，4秒），目标脚下裂开后隆起，造成50 + 30% 法强魔法伤害并把敌人掀向自己；飞过石雷时石雷爆炸，造成38 + 24% 法强魔法伤害并眩晕0.4秒。
 （冷却 1 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>墙幔：敌人在附近或已在交战：在目标处竖起长石墙（5秒），墙上的敌人被拖到她这一侧；敌人较远：从脚下拉出一道横墙，踩着石头沿墙冲刺，靠近敌人时跳下。碰到墙的敌人减速42%。
 （冷却 70 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>塔莉垭附加包（league_taliyah v0.1.0）
 竖墙（敌人近、或她已在打架）：同一块地方是真的墙：英雄、小兵、野怪、召唤物（两边都算，她自己也算）都过不去；立起时压在上面的单位推到她那一侧
 横墙（敌人远：骑墙）：每一段都是真的墙；她骑墙时站在墙顶上不受挡，跳下来那一 tick 推到近的一侧</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="3" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_taliyah.md</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>泰隆</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Talon</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>league_talon</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>腕刃攻击。刀锋之末：技能命中英雄叠一层伤口，叠满3层后下次普攻使其流血，2秒内受到40 + 120% 攻击力伤害。刺客之道（自动，10秒）：收刀或Q击杀时身边有2名敌方英雄，就翻身跃开并加速。
 （攻击间隔 0.92 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>斩草除根：扇形掷出飞刀造成30 + 40% 攻击力伤害，随后飞刀收回，造成40 + 70% 攻击力伤害并减速40%。
 （冷却 9 秒 · 施放距离 50000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>诺克萨斯式外交：跃向目标造成48 + 100% 攻击力伤害；目标就在身边时改为原地捅刺，造成150%暴击伤害。击杀目标回复60生命并返还冷却。
 （冷却 5 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>暗影突袭：向四周甩出一圈飞刀造成55 + 75% 攻击力伤害，随后隐身2.5秒、移速+40%；隐身结束或攻击时飞刀收回，再次造成同样伤害。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>泰隆「刺客之道」翻墙附加包（league_talon_vault v0.1.2）
 什么时候翻：照旧，另外：残血（低于 35%）而身边有敌方英雄，或被围（身边敌方英雄 ≥ 2、比身边友方多、生命低于 70%）时；残血敌方英雄（≤ 60%）躲在墙后、他自己生命 ≥ 40% 时
@@ -7271,190 +7339,190 @@
 冷却：同一个冷却（主包的 league_talon_e_cd），两种翻越不会连着出</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="3" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_talon.md</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>崔斯特</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Twisted Fate</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>league_twistedfate</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>扔牌攻击。被动灌铅骰子：普攻或万能牌击杀单位时掷骰子，按点数获得少量法强，死亡清空。卡牌骗术：每第4次攻击额外造成80 + 60% 法强魔法伤害。
 （攻击间隔 1.1 秒 · 攻击距离 57500）</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>万能牌：扔出三张牌，沿途每个敌人受到120 + 100% 法强魔法伤害。出手前方向就已锁定，可以躲开。
 （冷却 4 秒 · 施放距离 95000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>选牌：头顶蓝、红、金牌轮换，转到想要的就锁定，下次普攻扔出（另加100% 攻击力）：蓝牌60 + 100% 法强，技能冷却减半；红牌目标周围50 + 70% 法强并减速；金牌30 + 60% 法强并眩晕1.67秒。
 （冷却 5 秒 · 施放距离 75000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>命运：所有敌方英雄头顶出现标记。传送之门：引导1.5秒（被控打断）后传到远处队友正在打的敌方英雄身边，落地锁定金牌。身边没有敌人时才会用。
 （冷却 90 秒 · 施放距离 960000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 崔斯特 R：只在主包会传送的局面按：他身边 75000 内没有敌方英雄、生命不低于 40%，而且离他 100000–340000 有队友 50000 内贴着敌方英雄（在打架）。之后揭示、引导…</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="3" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_twistedfate.md</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>维迦</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Veigar</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>league_veigar</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>普攻射出暗能量弹，造成100% 攻击力的物理伤害。被动 超凡邪力：技能每命中一名敌方英雄，永久获得1 点法术强度；黑暗祭祀每击杀一个单位 +1，击杀敌方英雄 +5。死亡时清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>黑暗祭祀：射出一束黑暗能量，对最先命中的两个敌人造成70 + 60% 法术强度的魔法伤害。
 （冷却 4 秒 · 施放距离 75000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>扭曲空间：在敌方英雄处扭曲空间，0.4秒后形成持续3秒的牢笼，碰到它的敌人眩晕1秒（每人一次）。随后 黑暗物质 砸向牢笼中心，造成90 + 80% 法术强度的魔法伤害。
 （冷却 13 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>能量爆裂：向敌方英雄发射原始魔法，造成160 + 70% 法术强度的魔法伤害。此前技能每连续命中英雄一次（间隔不超过4秒），伤害提高25%，最多100%。
 （冷却 50 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>维迦法强常驻附加包（league_veigar_power v0.1.0）
 这个附加包把主包的维迦换成 override/ 里的副本（make_override.py 生成：技能一字不改，只加被动 league_veigar_power:keep， 普攻说明里的「死亡时清空」换成「【扩展包】死后保留」），被动每 tick 看一次： - 活着时把身上每一层 league_veigar_p_stack 原样记下来（记在被动里，被动在玩…</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_veigar.md</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>维克兹</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Vel'Koz</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>league_velkoz</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>发射虚空能量。每第3次普攻打开虚空裂隙，造成35 + 20% 法强魔法伤害，随后爆炸再造成55 + 25% 法强。有机体解构：技能命中英雄叠层，3层时造成45 + 45% 法强真实伤害。
 （攻击间隔 1.43 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>等离子裂变：发射一束等离子，造成85 + 65% 法强魔法伤害并减速50%，持续1.25秒。命中后一分为二，对周围敌人造成45 + 35% 法强魔法伤害和减速。
 （冷却 7 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>构造分解：让目标区域爆炸，造成75 + 40% 法强魔法伤害并击飞敌人0.75秒。
 （冷却 11 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>生命形态瓦解射线：引导一束射线2.5秒，共造成320 + 105% 法强魔法伤害。对被有机体解构研究过的英雄改为真实伤害。
 （冷却 35 秒 · 施放距离 95000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>维克兹附加包（league_velkoz v0.1.1）
 有机体解构：层数记在每个敌方英雄身上（每层 7 秒，再中一下全部刷新），第 3 层对那个英雄造成真实伤害；每叠一层都「研究」他 7 秒
@@ -7463,64 +7531,64 @@
 连招：AI 钩子按顺序：E -&gt; Q（AI 要 Q 英雄时先 E）、击飞后马上 Q、窗口里的普攻打英雄（裂隙打在他身上）、两层的英雄在射程里就放 R、R 先射被研究的英雄</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="3" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_velkoz.md</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>薇古丝</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Vex</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>league_vex</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>射出暗影弹。终焉暮气：每15秒下一个技能恐惧命中的敌人0.75秒。生人勿近：敌方英雄靠近时改为获得60 + 60% 法强护盾并震伤周围70 + 40% 法强（每12秒）。
 （攻击间隔 1.43 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>寒心波云：射出一道暗风，穿过路径上的所有敌人，造成105 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>溟濛渐染：影子飞到目标处扩散，造成80 + 60% 法强魔法伤害、减速35%2秒，并施加暮气：她下一次技能打中带暮气的英雄额外造成60 + 30% 法强魔法伤害。
 （冷却 10 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>愁煞：射出飞弹标记一名敌方英雄，造成80 + 20% 法强魔法伤害，随后冲到他身边再造成225 + 70% 法强魔法伤害。
 （冷却 35 秒 · 施放距离 110000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>薇古丝附加包（league_vex v0.1.0）
 暮气：照英雄联盟：暮气挂在每个被 E 打中的敌人身上（小兵、野怪也算），她身边突进的敌方英雄也被挂上；她之后打中带暮气的敌人（普攻也算）就引爆：补暮气伤害，终焉的等待缩短 25%
@@ -7528,248 +7596,248 @@
 愁煞：被愁煞打中的英雄 6 秒内阵亡就刷新愁煞（谁杀的都算）</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="3" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_vex.md</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>维克托</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Viktor</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>league_viktor</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>被动光荣进化：3级E附带余波，5级Q护盾更强并加速30%，7级技能命中减速20%，9级风暴变大、转移后持续更久。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>虹吸能量：能量弹造成60 + 45% 法强魔法伤害，获得40 + 20% 法强护盾；4秒内下次普攻额外造成30 + 45% 法强魔法伤害。
 （冷却 8 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>海克斯射线：先在敌方英雄脚下放重力场：减速35%，1.25秒后场内敌人晕眩1.25秒。再从目标处向后方射出海克斯射线，造成45 + 40% 法强魔法伤害。
 （冷却 10 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>奥术风暴：风暴落在敌方英雄身上，造成80 + 40% 法强魔法伤害，之后6秒每秒对周围敌人造成25 + 15% 法强魔法伤害，目标阵亡就转移到附近英雄。
 （冷却 70 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="3" t="inlineStr">
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_viktor.md</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>泽拉斯</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Xerath</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>league_xerath</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>发射奥术法球攻击。被动法力澎湃：每14秒下一次攻击额外造成40 + 40% 法强魔法伤害，并使小技能冷却缩短23%；他每击杀一个单位，等待缩短3.5秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>奥能脉冲：蓄力后射出贯穿光束，对直线上的敌人造成110 + 85% 法强魔法伤害。附近有敌方英雄时蓄满，射得更远；只打小兵时快速蓄力，伤害65%。
 （冷却 5 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>冲击法球：命中第一个敌人造成60 + 45% 法强并晕眩0.75~2秒（飞得越远越久）。随后毁灭之眼落在敌方英雄头上，造成60 + 50% 法强并减速，中心伤害+67%。
 （冷却 10 秒 · 施放距离 95000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>奥术仪式：飞升并原地引导，向远处的敌方英雄连发4次魔法炮击，落点预警后爆炸，每发造成120 + 45% 法强魔法伤害；每次命中英雄，之后的炮击伤害+20%。被控制会打断。
 （冷却 50 秒 · 施放距离 220000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J114" s="2" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="3" t="inlineStr">
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_xerath.md</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>亚索</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Yasuo</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>league_yasuo</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 浪客之道：20%暴击几率，暴击造成双倍伤害。剑意每15秒充满一次，充满后下一次出手获得40 + 40% 攻击力的护盾，持续2秒。
 （攻击间隔 0.92 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>斩钢闪：向前突刺，对直线上的敌人造成30 + 100% 攻击力的物理伤害，视为普攻，可以暴击。命中后获得一层旋风烈斩，满2层时下一次改为放出旋风，击飞直线上的敌人1秒。在踏前斩突进中施放时改为环状出剑。
 （冷却 4 秒 · 施放距离 45000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>踏前斩：冲刺穿过一名敌人，造成40 + 60% 攻击力的物理伤害。6秒内再次施放，伤害提高25%，最多提高50%。连招 Q3 E Q：旋风击飞英雄后2.5秒内施放，冲刺途中自动环状出剑。
 （冷却 5 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>狂风绝息斩：闪到一名被控制（击飞、眩晕、禁锢等）的敌方英雄身边，对附近所有被控制的敌方英雄造成150 + 150% 攻击力的物理伤害并再击飞1秒。之后10秒内无视目标30%护甲，剑意立即充满。连招 R Q：斩击后接一记较轻的环状出剑（15 + 50% 攻击力）。
 （冷却 40 秒 · 施放距离 100000 · 施放：指定目标 · 被控制的敌方英雄）</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>亚索风之障壁附加包（league_yasuo_wall v0.1.0）
 主包没有 W：游戏里没有能挡掉飞行物的效果，只画一面墙显得奇怪，当时用户决定删掉。亚索也没有空的技能格，所以风墙全由原生代码做（被动 league_yasuo_wall:wall，不占技能格、没有施法动作）。</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="3" t="inlineStr">
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_yasuo.md</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>永恩</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Yone</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>league_yone</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 狩人之道：20%暴击几率，暴击造成双倍伤害；每第二次普攻换用恶魔刀，造成50% 攻击力的物理伤害和40% 攻击力的真实伤害。
 （攻击间隔 0.92 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>错玉切：向前出剑，对直线上的敌人造成25 + 100% 攻击力的物理伤害，视为普攻，可以暴击。命中后获得一层风暴聚集，满2层时下一次改为向前冲刺，带着旋风击飞路径上的敌人1秒。
 （冷却 4 秒 · 施放距离 45000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>凛神斩：向前顺劈，造成15 + 25% 攻击力的物理伤害和10 + 15% 攻击力的真实伤害（英雄另受5% 最大生命值），每命中一名英雄得35 + 35% 攻击力护盾。每15秒先施放破障之锋：灵体冲向英雄，4秒后归位，以真实伤害重现期间对英雄伤害的25%。
 （冷却 7 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>封尘绝念斩：对一条直线上的所有敌人造成70 + 50% 攻击力的物理伤害和50 + 35% 攻击力的真实伤害并击飞0.75秒，永恩冲到目标身后。连招 Q3 R：Q3 击飞英雄后1.5秒内施放，不蓄力直接斩出；斩中英雄叠一层错玉切（R Q3）。
 （冷却 50 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>永恩 R 附加包（league_yone_r v0.1.0）
 落在哪里：直线上离他最远的那个被斩中的英雄身后 6000（一个都没斩中就照主包，落在 90000 内最近的敌方英雄身后）
@@ -7777,64 +7845,64 @@
 伤害、击飞、画面、Q3 连 R：一样</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J116" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="3" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_yone.md</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>劫</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Zed</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>league_zed</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>影忍法！灭魂劫：技能命中英雄后，下次攻击英雄附加其6%最大生命真实伤害（10秒）。影奥义！鬼斩（自动，4秒）：旋斩周围，造成65 + 75% 攻击力伤害，减速25%。
 （攻击间隔 0.92 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>影奥义！分身：影子落到敌方英雄脚下（5秒），接着鬼斩和诸刃；影子在时模仿他的每次诸刃和鬼斩。影子旁只有一名敌人时，和影子互换位置追击。
 （冷却 12 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>影奥义！诸刃：掷出手里剑，贯穿一条直线：首个敌人受到75 + 100% 攻击力伤害，之后的受到60%。
 （冷却 4 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>禁奥义！瞬狱影杀阵：对交战中的英雄发动：无法选中，突进穿过并留下影子（模仿诸刃和鬼斩）与印记，3秒后爆发110 + 100% 攻击力，期间每次命中+35（最多3次）。击杀、被包围或被控时，和影子互换位置。
 （冷却 50 秒 · 施放距离 60000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>劫读血附加包（league_zed_mark v0.1.3）
 主包 league 保持纯数据。数据读不到生命也读不到伤害，所以主包里劫的两处是替代做法： - 被动「影忍法！灭魂劫」：英雄联盟里是攻击生命低于 50% 的英雄时附加其最大生命的伤害；主包改成「技能刚打中过英雄」后的下一次普攻（league_zed_cw_ready），附加 6% 最大生命真实伤害，10 秒一次。 - 大招「禁奥义！瞬狱影杀阵」：英雄联盟里…
@@ -7842,128 +7910,128 @@
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="3" t="inlineStr">
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zed.md</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>吉格斯</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Ziggs</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>league_ziggs</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>扔小炸弹。一触即发：每12秒下次普攻多造成40 + 60% 法强魔法伤害，每放一个技能冷却-4秒。定点爆破：3级起，敌方英雄贴身时在脚下引爆，造成80 + 50% 法强魔法伤害并击退，自己也被炸开。
 （攻击间隔 1.47 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>弹跳炸弹：扔出炸弹沿直线弹跳，最多落地3次，落地时附近有敌人就爆炸：周围敌人受到105 + 85% 法强魔法伤害。
 （冷却 4.5 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>海克斯爆破雷区：撒下雷区5秒：敌人第一次踩雷受到65 + 45% 法强魔法伤害，之后每0.5秒受到其40%；每次踩雷减速30%。
 （冷却 12 秒 · 施放距离 75000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>科学的地狱火炮：把超大炸弹扔向远处的敌方英雄，落点先出现预警：范围内敌人受到250 + 85% 法强魔法伤害，中心共受到385 + 130% 法强。优先扔向被控制的敌方英雄。
 （冷却 60 秒 · 施放距离 220000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>吉格斯附加包（league_ziggs v0.1.1）
 定点爆破（W）：同上；另外 W 不在冷却时，身边 w_hex_r 以内有血量低于 w_ex% 的敌方防御塔，就在塔上炸开、直接把塔炸掉（算他的击杀），W 进入冷却（英雄联盟：W 能炸掉 25–3…
 一触即发（被动）：强化弹打中防御塔的那一下 ×p_tower%（1.75 倍，英雄联盟对建筑的加成）</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J118" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="3" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ziggs.md</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>佐伊</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Zoe</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>league_zoe</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>射出一颗小星星。烟火四射！：每放一个技能，下一次普攻多造成40 + 50% 法强魔法伤害。
 （攻击间隔 1.47 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>飞星乱入！：掷出一颗飞星，打中第一个敌人造成105 + 60% 法强魔法伤害；飞得越远伤害越高，最远250%。
 （冷却 6 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>催眠气泡：踢出气泡，打中敌方英雄造成60 + 40% 法强魔法伤害，困倦（减速30%）1.4秒后昏睡2秒；没打中就留在原地。昏睡中第一次被飞星打中伤害翻倍。
 （冷却 15 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>折返跃迁：跳进传送门闪向敌方英雄，掷出飞星造成200 + 90% 法强魔法伤害；窃法巧手：再射3颗飞弹，每颗45 + 15% 法强，加速40%。1.2秒后跳回原地。
 （冷却 30 秒 · 施放距离 110000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>佐伊附加包（league_zoe v0.3.0）
 催眠气泡的昏睡：照英雄联盟：困倦后昏睡 2.25 秒，受到任何伤害就醒（谁打的都算），那一下再来一遍真实伤害，最多 100 + 60% 法强
@@ -7972,64 +8040,64 @@
 召唤师技能（0.2.0）：用户：「可以改成召唤师技能那种效果吗 随机的」「能做成智能释放吗」：窃法巧手每次发动（大招射飞弹的那一刻、捡起碎片时）先放一个召唤师技能，按局面挑：被控 → 净化；残血、敌方英雄…</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="3" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zoe.md</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>婕拉</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Zyra</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>league_zyra</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>甩出一颗荆棘种子。荆棘花园：她每次放Q、E都先种下一颗种子，长成植物作战5秒，每1秒攻击一个敌人，造成20 + 12% 法强魔法伤害。
 （攻击间隔 1.43 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>致命棘刺：地面炸出棘刺，范围内的敌人受到80 + 55% 法强魔法伤害。种子长成荆棘喷射者，远距离攻击。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>缠绕之根：放出贯穿地面的藤蔓，路径上的敌人受到70 + 45% 法强魔法伤害并被禁锢1.25秒。种子长成藤蔓鞭击者，近距离攻击并减速30%。
 （冷却 11 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>绞杀之藤：召唤扭曲的密林，造成180 + 70% 法强魔法伤害，2秒后击飞仍在其中的敌人1秒。植物被激怒5秒，伤害提高50%。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t>婕拉附加包（league_zyra v0.1.1）
 荆棘花园 / 狂野生长：主包的照旧；另外种子掉在她身边的地上：每 10 秒一颗（有敌方英雄在附近就掉在朝他的方向），在地上留 30 秒、最多 4 颗；她参与击杀敌方英雄时马上掉一颗（英雄联盟：击杀缩短狂…
@@ -8039,64 +8107,64 @@
 R 绞杀之藤：主包的照旧；密林范围里种子长的植物 5 秒内出手间隔减半（英雄联盟：密林里的植物攻速提高）</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zyra.md</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>阿克尚</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Akshan</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>league_akshan</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>每次普攻开两枪，第二枪对英雄只有50%伤害。无所不用：普攻和技能每打中3下，多造成20 + 30% 攻击力物理伤害，打中英雄还获得40 + 35% 攻击力护盾2秒。赴险夺人：被2个以上敌方英雄围住时伪装2秒并加速40%。
 （攻击间隔 1.07 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>去而复还：朝敌人扔出回旋镖（先瞄准再出手，能躲开），去程和回程各造成45 + 90% 攻击力物理伤害；打中英雄加速20%，持续1秒。
 （冷却 7 秒 · 施放距离 95000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>骄行荡寇：甩出钩索朝敌方英雄荡过去，1.4秒内每0.23秒朝最近的敌人开一枪，造成25 + 60% 攻击力物理伤害，最后翻滚离开再开一枪。
 （冷却 15 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>恩怨相抵：锁定受伤的敌方英雄蓄力0.5秒，最多存5发子弹，被控制会中断；然后连射，每发打中路上第一个敌人，造成35 + 25% 攻击力物理伤害，前面每打中一发，后面的子弹多30%。
 （冷却 50 秒 · 施放距离 160000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>阿克尚扩展包（league_akshan v0.2.2）
 无所不用（第 3 下）：每个目标分别数 3 下（英雄联盟）
@@ -8108,64 +8176,64 @@
 赴险夺人：另外：杀了队友的敌方英雄成为恶徒 60 秒（头上有标记）；阿克尚在恶徒附近加速；阿克尚参与击杀恶徒时，被这个恶徒杀死、还在等复活的队友 1 秒后在泉水复活，阿克尚得 100 金</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="3" t="inlineStr">
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_akshan.md</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>厄斐琉斯</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Aphelios</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>league_aphelios</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>用主手武器开火，每把20发，打空换下一把：通碧射程更远，断魄吸血10%、攻速+20%，坠明减速25%，荧焰溅射，折镜每次命中攻击+5%（4秒，可叠加）。传知者与真知者：随等级额外成长。
 （攻击间隔 0.97 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>武器技能：主手武器的技能，各自冷却：通碧狙击造成110 + 100% 攻击力物理伤害并追射；断魄加速连射回血；坠明定身被它减速的敌人1秒；荧焰扇形波后副手追击；折镜放下哨塔5秒。
 （冷却 1 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>月相轮转：交换主手和副手武器：主手技能在冷却、副手技能已就绪且附近有敌方英雄时才交换。
 （冷却 1.5 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>清辉夜凝：爆点附近有2个以上敌方英雄或目标被控制时，射出月光，在第一个英雄处爆炸，造成160 + 120% 攻击力物理伤害，再按主手：通碧追射、断魄回血、坠明减速90%、荧焰加伤、折镜叠3层。
 （冷却 25 秒 · 施放距离 90000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>厄斐琉斯附加包（league_aphelios v0.2.1）
 武器在手里：整身换武器：主手是断魄 / 坠明 / 荧焰 / 折镜时，站着、跑着、挨打、出手的第一刻都画成那把武器在手里（只在游戏 0.6.4 上）
@@ -8175,301 +8243,301 @@
 厄斐琉斯 R（备好式，v0.4.0）：90000 内有敌方英雄就按：主包待命 6 秒，正被我方打的敌方英雄身边还有别人、或被控住才放，没用上缩短冷却</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="3" t="inlineStr">
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_aphelios.md</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>艾希</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Ashe</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>league_ashe</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>普攻射出冰霜箭，造成100% 攻击力的物理伤害。被动 冰霜射击：普攻使目标减速20%，持续1秒。
 （攻击间隔 1 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>射手的专注：艾希获得30% 攻击速度，持续4秒。期间普攻变为连射，造成130% 攻击力的物理伤害，并使目标减速30%。
 （冷却 7 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>万箭齐发：向前方扇形射出13支冰霜箭，对扇形内每个敌人造成40 + 100% 攻击力的物理伤害（每个敌人只会被命中一次），并使其减速25%，持续1.5秒。
 （冷却 8 秒 · 施放距离 70000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>魔法水晶箭：向目标方向射出一支飞得很远的水晶箭，命中第一个敌方英雄，造成150 + 100% 攻击力的物理伤害并眩晕1.75秒。水晶箭在命中处炸开，对周围敌人造成60 + 50% 攻击力的物理伤害并减速50%，持续2秒。
 （冷却 50 秒 · 施放距离 100000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="3" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ashe.md</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>凯特琳</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Caitlyn</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>league_caitlyn</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 爆头：每第6枪造成180% 攻击力；被夹住的英雄在1.5倍射程内优先爆头，再加40 + 40% 攻击力。90口径绳网：英雄贴身时改射网，造成60 + 60% 攻击力并减速50%，向后跳开，下一枪爆头（冷却12秒）。
 （攻击间隔 1 秒 · 攻击距离 65000）</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>和平使者：瞄准后朝锁定的位置射出穿透子弹（优先瞄敌方英雄，开枪前走开可躲），对第一个命中的敌人造成60 + 110% 攻击力的物理伤害，之后的敌人受到60%。
 （冷却 8 秒 · 施放距离 120000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>约德尔诱捕器：朝敌方英雄扔出夹子（3层充能，每层12秒），第一个落在他脚下，其余错开放在两人之间，存在8秒；第一个踩中的敌方英雄被禁锢1.5秒，凯特琳会对他爆头。
 （冷却 36 秒 · 可存 3 次 · 施放距离 80000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>让子弹飞：瞄准一名敌方英雄1秒（被控制会中断），然后开枪，对路上第一个敌方英雄造成250 + 150% 攻击力的物理伤害。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>凯特琳附加包（league_caitlyn v0.1.0）
 经典引擎模拟（下路对 4 个原版射手、3 套阵容、两边、8 个种子）：她前 5 分钟击杀差 +0.38（金克丝 +1.29、艾希 +0.95、 厄运小姐 +0.90），10 分钟 +1.65，前期伤害只有别的射手的六七成。加攻击、加 Q 伤害、加爆头、出手加快、Q 只能对英雄放等 9 个数值方案，前期最多 +0.6 左右，能拉高前期的也让后期太强。跟踪一局…</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_caitlyn.md</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>德莱文</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Draven</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>league_draven</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>德莱文联盟：每接住一把斧头+1层崇拜（最多6层，每层攻击+4），用斧头击杀英雄时兑现：每层回复25生命，攻速+30%4秒。血性冲刺（自动，12秒）：对英雄出手时移速+40%、攻速+35%，接住斧头即刷新。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>旋转飞斧：手中转起一把飞斧（最多2把），下次攻击额外造成40 + 55% 攻击力伤害。斧头弹回空中，0.4秒后落在他身边随机一处，他会跑进落点圈接住，继续旋转。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>开道利斧：掷出一对贯穿的斧刃，造成70 + 50% 攻击力伤害，击退敌人并减速30%2秒。
 （冷却 15 秒 · 施放距离 95000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>冷血追命：向远处交战中的英雄掷出两把宽大的巨斧，飞得很远，贯穿路上的敌人造成110 + 80% 攻击力伤害；碰到第一个英雄（或飞到尽头）后折返，回程再造成一次伤害。
 （冷却 45 秒 · 施放距离 250000 · 施放：方向 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="3" t="inlineStr">
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_draven.md</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>伊泽瑞尔</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Ezreal</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>league_ezreal</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动咒能高涨：技能每打中一个目标，攻击速度提高12%，持续6秒，最多叠加5层，再次打中时刷新。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>秘术射击：能量箭对命中的第一个敌人造成40 + 140% 攻击力的物理伤害（视为普攻，可暴击），命中后各技能冷却最多剩2/3。精华跃动（冷却6秒）：先向附近敌方英雄射出精华，粘住4秒，下次普攻或技能命中英雄时引爆，造成90 + 90% 攻击力的物理伤害。
 （冷却 5 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>奥术跃迁：交战中：有敌方英雄贴近时朝远离他的方向闪现，目标在普攻射程外时朝他闪现，然后射出追踪魔法箭，造成50 + 50% 攻击力的物理伤害，也会引爆精华跃动。
 （冷却 14 秒 · 施放距离 90000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>精准弹幕：蓄力1秒后射出飞得很远的能量波，对路径上的敌方英雄造成250 + 130% 攻击力的物理伤害，对小兵和野怪伤害减半。
 （冷却 60 秒 · 施放距离 120000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="3" t="inlineStr">
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_ezreal.md</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>烬</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Jhin</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>league_jhin</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>被动 低语：四发一轮，第四发必定暴击并附加目标10%最大生命值的伤害，然后装弹2.17秒（可走动、放技能）并加速25%。烬击杀的英雄会在倒下处绽放莲花。
 （攻击间隔 1.2 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>曼舞手雷：掷出手雷，炸到目标后弹向其身后的敌人，最多命中4次，每次造成60 + 70% 攻击力物理伤害；每击杀一个单位，之后每次+35%。
 （冷却 6 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>致命华彩：若万众倾倒就绪，先在敌方英雄脚下种莲花：踩中后减速35%，2秒后炸开造成60 + 120% 攻击力。随后超远射击第一个敌方英雄造成90 + 90% 攻击力；他近期受过我方伤害则禁锢1.67秒。
 （冷却 10 秒 · 施放距离 160000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>完美谢幕：架枪引导，开4枪锁定后射出的超远子弹（被控制会中断），各打中路上第一个敌方英雄造成90 + 55% 攻击力并减速80%；每中一枪后续+30%，第四枪伤害翻倍。
 （冷却 50 秒 · 施放距离 180000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr">
         <is>
           <t>烬低语附加包（league_jhin_whisper v0.1.0）
 额外攻速：不变快；每 1% 换成 0.25% 攻击力（+40% 攻速 = +10% 攻击力）
@@ -8479,190 +8547,190 @@
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="3" t="inlineStr">
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_jhin.md</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>金克丝</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Jinx</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>league_jinx</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>枪炮交响曲！：近处有敌人时用砰砰，造成100% 攻击力的物理伤害，每发加15% 攻击速度（至多3层）；否则换鱼骨头，射程更远，对目标及周围敌人造成110% 攻击力的伤害。罪恶快感：亲手击杀英雄后6秒内25% 攻击速度，100% 移动速度（逐渐回落）。
 （攻击间隔 1 秒 · 攻击距离 64500）</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>震荡电磁波！：蓄力0.4秒后射出电磁波，对命中的第一个敌人造成75 + 120% 攻击力的物理伤害并减速25%，持续2秒。
 （冷却 6 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>嚼火者手雷！：向敌方英雄脚下扔出3只嚼火者手雷，0.5秒后布好，最多留5秒。敌方英雄踩上时手雷爆炸，禁锢范围内的敌方英雄1.5秒并造成80 + 100% 攻击力的物理伤害，随后手雷消失。
 （冷却 10 秒 · 施放距离 80000 · 施放：地点 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>超究极死神飞弹！：发射一枚飞得很远的飞弹，穿过小兵和野怪，命中第一个敌方英雄后爆炸，对周围敌人造成175 + 90% 攻击力 + 10% 目标最大生命值的物理伤害。
 （冷却 50 秒 · 施放距离 250000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
 金克丝：每一次英雄击杀和助攻（几个人同时阵亡也各算一次）</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="3" t="inlineStr">
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_jinx.md</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>卡莎</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Kai'Sa</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>league_kaisa</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力物理伤害。体表活肤：普攻命中英雄叠电浆（被控制的英雄2层），每次命中附加18+9×层数魔法伤害；满5层引爆，造成80+60% 攻击力+8%最大生命真实伤害。极限超载：每8秒首次命中英雄时加速，随后4秒攻速+90%，9级起隐身0.5秒。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>艾卡西亚暴雨：朝周围敌人发射6枚导弹：第一枚射向目标，造成30+50% 攻击力物理伤害，其余每枚10+17% 攻击力。活体武器：攻击力达到200后变为12枚，每枚20+34% 攻击力。
 （冷却 8 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>虚空索敌：锁定后朝敌方英雄射出长距离虚空光束（开火前走开可躲），穿过小兵，命中的第一个英雄受到60+150% 攻击力物理伤害并叠2层电浆。活体武器：12级起叠3层并返还75%冷却。
 （冷却 12 秒 · 施放距离 150000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>猎手本能：冲向一名近期受伤的敌方英雄，落地获得220+180% 攻击力的护盾，持续2秒。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr">
         <is>
           <t>目标标记附加包（league_marks v0.1.0）
 卡莎 体表活肤：每个英雄各记各的（4 秒）：普攻每次附加 18 + 9 × 层数 + 20% 法强的魔法伤害，同一个人第五层引爆 80 + 60% 攻击力 + 8% 最大生命的真实伤害</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr">
+      <c r="J129" s="2" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="3" t="inlineStr">
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_kaisa.md</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>卡莉丝塔</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Kalista</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>league_kalista</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>投矛，命中的敌人身上插一支矛（4秒）。武术姿态：每次投矛后向后跳开。哨兵：有队友在目标身边时，额外造成目标14%最大生命值的真实伤害（5秒一次）。
 （攻击间隔 0.77 秒 · 攻击距离 52500）</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>穿刺：掷出长矛，对第一个敌人造成120 + 105% 攻击力物理伤害并插上一支矛；若将其击杀，长矛穿过去命中下一个。
 （冷却 7 秒 · 施放距离 100000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>撕裂：拔出所有敌人身上的矛：每支造成20 + 50% 攻击力物理伤害并减速8%。击杀英雄时刷新冷却。插满3支时自动拔出。
 （冷却 1.5 秒 · 施放距离 100000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>命运的召唤：把身边一名队友拉进身体保护0.5秒，然后甩向目标，落地击飞周围敌人1.25秒，造成80 + 60% 攻击力物理伤害。
 （冷却 80 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>卡莉丝塔附加包（league_kalista v0.1.1）
 武术姿态：每次投矛后自己判断往前还是往后：最近的敌方英雄残血（40% 以下），或者它在逃（越跑越远）而且快跑出射程（超过攻击距离 80%），就往前追；其余都往后跳开；身边没有敌方英雄时照主…
@@ -8673,311 +8741,311 @@
 卡莉丝塔 E：主包「矛够了」的标记（league_kalista_e_ok）在、撕裂不在冷却（league_kalista_e_cd）：按下就是撕裂，不会空按</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="3" t="inlineStr">
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_kalista.md</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>克格莫</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Kog'Maw</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>league_kogmaw</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>生化弹幕（自动，12秒）：攻击时开启8秒，射程+180，攻击附带目标5%最大生命值伤害。来自艾卡西亚的惊喜：死后虚空之力化身追向附近敌方英雄，爆炸造成80 + 100% 攻击力真实伤害。
 （攻击间隔 0.9 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>腐蚀唾液：吐出腐蚀唾液，命中首个敌人造成80 + 70% 攻击力伤害，护甲和魔抗-20%4秒。被动：攻速+35%。连招：生化弹幕开启时自动补一发Q。
 （冷却 8 秒 · 施放距离 95000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>虚空淤泥：吐出贯穿的虚空淤泥，造成70 + 60% 攻击力伤害并减速35%，留下4秒的减速淤泥带。连招：淤泥命中英雄后补一发活体大炮。
 （冷却 12 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>活体大炮：炮击远处交战中的英雄，0.67秒后落地造成90 + 65% 攻击力伤害；被炸后剩余生命不足50 + 35% 攻击力的英雄直接被击杀。一轮最多3发，冷却20秒。
 （冷却 20 秒 · 施放距离 130000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 克格莫 R：R 好了、射程（130000）内有引擎接受的敌方英雄（主包 R 只打最近被我方打过的）就按，先挑生命比例最低的（大招打残血更痛）。一轮三发、之后锁 20 秒都是主包的数据。不限时…</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="3" t="inlineStr">
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_kogmaw.md</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>卢锡安</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Lucian</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>league_lucian</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动圣光银弹：每放一个技能，下次普攻连开两枪，第二枪50% 攻击力（对小兵、野怪100%）。警惕：附近敌方英雄被定身后，接下来两次普攻额外造成20 + 25% 攻击力的真实伤害。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>透体圣光：射出穿透目标的光束，对直线上的敌人造成65 + 130% 攻击力的物理伤害。
 （冷却 6 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>冷酷追击：冲刺：敌方英雄贴近时后撤，射程内有敌人时后跳，否则追到射程内。接着射出热诚烈弹，爆炸造成60 + 60% 攻击力的真实伤害并标记6秒，期间每次命中移动速度+25%，持续1秒。之后两次普攻都连开两枪。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>圣枪洗礼：原地引导3秒，连射20发子弹，每发射向最近的敌方英雄（穿过小兵），造成12 + 30% 攻击力的物理伤害。受到眩晕、禁锢、击飞等控制或阵亡时中断。
 （冷却 60 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="3" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_lucian.md</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>梅尔</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Mel</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>league_mel</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>射出金色光弹。灼灼之光：每放一个技能，下次普攻多射3枚光弹（最多9枚），每枚12 + 5% 法强魔法伤害；打中英雄叠一层夺命残影。灵魂折镜：每25秒第一次打中英雄时张开屏障1.25秒，受到的伤害减少50%并反弹40%，移速+25%。
 （攻击间隔 1.17 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>耀光齐射：耀光飞弹落在目标处，连续爆炸6次，每次对范围内的敌人造成22 + 15% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>阳炎涡旋：射出阳炎法球，中心的敌人受到60 + 50% 法强魔法伤害并被禁锢1秒；周围的敌人减速30%，1.5秒内受到10 + 6% 法强×4魔法伤害。
 （冷却 10 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>鎏金蚀日：无视距离打击所有带夺命残影的敌方英雄，每层残影造成15 + 8% 法强魔法伤害。
 （冷却 35 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>梅尔附加包（league_mel v0.1.3）
 主包 league 保持纯数据。用户选了「做附加包」，又要求「有连招要做连招」。主包的数据做不到英雄联盟里梅尔的两件事——夺命残影的处决（数据读不到生命，也数不了目标身上的层数）和灵魂折镜的反弹（没有效果能挡住或拐弯一个弹体）——所以放在这个附加包里用原生代码做，外加连招： - 夺命残影的处决：英雄联盟里梅尔每次打中都叠一层残影，残影的伤害够了，下一次打中…</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="3" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_mel.md</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>厄运小姐</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Miss Fortune</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>league_missfortune</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>双枪射击，造成100% 攻击力的物理伤害。被动厄运的眷顾：对新目标的第一枪（她击杀上一个目标后，或1.25秒没开枪后）额外造成40% 攻击力的物理伤害。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>一箭双雕：射出一发子弹，对命中的第一个敌人造成20 + 100% 攻击力的物理伤害，子弹继续飞，对其身后的下一个敌人造成20 + 140% 攻击力的物理伤害（含厄运的眷顾）。第一发击杀目标时，第二发暴击，伤害翻倍。
 （冷却 6 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>枪林弹雨：向目标区域倾泻2秒弹雨，每0.25秒对区域内的敌人造成10 + 15% 攻击力的物理伤害（共80 + 120% 攻击力）并减速40%。随后大步流星：4秒内获得40% 攻击速度和20% 移动速度。
 （冷却 10 秒 · 施放距离 70000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>弹幕时间：原地引导3秒，向前方锥形区域连射12波子弹，每波对其中的敌人造成15 + 45% 攻击力的物理伤害，可以暴击。她受到眩晕、禁锢、击飞等控制或阵亡时引导中断。
 （冷却 50 秒 · 施放距离 75000 · 施放：地点 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>目标标记附加包（league_marks v0.1.0）
 厄运小姐 爱心一击：和上一枪打的不是同一个人就算新目标</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="3" t="inlineStr">
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_missfortune.md</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>尼菈</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Nilah</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>league_nilah</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>喜色川流：鞭刃近战攻击。游刃万变后4秒内，射程+125，攻击扇形顺劈，额外造成25% 攻击力物理伤害，并回复伤害10%的生命。
 （攻击间隔 0.93 秒 · 攻击距离 30000）</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>游刃万变：朝目标方向甩出鞭刃，对直线上的所有敌人造成40+100% 攻击力物理伤害，并强化之后4秒的攻击。
 （冷却 1 秒 · 施放距离 60000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>纵情逐流 / 轻纱飞漾：纵情逐流：穿过敌方英雄冲刺，落地对周围造成60+45% 攻击力物理伤害，2层充能。用完时放轻纱飞漾：2.25秒内闪避所有攻击，技能伤害-25%，移速+20%，附近友方英雄同样获得1.5秒。
 （冷却 1 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>神恩激荡：旋转鞭刃1秒，每段造成12+20% 攻击力物理伤害，最后造成100+110% 攻击力物理伤害并把周围敌人拉到身边；附近友方英雄回复40+30% 攻击力生命并获得40+30% 攻击力护盾。
 （冷却 40 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr">
         <is>
           <t>尼菈附加包（league_nilah v0.1.1）
 喜色川流（被动）：另外她和附近友方英雄每次回血、得到护盾都多 15%（英雄联盟的「乐无止境」：她给的、给她的治疗和护盾都更强）
@@ -8986,64 +9054,64 @@
 神恩激荡什么时候放：圈里有 2 个以上敌方英雄才放；只有 1 个时，他血量不到一半、她自己血量不到 40%、或者附近没有别的敌方英雄会赶来，也放；最多等 1.5 秒</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="3" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_nilah.md</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>莎弥拉</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Samira</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>league_samira</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>远处开枪，近身挥刀并附加15 + 20% 攻击力魔法伤害。被动悍勇本色：用和上一次不同的招式命中英雄，评价E→S升一级，每级移速+3%，9秒没打到英雄清零。攻击被控制的英雄时冲上去击飞0.5秒。
 （攻击间隔 0.97 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>交火：身边有敌人时挥刀斩击前方，否则开枪打中第一个敌人，造成30 + 130% 攻击力物理伤害。
 （冷却 5 秒 · 施放距离 90000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>狂飙：冲到敌方英雄身后，对周围敌人造成70 + 40% 攻击力魔法伤害，攻速+30%。随即锋旋：旋转0.75秒砍两次，每次25 + 70% 攻击力，期间受到的攻击伤害-60%。击杀英雄刷新冷却。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>炼狱扳机：评价到S时才会施放：原地旋转连射2秒，每0.2秒向周围所有敌人各开一枪，造成10 + 40% 攻击力物理伤害，期间生命偷取40%。放完评价清零。
 （冷却 5 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>莎弥拉边走边射附加包（league_samira_r v0.1.0）
 R 期间：旋转连射，同时走向 90000 内生命 + 护盾最少的敌方英雄，走到 30000 内站住；被硬控时不走
@@ -9053,127 +9121,127 @@
 莎弥拉 E、Q（攒评价）：S 要连着换五种出手打中英雄（枪 / 剑普攻、Q、E 冲刺、落地的 W 旋转），一下打不中 9 秒就掉。R 不按时：60000 内有敌方英雄、她生命不低于 50%、目标身边的敌方…</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>2.84</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="3" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_samira.md</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>希维尔</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Sivir</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>league_sivir</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>被动 敏锐疾行：攻击或技能命中英雄时移速+25%，2秒内递减。弹射：每10秒下一次攻击开启4秒弹射：攻速+45%，攻击再弹向目标身后最多3个敌人，各造成60% 攻击力物理伤害（可暴击）。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>回旋之刃：掷出十字刃，飞到尽头再飞回手中，往返都对路上所有敌人造成60 + 80% 攻击力物理伤害。附近有英雄时朝他所在的位置掷出（出手前锁定，可以躲开）。
 （冷却 8 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>法术护盾：张开法术护盾，最多3秒：免疫技能伤害和控制。第一次被击中时回复60 + 40% 攻击力生命并触发敏锐疾行，护盾再撑1秒后破碎。
 （冷却 12 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>狩猎：附近友方英雄（含自己）移速+30%，持续8秒。狩猎期间希维尔的攻击命中英雄会缩短回旋之刃和法术护盾的冷却，弹射冷却减半；她的攻击击杀英雄时刷新狩猎。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 希维尔 E：60000 内的敌方英雄刚放了技能（20 tick 内技能冷却开始走），或她生命不到 40% 而 40000 内有敌方英雄</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="3" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_sivir.md</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>斯莫德</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Smolder</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>league_smolder</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>喷出小火球。被动龙之研习：技能命中英雄、龙息击杀单位各获得1层（阵亡清空），每层使龙息、喷嚏、扑棱火球各+0.75/1.65/0.25魔法伤害。龙息在10/25/40层时依次获得爆炸、反冲火球、灼烧。
 （攻击间隔 0.93 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>超级灼热龙息：喷吐火球，造成60+120% 攻击力物理伤害。10层：爆炸波及周围敌人；25层：向目标身后喷出反冲火球（50%伤害）；40层：灼烧3秒，每秒造成10+10% 攻击力+1%最大生命真实伤害。
 （冷却 5 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>阿嚏！ / 扑棱，扑棱，扑棱！：打喷嚏喷出火焰，造成40+40% 攻击力物理伤害并减速35%，命中英雄时爆炸，再造成40+40% 攻击力物理伤害。被近身或追击残血时改用扑棱，扑棱，扑棱！：飞起并加速40%，向残血敌人连发5枚火球，各10+30% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>妈----！：呼唤妈妈沿直线喷火，造成110+80% 攻击力物理伤害，中心的敌人多受50%伤害并减速40%（2秒）。斯莫德站在中心线上时回复80+30% 攻击力生命。
 （冷却 50 秒 · 施放距离 90000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>斯莫德附加包（league_smolder v0.1.1）
 龙之研习的层数：死后保留（层数、计数器、三档全部原样补回）
@@ -9181,190 +9249,190 @@
 扑棱，扑棱，扑棱！：自己的冷却（20 秒），好了就每 3 tick 看一次：撤——生命低于 40% 而 40000 内有敌方英雄、30000 内有敌方英雄、或 40000 内敌方英雄 2 名以上且比…</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="3" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_smolder.md</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>崔丝塔娜</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Tristana</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>league_tristana</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>普攻发射炮弹，造成100% 攻击力的物理伤害。被动 瞄准：3/6/9/12级时射程各提高4.5%。爆炸火花：普攻击杀的敌人会爆炸，对周围敌人造成30 + 30% 攻击力的物理伤害。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>爆炸火花：向目标投掷炸弹，4秒后爆炸，对周围敌人造成70 + 80% 攻击力的物理伤害；她每命中一次伤害 +25%，第4次立即引爆。同时急速射击：攻速+80%，持续7秒。
 （冷却 8 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>火箭跳跃：炮弹打中炸弹已叠2层以上的敌方英雄时跳到他身边；开炮时有敌方英雄贴身则向后跳开。落地对周围敌人造成50 + 60% 攻击力的物理伤害并减速40%，持续2秒。冷却18秒；她击杀敌方英雄或满层引爆英雄身上的炸弹时刷新。
 （冷却 10 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>毁灭射击：对敌方英雄发射巨型炮弹（优先贴身的），对目标及周围敌人造成200 + 120% 攻击力的物理伤害，将他们击退，落地后眩晕0.5秒。
 （冷却 50 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
 崔丝塔娜：每一次英雄击杀和助攻都刷新（满层引爆照旧）</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="3" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_tristana.md</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>图奇</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Twitch</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>league_twitch</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>弩箭攻击。被动死亡毒液：普攻、毒桶和大招的箭每次挂一层毒，每层6秒内每秒造成1 + 2% 攻击力真实伤害。
 （攻击间隔 0.9 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>埋伏：伪装隐身最多5秒并加速20%，出手即现形，之后6秒攻速+35%。击杀敌方英雄时刷新冷却。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>剧毒之桶：扔出毒桶：范围内敌人挂一层毒并减速30%，毒池持续3秒。随后接毒性爆发：每层毒造成6 + 16% 攻击力物理伤害。
 （冷却 11 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>火力全开：6秒内射程+300、攻击力+15，弩箭穿透一条直线，每多穿一个少10%（最低60%）。两名敌方英雄在附近时施放。
 （冷却 60 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
 图奇：埋伏助攻也刷新；E 等到有人满 6 层毒、或这一爆能毒死人才引爆（v0.3.0），条件一满足下一箭就爆（v0.3.1）</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="3" t="inlineStr">
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_twitch.md</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>韦鲁斯</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Varus</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>league_varus</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>射箭攻击，附带20魔法伤害，命中英雄叠一层枯萎（最多3层）。被动复仇之欲：击杀英雄后攻速+60%，击杀小兵野怪+20%，持续5秒。
 （攻击间隔 0.93 秒 · 攻击距离 57500）</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>穿刺之箭：拉弓射出穿透箭：射程内有敌方英雄时蓄满力，造成110 + 130% 攻击力物理伤害，否则快速出手、伤害较低；之后每个敌人伤害递减。命中英雄时引爆枯萎：每层3%最大生命值真实伤害并缩短技能冷却。每40秒一次蓄满的箭再加6%。
 （冷却 6.67 秒 · 施放距离 95000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>恶灵箭雨：向目标区域射下箭雨，造成70 + 90% 攻击力物理伤害并引爆枯萎；地面腐化4秒，其中的敌人减速30%、受到的治疗降低40%。
 （冷却 8 秒 · 施放距离 90000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>腐败锁链：射出腐败锁链，命中第一个敌方英雄：150 + 80% 攻击力物理伤害、禁锢2秒、叠满3层枯萎；锁链随后扩散到附近的敌方英雄，禁锢1.5秒。
 （冷却 60 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>韦鲁斯枯萎附加包（league_varus_blight v0.1.0）
 枯萎记在哪里：每个敌方英雄自己身上（各最多 3 层，6 秒）
@@ -9373,191 +9441,191 @@
 R：一样（叠在被锁住的人身上）</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="3" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_varus.md</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>薇恩</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Vayne</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>league_vayne</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 暗夜猎手：附近有敌方英雄时移动速度+8%。圣银弩箭：3.5秒内连续第3次命中（普攻、技能都算）额外造成50的真实伤害，对英雄再加7%最大生命值。
 （攻击间隔 1 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>闪避突袭：翻滚：敌方英雄贴近时往后滚，射程内有敌人时后跳，否则滚进射程。7秒内的下一次普攻额外造成25 + 80% 攻击力的物理伤害。
 （冷却 5 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>恶魔审判：用大弩射出重箭，对敌方英雄造成60 + 70% 攻击力的物理伤害并击退，落地时再受到30 + 35% 攻击力的物理伤害并眩晕1秒。
 （冷却 10 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>终极时刻：8秒内攻击力+25%，技能冷却缩短50%，闪避突袭附带1秒隐身，暗夜猎手的移速变为3倍。期间她亲手击杀英雄时，终极时刻刷新为8秒。
 （冷却 50 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>薇恩圣银弩箭附加包（league_vayne_bolts v0.1.0）
 主包 league 保持纯数据。数据分不清一次攻击打中的是谁，所以主包里圣银弩箭的两层记在薇恩自己身上：她轮流打两个人也会凑满 3 下，在第三个被打中的人身上爆。这个附加包用原生代码做成英雄联盟的样子：同一个目标连续挨 3 下才爆。</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="3" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_vayne.md</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>霞</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Xayah</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>league_xayah</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>甩出羽刃攻击。被动锐切：每放一个技能，之后3次普攻（最多存5次）穿透直线，其他目标受到50%伤害，并在目标身后留下一根羽毛（6秒）。
 （攻击间隔 0.83 秒 · 攻击距离 57500）</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>双刃·倒钩：扔出两把穿透匕首，各造成60 + 80% 攻击力物理伤害（后续目标50%），各留一根羽毛；随后倒钩收回所有羽毛，每根对路过的敌人造成50 + 60% 攻击力伤害，一次收回命中英雄第3次起禁锢1.25秒。
 （冷却 7 秒 · 施放距离 75000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>致死羽衣：攻速+50%，持续4秒；期间每次普攻再甩出一片25%伤害的羽刃，命中英雄时移速+30%。洛在附近时，他也获得这些效果。
 （冷却 8 秒 · 施放距离 57500 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>暴风羽刃：跃向空中，1.1秒内不受伤害和控制，再向前方降下匕首雨，造成160 + 100% 攻击力物理伤害，留下一排羽毛并随即收回。
 （冷却 60 秒 · 施放距离 60000 · 施放：方向 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>霞羽毛附加包（league_xayah_feathers v0.1.0）
 定身条件：同一个英雄被 3 根羽毛打中（60 tick 内）
 定身时长、画面、伤害：一样</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="3" t="inlineStr">
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_xayah.md</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>芸阿娜</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Yunara</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>league_yunara</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>念珠普攻附带18 + 20% 法强魔法伤害。初生之誓：这段伤害也会暴击（基础暴击10%）。灵蕴拳：普攻攒灵蕴，满了自动开启5秒：攻速+40%，多附带18 + 20% 法强魔法伤害，并溅射周围敌人30% 攻击力物理伤害。
 （攻击间隔 0.83 秒 · 攻击距离 57500）</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>善恶轮：掷出旋转念珠，对路径上的敌人造成70 + 85% 攻击力物理伤害和衰减减速，终点再旋转1秒。超凡形态：改为射线，造成160 + 120% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>明踪步：附近有敌方英雄时，移速+40%（追击时+60%），持续1.5秒。超凡形态：敌方英雄贴近时改为向后冲刺。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>定圣诀：附近有2个以上敌方英雄或目标被控制时，进入超凡形态15秒：灵蕴拳持续开启，善恶轮变为射线，明踪步变为冲刺，两者冷却立刻减少80%。
 （冷却 70 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>芸阿娜附加包（league_yunara v0.1.1）
 夜影翻（超凡形态的 E）：按情况选方向：最近的敌方英雄残血（35% 以下）又快出射程就往前冲把它拉进射程；它贴身、或她自己残血（40% 以下）就往后冲
@@ -9566,185 +9634,185 @@
 超凡形态的样子：另外站着、跑着都画成带金边和头后光环的她（游戏 0.6.4）</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="3" t="inlineStr">
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_yunara.md</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>泽丽</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Zeri</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>league_zeri</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>普攻电火迸射：7发连射打第一个敌人。被动内能迁转：每5次攻击充满电，下一击为电击弹，额外造成40 + 100% 法强魔法伤害并减速，命中英雄再造成4%最大生命真实伤害，自己获得护盾和移速。
 （攻击间隔 0.93 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>强穿激光：发射电脉冲，对第一个敌人造成60 + 110% 攻击力物理伤害并减速35%。先打中小兵或野怪时，从那里化为长激光，伤害并减速身后所有敌人。
 （冷却 10 秒 · 施放距离 90000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>灿丽花火：短距冲刺（被贴身时后撤），之后5秒普攻贯穿：后面的敌人受到80%伤害，并额外造成20 + 30% 法强魔法伤害。命中英雄缩短冷却。
 （冷却 20 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>超限爆闪：电新星对周围敌人造成150 + 100% 法强魔法伤害，超载5秒：攻速+30%、移速+20%，命中英雄叠加移速并延长；普攻变为三连发，在敌人间连锁闪电。
 （冷却 60 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>泽丽附加包：W 撞墙激光 + 被动偷盾（league_zeri v0.1.1）
 - W「强穿激光」的脉冲先打中小兵或野怪时才在那里化为长激光（小兵代替墙）； - 被动「内能迁转」的电击弹打中英雄时给自己一个小护盾（代替偷盾）。</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="3" t="inlineStr">
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zeri.md</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>阿利斯塔</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Alistar</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>league_alistar</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>用双拳重击。被动凯旋怒吼：控制命中敌方英雄3次后怒吼，回复自己40 + 20% 法强、周围友方英雄50 + 30% 法强生命。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>大地粉碎：践踏接大地粉碎：先践踏3秒（每脚12 + 9% 法强），再砸地，周围敌人受到80 + 80% 法强魔法伤害并击飞1秒。踩中英雄5次后，下次普攻眩晕1秒。
 （冷却 10 秒 · 施放距离 24000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>野蛮冲撞：野蛮冲撞接大地粉碎：冲向敌方英雄，撞退并造成100 + 110% 法强魔法伤害，随即砸地击飞周围敌人，同时开始践踏。（和大地粉碎共用：6秒内只砸一次）
 （冷却 12 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>坚定意志：交战时怒吼：免疫控制1秒，7秒内受到的伤害降低50%。
 （冷却 60 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="3" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_alistar.md</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>巴德</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Bard</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>league_bard</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>射出星光。被动旅者的召唤：每3秒一只米普随攻击飞出，对目标周围的敌人造成45 + 50% 法强魔法伤害并减速25%（1秒）。
 （攻击间隔 1.5 秒 · 攻击距离 52000）</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>星界束缚：射出星界能量，命中的第一个敌人受到100 + 75% 法强魔法伤害并减速60%；若其身后还有敌人，两者都受到伤害并眩晕1.5秒。
 （冷却 7 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>游神圣坛 / 神奇旅程：游神圣坛：向交战中的友方英雄（或自己）投出圣坛，治疗140 + 60% 法强，移速+30%。神奇旅程：被敌人近身时开门，带身边的友方英雄远离，移速+40%（16秒一次）。
 （冷却 7 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>调和命运：向聚在一起的敌方英雄（或被控制的友方英雄）投出金色法球，范围内所有单位（含友军、自己和防御塔）时停2.5秒：无法行动、无法被选中、不受伤害。
 （冷却 60 秒 · 施放距离 90000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>巴德「神奇旅程」穿墙门附加包（league_bard v0.6.1）
 什么时候开门：冷却（16 秒）一好就每 3 tick 看一次：撤——生命低于 45% 而 30000 内有敌方英雄、15000 内有敌方英雄、或 30000 内敌方英雄 2 名以上且比身边友方…
@@ -9753,190 +9821,190 @@
 争大小龙（命运之轮）：用户：「给巴德加上争大小龙时主动对龙放大招拖时间」。大龙、小龙在大招射程 80000 内、生命低于 95%（已经有人在打）、35000 内有敌方英雄、命运之轮的圈（36000）里…</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="3" t="inlineStr">
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_bard.md</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>布里茨</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Blitzcrank</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>league_blitzcrank</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害；大招没在冷却时，1秒后再落一道闪电，造成20 + 15% 法术强度的魔法伤害。被动 法力屏障：被围攻或被控制时获得120 + 80% 法术强度的护盾（冷却60秒）。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>机械飞爪：射出机械手，抓住直线上第一个敌方英雄（穿过小兵），造成70 + 50% 法术强度的魔法伤害，眩晕并把它拉到身前。
 （冷却 10 秒 · 施放距离 70000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>能量铁拳：一记上勾拳，造成20 + 100% 攻击力的物理伤害并击飞1秒。过载运转（每15秒）：敌方英雄靠近时自动开启，4秒内移速+40%（逐渐降低）、攻速+25%，结束后减速25%1.5秒。
 （冷却 7 秒 · 施放距离 25000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>静电力场：释放静电，对身边敌人造成150 + 80% 法术强度的魔法伤害，并沉默敌方英雄1秒。打起来才放；放出后普攻的闪电停用，直到大招冷却结束。
 （冷却 50 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.0）
 布里茨 法力屏障：生命不高于 30%</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="3" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_blitzcrank.md</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>布隆</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Braum</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>league_braum</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>震荡猛击：普攻和寒冬之咬命中英雄叠一层，第4层眩晕1.25秒并造成85 + 60% 法强魔法伤害；之后8秒不再叠层，普攻额外造成12 + 10% 法强魔法伤害。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>寒冬之咬：从盾中甩出寒冰，造成105 + 60% 法强+最大生命2%魔法伤害，减速70%，2秒内渐弱到35%。
 （冷却 8 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>坚不可摧：举盾3.5秒：受到伤害降低50%，获得60 + 40% 法强护盾，身边友方英雄伤害降低20%。挺身而出：冲到友方英雄身边，两人护甲和魔抗+30，持续3秒。
 （冷却 1 秒 · 施放距离 45000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>冰川裂隙：猛砸地面，冰川裂隙冲向目标，造成180 + 70% 法强魔法伤害并击飞0.6秒（第一个英雄1.25秒），留下4秒的裂隙，减速40%。
 （冷却 60 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>布隆附加包（league_braum v0.1.1）
 Test build of Braum as in League (needs League of Legends Heroes): replaces the main pack's Braum so Concussive Blows stacks on each champion and his allies' attacks add stacks to…</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="3" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_braum.md</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>迦娜</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Janna</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>league_janna</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>普攻吹出一道风弹，造成100% 攻击力的物理伤害。被动 顺风而行：战斗中，她和身边的友方英雄移动速度提高8%。
 （攻击间隔 1.5 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>飓风呼啸：放出一道龙卷风，对直线上的敌人造成80 + 60% 法术强度的魔法伤害，并击飞0.75秒。
 （冷却 9 秒 · 施放距离 75000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>风暴之眼：对一名敌方英雄放出和风守护，造成60 + 40% 法术强度的魔法伤害并减速30%，持续2秒。同时以风暴之眼为身边一名友方英雄提供150 + 75% 法术强度的护盾，持续4秒，护盾存在时攻击力提高15%；身边没有队友时护住自己。
 （冷却 5 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>复苏季风：击退身边的敌人，然后引导3秒，每秒为身边的友方英雄（包括自己）回复130 + 50% 法术强度的生命值，共4次。受到控制或阵亡时中断。
 （冷却 50 秒 · 施放距离 40000 · 施放：指定目标 · 友方英雄）</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 迦娜 E 风暴之眼（50000 内）：有危险的队友（生命不高于 50%，或身边 25000 内有 2 个以上敌方英雄）里生命比例最低的；都没危险就给离敌方英雄最近的（正在打的那个）
@@ -9944,248 +10012,248 @@
 迦娜 R：她或身边 40000 内的队友生命不到 35% 而 50000 内有敌方英雄，或两人以上生命不到 60% 而她身边有敌方英雄。对生命最低的那位放（治疗是她身边一圈，对谁放都一样）</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="3" t="inlineStr">
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_janna.md</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>卡尔玛</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Karma</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>league_karma</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>射出灵能飞弹。聚能之炎：技能命中英雄，梵咒冷却最多缩短60%。鼓舞（自动，9秒）：给被控或交战中的队友（或自己）110 + 50% 法强护盾，移速+35%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>心灵烈焰：射出灵火，命中首个敌人爆炸，周围敌人受到100 + 70% 法强魔法伤害并减速35%。灵光闪耀（梵咒）：额外50 + 30% 法强伤害并留下火环，1.5秒后爆发造成70 + 50% 法强伤害、减速50%。
 （冷却 6 秒 · 施放距离 62000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>坚定不移：连住敌方英雄，造成60 + 40% 法强魔法伤害；1.33秒未挣脱则再次受伤并禁锢1.67秒。焕发（梵咒，被围攻时）：回复110 + 40% 法强生命，禁锢2.33秒。连招：禁锢时梵咒Q随即跟上。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>梵咒：强化6秒内的下一个技能：队友危险时立即蔑视（附近队友都获得60 + 30% 法强护盾和加速），否则强化Q或被围攻时的W。未使用则返还冷却。
 （冷却 35 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="3" t="inlineStr">
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_karma.md</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>蕾欧娜</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Leona</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>league_leona</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 日光：被蕾欧娜技能命中的敌人1.5秒内受到的伤害提高10%，每个技能各挂一层。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>破晓之盾：用盾猛击身边的一个敌人，造成100% 攻击力的物理伤害和40 + 40% 法术强度的魔法伤害，眩晕1秒。
 （冷却 5 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>天顶之刃：掷出剑光，对直线上的敌人造成60 + 40% 法术强度的魔法伤害，禁锢命中的第一个敌方英雄0.5秒并冲到它身边。日蚀：出手时举盾，3秒内受到的伤害降低25%，随后盾牌爆发，对周围敌人造成60 + 40% 法术强度的魔法伤害；命中敌人则减伤再持续3秒。
 （冷却 8 秒 · 施放距离 60000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>日炎耀斑：召唤一道阳光，0.6秒后落在敌方英雄所在处，对范围内的敌人造成150 + 80% 法术强度的魔法伤害并减速80%，中心的敌人改为眩晕，持续1.75秒。
 （冷却 60 秒 · 施放距离 80000 · 施放：地点 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="3" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_leona.md</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>璐璐</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Lulu</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>league_lulu</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>射出魔弹。被动皮克斯，仙灵伙伴：皮克斯朝同一目标射出3颗飞弹，每颗造成12 + 8% 法强魔法伤害。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>闪耀长枪：璐璐和皮克斯各射出一道贯穿魔弹，直线上的敌人受到80 + 60% 法强魔法伤害并减速80%，1.5秒内逐渐减弱。
 （冷却 6 秒 · 施放距离 60000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>奇思妙想：把敌方英雄变形1.75秒（无法攻击和施法、减速），造成70 + 40% 法强魔法伤害；帮忙，皮克斯！：附近友方英雄获得110 + 50% 法强护盾和25%移速、攻速（3.5秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>狂野生长：交战时让被控制或被敌人贴身的友方英雄（或自己）变大：生命+350，周围敌人击飞1秒，7秒内身边敌人减速30%。
 （冷却 60 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 璐璐 E 帮忙，皮克斯！（先 30000，再 60000 内）：同迦娜</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="3" t="inlineStr">
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_lulu.md</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>茂凯</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Maokai</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>league_maokai</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>巨臂砸击。吸元秘术：技能命中后下一次普攻额外造成2%最大生命魔法伤害，回复40 + 60% 法强生命（4秒一次）。树苗投掷：每10秒自动向敌方英雄扔树苗，敌人靠近就爆炸：100 + 50% 法强魔法伤害，减速35%。
 （攻击间隔 1.25 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>荆棘重击：巨拳砸地，推开身边的敌人，冲击波对前方敌人造成100 + 40% 法强魔法伤害外加目标2%最大生命伤害，并减速95%（很快减弱）。
 （冷却 6 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>扭曲突刺：化作树根冲向敌方英雄（途中免伤免控），到达后禁锢1.3秒，造成100 + 40% 法强魔法伤害。身边有友方英雄或正在交战时才放。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>自然之握：召唤荆棘墙缓缓向前推进，碰到的敌人受到180 + 75% 法强魔法伤害并被禁锢0.8~2.4秒（推得越远越久），撞到英雄后他加速。有2名敌方英雄或交战时才放。
 （冷却 60 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>茂凯附加包（league_maokai v0.1.0）
 吸元秘术回血：按等级回复最大生命的 4.5%–12%（英雄联盟）
@@ -10193,64 +10261,64 @@
 草丛里的树苗：读地图的草丛格子；立在草丛里的树苗爆炸半径更大（34000）、伤害 ×1.6、减速 45%（英雄联盟草丛里的树苗更强）</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="K153" s="2" t="inlineStr"/>
-      <c r="L153" s="3" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_maokai.md</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>米利欧</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Milio</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>league_milio</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>射出小火球。被动热情洋溢！：技能触及的友方获得30%攻击力和法术强度（5秒），米利欧获得15%移速。
 （攻击间隔 1.5 秒 · 攻击距离 53000）</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>火爆飞踢：踢出火球，击退命中的第一个敌人，随后火球落下，对周围敌人造成120 + 70% 法强魔法伤害并减速40%（1.5秒）。
 （冷却 7 秒 · 施放距离 75000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>融融情谊 / 依依不舍：融融情谊（2次）：友方英雄获得80 + 40% 法强护盾和16%移速（2.5秒）。依依不舍：在其身上点燃营火6秒，每1秒治疗周围友方22 + 4% 法强并增加攻击距离。
 （冷却 18 秒 · 可存 2 次 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>生生不息：友方被控制或被敌人贴身时，为周围友方英雄恢复150 + 50% 法强生命，免疫控制1秒并获得65%韧性（3秒）。
 （冷却 60 秒 · 施放距离 75000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>米利欧附加包（league_milio v0.1.2）
 热情洋溢！：E、R 触及的友方（营火每一跳也算）身上挂记号（画面不变，攻击力、法强 +20%）；他下一次打中敌人（普攻或技能，不算防御塔）就把那个敌人点燃：1.5 秒内 20-100 魔法伤…
@@ -10258,243 +10326,243 @@
 解控：R 生效时圈里身上有控制的友方英雄真的被解控（再加主包的 1 秒免控和韧性）</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="3" t="inlineStr">
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_milio.md</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>莫甘娜</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Morgana</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>league_morgana</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>普攻射出一团暗影，造成100% 攻击力的物理伤害。被动 灵魂吸取：技能对英雄造成伤害时，为自己回复约为伤害15%的生命值。
 （攻击间隔 1.5 秒 · 攻击距离 50000）</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>暗之禁锢：射出暗之禁锢，穿过小兵和野怪，对沿途敌人造成80 + 60% 法术强度的魔法伤害，停在第一个敌方英雄身上并将其禁锢2秒。每12秒同时在其脚下留下折磨之影，4秒内共造成80 + 40% 法术强度的魔法伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>黑暗之盾：对敌方英雄施法，为身边一名友方英雄套上150 + 70% 法术强度的护盾，持续5秒，护盾存在时免疫控制。身边没有队友时护住自己。
 （冷却 8 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>灵魂镣铐：锁住身边所有敌方英雄，造成170 + 80% 法术强度的魔法伤害并减速20%，自身移动速度提高20%。跑出锁链范围的敌人会挣断锁链；3秒后仍被锁住的敌方英雄再受到一次伤害并被眩晕1.5秒。
 （冷却 50 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="3" t="inlineStr">
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_morgana.md</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>娜美</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Nami</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>league_nami</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>普攻射出一颗水弹，造成100% 攻击力的物理伤害。被动 踏浪之行：技能命中友方英雄时，使其移动速度提高20%，持续1.5秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>冲击之潮：水流冲击敌人，造成65 + 45% 法术强度的魔法伤害，弹向附近友方英雄回复70 + 35% 法术强度的生命值，再弹向另一名敌方英雄造成60 + 40% 法术强度伤害。唤潮之佑：被治疗者4秒内攻击力和法术强度提高15%，被击中者减速25%。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>碧波之牢：向敌人（优先敌方英雄）扔出水泡，落地时对范围内的敌人造成80 + 60% 法术强度的魔法伤害，并将其困在水泡中击飞1.25秒。
 （冷却 10 秒 · 施放距离 70000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>怒涛之啸：召唤一道巨浪朝敌方英雄推进，对沿途敌人造成150 + 70% 法术强度的魔法伤害，击飞0.5秒并减速60%，巨浪走得越远减速越久（2至3秒）。经过的友方英雄获得双倍踏浪之行加速。
 （冷却 50 秒 · 施放距离 90000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="3" t="inlineStr">
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_nami.md</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>诺提勒斯</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Nautilus</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>league_nautilus</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>排山倒海：普攻敌方英雄时将其禁锢0.83秒，并额外造成20 + 30% 法强魔法伤害，之后6秒内不再触发。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>疏通航道：抛出铁锚，钩中第一个敌方英雄，造成75 + 60% 法强魔法伤害，并把双方拉向彼此。
 （冷却 10 秒 · 施放距离 75000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>泰坦之怒：获得110 + 60% 法强护盾，6秒内普攻还会伤及目标周围的敌人15 + 20% 法强。暗流涌动：地面震荡三波，周围敌人受到70 + 50% 法强魔法伤害并减速40%1.25秒。
 （冷却 8 秒 · 施放距离 25000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>深海冲击：对射程内一名敌方英雄发出深海冲击波：沿途敌人被击飞并受到60 + 30% 法强伤害；目标受到150 + 80% 法强魔法伤害，击飞1秒后眩晕0.75秒。
 （冷却 50 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>诺提勒斯钩墙附加包（league_nautilus v0.1.2）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个附加包里（合集 league_addons 也带着它）。 装上后，诺提勒斯的 Q「疏通航道」：锚沿路线先碰到野区的墙（引擎的碰撞墙，5v5 地图 90 格）时，把他拉到墙边，并返还一半冷却—— 和英雄联盟一样；先碰到敌方英雄时照主包钩人（两人拉向彼此）。</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="3" t="inlineStr">
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_nautilus.md</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>波比</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Poppy</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>league_poppy</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>钢铁大使：每8秒普攻远远扔出圆盾，多造成60 + 30% 法强魔法伤害；盾落在地上，捡起得120 + 60% 攻击力护盾。坚定风采：双抗+16%；敌方英雄靠近时移速+40%，2秒内身边敌人不能位移。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>圣锤猛击：锤击地面，造成60 + 70% 攻击力物理伤害（英雄另受6%最大生命），地面减速25%，1秒后再炸一次。
 （冷却 7 秒 · 施放距离 30000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>英勇冲锋：冲向敌方英雄，造成70 + 80% 攻击力物理伤害并推着他走，结束时眩晕0.75秒。
 （冷却 11 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>持卫的裁决：身边有2个以上敌方英雄时砸地：80 + 40% 攻击力物理伤害并击飞1秒；否则蓄力抡锤推出冲击波，打中的英雄受150 + 70% 攻击力物理伤害并被打飞到远处。
 （冷却 60 秒 · 施放距离 55000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>波比附加包（league_poppy v0.1.0）
 坚定风采的光环：光环里正在突进的敌方英雄被挡下：击飞 0.5 秒、受魔法伤害，然后缚地并减速 2 秒（每次光环每人一次）
@@ -10504,185 +10572,185 @@
 钢铁大使的护盾：最大生命的 11%（1 级）到 21%（18 级）</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="3" t="inlineStr">
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_poppy.md</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>派克</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Pyke</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>league_pyke</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>鱼叉挥砍。被动溺水之幸：挨打积攒灰血（最多5层），潜行或3秒没挨打时每层回复15 + 8% 攻击力生命。无法靠生命成长，攻击力成长更高。
 （攻击间隔 0.92 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>透骨尖钉：英雄贴身时戳刺，否则蓄力扔出鱼叉，命中第一个敌人：35 + 60% 攻击力物理伤害，减速90%，鱼叉命中的会被拉回。
 （冷却 7 秒 · 施放距离 100000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>魅影浪洄：幽潭潜行：潜行并加速，回复灰血。随即魅影浪洄：冲过敌方英雄，魅影随后飞回他身边，途经的英雄受到50 + 60% 攻击力物理伤害并晕眩1秒。
 （冷却 11 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>涌泉之恨：X形打击：英雄受到180 + 60% 攻击力真实伤害，低于此值被处决，否则只受一半；其他敌人受一半物理伤害。有英雄死在X里时派克闪到其身上并刷新大招。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>派克精确斩杀附加包（league_pyke v0.1.1）
 主包 league 保持纯数据。数据读不到当前生命，主包里派克的 R 由 AI 对「队伍刚打过的敌方英雄」放出，满血的也会被砍 （用户：「大招逻辑也有点问题 总是满血砍人」）；X 里的英雄先吃斩杀线的真实伤害、下一 tick 活下来的回一半，近似「低于斩杀线处决」。 这个附加包用原生代码读生命，做成 League 的样子： - 只砍斩得死的人：AI 钩子 …</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="3" t="inlineStr">
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_pyke.md</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>洛</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Rakan</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>league_rakan</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>掷出羽毛攻击。被动异色羽裳：获得70 + 70% 法强的护盾，破掉12秒后再生；攻击和技能每命中一名敌方英雄，再生快1秒。
 （攻击间隔 1.42 秒 · 攻击距离 40000）</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>微光飞翎：掷出羽毛，第一个敌人受到100 + 80% 法强的魔法伤害。命中英雄后，3秒后或碰到友方英雄时，为自己和身边的友方英雄回复70 + 50% 法强生命值。
 （冷却 5.5 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>盛大登场·轻舞成双：盛大登场：冲向一名敌方英雄，旋上空中，击飞周围敌人0.8秒并造成100 + 70% 法强的魔法伤害；随后轻舞成双：飞到最近的友方英雄身边，给他90 + 70% 法强的护盾（3秒）。霞在附近时飞得更远。
 （冷却 7.5 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>惊鸿过隙：4秒内疾速穿梭于敌人之间：碰到的每个敌人受到140 + 70% 法强的魔法伤害并被魅惑1.25秒（每个敌人一次）；碰到第一个英雄后更快。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="3" t="inlineStr">
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_rakan.md</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>芮尔</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Rell</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>league_rell</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>骑枪突刺，附带6+最大生命1%魔法伤害。溃敌沉力：普攻和技能命中英雄，5秒内削减其3%护甲和魔抗，自己获得3点护甲和魔抗（可叠加）。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>裂阵：前冲一刺，对直线上的敌人造成80 + 60% 法强魔法伤害并晕眩0.65秒。全速冲锋：与身边一名队友加速15%→30%，下次普攻或裂阵爆炸，额外造成英雄最大生命5%真实伤害。
 （冷却 10 秒 · 施放距离 38000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>驭铁术：轰落：跃向敌方英雄砸下，造成80 + 60% 法强魔法伤害并击飞0.83秒，获得90 + 40% 法强护盾，下马作战15秒（双抗、攻速提升）。驾临：上马冲锋，晕眩0.6秒并掀飞目标。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>极涌：把附近敌人猛地拉到身边，2秒内持续拖拽并共造成280 + 112% 法强魔法伤害。等到身边有2个敌方英雄或有被控住的敌人时才放。
 （冷却 60 秒 · 施放距离 64000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>芮尔附加包（league_rell v0.1.2）
 下马作战：整个身体换成披甲步行的她：站着、走着、挨打、普攻、放裂阵、阵亡都是步行的样子（游戏 0.6.4），上马换回骑马
@@ -10691,64 +10759,64 @@
 全速冲锋：一直 15%，她或那名队友朝最近的敌方英雄、或朝对方跑时再加 15%（英雄联盟：朝敌人或彼此时翻倍）</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="3" t="inlineStr">
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_rell.md</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>烈娜塔</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Renata</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>league_renata</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>手枪普攻。物尽其用：命中英雄时额外造成最大生命2%真实伤害并标记；队友在旁攻击时引爆，造成30 + 20% 法强魔法伤害。及时救难：队友被控或团战时自动施放，攻速+40%、移速+20%，5秒内不会阵亡，结束时回复200 + 60% 法强生命。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>忠诚激励：发射一对飞弹，命中敌人或飞到尽头时爆炸，造成85 + 60% 法强魔法伤害并减速30%；途经的友方英雄获得90 + 50% 法强护盾，持续3秒。
 （冷却 10 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>铁腕竞合：射出机械手，抓住第一个敌人，造成95 + 85% 法强魔法伤害并禁锢0.83秒，随后把它甩向身后；落点周围的敌人受到75 + 50% 法强魔法伤害，甩出的是英雄时还会被眩晕0.5秒。
 （冷却 15 秒 · 施放距离 85000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>恶意收购：附近有2个以上敌方英雄，或敌方英雄被控制时，放出化学波：命中的敌方英雄狂暴1.75秒，不能攻击我方、不能施法，每0.5秒攻击身边的队友，造成70 + 40% 法强魔法伤害。
 （冷却 80 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>烈娜塔附加包（league_renata v0.1.2）
 物尽其用：队友真的打中它才引爆（普攻或技能）：魔法伤害 + 最大生命 3% 的真实伤害
@@ -10756,185 +10824,185 @@
 恶意收购的狂暴：真的转身打自己人：走向最近的队友（英雄优先），按他自己的攻击间隔、用他自己的攻击力打；打死队友的击杀和助攻算烈娜塔的（和英雄联盟一样）</t>
         </is>
       </c>
-      <c r="J162" s="2" t="inlineStr">
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="3" t="inlineStr">
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_renata.md</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>赛娜</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Senna</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>league_senna</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>赦除：技能和普攻标记敌方英雄，下次普攻吸走：额外3%最大生命伤害+1层黑雾；每6秒一次普攻和击杀英雄也+1层。每层攻击+1、射程略增，每2层暴击+1%（死亡清空）。黑雾咒附（自动）：英雄贴近时，她和身边队友隐身4秒、移速+20%。
 （攻击间隔 1.6 秒 · 攻击距离 62000）</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>黑暗洞灭：遗物炮射出穿透目标的暗影光束：直线上的敌人受到60 + 50% 攻击力物理伤害并减速20%1.25秒，队友英雄回复70 + 35% 攻击力生命。
 （冷却 9 秒 · 施放距离 62000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>无尽厮守：射出黑雾，附着在首个命中的敌人身上并造成70 + 60% 攻击力物理伤害；1秒后黑雾扩散，禁锢它和周围的敌人1.5秒。
 （冷却 11 秒 · 施放距离 90000 · 施放：方向 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>暗影燎原：蓄力后朝远方交战中的英雄射出横贯战场的光束：中心对敌方英雄造成150 + 75% 攻击力物理伤害，两侧宽阔的光芒给她和沿途队友英雄120 + 40% 攻击力护盾3秒。
 （冷却 50 秒 · 施放距离 250000 · 施放：方向 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>赛娜黑雾常驻附加包（league_senna_mist v0.1.0）
 这个附加包把主包的赛娜换成 override/ 里的副本（make_override.py 用 tools/kit/build_senna.py 的 --native 生成：技能 一字不改，只加被动 league_senna_mist:keep，普攻说明里的「（死亡清空）」换成「（扩展包保留）」），被动每 tick 看一次： - 活着时把身上每一层 lea…</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="3" t="inlineStr">
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_senna.md</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>萨勒芬妮</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Seraphine</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>league_seraphine</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>被动星光漫射：每第3个技能回音再放一次。放技能时得到一个音符，身边每个友方英雄再给一个（最多4个），下次普攻每个音符额外造成8 + 8% 法强魔法伤害，有音符时射程更远。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>清籁穿云：在目标处落下高音，对范围内敌人造成55 + 40% 法强魔法伤害；被控制的敌方英雄多受50%。
 （冷却 9 秒 · 施放距离 75000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>增幅节拍：声波对直线上的敌人造成45 + 35% 法强魔法伤害并减速30%；回音的声波定身被减速的英雄、晕眩被控制的英雄。接着聚和心声：身边友方英雄获得50 + 25% 法强护盾和移速+20%，2.5秒后按身边友方英雄数各回复8 + 6% 法强生命。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>炫音返场：放出一道音波，碰到友方英雄后传得更远，对敌方英雄造成120 + 50% 法强魔法伤害并魅惑1.5秒。附近有两名敌方英雄时施放。
 （冷却 55 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="3" t="inlineStr">
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_seraphine.md</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>娑娜</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Sona</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>league_sona</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>弹出音符攻击。被动能量和弦：每放3次技能，下次普攻额外造成50 + 50% 法强的魔法伤害，并按最后一首歌：断奏 伤害翻倍；渐弱 目标伤害降低25%（3秒）；节奏 减速40%（2秒）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>英勇赞美诗：对附近两个敌人（英雄优先）各造成95 + 60% 法强的魔法伤害。旋律：3秒内来到她身边的友方英雄3秒内获得15% 攻击力和15% 法强。
 （冷却 7 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>坚毅咏叹调：为自己和一名附近的友方英雄回复100 + 40% 法强生命值。旋律：身边的友方英雄获得70 + 40% 法强的护盾1.5秒。每14秒同时弹迅捷奏鸣曲：身边友方英雄移速+20%（自己+30%）3秒。
 （冷却 8 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>狂舞终乐章：朝敌方英雄弹出一道音波，途经的敌方英雄受到150 + 60% 法强的魔法伤害并被晕眩1.5秒。被动：每条命放出大招后，技能冷却缩短20%。
 （冷却 50 秒 · 施放距离 75000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 娑娜 W 回血（60000 内）：损失生命最多的队友
@@ -10942,122 +11010,122 @@
 娑娜 W：她或 60000 内的队友生命不到 70%，射程内有敌方英雄</t>
         </is>
       </c>
-      <c r="J165" s="2" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K165" s="2" t="inlineStr"/>
-      <c r="L165" s="3" t="inlineStr">
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_sona.md</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>索拉卡</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Soraka</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>league_soraka</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>普攻用法杖射出星光弹，造成100% 攻击力的物理伤害。
 （攻击间隔 1.5 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>流星坠落：造成70+50%法术强度的魔法伤害并减速30%，命中敌方英雄时获得活力焕发：2.5秒内回复75+30%法术强度的生命值并加速20%。每16秒一次附带星体结界：沉默圈内敌人，1.5秒后仍在圈内的禁锢1秒并受到40+30%法术强度的魔法伤害。
 （冷却 8 秒 · 施放距离 70000 · 施放：地点 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>星之灌注：消耗自身6%最大生命值（不会致死），为一名其他友方英雄回复200+50%法术强度的生命值。带活力焕发时不消耗生命值，目标也获得活力焕发。被动拯救：施放后2秒内移动速度提高30%。
 （冷却 4 秒 · 施放距离 90000 · 施放：指定目标 · 友方（不含自己））</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>祈愿：为全图所有友方英雄（包括自己）回复220 + 60% 法术强度的生命值。
 （冷却 50 秒 · 施放距离 960000 · 施放：指定目标 · 友方英雄）</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="3" t="inlineStr">
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_soraka.md</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>塔姆</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Tahm Kench</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>league_tahmkench</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>培养品味：普攻额外造成30 + 2%最大生命魔法伤害，普攻、Q、W命中英雄叠一层，最多3层。厚实表皮：受到伤害降低15%，被两名敌方英雄围住时获得160 + 80% 法强护盾。
 （攻击间隔 1.33 秒 · 攻击距离 28000）</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>巨舌鞭笞：舌头鞭打第一个单位，造成170 + 60% 法强 + 2%最大生命魔法伤害，减速40%1.5秒；命中英雄回复40 + 30% 法强生命并叠一层，3层时眩晕1.25秒。
 （冷却 6 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>深渊潜航：潜入地下1秒（不可选中），在目标处冒出，造成160 + 70% 法强 + 2%最大生命魔法伤害并击飞1秒。
 （冷却 1 秒 · 施放距离 70000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>大快朵颐：吞下被控制、身陷敌群的队友2.5秒，吐出时给予150 + 100% 法强护盾；或吞下3层的敌方英雄2.5秒，造成220 + 50% 法强 + 3%最大生命魔法伤害和其最大生命6%真实伤害。
 （冷却 60 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>塔姆附加包（league_tahmkench v0.1.2）
 培养品味的层数：每个敌方英雄各自记层（最多 3 层，5 秒），鱼标记按那个人自己的层数画
@@ -11068,122 +11136,122 @@
 深渊潜航：同样的条件，再加上落点附近的敌方英雄不多于身边队友加一、他自己生命不低于 30%；不放时改成普攻或回到队友身边</t>
         </is>
       </c>
-      <c r="J167" s="2" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="3" t="inlineStr">
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_tahmkench.md</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>塔里克</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Taric</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>league_taric</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>普攻造成100% 攻击力的物理伤害。被动 正气凌人：施放技能后4秒内的下2次普攻攻速+100%，额外造成30 + 20% 法强 + 3% 最大生命值的魔法伤害，缩短基础技能冷却，并为星光之触充能1层。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>炫光：朝敌人投射一道星光，0.75秒后沿直线爆裂，造成95 + 60% 法强 + 2% 最大生命值的魔法伤害并晕眩1.25秒。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>星光之触：消耗全部层数（最多3层），每层为自己和附近友方英雄回复40 + 12% 法强的生命值。坚毅壁垒（12秒）：给身边队友80 + 40% 法强的护盾和15护甲并相连，技能也会在他身边施放。
 （冷却 6 秒 · 施放距离 30000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>宇宙之辉：团战开始时召唤星光，2.5秒后自己和附近的友方英雄（相连的队友身边也算）免疫伤害2.5秒。
 （冷却 60 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="3" t="inlineStr">
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_taric.md</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>锤石</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Thresh</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>league_thresh</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>普攻甩出锁链，造成100% 攻击力的物理伤害。被动 厄运钟摆：超过2秒没有普攻时，下一次普攻额外造成40 + 50% 法术强度的魔法伤害。地狱诅咒：收割的灵魂化为每级成长的护甲与法术强度。
 （攻击间隔 1.5 秒 · 攻击距离 48000）</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>死亡判决：掷出镰刀，钩住直线上第一个敌方英雄（穿过小兵），造成80 + 60% 法术强度的魔法伤害，眩晕1秒并把它拉到身前。魂引之灯：每14秒同时掷出灯笼，为自己和身边一名友方英雄提供60 + 40% 法术强度的护盾，持续2.5秒。
 （冷却 8 秒 · 施放距离 65000 · 施放：方向 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>厄运钟摆：挥动锁链横扫身边，对敌人造成60 + 40% 法术强度的魔法伤害并减速40%，持续1秒。刚钩中英雄或没有敌方英雄贴身时，把敌人拉向并越过锤石；有敌方英雄贴身时把敌人推开。
 （冷却 6 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>幽冥监牢：在脚下立起幽冥监牢，持续5秒。第一个碰到监牢的敌方英雄受到150 + 80% 法术强度的魔法伤害并被减速99%，持续2秒；之后碰到的敌方英雄不受伤害，减速时间减半。
 （冷却 60 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>锤石灯笼附加包（league_thresh_lantern v0.1.0）
 灯笼给谁：50000 内有危险的友方英雄（生命不高于 45%，或身边 25000 内有 2 个以上敌方英雄），几个时挑生命比例最低的；都没危险就给最近的
@@ -11191,64 +11259,64 @@
 拉回来：有危险的队友离锤石超过 15000、没被硬控时，拉到锤石身边（每 tick 3000）</t>
         </is>
       </c>
-      <c r="J169" s="2" t="inlineStr">
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="3" t="inlineStr">
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_thresh.md</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>悠米</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Yuumi</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>league_yuumi</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>射出书页光弹。猫的博爱：每6秒普攻命中英雄时多造成50 + 25% 法强魔法伤害，回复自己60 + 20% 法强生命，下次附身时队友也回复同样多。
 （攻击间隔 1.5 秒 · 攻击距离 50000）</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>摸鱼飞弹：发射飞弹，打中第一个敌人造成110 + 50% 法强魔法伤害并减速20%；飞了0.33秒以上改为170 + 70% 法强，减速50%。
 （冷却 7 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>悠米出动！：附身在交战中的队友身上4秒（不可选取、跟着他走，照样能放摸鱼飞弹和魔典终章），他每秒回复45 + 15% 法强生命。旺盛精力：给他130 + 60% 法强护盾，攻速+20%、移速+10%。
 （冷却 6 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>魔典终章：翻开魔典连发5道波纹，每道造成110 + 35% 法强魔法伤害并减速，沿途友军回复60 + 10% 法强生命；第3道定身1.25秒。
 （冷却 45 秒 · 施放距离 80000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>悠米附加包（league_yuumi v0.1.1）
 附身多久：不限时，队友死了才跳下来
@@ -11258,64 +11326,64 @@
 猫的博爱：普攻或摸鱼飞弹命中英雄（附身时她不普攻）</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="3" t="inlineStr">
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_yuumi.md</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>基兰</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Zilean</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>league_zilean</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>发射时光法球。被动瓶中时光：每90秒攒满一瓶，下次时光发条加速友方英雄时送给他：他和基兰各获得10攻击力、10法强和80生命值，直到阵亡。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>定时炸弹：向目标脚下扔出炸弹（出手时锁定落点，可躲开），粘在附近第一个敌人身上（英雄优先），3秒后爆炸，造成80 + 70% 法强的魔法伤害。穿梭未来（每12秒）：炸弹粘上英雄时倒转时间再扔一颗，两颗立即爆炸并晕眩1.25秒，技能冷却缩短。
 （冷却 7 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>时光发条：使一名敌方英雄减速35%，同时让身边一名友方英雄（没有则自己）移速+35%，持续2.5秒。
 （冷却 10 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>时光倒流：附近的友方英雄被控制、或基兰被两名以上敌方英雄贴身时，为其挂上时光符文：5秒内不会阵亡，结束时时光回溯，回复400 + 150% 法强生命值。
 （冷却 60 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>基兰复活附加包（league_zilean_rewind v0.2.0）
 主包 league 保持纯数据。主包里基兰的 R 由 AI 在敌方英雄 60000 内时放出、待命 900 tick（没用上就退还冷却）； 待命期间他每次出手查一次：附近有被控制的友方英雄、或自己被两名以上敌方英雄贴身，才给那个人挂 5 秒的时光符文 （league_zilean_r_rune，带「不死」，生命最低停在 1），到第 299 tick 不管有…
@@ -11323,78 +11391,78 @@
 奥莉安娜 E、基兰 E：在打架：她 / 他或射程内的队友 40000 内有敌方英雄（基兰也追射程内生命不到 40% 的）</t>
         </is>
       </c>
-      <c r="J171" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="3" t="inlineStr">
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/league_zilean.md</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="3" t="inlineStr">
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L172"/>
+  <autoFilter ref="A1:L173"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -11567,6 +11635,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -8356,7 +8356,7 @@
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:L176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11537,63 +11537,128 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>拉露恩</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Alune</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>tft_alune</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>中单</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
+（攻击间隔 1.5 秒 · 攻击距离 55000）</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>月之降临：月光碎片从天而降，落在3个敌人身上（一个是目标），每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
+（冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
+（冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：范围内的敌人受到165 + 72% 法强魔法伤害，中心的敌人眩晕0.83秒。
+（冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>拉露恩附加包（tft_alune v0.1.0）
+月之降临：落在离她最近的 q_n 个敌人身上（金铲铲的规则），每枚 q_dmg + q_ratio% 法强、月蚀印记（魔抗 -q_shred%）
+月曜降临：整颗月亮的伤害（含月相加成）× r_split% 由命中的敌人平分，每人最多 r_cap%：只砸中一个人时最痛
+普攻：月环飞回来，穿过路上的每个敌人（a_back_r% 攻击力），打中的那个人回来时再挨一下</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="3" t="inlineStr">
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L175"/>
+  <autoFilter ref="A1:L176"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -11769,6 +11834,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId175"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -11557,13 +11557,13 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>星光弹造成100% 攻击力物理伤害。寄情琐物：每10秒，下个技能落点留下琐物4秒，走进的敌方英雄受到30 + 20% 法强魔法伤害并挂线缕。奇异旅程：普攻时敌方英雄贴身，开门造成40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒（每25秒）。
+          <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，英雄挂上线缕；那里有琐物时一并引爆，附近的敌方英雄再受琐物伤害。
+          <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
@@ -11575,20 +11575,11 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波毛线球横穿，共4波：裂隙里的敌方英雄每波受到30 + 15% 法强魔法伤害并减速80%0.5秒，第4波伤害+40%。
+          <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>诺拉附加包（tft_norra v0.1.0）
-寄情琐物（被动）：落点撒 3 个（手游按等级 2/3/4 个）：中间茶杯、左右各一个水晶，敌方英雄踩到哪个，哪个飞到他身上炸开，别的还在
-琐物冷却：技能（Q、W、E）命中敌方英雄，冷却减少总冷却的 20%
-回忆涌现（Q）：对已有线缕的英雄多打最大生命 q_bonus‰；蓄满的 Q 打中英雄，地上的琐物变成「附近有人就炸」：敌方英雄走到 q_prime_r 以内就飞过去
-奇异旅程（W，并进被动）：敌方英雄一贴身就开门（她活着、能被选中、不在控制里、冷却好了）
-传送门欢腾！（R）：每波两个毛线球从裂隙两头沿一条线对飞（线穿过裂隙里的一个敌方英雄，每波轮到下一个），路上敌人每波挨一次，每个球碰到的第一个英雄减速</t>
-        </is>
-      </c>
+      <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="inlineStr">
         <is>
           <t>2</t>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -11557,13 +11557,13 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
+          <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>月之降临：月光碎片从天而降，落在3个敌人身上（一个是目标），每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
+          <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
@@ -11575,18 +11575,11 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：范围内的敌人受到165 + 72% 法强魔法伤害，中心的敌人眩晕0.83秒。
+          <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>拉露恩附加包（tft_alune v0.1.0）
-月之降临：落在离她最近的 q_n 个敌人身上（金铲铲的规则），每枚 q_dmg + q_ratio% 法强、月蚀印记（魔抗 -q_shred%）
-月曜降临：整颗月亮的伤害（含月相加成）× r_split% 由命中的敌人平分，每人最多 r_cap%：只砸中一个人时最痛
-普攻：月环飞回来，穿过路上的每个敌人（a_back_r% 攻击力），打中的那个人回来时再挨一下</t>
-        </is>
-      </c>
+      <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="inlineStr">
         <is>
           <t>2</t>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -4087,7 +4087,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.13）
+          <t>俄洛伊附加包（league_illaoi v0.2.14）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -4087,7 +4087,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -685,13 +685,13 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>海克斯最后通牒：跳向一名敌方英雄（空中免疫伤害和控制），落地震开周围其他敌人，在落点展开固定的力场3秒：目标无法使用位移技能、走不出力场；她自己可以离开，离开后力场消失。期间她踢中英雄额外造成10 + 3%最大生命值的真实伤害。
+          <t>海克斯最后通牒：跳向一名敌方英雄（空中免疫伤害和控制），落地震开周围其他敌人，在落点展开固定的力场4秒：目标无法使用位移技能、走不出力场；她自己可以离开，离开后力场消失。期间她踢中英雄额外造成10 + 3%最大生命值的真实伤害。
 （冷却 50 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>青钢影钩墙附加包（league_camille_wall v0.4.3）
+          <t>青钢影钩墙附加包（league_camille_wall v0.4.4）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个单独的附加包里。 装上后，青钢影的 E「钩索」钩墙、地图四边和防御塔，不再钩小兵、野怪；英雄、树林、草丛也不钩（墙就在树林里）。
 游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 卡蜜尔 E：E 好了、60000 内有敌方英雄就按，目标是最近的那个（钩墙附加包的 E 射程是 85000，取小的）。钩索、钩墙、冲向敌人照旧由主包 / 钩墙附加包决定</t>
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>蒙多附加包（league_drmundo v0.1.5）
+          <t>蒙多附加包（league_drmundo v0.1.6）
 想去哪就去哪：控制落下的那个 tick 就清掉（只认硬控：击飞、眩晕、定身、嘲讽、恐惧、魅惑、强制位移），扣当前生命的 7%，丢药罐；生命不满 85%、身边没有敌方英雄时走回去捡药罐（该放大招…
 病毒屠刀打英雄：按目标当前生命的 20% 算魔法伤害（至少是 Q 的基础伤害）
 大力行医：按他的已损生命最多再翻一倍；攻击力随额外生命（装备给的）涨 2.5%

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -4207,7 +4207,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
+          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.2）
 易：每一次英雄击杀和助攻，阿尔法突袭和冥想的剩余冷却减 70%，无极剑道开着时再延长 4 秒；每次普攻阿尔法突袭冷却减 1 秒；无极剑道期间免疫减速</t>
         </is>
       </c>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>阿兹尔附加包（league_azir v0.1.2）
+          <t>阿兹尔附加包（league_azir v0.1.3）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
 禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害和击退还是数据那道墙的
 沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…</t>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.8）
+          <t>塞拉斯附加包（league_sylas v0.2.9）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>塔莉垭附加包（league_taliyah v0.1.0）
+          <t>塔莉垭附加包（league_taliyah v0.2.0）
 竖墙（敌人近、或她已在打架）：同一块地方是真的墙：英雄、小兵、野怪、召唤物（两边都算，她自己也算）都过不去；立起时压在上面的单位推到她那一侧
 横墙（敌人远：骑墙）：每一段都是真的墙；她骑墙时站在墙顶上不受挡，跳下来那一 tick 推到近的一侧</t>
         </is>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
+          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.2）
 金克丝：每一次英雄击杀和助攻（几个人同时阵亡也各算一次）</t>
         </is>
       </c>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>卡莉丝塔附加包（league_kalista v0.1.1）
+          <t>卡莉丝塔附加包（league_kalista v0.1.2）
 武术姿态：每次投矛后自己判断往前还是往后：最近的敌方英雄残血（40% 以下），或者它在逃（越跑越远）而且快跑出射程（超过攻击距离 80%），就往前追；其余都往后跳开；身边没有敌方英雄时照主…
 誓约者：开局绑定一名队友（辅助位优先，没有就最近的队友英雄，每条命出生时重新看），大招对誓约者施放
 命运的召唤：把誓约者拉进来保护、定身，然后逐 tick 飞向离她最近的敌方英雄现在的位置（90000 内，没有就两倍范围），到了就在脚下击飞周围敌人
@@ -9439,7 +9439,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
+          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.2）
 崔丝塔娜：每一次英雄击杀和助攻都刷新（满层引爆照旧）</t>
         </is>
       </c>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.1）
+          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.2）
 图奇：埋伏助攻也刷新；E 等到有人满 6 层毒、或这一爆能毒死人才引爆（v0.3.0），条件一满足下一箭就爆（v0.3.1）</t>
         </is>
       </c>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>青钢影钩墙附加包（league_camille_wall v0.4.4）
+          <t>青钢影钩墙附加包（league_camille_wall v0.4.5）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个单独的附加包里。 装上后，青钢影的 E「钩索」钩墙、地图四边和防御塔，不再钩小兵、野怪；英雄、树林、草丛也不钩（墙就在树林里）。
 游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 卡蜜尔 E：E 好了、60000 内有敌方英雄就按，目标是最近的那个（钩墙附加包的 E 射程是 85000，取小的）。钩索、钩墙、冲向敌人照旧由主包 / 钩墙附加包决定</t>
@@ -750,13 +750,13 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>盛宴：吞噬受伤的敌方英雄，造成300 + 自身5%最大生命的真实伤害和50% 法强无视魔抗的魔法伤害；吃掉则叠一层：最大生命+70、体型变大（不封顶，死亡清空）。
+          <t>盛宴：吞噬受伤的敌方英雄，造成300 + 自身5%最大生命的真实伤害和50% 法强无视魔抗的魔法伤害；吃掉则叠一层：最大生命+70、体型变大（最多 2 倍，死亡清空）。
 （冷却 60 秒 · 施放距离 30000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>科加斯附加包（league_chogath v0.1.0）
+          <t>科加斯附加包（league_chogath v0.1.1）
 盛宴的层数：死后原样补回，层数一局里只增不减
 什么时候放盛宴：读射程内敌方英雄的生命、护盾、免死和受到伤害的增减，一口吃得死才放（几个时吃生命 + 护盾最少的，AI 没想放也放）；吃不死时 AI 想放就改成普攻那个人</t>
         </is>
@@ -8995,7 +8995,7 @@
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L177"/>
+  <dimension ref="A1:L178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.14）
+          <t>俄洛伊附加包（league_illaoi v0.2.15）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>希瓦娜附加包（league_shyvana v0.1.0）
+          <t>希瓦娜附加包（league_shyvana v0.1.1）
 龙形的样子：整身变龙：龙形期间（league_shyvana_dg，和龙形刚结束、还没播变回动作时的 league_shyvana_was_dg）站、跑、挨打、阵亡都换成 d_idle / …</t>
         </is>
       </c>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.3）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.4）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.9）
+          <t>塞拉斯附加包（league_sylas v0.2.10）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11708,8 +11708,66 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>希尔科</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Silco</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>tft_silco</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>中单</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
+（攻击间隔 1.5 秒 · 攻击距离 55000）</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
+（冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
+（冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
+（冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L177"/>
+  <autoFilter ref="A1:L178"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -11887,6 +11945,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId177"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:L179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.15）
+          <t>俄洛伊附加包（league_illaoi v0.2.16）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.4）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.5）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.10）
+          <t>塞拉斯附加包（league_sylas v0.2.11）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11766,8 +11766,66 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>麦迪</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Maddie</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>tft_maddie</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
+（攻击间隔 1.1 秒 · 攻击距离 68000）</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
+（冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
+（冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
+（冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L178"/>
+  <autoFilter ref="A1:L179"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -11946,6 +12004,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:L180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.16）
+          <t>俄洛伊附加包（league_illaoi v0.2.17）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.5）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.6）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.11）
+          <t>塞拉斯附加包（league_sylas v0.2.12）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11824,8 +11824,66 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>洛里斯</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Loris</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>tft_loris</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>辅助</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
+（攻击间隔 1.4 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
+（冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
+（冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
+（冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L179"/>
+  <autoFilter ref="A1:L180"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12005,6 +12063,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId179"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.17）
+          <t>俄洛伊附加包（league_illaoi v0.2.18）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.6）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.7）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.12）
+          <t>塞拉斯附加包（league_sylas v0.2.13）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11537,353 +11537,411 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>可酷伯</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Kobuko</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>tft_kobuko</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>上单</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>猫爪掌，造成100% 攻击力物理伤害。第二阶段：每条命第一次生命低于50%时进入狂怒，直到阵亡：攻击速度+40%、生命偷取20%。
+（攻击间隔 1.2 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>金爪真言：获得70 + 50% 法强的护盾（4秒）；4秒内下一次普攻变为金爪重掌，造成40 + 105% 攻击力 + 2%最大生命物理伤害并晕眩1秒。
+（冷却 9.5 秒 · 施放距离 25000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>猛虎扑：扑向目标，落地时周围的敌人受到40 + 70% 攻击力 + 2%最大生命物理伤害并被击飞0.4秒。
+（冷却 10.5 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>游戏结束！：一跃冲天（期间不可选中、免疫控制），砸落在敌方英雄身上：目标受到70 + 100% 攻击力 + 6%最大生命物理伤害，周围的敌人（含目标）再受到70 + 60% 攻击力 + 3%最大生命物理伤害并被击飞0.8秒。
+（冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_kobuko.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="3" t="inlineStr">
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="3" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="3" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L180"/>
+  <autoFilter ref="A1:L181"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12064,6 +12122,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.18）
+          <t>俄洛伊附加包（league_illaoi v0.2.19）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.7）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.8）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.13）
+          <t>塞拉斯附加包（league_sylas v0.2.14）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11595,353 +11595,411 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
+          <t>范德尔</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Vander</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>tft_vander</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
+（攻击间隔 1.07 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
+（冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
+（冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
+（冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="3" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="3" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L181"/>
+  <autoFilter ref="A1:L182"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12123,6 +12181,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId181"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -4789,7 +4789,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -7343,7 +7343,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5684,7 +5684,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>冲击之潮：水流冲击敌人，造成65 + 45% 法术强度的魔法伤害，弹向附近友方英雄回复70 + 35% 法术强度的生命值，再弹向另一名敌方英雄造成60 + 40% 法术强度伤害。唤潮之佑：被治疗者4秒内攻击力和法术强度提高15%，被击中者减速25%。
+          <t>冲击之潮：水流先治疗身边一名友方英雄（没有则治疗自己）70 + 35% 法术强度的生命值，再弹向附近敌人造成65 + 45% 法术强度的魔法伤害，不会弹回娜美。唤潮之佑：被治疗者4秒内攻击力和法术强度提高15%，被击中者减速25%。
 （冷却 7 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L182"/>
+  <dimension ref="A1:L183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>青钢影钩墙附加包（league_camille_wall v0.4.5）
+          <t>青钢影钩墙附加包（league_camille_wall v0.4.6）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个单独的附加包里。 装上后，青钢影的 E「钩索」钩墙、地图四边和防御塔，不再钩小兵、野怪；英雄、树林、草丛也不钩（墙就在树林里）。
 游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 卡蜜尔 E：E 好了、60000 内有敌方英雄就按，目标是最近的那个（钩墙附加包的 E 射程是 85000，取小的）。钩索、钩墙、冲向敌人照旧由主包 / 钩墙附加包决定</t>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.19）
+          <t>俄洛伊附加包（league_illaoi v0.2.20）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.8）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.9）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.14）
+          <t>塞拉斯附加包（league_sylas v0.2.15）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -8992,10 +8992,15 @@
 （冷却 60 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>卢锡安附加包（league_lucian v0.1.0）
+Lucian walks firing The Culling (needs League of Legends Heroes): while his ult fires, his walk is drawn with both pistols levelled forward instead of his plain run. Picture only;…</t>
+        </is>
+      </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
@@ -11449,7 +11454,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.1）
+          <t>悠米附加包（league_yuumi v0.1.3）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11653,353 +11658,411 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
+          <t>蔚奥莱</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Violet</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>tft_violet</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
+（攻击间隔 0.93 秒 · 攻击距离 24000）</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
+（冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
+（冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
+（冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="3" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L182"/>
+  <autoFilter ref="A1:L183"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12182,6 +12245,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId182"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L183"/>
+  <dimension ref="A1:L184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.20）
+          <t>俄洛伊附加包（league_illaoi v0.2.21）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.9）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.10）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.15）
+          <t>塞拉斯附加包（league_sylas v0.2.16）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.3）
+          <t>悠米附加包（league_yuumi v0.1.4）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11600,469 +11600,527 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
+          <t>远古石甲虫</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Krug</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>tft_krug</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>岩拳砸地，造成100% 攻击力物理伤害。碎岩重生：每条命第一次受到致命伤害时碎成石堆0.75秒，再以小石甲虫站起：生命35%、攻速+30%，嘲讽周围敌人1秒（至少隔60秒）。
+（攻击间隔 1.2 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>岩之摇滚：获得80 + 60% 法强的护盾（4秒），缩成石球滚向目标，造成40 + 140% 攻击力 + 6%最大生命物理伤害并击退。
+（冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>坚岩外壳：缩进巨石2.5秒：护甲+40、魔抗+30；周围的敌人被嘲讽0.75秒。
+（冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>远古崩落：一跃而起（不可选中、免疫控制），砸进敌方英雄身边：周围敌人受到70 + 100% 攻击力 + 6%最大生命物理伤害并被击飞0.8秒；随后落石再造成40 + 4%最大生命物理伤害。
+（冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_krug.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="3" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="3" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L183"/>
+  <autoFilter ref="A1:L184"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12246,6 +12304,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId183"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L184"/>
+  <dimension ref="A1:L185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.21）
+          <t>俄洛伊附加包（league_illaoi v0.2.22）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.10）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.11）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.16）
+          <t>塞拉斯附加包（league_sylas v0.2.17）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.4）
+          <t>悠米附加包（league_yuumi v0.1.5）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11832,295 +11832,353 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
+          <t>敖兴</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Ao Shin</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>tft_aoshin</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>中单</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
+（攻击间隔 1.5 秒 · 攻击距离 55000）</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
+（冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
+（冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
+（冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L184"/>
+  <autoFilter ref="A1:L185"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12305,6 +12363,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId184"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L185"/>
+  <dimension ref="A1:L186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.22）
+          <t>俄洛伊附加包（league_illaoi v0.2.23）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.11）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.12）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.17）
+          <t>塞拉斯附加包（league_sylas v0.2.18）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.5）
+          <t>悠米附加包（league_yuumi v0.1.6）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11600,585 +11600,643 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
+          <t>刀疤</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Scar</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>tft_scar</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>上单</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>长矛刺击造成100% 攻击力物理伤害。野火冲刺：每6秒下一击踩滑板冲刺，造成40 + 110% 攻击力+30% 法强伤害，回复上次冲刺以来所受伤害的25%。监察：生命不低于50%时减伤20%，否则10%。
+（攻击间隔 1.2 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>水坑狙击惊喜：向最近的3名敌人各扔一颗炸弹，造成70 + 80% 法强魔法伤害并晕眩1秒；自己回复60 + 60% 法强生命。
+（冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>长矛横扫：长矛横扫前方，造成50 + 80% 攻击力+2% 最大生命物理伤害并击退敌人。
+（冷却 9 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>野火突袭：踩滑板冲向敌人，途中丢下两颗燃烧弹（各40 + 40% 法强魔法伤害）；落地爆炸，周围敌人受到120 + 100% 法强魔法伤害并被击飞0.5秒，之后4秒内减伤40%。
+（冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_scar.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
           <t>远古石甲虫</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Krug</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>tft_krug</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>岩拳砸地，造成100% 攻击力物理伤害。碎岩重生：每条命第一次受到致命伤害时碎成石堆0.75秒，再以小石甲虫站起：生命35%、攻速+30%，嘲讽周围敌人1秒（至少隔60秒）。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>岩之摇滚：获得80 + 60% 法强的护盾（4秒），缩成石球滚向目标，造成40 + 140% 攻击力 + 6%最大生命物理伤害并击退。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>坚岩外壳：缩进巨石2.5秒：护甲+40、魔抗+30；周围的敌人被嘲讽0.75秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>远古崩落：一跃而起（不可选中、免疫控制），砸进敌方英雄身边：周围敌人受到70 + 100% 攻击力 + 6%最大生命物理伤害并被击飞0.8秒；随后落石再造成40 + 4%最大生命物理伤害。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="3" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_krug.md</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="3" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L185"/>
+  <autoFilter ref="A1:L186"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12364,6 +12422,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -9322,7 +9322,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.12）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.13）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.18）
+          <t>塞拉斯附加包（league_sylas v0.2.19）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.13）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.14）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -6692,7 +6692,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.0）
+          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.1）
 乐芙兰 镜花水月：生命不高于 40%</t>
         </is>
       </c>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.0）
+          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.1）
 丽桑卓 大招冰封自己：生命不高于 35%</t>
         </is>
       </c>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.19）
+          <t>塞拉斯附加包（league_sylas v0.2.20）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr"/>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.0）
+          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.1）
 布里茨 法力屏障：生命不高于 30%</t>
         </is>
       </c>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L186"/>
+  <dimension ref="A1:L187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>青钢影钩墙附加包（league_camille_wall v0.4.6）
+          <t>青钢影钩墙附加包（league_camille_wall v0.4.9）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个单独的附加包里。 装上后，青钢影的 E「钩索」钩墙、地图四边和防御塔，不再钩小兵、野怪；英雄、树林、草丛也不钩（墙就在树林里）。
 游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
 卡蜜尔 E：E 好了、60000 内有敌方英雄就按，目标是最近的那个（钩墙附加包的 E 射程是 85000，取小的）。钩索、钩墙、冲向敌人照旧由主包 / 钩墙附加包决定</t>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>火药桶：向敌方英雄扔火药桶（最多2个，留8秒），1秒后引线点燃。被枪火谈判、贴身攻击或另一个桶的爆炸引爆：范围内敌人受到40 + 100% 攻击力物理伤害（英雄再加60），无视40%护甲，减速40%2秒。
+          <t>火药桶：向敌方英雄扔火药桶（最多3个，留8秒），1秒后引线点燃。被枪火谈判、贴身攻击或另一个桶的爆炸引爆：范围内敌人受到40 + 100% 攻击力物理伤害（英雄再加60），无视40%护甲，减速40%2秒。
 （冷却 8 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
@@ -1017,9 +1017,11 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>普朗克附加包（league_gangplank v0.1.0）
+          <t>普朗克附加包（league_gangplank v0.2.0）
 坏血病疗法（W）：同上，另外吃下去的那个 tick 清掉他身上的硬控（英雄联盟：W 解除控制）；生命低于 40% 也会吃
-火药桶连锁（E）：两个桶相距不超过 e_chain（70000）才连锁；桶边有敌人照样由数据炸，桶边没人也空炸（画面、声音、刷新烈火审讯和加速都有）</t>
+火药桶连锁（E）：两个桶相距不超过 e_chain（70000）才连锁；桶边有敌人照样由数据炸，桶边没人也空炸（画面、声音、刷新烈火审讯和加速都有），空炸的桶接着往下连
+火药桶充能（E）：能存 3 个桶（e_stock），每过一轮 E 的冷却回一个；手里还有桶时扔完只等 e_gap（60 tick）就能再扔
+三连桶（E + Q）：枪火谈判打中时，两个点燃的桶连着、有敌方英雄在其中一个桶的 e_chain 以内却不在任何桶的爆炸范围里、手里还有桶：往他脚下补第三个桶，离他最近的桶先炸，连锁带上另一个，6 t…</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1275,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.23）
+          <t>俄洛伊附加包（league_illaoi v0.2.24）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -3888,7 +3890,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>凯隐「暗裔魔镰」附加包（league_kayn_form v0.3.3）
+          <t>凯隐「暗裔魔镰」附加包（league_kayn_form v0.3.5）
 攒哪种形态：打中近战英雄攒暗裔、打中远程英雄攒影流（普攻和技能都算，各 14 次），按英雄的攻击距离分
 形态能留多久：整局：阵亡复活后光环和形态效果直接回来
 变身后的样子：整个身体都是形态的（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -4081,7 +4083,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>盲僧 W 位移附加包（league_leesin_hop v0.1.9）
+          <t>盲僧 W 位移附加包（league_leesin_hop v0.1.10）
 主包 league 保持纯数据。主包的李青不能「摸眼」：R 身后没人时直接冲过目标落到他身后回旋踢，W 并进了 E、不冲刺。 英雄联盟手游里李青的 W 不用插眼就能冲到一个点，这个附加包照这个做（不画眼）： - 回旋踢（照高手的打法，v0.1.6）：R 时目标身后没有别的敌方英雄（有人就照旧正面踢进人堆），第 7 tick 先定往哪踢—— 踢回自己队伍那边…</t>
         </is>
       </c>
@@ -4144,7 +4146,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>莉莉娅梦尘与昏睡附加包（league_lillia v0.1.2）
+          <t>莉莉娅梦尘与昏睡附加包（league_lillia v0.1.3）
 主包 league 保持纯数据。数据里能读最大生命值的只有真实伤害，也没有「受到伤害就醒」的效果，所以主包莉莉娅： 被动「梦满枝」的梦尘对英雄每 0.75 秒造成 1% 最大生命值的真实伤害；大招「夜阑谣」让带梦尘的敌方英雄困倦 1.5 秒后 眩晕 1.5 秒（打不醒），她的 Q / W 打到眩晕中的英雄时多造成一段惊醒伤害。英雄联盟里梦尘是魔法伤害，昏睡…</t>
         </is>
       </c>
@@ -5292,7 +5294,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.14）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.16）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -5998,7 +6000,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>阿兹尔附加包（league_azir v0.1.3）
+          <t>阿兹尔附加包（league_azir v0.1.4）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
 禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害和击退还是数据那道墙的
 沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…</t>
@@ -7272,7 +7274,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.20）
+          <t>塞拉斯附加包（league_sylas v0.2.23）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -7464,7 +7466,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>泰隆「刺客之道」翻墙附加包（league_talon_vault v0.1.2）
+          <t>泰隆「刺客之道」翻墙附加包（league_talon_vault v0.1.3）
 什么时候翻：照旧，另外：残血（低于 35%）而身边有敌方英雄，或被围（身边敌方英雄 ≥ 2、比身边友方多、生命低于 70%）时；残血敌方英雄（≤ 60%）躲在墙后、他自己生命 ≥ 40% 时
 往哪翻：翻过墙：撤离时找背向敌人、16000 内的墙翻到另一边（落地后离敌人最远的那处）；追击时朝目标左右 35° 内找墙翻过去，落点要近 15000 以上、不翻进人堆
 冷却：同一个冷却（主包的 league_talon_e_cd），两种翻越不会连着出</t>
@@ -8152,7 +8154,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>催眠气泡：踢出气泡，打中敌方英雄造成60 + 40% 法强魔法伤害，困倦（减速30%）1.4秒后昏睡2秒；没打中就留在原地。昏睡中第一次被飞星打中伤害翻倍。
+          <t>催眠气泡：踢出气泡，打中敌方英雄造成60 + 40% 法强魔法伤害，困倦（减速30%）1.4秒后睡眠2秒，受到任何伤害就醒，打醒的那一下伤害提高100%；没打中就留在原地。
 （冷却 15 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
@@ -8164,8 +8166,8 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>佐伊附加包（league_zoe v0.3.0）
-催眠气泡的昏睡：照英雄联盟：困倦后昏睡 2.25 秒，受到任何伤害就醒（谁打的都算），那一下再来一遍真实伤害，最多 100 + 60% 法强
+          <t>佐伊附加包（league_zoe v0.4.0）
+催眠气泡的睡眠：一样是官方睡眠，2.25 秒（英雄联盟的时长）；睡着时头上有睡泡，醒了就摘掉，被打醒的放醒来的画面
 飞星的伤害：按真实飞行距离：出手点 20000 以内 100%，到 85000 线性加到 250%
 窃法巧手：另外：敌方英雄放大招时原地掉下一块法术碎片（20 秒，最多 3 块），她走到 18000 以内就捡起来，射 3 颗飞弹（打 70000 内最近的敌方英雄，每颗 45 + 15% …
 召唤师技能（0.2.0）：用户：「可以改成召唤师技能那种效果吗 随机的」「能做成智能释放吗」：窃法巧手每次发动（大招射飞弹的那一刻、捡起碎片时）先放一个召唤师技能，按局面挑：被控 → 净化；残血、敌方英雄…</t>
@@ -9379,7 +9381,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>斯莫德附加包（league_smolder v0.1.1）
+          <t>斯莫德附加包（league_smolder v0.1.2）
 龙之研习的层数：死后保留（层数、计数器、三档全部原样补回）
 三档龙息：灼烧之外，被打中的单位生命不高于最大生命的 6.5% 就处决（真实伤害，击杀算他的）
 扑棱，扑棱，扑棱！：自己的冷却（20 秒），好了就每 3 tick 看一次：撤——生命低于 40% 而 40000 内有敌方英雄、30000 内有敌方英雄、或 40000 内敌方英雄 2 名以上且比…</t>
@@ -9950,7 +9952,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>巴德「神奇旅程」穿墙门附加包（league_bard v0.6.1）
+          <t>巴德「神奇旅程」穿墙门附加包（league_bard v0.6.2）
 什么时候开门：冷却（16 秒）一好就每 3 tick 看一次：撤——生命低于 45% 而 30000 内有敌方英雄、15000 内有敌方英雄、或 30000 内敌方英雄 2 名以上且比身边友方…
 往哪走：只在墙上开门、穿到墙的另一边（英雄联盟的神奇旅程）：撤——背向身边敌人中心左右 75° 内、60000 内有墙的方向（20000 时他在线上只有 15% 的时间附近有墙，一局开不…
 队友：门边 25000 内的友方英雄一起穿过去（同样的位移；落点在墙里就落在他出口旁，再不行就不带）
@@ -10700,7 +10702,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>波比附加包（league_poppy v0.1.0）
+          <t>波比附加包（league_poppy v0.1.1）
 坚定风采的光环：光环里正在突进的敌方英雄被挡下：击飞 0.5 秒、受魔法伤害，然后缚地并减速 2 秒（每次光环每人一次）
 坚定风采的双抗：生命低于 40% 时翻倍
 英勇冲锋：撞到墙上（地图的墙格、5v5 地图的四边）才再受一次伤害并眩晕；没墙就只推开
@@ -11454,7 +11456,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.6）
+          <t>悠米附加包（league_yuumi v0.1.7）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11600,643 +11602,701 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
+          <t>荏妮</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Renni</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>tft_renni</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>上单</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>链锯每次咬3下，每下造成42% 攻击力物理伤害。微光狂热：生命低于40%时注射微光（每30秒一次），4秒内攻速+40%，并回复20%最大生命。
+（攻击间隔 1.2 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>链锯冲撞：冲向目标，在前方扇形里锯3次，每次造成40 + 60% 攻击力物理伤害并减速30%，持续1.5秒。
+（冷却 9 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>锯刃格挡：竖起链锯格挡：获得100+80% 攻击力护盾，持续2.5秒，期间减伤20%。
+（冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>泥奔者重击：把目标挑起举过头顶，造成120 + 190% 攻击力物理伤害并击飞1.1秒，期间回复15%最大生命；再狠狠砸下，对前方周围敌人造成70 + 110% 攻击力物理伤害。
+（冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_renni.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
           <t>刀疤</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Scar</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>tft_scar</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>上单</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>长矛刺击造成100% 攻击力物理伤害。野火冲刺：每6秒下一击踩滑板冲刺，造成40 + 110% 攻击力+30% 法强伤害，回复上次冲刺以来所受伤害的25%。监察：生命不低于50%时减伤20%，否则10%。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>水坑狙击惊喜：向最近的3名敌人各扔一颗炸弹，造成70 + 80% 法强魔法伤害并晕眩1秒；自己回复60 + 60% 法强生命。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>长矛横扫：长矛横扫前方，造成50 + 80% 攻击力+2% 最大生命物理伤害并击退敌人。
 （冷却 9 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>野火突袭：踩滑板冲向敌人，途中丢下两颗燃烧弹（各40 + 40% 法强魔法伤害）；落地爆炸，周围敌人受到120 + 100% 法强魔法伤害并被击飞0.5秒，之后4秒内减伤40%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="3" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_scar.md</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>远古石甲虫</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Krug</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>tft_krug</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>岩拳砸地，造成100% 攻击力物理伤害。碎岩重生：每条命第一次受到致命伤害时碎成石堆0.75秒，再以小石甲虫站起：生命35%、攻速+30%，嘲讽周围敌人1秒（至少隔60秒）。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>岩之摇滚：获得80 + 60% 法强的护盾（4秒），缩成石球滚向目标，造成40 + 140% 攻击力 + 6%最大生命物理伤害并击退。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>坚岩外壳：缩进巨石2.5秒：护甲+40、魔抗+30；周围的敌人被嘲讽0.75秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>远古崩落：一跃而起（不可选中、免疫控制），砸进敌方英雄身边：周围敌人受到70 + 100% 攻击力 + 6%最大生命物理伤害并被击飞0.8秒；随后落石再造成40 + 4%最大生命物理伤害。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_krug.md</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="3" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L186"/>
+  <autoFilter ref="A1:L187"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12423,6 +12483,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$188</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L187"/>
+  <dimension ref="A1:L188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.24）
+          <t>俄洛伊附加包（league_illaoi v0.2.25）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -1720,7 +1720,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>克烈附加包（league_kled v0.1.0）
+          <t>克烈附加包（league_kled v0.1.1）
 斯嘎尔的血：本包自己记斯嘎尔的血：这条命第一次骑上 sk_hp + 攻击 sk_ad%，勇气满了重新骑上 re_hp + 攻击 re_ad%，骑着时受到的伤害从这里扣，扣完就让他下马
 捕熊夹的绳子：被夹住的英雄离克烈超过 q_break，绳子断，不拽
 下马的样子：整身步行：下马时站着、跑着、挨打和普攻第一帧都画步行的克烈</t>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.17）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.18）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -6313,7 +6313,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>加里奥附加包（league_galio v0.1.1）
+          <t>加里奥附加包（league_galio v0.1.2）
 主包 league 保持纯数据。用户选了「主包数据 + 附加包」。这个附加包用原生代码做主包数据做不到的三件事： - 杜朗护盾的被动护盾按「多久没挨打」给：主包里加里奥普攻时给护盾（每 12 秒最多一次），因为数据读不到「多久没受伤」。 附加包的被动 league_galio:colossus 记下他最后一次受伤的 tick，12 秒没受伤就给 90 + …</t>
         </is>
       </c>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.23）
+          <t>塞拉斯附加包（league_sylas v0.2.25）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.7）
+          <t>悠米附加包（league_yuumi v0.1.8）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11776,527 +11776,585 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
+          <t>史密奇</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Smeech</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>tft_smeech</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>双爪轮流挥抓，造成100% 攻击力物理伤害。伏击专家：暴击率25%；技能也能暴击，技能暴击造成220%伤害。
+（攻击间隔 0.9 秒 · 攻击距离 23000）</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>废铁黑客：跳向范围内生命最低的敌人，连斩3次，每次造成25 + 70% 攻击力物理伤害；目标阵亡则再跳一次，伤害为70%。
+（冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>拆解：双爪撕扯目标，造成45 + 110% 攻击力物理伤害，并使其护甲降低30%，持续4秒。
+（冷却 8 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>废铁狂潮：1.2秒内不受控制、减伤30%，接连跳斩最多5名未被斩过的敌人，每次造成55 + 100% 攻击力物理伤害并获得10%暴击率（5秒）。
+（冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_smeech.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L187"/>
+  <autoFilter ref="A1:L188"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12484,6 +12542,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L189"/>
+  <dimension ref="A1:L190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.26）
+          <t>俄洛伊附加包（league_illaoi v0.2.27）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.19）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.20）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7274,7 +7274,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.26）
+          <t>塞拉斯附加包（league_sylas v0.2.27）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.9）
+          <t>悠米附加包（league_yuumi v0.1.10）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -12411,8 +12411,66 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>斯特卜</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Steb</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>tft_steb</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>辅助</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
+（攻击间隔 1.5 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
+（冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
+（冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
+（冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L189"/>
+  <autoFilter ref="A1:L190"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12602,6 +12660,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.21）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.22）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -6000,9 +6000,9 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>阿兹尔附加包（league_azir v0.1.4）
+          <t>阿兹尔附加包（league_azir v0.1.5）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
-禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害和击退还是数据那道墙的
+禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害还是数据那道墙的。墙停下后再立 3 秒，敌方英雄走不过去；墙打中的敌人被带到墙停下的地方外面（正…
 沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…</t>
         </is>
       </c>
@@ -11334,7 +11334,7 @@
       <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5419,19 +5419,21 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>大闹天宫：伸长金箍棒旋转2秒，每0.25秒造成10 + 35% 攻击力外加英雄2%最大生命的物理伤害，第一下击飞0.6秒；8秒内可再转一次。没有分身时召出一个一起转。身边有敌方英雄时才放。
+          <t>大闹天宫：伸长金箍棒旋转2秒，每0.25秒造成10 + 35% 攻击力外加英雄2%最大生命的物理伤害，第一下击飞0.6秒；8秒内可再转一次。身边有敌方英雄时才放。
 （冷却 60 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>悟空附加包（league_wukong v0.1.1）
-金刚不坏的回血：每 5 秒回复最大生命的 0.35%，每层再多 0.35%（叠满 5 层 2.1%，英雄联盟）</t>
+          <t>悟空附加包（league_wukong v0.1.2）
+金刚不坏的回血：每 5 秒回复最大生命的 0.35%，每层再多 0.35%（叠满 5 层 2.1%，英雄联盟）
+W 的分身：本包在分身站的地方每格画一次：站着、出手，他开大时跟着转
+放 W：W 好了、射程内有敌方英雄时替他按（英雄联盟里 W 开团、接大招）</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -11267,12 +11267,13 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>塔姆附加包（league_tahmkench v0.1.2）
+          <t>塔姆附加包（league_tahmkench v0.1.3）
 培养品味的层数：每个敌方英雄各自记层（最多 3 层，5 秒），鱼标记按那个人自己的层数画
 巨舌鞭笞打 3 层的人：大招冷却好了就留着层数给大招吞，否则眩晕并吃掉层数
 厚实表皮：真的灰色生命：受到伤害的 30% 存起来（最多最大生命的一半），3 秒没挨英雄打就慢慢回成生命；被两名敌方英雄围住、或生命低于 40% 且身边有敌人时，把存的全部加 160 + …
 大快朵颐吞谁：按真实生命判断：生命低于 35% 且附近有敌人、或 1 秒内掉了四分之一以上生命、或被控住且身边两个敌人的队友（生命最低的先）；没有就吞近身 3 层的敌人；都没有就不放（改成普攻）
 吞着人的时候：吞着队友往远离敌人的方向走，吞着敌人往队友那边走；吐出时把人放到他身边（队友在他背后，敌人在他前面）
+吞开着法术护盾的敌人：免疫控制的敌人吞不了：挑人时跳过，探针落下时再查一次（希维尔开着法术护盾，用户 2026-10-29「希维尔开盾时塔姆可以吞」）；大招照样用掉，同英雄联盟里被法术护盾挡下
 深渊潜航：同样的条件，再加上落点附近的敌方英雄不多于身边队友加一、他自己生命不低于 30%；不放时改成普攻或回到队友身边</t>
         </is>
       </c>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.22）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.23）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -2298,8 +2298,9 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>兰博附加包（league_rumble v0.1.0）
-过热的样子：整身红温：过热期间（league_rumble_oh）站、跑、挨打、阵亡都换成 oh_idle / oh_run / oh_hit / oh_dead，普攻第一 tick 换成 …</t>
+          <t>兰博附加包（league_rumble v0.2.0）
+过热的样子：整身红温：过热期间（league_rumble_oh）站、跑、挨打、阵亡都换成 oh_idle / oh_run / oh_hit / oh_dead，普攻第一 tick 换成 …
+纵火盛宴：边走边喷：只站着端平炮口（8 tick），之后照常每 0.25 秒喷一下、能走；喷火时站着、跑着都是炮口喷着火的样子（q_stand / q_run）。锥形还是从他当时的位置朝 …</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5294,7 +5295,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.22）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.23）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -2875,10 +2875,11 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>沃利贝尔附加包（league_volibear v0.1.0）
+          <t>沃利贝尔附加包（league_volibear v0.2.0）
 狂雷渐起的闪电（满 5 层）：打目标和离它最近的 4 个敌人（22000 以内，防御塔不算），每个身上闪一下
 暴怒撕咬的标记：标记记在被咬的那个英雄身上（8 秒）：再咬同一个人才是第二口；第二口回复再加已损失生命的 12%
-天声震落：另外让落点 55000 以内的敌方防御塔 4 秒不能攻击（塔身上缠着电光）</t>
+天声震落：另外让落点 55000 以内的敌方防御塔 4 秒不能攻击（塔身上缠着电光）
+天声震落后的 12 秒风暴形态：他整个人变成雷电蓝：白毛变浅电蓝、腿变深蓝，符文和冰晶爪子发亮青光，外圈一道电蓝描边；形态结束或阵亡时变回来</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5295,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.24）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.25）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -6003,7 +6004,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>阿兹尔附加包（league_azir v0.1.5）
+          <t>阿兹尔附加包（league_azir v0.1.6）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
 禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害还是数据那道墙的。墙停下后再立 3 秒，敌方英雄走不过去；墙打中的敌人被带到墙停下的地方外面（正…
 沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…</t>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>剑魔 W 锁链附加包（league_aatrox_chain v0.2.3）
+          <t>剑魔 W 锁链附加包（league_aatrox_chain v0.2.4）
 主包 league 保持纯数据。主包里剑魔的 W「恶火束链」：锁链停在第一个敌人身上（40 + 40% 攻击力、减速 25% 1.5 秒）； 锁链旁边有敌方英雄时在落点放圈，1.5 秒后那个英雄再受一次伤害、被拉向剑魔。League 的两条数据写不出来： 走出圈锁链就断，以及拉回的是圈的中心。这个附加包用原生代码照 League 原版做： - 只锁锁链真正…</t>
         </is>
       </c>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>莫德凯撒附加包（league_mordekaiser v0.1.3）
+          <t>莫德凯撒附加包（league_mordekaiser v0.1.4）
 主包 league 保持纯数据。用户要了附加包；问到「R做不了独特空间吗？」，选了「放逐两人 + 附加包算单挑」，并且「嘲讽不做」（和英雄联盟一样）。这个附加包用原生代码做主包数据做不到的两件事： - 轮回绝境（R）真的把人拖进领域：主包里 R 是诅咒 7 秒、按固定数值偷属性、跑远了被拉回。附加包的 league_mordekaiser:realm 在 …</t>
         </is>
       </c>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>亚恒附加包（league_zaahen v0.1.0）
+          <t>亚恒附加包（league_zaahen v0.1.1）
 不落之志（果决）：每一下打在敌方英雄身上的伤害都算一层（普攻、Q 的每一斩、上挑、W、E、R），每层攻击力 +det_pct%，最多 det_n 层、叠满翻倍；最后一下之后 det_t 拍没打中英…
 叠满后的复活：叠满时受到致命伤害就倒下：生命停在 1，放逐 rv_rise 拍（无敌、选不中、不能行动），慢慢回到最大生命 rv_hp%，再展翼站起来、果决叠满；每 rv_cd 拍一次。别人给…
 赤金突袭（E）：有自己的技能位：每 e_cd 拍一次，e_reach 内有敌方英雄、他能行动时，朝最近的那个冲过去（最多 e_dash，停在让对方正好落在外圈的地方），落地绕身斩：内圈 e_r0…
@@ -4085,7 +4085,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>盲僧 W 位移附加包（league_leesin_hop v0.1.10）
+          <t>盲僧 W 位移附加包（league_leesin_hop v0.1.11）
 主包 league 保持纯数据。主包的李青不能「摸眼」：R 身后没人时直接冲过目标落到他身后回旋踢，W 并进了 E、不冲刺。 英雄联盟手游里李青的 W 不用插眼就能冲到一个点，这个附加包照这个做（不画眼）： - 回旋踢（照高手的打法，v0.1.6）：R 时目标身后没有别的敌方英雄（有人就照旧正面踢进人堆），第 7 tick 先定往哪踢—— 踢回自己队伍那边…</t>
         </is>
       </c>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>瑟庄妮附加包（league_sejuani v0.1.0）
+          <t>瑟庄妮附加包（league_sejuani v0.1.1）
 永冻领域（霜冻叠满冻住）：层数挂在每个敌方英雄自己身上（league_sejuani_frost），某一个满 f_n 层才冻住它
 碎冰：她打中的英雄正被眩晕或击飞就碎冰，队友控的也算；每个英雄单独冷却 sh_cd
 冰霜护甲：护甲在身时每 tick 清掉她身上所有减速（免疫减速，副本不给韧性）；受到伤害也算进入战斗
@@ -6824,7 +6824,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>洛克附加包（league_locke v0.1.0）
+          <t>洛克附加包（league_locke v0.1.1）
 圣银穿心（被动）：再加目标已损失生命 p_miss% 的魔法伤害
 灵焰仪式（W，并入被动）：每秒烧当前生命 w_cost%（不会把自己烧死），结束时补回烧掉的 w_back%
 万魔狱（R）的处决：被标记的英雄当前生命低于最大生命 r_exec%（每层封印 +r_exec_step%）就处决

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -6317,7 +6317,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>加里奥附加包（league_galio v0.1.2）
+          <t>加里奥附加包（league_galio v0.1.3）
 主包 league 保持纯数据。用户选了「主包数据 + 附加包」。这个附加包用原生代码做主包数据做不到的三件事： - 杜朗护盾的被动护盾按「多久没挨打」给：主包里加里奥普攻时给护盾（每 12 秒最多一次），因为数据读不到「多久没受伤」。 附加包的被动 league_galio:colossus 记下他最后一次受伤的 tick，12 秒没受伤就给 90 + …</t>
         </is>
       </c>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.11）
+          <t>悠米附加包（league_yuumi v0.1.12）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L191"/>
+  <dimension ref="A1:L192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>阿兹尔附加包（league_azir v0.1.5）
+          <t>阿兹尔附加包（league_azir v0.1.6）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
 禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害还是数据那道墙的。墙停下后再立 3 秒，敌方英雄走不过去；墙打中的敌人被带到墙停下的地方外面（正…
 沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…</t>
@@ -12418,121 +12418,179 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
+          <t>艾达丝</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Idas</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>tft_idas</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>辅助</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
+（攻击间隔 1.4 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
+（冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
+（冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
+（冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L191"/>
+  <autoFilter ref="A1:L192"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12724,6 +12782,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId191"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.28）
+          <t>俄洛伊附加包（league_illaoi v0.2.29）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.25）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.26）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7278,7 +7278,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.28）
+          <t>塞拉斯附加包（league_sylas v0.2.29）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.12）
+          <t>悠米附加包（league_yuumi v0.1.13）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L192"/>
+  <dimension ref="A1:L193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.29）
+          <t>俄洛伊附加包（league_illaoi v0.2.30）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.26）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.27）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7278,7 +7278,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.29）
+          <t>塞拉斯附加包（league_sylas v0.2.30）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.13）
+          <t>悠米附加包（league_yuumi v0.1.14）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -12361,237 +12361,295 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
+          <t>迭嘉</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Daeja</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>tft_daeja</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
+（攻击间隔 1.2 秒 · 攻击距离 60000）</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
+（冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
+（冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
+（冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L192"/>
+  <autoFilter ref="A1:L193"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12784,6 +12842,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId192"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.30）
+          <t>俄洛伊附加包（league_illaoi v0.2.31）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.27）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.28）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7278,7 +7278,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.30）
+          <t>塞拉斯附加包（league_sylas v0.2.31）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.14）
+          <t>悠米附加包（league_yuumi v0.1.15）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11781,875 +11781,933 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
+          <t>石傲玉</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Shi Oh Yu</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>tft_shiohyu</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>上单</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>左右爪交替挥击，第3下造成20 + 130% 攻击力物理伤害。玉石之肤：生命低于50%时化作玉石，减伤40%（3秒，冷却30秒）。
+（攻击间隔 1.1 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>玉拳连打：冲向目标连打4拳，每拳造成15 + 45% 攻击力物理伤害。
+（冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>震地：一拳砸地，周围敌人受到50 + 110% 攻击力物理伤害，被击飞0.75秒并减速35%。
+（冷却 9 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>玉龙形态：减伤35%、免疫控制，接下来3次普攻各造成40 + 175% 攻击力伤害：第1下晕眩1秒；第2下为真实伤害；第3下打出直线冲击波，晕眩沿线敌人。
+（冷却 25 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_shiohyu.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
           <t>远古石甲虫</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Krug</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_krug</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>岩拳砸地，造成100% 攻击力物理伤害。碎岩重生：每条命第一次受到致命伤害时碎成石堆0.75秒，再以小石甲虫站起：生命35%、攻速+30%，嘲讽周围敌人1秒（至少隔60秒）。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>岩之摇滚：获得80 + 60% 法强的护盾（4秒），缩成石球滚向目标，造成40 + 140% 攻击力 + 6%最大生命物理伤害并击退。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>坚岩外壳：缩进巨石2.5秒：护甲+40、魔抗+30；周围的敌人被嘲讽0.75秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>远古崩落：一跃而起（不可选中、免疫控制），砸进敌方英雄身边：周围敌人受到70 + 100% 攻击力 + 6%最大生命物理伤害并被击飞0.8秒；随后落石再造成40 + 4%最大生命物理伤害。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_krug.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>史密奇</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Smeech</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_smeech</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>双爪轮流挥抓，造成100% 攻击力物理伤害。伏击专家：暴击率25%；技能也能暴击，技能暴击造成220%伤害。
 （攻击间隔 0.9 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>废铁黑客：跳向范围内生命最低的敌人，连斩3次，每次造成25 + 70% 攻击力物理伤害；目标阵亡则再跳一次，伤害为70%。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>拆解：双爪撕扯目标，造成45 + 110% 攻击力物理伤害，并使其护甲降低30%，持续4秒。
 （冷却 8 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>废铁狂潮：1.2秒内不受控制、减伤30%，接连跳斩最多5名未被斩过的敌人，每次造成55 + 100% 攻击力物理伤害并获得10%暴击率（5秒）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_smeech.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>诺姆希</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Nomsy</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_nomsy</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>吐出小火团，造成100% 攻击力物理伤害。龙神之躯：生命值低于40%时每秒回复3%最大生命值。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>火球！：抛出大火球，爆炸造成90 + 63% 法强魔法伤害，再弹出2颗小火球打附近的敌人，各造成55%伤害。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>龙息：向前喷出扇形龙息，造成55 + 36% 法强魔法伤害并灼烧2秒，魔抗降低20%（4秒）。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>龙神飞升：飞上天空（减伤50%、免疫控制），降下10颗火球，各造成60 + 35% 法强魔法伤害；落地后攻速+30%、法强+25%（5秒）。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_nomsy.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="3" t="inlineStr">
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>迭嘉</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Daeja</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>tft_daeja</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
 （攻击间隔 1.2 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L193"/>
+  <autoFilter ref="A1:L194"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12843,6 +12901,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId193"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$195</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.31）
+          <t>俄洛伊附加包（league_illaoi v0.2.32）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.28）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.29）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7278,7 +7278,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.31）
+          <t>塞拉斯附加包（league_sylas v0.2.32）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.15）
+          <t>悠米附加包（league_yuumi v0.1.16）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11955,759 +11955,817 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
+          <t>赛芬</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Sy'fen</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>tft_syfen</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>翼爪和甩尾交替攻击，造成100% 攻击力物理伤害。幽影低语：他的伤害让敌人缩小4秒（护甲、魔抗-20%）；打缩小的敌人叠怒气，每层+5攻击力，最多5层。
+（攻击间隔 1 秒 · 攻击距离 30000）</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>噬咬：扑上去咬住目标，造成40 + 160% 攻击力物理伤害，无视33%护甲，回复30 + 30% 攻击力生命。
+（冷却 8 秒 · 施放距离 32000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>翼刃横扫：张开双翼横扫身边，造成40 + 100% 攻击力物理伤害并减速30%（1.5秒）。
+（冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>暴走：龙吼后冲向最远的敌方英雄（免疫控制），路上的敌人受到30 + 140% 攻击力物理伤害并晕眩1.25秒，最后猛咬一口造成60 + 235% 攻击力物理伤害，无视33%护甲。
+（冷却 40 秒 · 施放距离 72000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_syfen.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>诺姆希</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Nomsy</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_nomsy</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>吐出小火团，造成100% 攻击力物理伤害。龙神之躯：生命值低于40%时每秒回复3%最大生命值。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>火球！：抛出大火球，爆炸造成90 + 63% 法强魔法伤害，再弹出2颗小火球打附近的敌人，各造成55%伤害。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>龙息：向前喷出扇形龙息，造成55 + 36% 法强魔法伤害并灼烧2秒，魔抗降低20%（4秒）。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>龙神飞升：飞上天空（减伤50%、免疫控制），降下10颗火球，各造成60 + 35% 法强魔法伤害；落地后攻速+30%、法强+25%（5秒）。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_nomsy.md</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="3" t="inlineStr">
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>迭嘉</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Daeja</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_daeja</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
 （攻击间隔 1.2 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="3" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L194"/>
+  <autoFilter ref="A1:L195"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12902,6 +12960,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId194"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.32）
+          <t>俄洛伊附加包（league_illaoi v0.2.33）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.29）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.30）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7278,7 +7278,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.32）
+          <t>塞拉斯附加包（league_sylas v0.2.33）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.16）
+          <t>悠米附加包（league_yuumi v0.1.17）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -12477,295 +12477,353 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
+          <t>索姆</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Sohm</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>tft_sohm</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>中单</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>吐出水泡弹，造成100% 攻击力物理伤害。碧波之力：每次施放技能叠一层潮水（6秒，最多5层），每层法强+9%、攻速+9%。
+（攻击间隔 1.5 秒 · 攻击距离 55000）</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>潮涌：朝没开花的敌人冲出一道潮涌，沿途敌人受到95 + 65% 法强魔法伤害，目标头上开出水之花（15秒）；带花的敌人倒下，花跳到附近的敌人。
+（冷却 4 秒 · 施放距离 62000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>海潮护佑：给附近生命比例最低的队友套上95 + 65% 法强的水盾（3秒），攻速+25%。
+（冷却 8 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>潮汐绽放：所有水之花一齐绽放，每朵花周围的敌人受到180 + 90% 法强魔法伤害，花随之散去；没有花时在目标身上绽放。
+（冷却 35 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sohm.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
           <t>迭嘉</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Daeja</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_daeja</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
 （攻击间隔 1.2 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="3" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="3" t="inlineStr">
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L195"/>
+  <autoFilter ref="A1:L196"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -12961,6 +13019,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId193"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId195"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -6004,10 +6004,11 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>阿兹尔附加包（league_azir v0.1.6）
+          <t>阿兹尔附加包（league_azir v0.1.7）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
 禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害还是数据那道墙的。墙停下后再立 3 秒，敌方英雄走不过去；墙打中的敌人被带到墙停下的地方外面（正…
-沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…</t>
+沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…
+沙兵和他之间的线（用户 2026-10-30：「沙皇和召唤的士兵之间没连接线 LOL是有的」）：照英雄联盟（牵引半径 660 内的沙兵和阿兹尔之间连一道流沙光束）：他和 66000 内每个站着的沙兵之间连一条金色流沙线，沙粒朝沙兵流；沙兵还在升起、离他超过 66000、他死…</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.30）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.31）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -10278,7 +10278,7 @@
       <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -2617,10 +2617,10 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>提莫蘑菇附加包（league_teemo_shrooms v0.1.0）
+          <t>提莫蘑菇附加包（league_teemo_shrooms v0.2.0）
 蘑菇在地上多久：3 分钟（10800 tick），提莫阵亡也在；最多 9 个，再多收掉最早的
 扔、布好、踩发距离 8000、毒云 30000 内中毒 4 秒共 100 + 48% 法强、减速 40% 2 秒、画面：一样
-往哪扔：一样（没有改成往草丛扔）</t>
+往哪扔：打架时一样；不打架时往身边最近的草丛里种（0.2.0：R 留一次充能给打架，没埋过的草丛、不在自家基地）</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.31）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.32）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -11155,7 +11155,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -8304,7 +8304,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>阿克尚扩展包（league_akshan v0.2.2）
+          <t>阿克尚扩展包（league_akshan v0.2.3）
 无所不用（第 3 下）：每个目标分别数 3 下（英雄联盟）
 恩怨相抵的子弹：按目标已损失生命：最低伤害到 3 倍（少 67% 生命时封顶，英雄联盟）
 恩怨相抵什么时候开火：存的子弹打得死射程里血最少的英雄、或者他快跑出射程，就提前开火

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.32）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.33）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5427,7 +5427,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>悟空附加包（league_wukong v0.1.2）
+          <t>悟空附加包（league_wukong v0.1.3）
 金刚不坏的回血：每 5 秒回复最大生命的 0.35%，每层再多 0.35%（叠满 5 层 2.1%，英雄联盟）
 W 的分身：本包在分身站的地方每格画一次：站着、出手，他开大时跟着转
 放 W：W 好了、射程内有敌方英雄时替他按（英雄联盟里 W 开团、接大招）</t>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -693,7 +693,7 @@
         <is>
           <t>青钢影钩墙附加包（league_camille_wall v0.4.9）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个单独的附加包里。 装上后，青钢影的 E「钩索」钩墙、地图四边和防御塔，不再钩小兵、野怪；英雄、树林、草丛也不钩（墙就在树林里）。
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 卡蜜尔 E：E 好了、60000 内有敌方英雄就按，目标是最近的那个（钩墙附加包的 E 射程是 85000，取小的）。钩索、钩墙、冲向敌人照旧由主包 / 钩墙附加包决定</t>
         </is>
       </c>
@@ -756,7 +756,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>科加斯附加包（league_chogath v0.1.1）
+          <t>科加斯附加包（league_chogath v0.1.2）
 盛宴的层数：死后原样补回，层数一局里只增不减
 什么时候放盛宴：读射程内敌方英雄的生命、护盾、免死和受到伤害的增减，一口吃得死才放（几个时吃生命 + 护盾最少的，AI 没想放也放）；吃不死时 AI 想放就改成普攻那个人</t>
         </is>
@@ -1214,7 +1214,7 @@
         <is>
           <t>格温被动附加包（league_gwen v0.1.1）
 主包 league 保持纯数据。数据里能读目标最大生命值的只有真实伤害，读不到法强，所以主包格温的被动「千穿百孔」对英雄造成 1% 最大生命值的真实伤害（用户：「这个可以改rust」）。这个附加包用原生代码做成英雄联盟的样子： - 百分比最大生命值魔法伤害：原生效果 league_gwen:cuts 代替主包里那段真实伤害。被动每次打到敌方英雄（普攻、E …
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -1594,7 +1594,7 @@
         <is>
           <t>凯尔升阶附加包：按真实等级升阶、死后不掉（league_kayle v0.2.0）
 这个附加包把主包的凯尔换成 override/ 里的副本（make_override.py 生成），和主包有两处不同：
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>目标标记附加包（league_marks v0.1.0）
+          <t>目标标记附加包（league_marks v0.1.1）
 凯南 雷缚印：每个英雄各记各的（6 秒），同一个人第三层眩晕 1.25 秒，7 秒内再次只有 0.5 秒</t>
         </is>
       </c>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>莫德凯撒附加包（league_mordekaiser v0.1.4）
+          <t>莫德凯撒附加包（league_mordekaiser v0.1.5）
 主包 league 保持纯数据。用户要了附加包；问到「R做不了独特空间吗？」，选了「放逐两人 + 附加包算单挑」，并且「嘲讽不做」（和英雄联盟一样）。这个附加包用原生代码做主包数据做不到的两件事： - 轮回绝境（R）真的把人拖进领域：主包里 R 是诅咒 7 秒、按固定数值偷属性、跑远了被拉回。附加包的 league_mordekaiser:realm 在 …</t>
         </is>
       </c>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>奥恩附加包（league_ornn v0.1.1）
+          <t>奥恩附加包（league_ornn v0.1.2）
 熔岩柱：真的地形：立在裂隙的尽头 4 秒，立起时把站在上面的单位推开，之后谁都走不进去（两边的英雄、小兵、野怪，他自己也算）
 E 的地震：撞上柱子或墙才地震：撞上目标的那一刻柱子够近（30000 加上柱子和他的半径），或冲撞方向 14000 内是墙（卡蜜尔附加包的墙格、地图的四边）；撞上的柱子随之碎掉
 易碎：记在每个英雄身上：只有带着易碎的英雄被他普攻打中才引爆（最大生命 8% 的真实伤害、击飞、从他身边击退）
@@ -2172,7 +2172,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>雷克顿低血怒气附加包（league_renekton v0.1.1）
+          <t>雷克顿低血怒气附加包（league_renekton v0.1.2）
 主包 league 保持纯数据。数据读不到当前生命，所以主包雷克顿的被动「怒之领域」只做了怒气本身：普攻和技能命中积攒怒气 （雷克顿身上的一条阶梯，最多 5 层，8 秒没积攒就清空），满层时下一个技能被强化并耗尽怒气。英雄联盟里生命低于一半时怒气获取 +50%，这一条要读生命，放在这个附加包里： - 原生被动 league_renekton:anger 每…</t>
         </is>
       </c>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>提莫蘑菇附加包（league_teemo_shrooms v0.2.0）
+          <t>提莫蘑菇附加包（league_teemo_shrooms v0.2.1）
 蘑菇在地上多久：3 分钟（10800 tick），提莫阵亡也在；最多 9 个，再多收掉最早的
 扔、布好、踩发距离 8000、毒云 30000 内中毒 4 秒共 100 + 48% 法强、减速 40% 2 秒、画面：一样
 往哪扔：打架时一样；不打架时往身边最近的草丛里种（0.2.0：R 留一次充能给打架，没埋过的草丛、不在自家基地）</t>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>蛮王残血开大附加包（league_tryndamere_rage v0.2.0）
+          <t>蛮王残血开大附加包（league_tryndamere_rage v0.2.1）
 主包 league 保持纯数据。数据读不到当前生命，主包里蛮王的 R 由 AI 在敌方英雄 60000 内时放出、待命 900 tick （没用上就退还冷却）；待命期间他每次普攻查一次：被两名以上敌方英雄贴身、或连续 5 次检查都挨了打，才爆发「无尽怒火」。 SDK 模拟里这样开大时他的生命中位数是 75%，一半的阵亡发生在大招待命却没认出危险的时候。用户…</t>
         </is>
       </c>
@@ -2812,7 +2812,7 @@
         <is>
           <t>弗拉基米尔残血血池附加包（league_vladimir_pool v0.2.0）
 主包 league 保持纯数据。数据读不到当前生命，主包里弗拉基米尔的 W「血红之池」是自动的：他身上一直跑着一个每 3 tick 看一次的轮询， 看到 league_vladimir_w_go 就化成血池（2 秒不可选取、脚下敌人减速吸血、20 秒冷却）；w_go 由普攻里的危险信号加上—— 两名以上敌方英雄贴身，或连续两次检查都挨了打。用户选了「危险信…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 弗拉基米尔 R（v0.4.0）：60000 内最近被我方打过的敌方英雄生命不到一半，或他身边 26000（血云半径）内有两个以上敌方英雄；生命比例最低的在前</t>
         </is>
       </c>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>目标标记附加包（league_marks v0.1.0）
+          <t>目标标记附加包（league_marks v0.1.1）
 黛安娜 E 月光冲击：E 冲向的目标身上带月光时才再冲一次；冲到后所有敌人身上的月光都消耗掉</t>
         </is>
       </c>
@@ -3455,7 +3455,7 @@
         <is>
           <t>斩杀附加包：伊芙琳、阿卡丽、锐雯（league_executes v0.2.0）
 伊芙琳 R：150 + 75% 法强，对生命不高于 30% 的目标 ×2.4
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 费德提克 R：他生命 ≥ 40%；80000 内的敌方英雄脚下 45000 内有两个以上（挑人最多的一处，一样多挑残血），或只有一个但生命不到 40%；那里不在敌方塔下；那里 60000 内的…</t>
         </is>
       </c>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>艾翁附加包（league_ivern v0.1.0）
+          <t>艾翁附加包（league_ivern v0.1.1）
 揠苗助攻：草丛记在他长草的地方（半径 w_r、w_t tick 后枯掉，他死了也还在）；站在里面的队友每 tick 续上攻击 +w_atk%；站在里面的每个英雄（两边都算）挂 2 tick…
 联动：雷恩加尔（league_rengar_bush 0.1.2 起）身上有这个标记就算站在草丛里，能扑；奇亚娜（league_qiyana 0.2.1 起）突进落地时身上有它就算身边…</t>
         </is>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.2）
+          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.3）
 易：每一次英雄击杀和助攻，阿尔法突袭和冥想的剩余冷却减 70%，无极剑道开着时再延长 4 秒；每次普攻阿尔法突袭冷却减 1 秒；无极剑道期间免疫减速</t>
         </is>
       </c>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.33）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.34）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
 附身后的招式：按那个英雄的类别换成五套招式之一：近战（重斩、震地减速、冲锋眩晕）、射手（远程射击、穿透射击、三连射）、法师（法球、溅射爆发、定身）、辅助（远程射击、治疗周围友方英雄、减速周围敌…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>悟空附加包（league_wukong v0.1.3）
+          <t>悟空附加包（league_wukong v0.1.4）
 金刚不坏的回血：每 5 秒回复最大生命的 0.35%，每层再多 0.35%（叠满 5 层 2.1%，英雄联盟）
 W 的分身：本包在分身站的地方每格画一次：站着、出手，他开大时跟着转
 放 W：W 好了、射程内有敌方英雄时替他按（英雄联盟里 W 开团、接大招）</t>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>库奇智能火箭 + 脱身方向附加包（league_corki v0.1.0）
+          <t>库奇智能火箭 + 脱身方向附加包（league_corki v0.1.1）
 主包 league 保持纯数据、全平台可用；数据读不到敌人站在哪、血量多少，主包的火箭朝 AI 选的英雄直线飞（Q 炸到人时改打「刚被打过的 英雄」），瓦尔基里俯冲只能「背对身边那个英雄往后跳」，不看墙、塔和队友。英雄联盟里高手把火箭打向能炸到最多人的地方、大火箭留给残血， 俯冲往安全的地方飞——要读每个单位的位置和血量，只能用原生代码，所以放在这个附加包…</t>
         </is>
       </c>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>加里奥附加包（league_galio v0.1.3）
+          <t>加里奥附加包（league_galio v0.1.4）
 主包 league 保持纯数据。用户选了「主包数据 + 附加包」。这个附加包用原生代码做主包数据做不到的三件事： - 杜朗护盾的被动护盾按「多久没挨打」给：主包里加里奥普攻时给护盾（每 12 秒最多一次），因为数据读不到「多久没受伤」。 附加包的被动 league_galio:colossus 记下他最后一次受伤的 tick，12 秒没受伤就给 90 + …</t>
         </is>
       </c>
@@ -6632,10 +6632,10 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>卡特琳娜附加包（league_katarina v0.1.0）
+          <t>卡特琳娜附加包（league_katarina v0.1.1）
 瞬步：另外瞬步一好就自己判断：射程内哪把匕首旁有敌方英雄就跳过去（那里生命比例最低的英雄优先），落地捡刀旋斩、冷却缩短，接着跳下一把——匕首循环；生命低于 30% 而身边有敌方英雄时，…
 贪婪：她参与的每一次英雄击杀（击杀或助攻）都刷新，几个人同时阵亡各算一次
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …
 卡特琳娜 R：她生命 ≥ 30%、自己不在敌方塔下（目标残血除外）；25000 内的敌方英雄，身边 50000 内有两个以上，或目标生命不到一半</t>
         </is>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>洛克附加包（league_locke v0.1.1）
+          <t>洛克附加包（league_locke v0.1.2）
 圣银穿心（被动）：再加目标已损失生命 p_miss% 的魔法伤害
 灵焰仪式（W，并入被动）：每秒烧当前生命 w_cost%（不会把自己烧死），结束时补回烧掉的 w_back%
 万魔狱（R）的处决：被标记的英雄当前生命低于最大生命 r_exec%（每层封印 +r_exec_step%）就处决
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>目标标记附加包（league_marks v0.1.0）
+          <t>目标标记附加包（league_marks v0.1.1）
 拉克丝 光芒四射：光芒留在被技能打中的敌人身上（5 秒），普攻打中带光芒的人才引爆 50 + 35% 法强的魔法伤害</t>
         </is>
       </c>
@@ -7087,7 +7087,7 @@
 E 送给谁：送给最危险的队友：身边有敌方英雄的队友里，近一秒受到的伤害比例 × 2 + 已损失生命比例最高的；她自己身边有敌人而且更危险时留给自己
 R 什么时候放：同主包；每个人能不能被冲击波打死照样算（按他的魔抗：伤害 × 100 / (100 + 魔抗)），写进日志（v0.1.0 是「2 个敌方英雄或能打死 1 个」，用户：「发条的大招…
 补兵：走上去补刀（v0.2.0）：附近没有敌方英雄时，普攻距离内的小兵先打这一下打得死的、其次血最少的；60k 内的兵线走上去打；塔下要有己方小兵扛塔才去
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 奥莉安娜 E、基兰 E：在打架：她 / 他或射程内的队友 40000 内有敌方英雄（基兰也追射程内生命不到 40% 的）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 瑞兹 R（备好式）：逃命：生命不到 35% 而 60000 内有敌方英雄；去打架：照崔斯特的规则（身边没敌人、远处队友在打）。传到哪里由主包判断</t>
         </is>
       </c>
@@ -7344,7 +7344,7 @@
         <is>
           <t>辛德拉举小兵附加包（league_syndra v0.1.1）
 这个附加包把主包的辛德拉换成 override/ 里的副本（make_override.py 用 tools/kit/build_syndra.py 的 --native 生成：技能 一样，W 施放时在她身上挂 league_syndra_w_grab、在投掷目标身上挂 league_syndra_w_at；她身上有 league_syndra_w_uni…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 辛德拉 R：75000 内的敌方英雄生命不到 60%、被控住，或射程内有两个以上；主包再按法球数和控制决定立刻放还是待命 8 秒（没用上退还冷却）</t>
         </is>
       </c>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>泰隆「刺客之道」翻墙附加包（league_talon_vault v0.1.3）
+          <t>泰隆「刺客之道」翻墙附加包（league_talon_vault v0.1.4）
 什么时候翻：照旧，另外：残血（低于 35%）而身边有敌方英雄，或被围（身边敌方英雄 ≥ 2、比身边友方多、生命低于 70%）时；残血敌方英雄（≤ 60%）躲在墙后、他自己生命 ≥ 40% 时
 往哪翻：翻过墙：撤离时找背向敌人、16000 内的墙翻到另一边（落地后离敌人最远的那处）；追击时朝目标左右 35° 内找墙翻过去，落点要近 15000 以上、不翻进人堆
 冷却：同一个冷却（主包的 league_talon_e_cd），两种翻越不会连着出</t>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 崔斯特 R：只在主包会传送的局面按：他身边 75000 内没有敌方英雄、生命不低于 40%，而且离他 100000–340000 有队友 50000 内贴着敌方英雄（在打架）。之后揭示、引导…</t>
         </is>
       </c>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>亚索风之障壁附加包（league_yasuo_wall v0.1.0）
+          <t>亚索风之障壁附加包（league_yasuo_wall v0.1.1）
 主包没有 W：游戏里没有能挡掉飞行物的效果，只画一面墙显得奇怪，当时用户决定删掉。亚索也没有空的技能格，所以风墙全由原生代码做（被动 league_yasuo_wall:wall，不占技能格、没有施法动作）。</t>
         </is>
       </c>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>永恩 R 附加包（league_yone_r v0.1.0）
+          <t>永恩 R 附加包（league_yone_r v0.1.1）
 落在哪里：直线上离他最远的那个被斩中的英雄身后 6000（一个都没斩中就照主包，落在 90000 内最近的敌方英雄身后）
 拉人：落地后把斩中的英雄拉向他（每 tick 2000，每个最多 16000，停在他身前 6000）
 伤害、击飞、画面、Q3 连 R：一样</t>
@@ -8044,7 +8044,7 @@
         <is>
           <t>劫读血附加包（league_zed_mark v0.1.3）
 主包 league 保持纯数据。数据读不到生命也读不到伤害，所以主包里劫的两处是替代做法： - 被动「影忍法！灭魂劫」：英雄联盟里是攻击生命低于 50% 的英雄时附加其最大生命的伤害；主包改成「技能刚打中过英雄」后的下一次普攻（league_zed_cw_ready），附加 6% 最大生命真实伤害，10 秒一次。 - 大招「禁奥义！瞬狱影杀阵」：英雄联盟里…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -8377,7 +8377,7 @@
 武器在手里：整身换武器：主手是断魄 / 坠明 / 荧焰 / 折镜时，站着、跑着、挨打、出手的第一刻都画成那把武器在手里（只在游戏 0.6.4 上）
 打空换枪：先进先出的队列（英雄联盟）：打空的那把排到队尾，换上队列最前面的那把；W 换过手以后和固定循环不一样
 残血：另外生命低于 35%、副手是断魄、60000 内有看得见的敌方英雄时直接换上断魄（吸血），每 6 秒最多一次
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 厄斐琉斯 R（备好式，v0.4.0）：90000 内有敌方英雄就按：主包待命 6 秒，正被我方打的敌方英雄身边还有别人、或被控住才放，没用上缩短冷却</t>
         </is>
       </c>
@@ -8681,7 +8681,7 @@
 额外攻速：不变快；每 1% 换成 0.25% 攻击力（+40% 攻速 = +10% 攻击力）
 攻速减益：一样
 低语、第四发、装弹：一样
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.2）
+          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.3）
 金克丝：每一次英雄击杀和助攻（几个人同时阵亡也各算一次）</t>
         </is>
       </c>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>目标标记附加包（league_marks v0.1.0）
+          <t>目标标记附加包（league_marks v0.1.1）
 卡莎 体表活肤：每个英雄各记各的（4 秒）：普攻每次附加 18 + 9 × 层数 + 20% 法强的魔法伤害，同一个人第五层引爆 80 + 60% 攻击力 + 8% 最大生命的真实伤害</t>
         </is>
       </c>
@@ -8875,7 +8875,7 @@
 誓约者：开局绑定一名队友（辅助位优先，没有就最近的队友英雄，每条命出生时重新看），大招对誓约者施放
 命运的召唤：把誓约者拉进来保护、定身，然后逐 tick 飞向离她最近的敌方英雄现在的位置（90000 内，没有就两倍范围），到了就在脚下击飞周围敌人
 撕裂：另外按护甲算拔矛伤害，够杀就立刻拔（矛不够 3 根也拔）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 卡莉丝塔 E：主包「矛够了」的标记（league_kalista_e_ok）在、撕裂不在冷却（league_kalista_e_cd）：按下就是撕裂，不会空按</t>
         </is>
       </c>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 克格莫 R：R 好了、射程（130000）内有引擎接受的敌方英雄（主包 R 只打最近被我方打过的）就按，先挑生命比例最低的（大招打残血更痛）。一轮三发、之后锁 20 秒都是主包的数据。不限时…</t>
         </is>
       </c>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>目标标记附加包（league_marks v0.1.0）
+          <t>目标标记附加包（league_marks v0.1.1）
 厄运小姐 爱心一击：和上一枪打的不是同一个人就算新目标</t>
         </is>
       </c>
@@ -9259,7 +9259,7 @@
           <t>莎弥拉边走边射附加包（league_samira_r v0.1.0）
 R 期间：旋转连射，同时走向 90000 内生命 + 护盾最少的敌方英雄，走到 30000 内站住；被硬控时不走
 枪、伤害、生命偷取、画面：主包（一样）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 莎弥拉 R：R 好了、R 射程（50000）内有敌方英雄就按，目标是最近的那个。S 评价时这一下就放出炼狱扳机，不到 S 就备好 330 tick，期间到了 S 再放
 莎弥拉 E、Q（攒评价）：S 要连着换五种出手打中英雄（枪 / 剑普攻、Q、E 冲刺、落地的 W 旋转），一下打不中 9 秒就掉。R 不按时：60000 内有敌方英雄、她生命不低于 50%、目标身边的敌方…</t>
         </is>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 希维尔 E：60000 内的敌方英雄刚放了技能（20 tick 内技能冷却开始走），或她生命不到 40% 而 40000 内有敌方英雄</t>
         </is>
       </c>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.2）
+          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.3）
 崔丝塔娜：每一次英雄击杀和助攻都刷新（满层引爆照旧）</t>
         </is>
       </c>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.2）
+          <t>参与击杀附加包：金克丝、崔丝塔娜、易、图奇（league_takedowns v0.3.3）
 图奇：埋伏助攻也刷新；E 等到有人满 6 层毒、或这一爆能毒死人才引爆（v0.3.0），条件一满足下一箭就爆（v0.3.1）</t>
         </is>
       </c>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>薇恩圣银弩箭附加包（league_vayne_bolts v0.1.0）
+          <t>薇恩圣银弩箭附加包（league_vayne_bolts v0.1.1）
 主包 league 保持纯数据。数据分不清一次攻击打中的是谁，所以主包里圣银弩箭的两层记在薇恩自己身上：她轮流打两个人也会凑满 3 下，在第三个被打中的人身上爆。这个附加包用原生代码做成英雄联盟的样子：同一个目标连续挨 3 下才爆。</t>
         </is>
       </c>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>泽丽附加包：W 撞墙激光 + 被动偷盾（league_zeri v0.1.1）
+          <t>泽丽附加包：W 撞墙激光 + 被动偷盾（league_zeri v0.1.2）
 - W「强穿激光」的脉冲先打中小兵或野怪时才在那里化为长激光（小兵代替墙）； - 被动「内能迁转」的电击弹打中英雄时给自己一个小护盾（代替偷盾）。</t>
         </is>
       </c>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>布隆附加包（league_braum v0.1.1）
+          <t>布隆附加包（league_braum v0.1.2）
 Test build of Braum as in League (needs League of Legends Heroes): replaces the main pack's Braum so Concussive Blows stacks on each champion and his allies' attacks add stacks to…</t>
         </is>
       </c>
@@ -10151,7 +10151,7 @@
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 迦娜 E 风暴之眼（50000 内）：有危险的队友（生命不高于 50%，或身边 25000 内有 2 个以上敌方英雄）里生命比例最低的；都没危险就给离敌方英雄最近的（正在打的那个）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 迦娜 R：她或身边 40000 内的队友生命不到 35% 而 50000 内有敌方英雄，或两人以上生命不到 60% 而她身边有敌方英雄。对生命最低的那位放（治疗是她身边一圈，对谁放都一样）</t>
         </is>
       </c>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>烈娜塔附加包（league_renata v0.1.2）
+          <t>烈娜塔附加包（league_renata v0.1.3）
 物尽其用：队友真的打中它才引爆（普攻或技能）：魔法伤害 + 最大生命 3% 的真实伤害
 及时救难：英雄联盟的规则：给危急的队友（身边有敌方英雄，被硬控或生命不到 45%），5 秒内受到致命伤害就回满生命，3 秒内流失到 1；这 3 秒里参与击杀就保住，没参与就阵亡
 恶意收购的狂暴：真的转身打自己人：走向最近的队友（英雄优先），按他自己的攻击间隔、用他自己的攻击力打；打死队友的击杀和助攻算烈娜塔的（和英雄联盟一样）</t>
@@ -11149,7 +11149,7 @@
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 娑娜 W 回血（60000 内）：损失生命最多的队友
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 娑娜 W：她或 60000 内的队友生命不到 70%，射程内有敌方英雄</t>
         </is>
       </c>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>塔姆附加包（league_tahmkench v0.1.3）
+          <t>塔姆附加包（league_tahmkench v0.1.4）
 培养品味的层数：每个敌方英雄各自记层（最多 3 层，5 秒），鱼标记按那个人自己的层数画
 巨舌鞭笞打 3 层的人：大招冷却好了就留着层数给大招吞，否则眩晕并吃掉层数
 厚实表皮：真的灰色生命：受到伤害的 30% 存起来（最多最大生命的一半），3 秒没挨英雄打就慢慢回成生命；被两名敌方英雄围住、或生命低于 40% 且身边有敌人时，把存的全部加 160 + …
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.17）
+          <t>悠米附加包（league_yuumi v0.1.18）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11531,7 +11531,7 @@
         <is>
           <t>基兰复活附加包（league_zilean_rewind v0.2.0）
 主包 league 保持纯数据。主包里基兰的 R 由 AI 在敌方英雄 60000 内时放出、待命 900 tick（没用上就退还冷却）； 待命期间他每次出手查一次：附近有被控制的友方英雄、或自己被两名以上敌方英雄贴身，才给那个人挂 5 秒的时光符文 （league_zilean_r_rune，带「不死」，生命最低停在 1），到第 299 tick 不管有…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.5）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
 奥莉安娜 E、基兰 E：在打架：她 / 他或射程内的队友 40000 内有敌方英雄（基兰也追射程内生命不到 40% 的）</t>
         </is>
       </c>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.33）
+          <t>俄洛伊附加包（league_illaoi v0.2.34）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.34）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.35）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7279,7 +7279,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.33）
+          <t>塞拉斯附加包（league_sylas v0.2.34）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.18）
+          <t>悠米附加包（league_yuumi v0.1.19）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11840,991 +11840,1049 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
+          <t>泰拉</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Terra</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>tft_terra</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>上单</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>岩爪一拍，造成100% 攻击力物理伤害。巨岩之躯：受到的伤害永久减少18%。
+（攻击间隔 1.1 秒 · 攻击距离 30000）</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>裂地咬：低头扑咬目标，造成40 + 130% 攻击力 + 50% 护甲物理伤害（=护甲+魔抗），减速30%（1.5秒）。
+（冷却 8 秒 · 施放距离 34000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>龙威咆哮：仰天咆哮，嘲讽周围敌人1.5秒，自己获得80 + 80% 攻击力的岩石护盾（3秒）。
+（冷却 12 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>地震：重踏三次（施放中免疫控制），每踏对周围敌人造成30 + 70% 攻击力 + 32% 护甲物理伤害；之后护甲和魔抗+60（8秒）。
+（冷却 40 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_terra.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
           <t>远古石甲虫</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Krug</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_krug</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>岩拳砸地，造成100% 攻击力物理伤害。碎岩重生：每条命第一次受到致命伤害时碎成石堆0.75秒，再以小石甲虫站起：生命35%、攻速+30%，嘲讽周围敌人1秒（至少隔60秒）。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>岩之摇滚：获得80 + 60% 法强的护盾（4秒），缩成石球滚向目标，造成40 + 140% 攻击力 + 6%最大生命物理伤害并击退。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>坚岩外壳：缩进巨石2.5秒：护甲+40、魔抗+30；周围的敌人被嘲讽0.75秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>远古崩落：一跃而起（不可选中、免疫控制），砸进敌方英雄身边：周围敌人受到70 + 100% 攻击力 + 6%最大生命物理伤害并被击飞0.8秒；随后落石再造成40 + 4%最大生命物理伤害。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_krug.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>史密奇</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Smeech</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_smeech</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>双爪轮流挥抓，造成100% 攻击力物理伤害。伏击专家：暴击率25%；技能也能暴击，技能暴击造成220%伤害。
 （攻击间隔 0.9 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>废铁黑客：跳向范围内生命最低的敌人，连斩3次，每次造成25 + 70% 攻击力物理伤害；目标阵亡则再跳一次，伤害为70%。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>拆解：双爪撕扯目标，造成45 + 110% 攻击力物理伤害，并使其护甲降低30%，持续4秒。
 （冷却 8 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>废铁狂潮：1.2秒内不受控制、减伤30%，接连跳斩最多5名未被斩过的敌人，每次造成55 + 100% 攻击力物理伤害并获得10%暴击率（5秒）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_smeech.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>赛芬</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Sy'fen</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_syfen</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>翼爪和甩尾交替攻击，造成100% 攻击力物理伤害。幽影低语：他的伤害让敌人缩小4秒（护甲、魔抗-20%）；打缩小的敌人叠怒气，每层+5攻击力，最多5层。
 （攻击间隔 1 秒 · 攻击距离 30000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>噬咬：扑上去咬住目标，造成40 + 160% 攻击力物理伤害，无视33%护甲，回复30 + 30% 攻击力生命。
 （冷却 8 秒 · 施放距离 32000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>翼刃横扫：张开双翼横扫身边，造成40 + 100% 攻击力物理伤害并减速30%（1.5秒）。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>暴走：龙吼后冲向最远的敌方英雄（免疫控制），路上的敌人受到30 + 140% 攻击力物理伤害并晕眩1.25秒，最后猛咬一口造成60 + 235% 攻击力物理伤害，无视33%护甲。
 （冷却 40 秒 · 施放距离 72000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2.52</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_syfen.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>诺姆希</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Nomsy</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>tft_nomsy</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>吐出小火团，造成100% 攻击力物理伤害。龙神之躯：生命值低于40%时每秒回复3%最大生命值。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>火球！：抛出大火球，爆炸造成90 + 63% 法强魔法伤害，再弹出2颗小火球打附近的敌人，各造成55%伤害。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>龙息：向前喷出扇形龙息，造成55 + 36% 法强魔法伤害并灼烧2秒，魔抗降低20%（4秒）。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>龙神飞升：飞上天空（减伤50%、免疫控制），降下10颗火球，各造成60 + 35% 法强魔法伤害；落地后攻速+30%、法强+25%（5秒）。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_nomsy.md</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="3" t="inlineStr">
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>索姆</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Sohm</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_sohm</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>吐出水泡弹，造成100% 攻击力物理伤害。碧波之力：每次施放技能叠一层潮水（6秒，最多5层），每层法强+9%、攻速+9%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>潮涌：朝没开花的敌人冲出一道潮涌，沿途敌人受到95 + 65% 法强魔法伤害，目标头上开出水之花（15秒）；带花的敌人倒下，花跳到附近的敌人。
 （冷却 4 秒 · 施放距离 62000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>海潮护佑：给附近生命比例最低的队友套上95 + 65% 法强的水盾（3秒），攻速+25%。
 （冷却 8 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>潮汐绽放：所有水之花一齐绽放，每朵花周围的敌人受到180 + 90% 法强魔法伤害，花随之散去；没有花时在目标身上绽放。
 （冷却 35 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sohm.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>迭嘉</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Daeja</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_daeja</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
 （攻击间隔 1.2 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="3" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="3" t="inlineStr">
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="3" t="inlineStr">
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L196"/>
+  <autoFilter ref="A1:L197"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13021,6 +13079,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId193"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.34）
+          <t>俄洛伊附加包（league_illaoi v0.2.36）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.35）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.37）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7279,7 +7279,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.34）
+          <t>塞拉斯附加包（league_sylas v0.2.36）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.19）
+          <t>悠米附加包（league_yuumi v0.1.21）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11956,933 +11956,991 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
+          <t>苍蓝雕纹魔像</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Sentinel</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>tft_sentinel</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>巨拳砸下，造成100% 攻击力物理伤害。蓝霸符：每放一个技能，身边友军的技能剩余冷却立刻降到最多67%。
+（攻击间隔 1.27 秒 · 攻击距离 26000）</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>双拳重砸：双拳砸地，对周围敌人造成85 + 105% 法强 + 4% 最大生命魔法伤害并减速30%（2秒）。
+（冷却 6.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>雕纹石肤：符文亮起，获得120 + 120% 法强护盾（4秒），嘲讽周围敌人1.2秒。
+（冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>蔚蓝冲击波：获得150 + 120% 法强护盾，猛砸地面，朝敌方英雄最多的方向裂开裂隙：击飞、170 + 170% 法强 + 4% 最大生命魔法伤害，破法（下一个技能晚2秒）。
+（冷却 50 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sentinel.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
           <t>史密奇</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Smeech</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_smeech</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>双爪轮流挥抓，造成100% 攻击力物理伤害。伏击专家：暴击率25%；技能也能暴击，技能暴击造成220%伤害。
 （攻击间隔 0.9 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>废铁黑客：跳向范围内生命最低的敌人，连斩3次，每次造成25 + 70% 攻击力物理伤害；目标阵亡则再跳一次，伤害为70%。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>拆解：双爪撕扯目标，造成45 + 110% 攻击力物理伤害，并使其护甲降低30%，持续4秒。
 （冷却 8 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>废铁狂潮：1.2秒内不受控制、减伤30%，接连跳斩最多5名未被斩过的敌人，每次造成55 + 100% 攻击力物理伤害并获得10%暴击率（5秒）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_smeech.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>赛芬</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Sy'fen</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_syfen</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>翼爪和甩尾交替攻击，造成100% 攻击力物理伤害。幽影低语：他的伤害让敌人缩小4秒（护甲、魔抗-20%）；打缩小的敌人叠怒气，每层+5攻击力，最多5层。
 （攻击间隔 1 秒 · 攻击距离 30000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>噬咬：扑上去咬住目标，造成40 + 160% 攻击力物理伤害，无视33%护甲，回复30 + 30% 攻击力生命。
 （冷却 8 秒 · 施放距离 32000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>翼刃横扫：张开双翼横扫身边，造成40 + 100% 攻击力物理伤害并减速30%（1.5秒）。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>暴走：龙吼后冲向最远的敌方英雄（免疫控制），路上的敌人受到30 + 140% 攻击力物理伤害并晕眩1.25秒，最后猛咬一口造成60 + 235% 攻击力物理伤害，无视33%护甲。
 （冷却 40 秒 · 施放距离 72000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>2.52</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_syfen.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>诺姆希</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Nomsy</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>tft_nomsy</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>吐出小火团，造成100% 攻击力物理伤害。龙神之躯：生命值低于40%时每秒回复3%最大生命值。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>火球！：抛出大火球，爆炸造成90 + 63% 法强魔法伤害，再弹出2颗小火球打附近的敌人，各造成55%伤害。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>龙息：向前喷出扇形龙息，造成55 + 36% 法强魔法伤害并灼烧2秒，魔抗降低20%（4秒）。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>龙神飞升：飞上天空（减伤50%、免疫控制），降下10颗火球，各造成60 + 35% 法强魔法伤害；落地后攻速+30%、法强+25%（5秒）。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="3" t="inlineStr">
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_nomsy.md</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>索姆</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Sohm</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_sohm</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>吐出水泡弹，造成100% 攻击力物理伤害。碧波之力：每次施放技能叠一层潮水（6秒，最多5层），每层法强+9%、攻速+9%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>潮涌：朝没开花的敌人冲出一道潮涌，沿途敌人受到95 + 65% 法强魔法伤害，目标头上开出水之花（15秒）；带花的敌人倒下，花跳到附近的敌人。
 （冷却 4 秒 · 施放距离 62000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>海潮护佑：给附近生命比例最低的队友套上95 + 65% 法强的水盾（3秒），攻速+25%。
 （冷却 8 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>潮汐绽放：所有水之花一齐绽放，每朵花周围的敌人受到180 + 90% 法强魔法伤害，花随之散去；没有花时在目标身上绽放。
 （冷却 35 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sohm.md</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>迭嘉</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Daeja</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>tft_daeja</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
 （攻击间隔 1.2 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="3" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="3" t="inlineStr">
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="3" t="inlineStr">
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="3" t="inlineStr">
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L197"/>
+  <autoFilter ref="A1:L198"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13080,6 +13138,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId197"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.36）
+          <t>俄洛伊附加包（league_illaoi v0.2.37）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.37）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.38）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7279,7 +7279,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.36）
+          <t>塞拉斯附加包（league_sylas v0.2.37）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.21）
+          <t>悠米附加包（league_yuumi v0.1.22）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11898,1107 +11898,1165 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
+          <t>绯红印记树怪</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Brambleback</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>tft_brambleback</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>大爪横扫，造成100% 攻击力物理伤害。红霸符：普攻灼烧目标3秒（每秒1.2% 最大生命真实伤害），回复1.5%生命；击杀后扑向下一个敌人，造成60 + 120% 攻击力物理伤害。
+（攻击间隔 1.1 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>荆棘飞扑：跃起扑向目标，造成60 + 150% 攻击力物理伤害并减速30%（1秒）。
+（冷却 7 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>绯红咆哮：人立怒吼：周围敌人减速30%、攻击力降低20%，自己受到的伤害降低25%，持续3秒。
+（冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>猩红之怒：狂暴6秒：攻击力+55%、攻速+35%，无视目标40%护甲。
+（冷却 50 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_brambleback.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
           <t>远古石甲虫</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Krug</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_krug</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>岩拳砸地，造成100% 攻击力物理伤害。碎岩重生：每条命第一次受到致命伤害时碎成石堆0.75秒，再以小石甲虫站起：生命35%、攻速+30%，嘲讽周围敌人1秒（至少隔60秒）。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>岩之摇滚：获得80 + 60% 法强的护盾（4秒），缩成石球滚向目标，造成40 + 140% 攻击力 + 6%最大生命物理伤害并击退。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>坚岩外壳：缩进巨石2.5秒：护甲+40、魔抗+30；周围的敌人被嘲讽0.75秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>远古崩落：一跃而起（不可选中、免疫控制），砸进敌方英雄身边：周围敌人受到70 + 100% 攻击力 + 6%最大生命物理伤害并被击飞0.8秒；随后落石再造成40 + 4%最大生命物理伤害。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_krug.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>苍蓝雕纹魔像</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Sentinel</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_sentinel</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>巨拳砸下，造成100% 攻击力物理伤害。蓝霸符：每放一个技能，身边友军的技能剩余冷却立刻降到最多67%。
 （攻击间隔 1.27 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>双拳重砸：双拳砸地，对周围敌人造成85 + 105% 法强 + 4% 最大生命魔法伤害并减速30%（2秒）。
 （冷却 6.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>雕纹石肤：符文亮起，获得120 + 120% 法强护盾（4秒），嘲讽周围敌人1.2秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>蔚蓝冲击波：获得150 + 120% 法强护盾，猛砸地面，朝敌方英雄最多的方向裂开裂隙：击飞、170 + 170% 法强 + 4% 最大生命魔法伤害，破法（下一个技能晚2秒）。
 （冷却 50 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sentinel.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>史密奇</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Smeech</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_smeech</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>双爪轮流挥抓，造成100% 攻击力物理伤害。伏击专家：暴击率25%；技能也能暴击，技能暴击造成220%伤害。
 （攻击间隔 0.9 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>废铁黑客：跳向范围内生命最低的敌人，连斩3次，每次造成25 + 70% 攻击力物理伤害；目标阵亡则再跳一次，伤害为70%。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>拆解：双爪撕扯目标，造成45 + 110% 攻击力物理伤害，并使其护甲降低30%，持续4秒。
 （冷却 8 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>废铁狂潮：1.2秒内不受控制、减伤30%，接连跳斩最多5名未被斩过的敌人，每次造成55 + 100% 攻击力物理伤害并获得10%暴击率（5秒）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_smeech.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>赛芬</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Sy'fen</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_syfen</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>翼爪和甩尾交替攻击，造成100% 攻击力物理伤害。幽影低语：他的伤害让敌人缩小4秒（护甲、魔抗-20%）；打缩小的敌人叠怒气，每层+5攻击力，最多5层。
 （攻击间隔 1 秒 · 攻击距离 30000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>噬咬：扑上去咬住目标，造成40 + 160% 攻击力物理伤害，无视33%护甲，回复30 + 30% 攻击力生命。
 （冷却 8 秒 · 施放距离 32000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>翼刃横扫：张开双翼横扫身边，造成40 + 100% 攻击力物理伤害并减速30%（1.5秒）。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>暴走：龙吼后冲向最远的敌方英雄（免疫控制），路上的敌人受到30 + 140% 攻击力物理伤害并晕眩1.25秒，最后猛咬一口造成60 + 235% 攻击力物理伤害，无视33%护甲。
 （冷却 40 秒 · 施放距离 72000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>2.52</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_syfen.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>呲呲</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Zippy</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>tft_zippy</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>抬腿一蹬，造成100% 攻击力物理伤害。冒险家之魂：身边每有一个友方英雄，护甲和魔抗+10（最多4个）。
 （攻击间隔 0.97 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>后空翻踢：后空翻踢中目标，造成30 + 140% 攻击力物理伤害并击飞0.67秒。
 （冷却 7 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>翻滚冲锋：缩成羽毛球滚向敌人，路上的敌人受到40 + 80% 攻击力物理伤害；身边友方英雄移速+20%（2.5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>翻滚突袭：获得120 + 100% 攻击力护盾（2秒），跃起砸向生命百分比最高的敌方英雄（免疫控制），造成80 + 220% 攻击力物理伤害，晕眩1.5秒并略微击退。
 （冷却 40 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_zippy.md</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="3" t="inlineStr">
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>诺姆希</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Nomsy</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_nomsy</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>吐出小火团，造成100% 攻击力物理伤害。龙神之躯：生命值低于40%时每秒回复3%最大生命值。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>火球！：抛出大火球，爆炸造成90 + 63% 法强魔法伤害，再弹出2颗小火球打附近的敌人，各造成55%伤害。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>龙息：向前喷出扇形龙息，造成55 + 36% 法强魔法伤害并灼烧2秒，魔抗降低20%（4秒）。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>龙神飞升：飞上天空（减伤50%、免疫控制），降下10颗火球，各造成60 + 35% 法强魔法伤害；落地后攻速+30%、法强+25%（5秒）。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_nomsy.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>索姆</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Sohm</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>tft_sohm</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>吐出水泡弹，造成100% 攻击力物理伤害。碧波之力：每次施放技能叠一层潮水（6秒，最多5层），每层法强+9%、攻速+9%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>潮涌：朝没开花的敌人冲出一道潮涌，沿途敌人受到95 + 65% 法强魔法伤害，目标头上开出水之花（15秒）；带花的敌人倒下，花跳到附近的敌人。
 （冷却 4 秒 · 施放距离 62000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>海潮护佑：给附近生命比例最低的队友套上95 + 65% 法强的水盾（3秒），攻速+25%。
 （冷却 8 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>潮汐绽放：所有水之花一齐绽放，每朵花周围的敌人受到180 + 90% 法强魔法伤害，花随之散去；没有花时在目标身上绽放。
 （冷却 35 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="3" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sohm.md</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>迭嘉</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Daeja</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>tft_daeja</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
 （攻击间隔 1.2 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="3" t="inlineStr">
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="3" t="inlineStr">
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="3" t="inlineStr">
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="3" t="inlineStr">
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="3" t="inlineStr">
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L199"/>
+  <autoFilter ref="A1:L200"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13198,6 +13256,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId199"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.37）
+          <t>俄洛伊附加包（league_illaoi v0.2.38）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.38）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.39）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7279,7 +7279,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.37）
+          <t>塞拉斯附加包（league_sylas v0.2.38）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.22）
+          <t>悠米附加包（league_yuumi v0.1.23）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -12884,179 +12884,237 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
+          <t>深红锋喙鸟</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Mama Beak</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>tft_raptor</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>甩出一根锋羽，造成100% 攻击力物理伤害。橙霸符：它的物理伤害使目标护甲-6（3秒，最多5层）。
+（攻击间隔 1.17 秒 · 攻击距离 60000）</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>羽刃扇射：张开翅膀，扇形甩出5根羽刃，每根命中第一个敌人，造成35 + 55% 攻击力物理伤害。
+（冷却 6 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>惊飞跃退：受惊尖叫，往后一跳，之后3秒攻速+70%。
+（冷却 9 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>鸟群之家：召唤4只不可选中的小锋喙鸟（7秒）：它每次普攻，小鸟们一起啄同一目标，各造成18 + 30% 攻击力物理伤害。
+（冷却 45 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_raptor.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="3" t="inlineStr">
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="3" t="inlineStr">
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="3" t="inlineStr">
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L200"/>
+  <autoFilter ref="A1:L201"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13257,6 +13315,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId200"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.39）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.40）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7479,7 +7479,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
@@ -10278,7 +10278,7 @@
       <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -9133,7 +9133,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -750,13 +750,13 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>盛宴：吞噬受伤的敌方英雄，造成300 + 自身5%最大生命的真实伤害和50% 法强无视魔抗的魔法伤害；吃掉则叠一层：最大生命+70、体型变大（最多 2 倍，死亡清空）。
+          <t>盛宴：吞噬受伤的敌方英雄，造成300 + 自身5%最大生命的真实伤害和50% 法强无视魔抗的魔法伤害；吃掉则叠一层：最大生命+70、移速-3%、体型变大（不封顶，死亡清空）。
 （冷却 60 秒 · 施放距离 30000 · 施放：指定目标 · 刚交过手的敌方英雄）</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>科加斯附加包（league_chogath v0.1.2）
+          <t>科加斯附加包（league_chogath v0.1.3）
 盛宴的层数：死后原样补回，层数一局里只增不减
 什么时候放盛宴：读射程内敌方英雄的生命、护盾、免死和受到伤害的增减，一口吃得死才放（几个时吃生命 + 护盾最少的，AI 没想放也放）；吃不死时 AI 想放就改成普攻那个人</t>
         </is>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>甩出一颗星星。星海焕然：技能命中英雄收集星尘（每层法强+3%，最多15层），每6层下一次大招变为天瀑。星穹流丽：击杀英雄后起飞4秒，移速+60%、法强+20%。
+          <t>甩出一颗星星。星海焕然：技能命中英雄收集星尘（最多30层，前15层每层法强+3%），每6层下一次大招变为天瀑。星穹流丽：击杀英雄后起飞4秒，移速+60%、法强+20%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
@@ -5871,15 +5871,15 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>星天落瀑：星落：星星坠落在目标处，造成270 + 85% 法强魔法伤害并眩晕1秒。天瀑：范围更大，350 + 105% 法强并击飞0.83秒，外圈冲击波再造成80 + 30% 法强并减速50%。
+          <t>星天落瀑：星落：星星坠落在目标处，造成270 + 85% 法强魔法伤害并眩晕1秒。天瀑：范围更大，350 + 105% 法强并击飞0.83秒，外圈冲击波再造成80 + 30% 法强并减速50%。星尘每5层，星落、天瀑和黑洞的范围大一档（满层2倍）。
 （冷却 35 秒 · 施放距离 125000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>奥瑞利安·索尔附加包（league_aurelionsol v0.1.0）
-星海焕然（星尘）：活着时记下每一层，死亡清掉后原样补回（最多 d_max 层）
-星芒凝汇（黑洞中心）：同样的伤害，另外英雄生命低于 e_low% + 每层星尘 e_low_d%（默认 5% + 1%/层，最多 20%）就直接处决</t>
+          <t>奥瑞利安·索尔附加包（league_aurelionsol v0.2.0）
+星海焕然（星尘）：活着时记下每一层，死亡清掉后原样补回（最多 d_max 层，范围的档位跟着回来）
+星芒凝汇（黑洞中心）：同样的伤害，另外英雄生命低于 e_low% + 每层星尘 e_low_d%（只算前 e_low_n 层：默认 5% + 1%/层，最多 20%）就直接处决</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -693,7 +693,7 @@
         <is>
           <t>青钢影钩墙附加包（league_camille_wall v0.4.9）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个单独的附加包里。 装上后，青钢影的 E「钩索」钩墙、地图四边和防御塔，不再钩小兵、野怪；英雄、树林、草丛也不钩（墙就在树林里）。
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 卡蜜尔 E：E 好了、60000 内有敌方英雄就按，目标是最近的那个（钩墙附加包的 E 射程是 85000，取小的）。钩索、钩墙、冲向敌人照旧由主包 / 钩墙附加包决定</t>
         </is>
       </c>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>纳尔附加包（league_gnar v0.1.2）
+          <t>纳尔附加包（league_gnar v0.1.3）
 巨型纳尔的样子：整身变巨型：巨型期间（和巨型刚结束、还没播变回动作时）站、跑、挨打、阵亡都换成 m_*
 呐啊！：所有人往同一个方向掀飞（挑能把最多人砸上墙的方向，敌方英雄顶十个小兵；哪边都没墙就从他身边掀开）；撞到墙上的再受一半伤害并眩晕，没撞墙的不晕</t>
         </is>
@@ -1214,7 +1214,7 @@
         <is>
           <t>格温被动附加包（league_gwen v0.1.1）
 主包 league 保持纯数据。数据里能读目标最大生命值的只有真实伤害，读不到法强，所以主包格温的被动「千穿百孔」对英雄造成 1% 最大生命值的真实伤害（用户：「这个可以改rust」）。这个附加包用原生代码做成英雄联盟的样子： - 百分比最大生命值魔法伤害：原生效果 league_gwen:cuts 代替主包里那段真实伤害。被动每次打到敌方英雄（普攻、E …
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>杰斯附加包（league_jayce v0.1.0）
+          <t>杰斯附加包（league_jayce v0.1.1）
 炮形态的样子：整个身体都是炮：待机、跑步、受击播 c_idle / c_run / c_hit（只在游戏 0.6.4 上，别的版本退回左边那样）；阵亡还是锤子的倒地
 雷霆一击往哪推：打中的敌方英雄推向他这边：8 万内有他的友方英雄就推向它们的中心，没有就推向离目标最近的己方塔；这个方向 35000 内碰到墙就左右最多偏 60°，都不行（或者没有友方和塔）才笔…
 加速电炮打谁：射程内、线上没有别的英雄挡着（电炮停在第一个英雄身上）的敌方英雄：这一炮打得死的先（生命 + 护盾不超过估算的伤害，按护甲打折），再是受了伤的里生命比例最低的，都满血就挑最远的</t>
@@ -1594,7 +1594,7 @@
         <is>
           <t>凯尔升阶附加包：按真实等级升阶、死后不掉（league_kayle v0.2.0）
 这个附加包把主包的凯尔换成 override/ 里的副本（make_override.py 生成），和主包有两处不同：
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>奥恩附加包（league_ornn v0.1.2）
+          <t>奥恩附加包（league_ornn v0.1.3）
 熔岩柱：真的地形：立在裂隙的尽头 4 秒，立起时把站在上面的单位推开，之后谁都走不进去（两边的英雄、小兵、野怪，他自己也算）
 E 的地震：撞上柱子或墙才地震：撞上目标的那一刻柱子够近（30000 加上柱子和他的半径），或冲撞方向 14000 内是墙（卡蜜尔附加包的墙格、地图的四边）；撞上的柱子随之碎掉
 易碎：记在每个英雄身上：只有带着易碎的英雄被他普攻打中才引爆（最大生命 8% 的真实伤害、击飞、从他身边击退）
@@ -2490,7 +2490,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>辛吉德附加包（league_singed v0.1.0）
+          <t>辛吉德附加包（league_singed v0.1.1）
 过肩摔怎么飞：击飞 e_fly tick（16），从他头顶飞过、落到他身后 e_behind（30000）远；路上碰到墙就落在墙边
 落进粘胶禁锢：真的落进胶里才禁锢 e_root tick（60）</t>
         </is>
@@ -2812,7 +2812,7 @@
         <is>
           <t>弗拉基米尔残血血池附加包（league_vladimir_pool v0.2.0）
 主包 league 保持纯数据。数据读不到当前生命，主包里弗拉基米尔的 W「血红之池」是自动的：他身上一直跑着一个每 3 tick 看一次的轮询， 看到 league_vladimir_w_go 就化成血池（2 秒不可选取、脚下敌人减速吸血、20 秒冷却）；w_go 由普攻里的危险信号加上—— 两名以上敌方英雄贴身，或连续两次检查都挨了打。用户选了「危险信…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 弗拉基米尔 R（v0.4.0）：60000 内最近被我方打过的敌方英雄生命不到一半，或他身边 26000（血云半径）内有两个以上敌方英雄；生命比例最低的在前</t>
         </is>
       </c>
@@ -3455,7 +3455,7 @@
         <is>
           <t>斩杀附加包：伊芙琳、阿卡丽、锐雯（league_executes v0.2.0）
 伊芙琳 R：150 + 75% 法强，对生命不高于 30% 的目标 ×2.4
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 费德提克 R：他生命 ≥ 40%；80000 内的敌方英雄脚下 45000 内有两个以上（挑人最多的一处，一样多挑残血），或只有一个但生命不到 40%；那里不在敌方塔下；那里 60000 内的…</t>
         </is>
       </c>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>格雷福斯附加包（league_graves v0.2.1）
+          <t>格雷福斯附加包（league_graves v0.2.2）
 主包 league 保持纯数据。用户选了「做附加包」。这个附加包用原生代码做主包数据做不到的三件事，外加连招（0.2.0）： - 快速拔枪的冷却：英雄联盟里格雷福斯的普攻每有一颗弹丸打中，E 的冷却少 0.5 秒。数据不能减冷却。副本里霰弹枪正面那颗 弹丸和扇形每打中一个单位就调一次 league_graves:hit，本包把 E（技能 2）的冷却减 e_…</t>
         </is>
       </c>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>凯隐「暗裔魔镰」附加包（league_kayn_form v0.3.5）
+          <t>凯隐「暗裔魔镰」附加包（league_kayn_form v0.3.6）
 攒哪种形态：打中近战英雄攒暗裔、打中远程英雄攒影流（普攻和技能都算，各 14 次），按英雄的攻击距离分
 形态能留多久：整局：阵亡复活后光环和形态效果直接回来
 变身后的样子：整个身体都是形态的（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>莉莉娅梦尘与昏睡附加包（league_lillia v0.1.3）
+          <t>莉莉娅梦尘与昏睡附加包（league_lillia v0.1.4）
 主包 league 保持纯数据。数据里能读最大生命值的只有真实伤害，也没有「受到伤害就醒」的效果，所以主包莉莉娅： 被动「梦满枝」的梦尘对英雄每 0.75 秒造成 1% 最大生命值的真实伤害；大招「夜阑谣」让带梦尘的敌方英雄困倦 1.5 秒后 眩晕 1.5 秒（打不醒），她的 Q / W 打到眩晕中的英雄时多造成一段惊醒伤害。英雄联盟里梦尘是魔法伤害，昏睡…</t>
         </is>
       </c>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>奇亚娜附加包（league_qiyana v0.2.1）
+          <t>奇亚娜附加包（league_qiyana v0.2.2）
 元素：按身边的地形（英雄联盟的 W 朝哪块地形放就拿哪种）：天纵之勇落地时看她身边两格（64000）内——草丛格子给草丛，墙格子和地图四边的石墙给岩石，河道给河流；几种都在时拿局势想要…
 凌人贵气：每个敌人单独算：对同一个敌人 10 秒内只加一次（英雄联盟：对每个敌人的第一次普攻或技能）
 岩石：只对生命 50% 以下的敌人多打，加倍为 50 + 80% 攻击力，50% 以上不加</t>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>斯卡纳附加包（league_skarner v0.1.0）
+          <t>斯卡纳附加包（league_skarner v0.1.1）
 战栗：层数叠在每个英雄身上（按这个斯卡纳起名），满 p_n 层开始战栗：每 p_p 拍最大生命 p_pct% 的魔法伤害，战栗中不再叠层
 以绪塔尔冲击：拖的路上碰到墙才砸、才晕（伤害 e_wall_dmg + e_ratio% 攻击力 + 最大生命 e_wall_hp%），没墙就只是拖走
 毒刺贯体：只压最先碰到的 r_n 个英雄：魔法伤害、压制 r_sup 拍，压制期间每拍摆在他身边（保持被打中时的方向，离他最多 R_GAP），他走到哪拖到哪</t>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.40）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.41）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
 附身后的招式：按那个英雄的类别换成五套招式之一：近战（重斩、震地减速、冲锋眩晕）、射手（远程射击、穿透射击、三连射）、法师（法球、溅射爆发、定身）、辅助（远程射击、治疗周围友方英雄、减速周围敌…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>阿兹尔附加包（league_azir v0.1.7）
+          <t>阿兹尔附加包（league_azir v0.1.8）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
 禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害还是数据那道墙的。墙停下后再立 3 秒，敌方英雄走不过去；墙打中的敌人被带到墙停下的地方外面（正…
 沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…
@@ -6381,7 +6381,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>黑默丁格附加包（league_heimerdinger v0.2.0）
+          <t>黑默丁格附加包（league_heimerdinger v0.2.1）
 炮台的样子：侧面、炮口朝目标那边（用户：「炮台改成侧面朝敌人」）：英雄联盟模型的侧面，PPU 1.75（用户：「灵活利用PPU 炮也可以调的清晰」，PPU 3 时又「炮太高清了 降低点像素」…
 炮台出手：炮弹（t_shot）、充能光束（t_beam_line）、巨型炮台的等离子弹（x_shot）从侧面炮台的炮口飞向目标，飞到才扣血
 打谁：同样的顺序，每档里打最近的
@@ -6506,7 +6506,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>卡尔萨斯附加包（league_karthus v0.2.0）
+          <t>卡尔萨斯附加包（league_karthus v0.3.1）
 主包 league 保持纯数据。用户选了「被动做附加包」。这个附加包用原生代码做主包数据做不到的死亡契约： - 英雄联盟里卡尔萨斯死后化成灵体，7 秒内照样放技能，然后才倒下。数据读不到血量，主包做不了。 附加包的被动 league_karthus:death_defied 每 10 tick 给他挂一个 30 tick 的不死 buff league_k…</t>
         </is>
       </c>
@@ -6635,7 +6635,7 @@
           <t>卡特琳娜附加包（league_katarina v0.1.1）
 瞬步：另外瞬步一好就自己判断：射程内哪把匕首旁有敌方英雄就跳过去（那里生命比例最低的英雄优先），落地捡刀旋斩、冷却缩短，接着跳下一把——匕首循环；生命低于 30% 而身边有敌方英雄时，…
 贪婪：她参与的每一次英雄击杀（击杀或助攻）都刷新，几个人同时阵亡各算一次
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …
 卡特琳娜 R：她生命 ≥ 30%、自己不在敌方塔下（目标残血除外）；25000 内的敌方英雄，身边 50000 内有两个以上，或目标生命不到一半</t>
         </is>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.1）
+          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.2）
 乐芙兰 镜花水月：生命不高于 40%</t>
         </is>
       </c>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.1）
+          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.2）
 丽桑卓 大招冰封自己：生命不高于 35%</t>
         </is>
       </c>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>玛尔扎哈附加包（league_malzahar v0.1.0）
+          <t>玛尔扎哈附加包（league_malzahar v0.1.1）
 主包 league 保持纯数据。用户选了「做：E 跳转 + 被动精确」。这个附加包用原生代码做主包数据做不准的两件事： - 虚空穿越（被动）：英雄联盟里玛尔扎哈身上有一层法术护盾：受到的伤害大幅减少、免疫控制；被非小兵的伤害打中后很快消失， 一段时间没受到英雄伤害才回来。主包数据读不到「被谁打了」「多久没挨打」，只能做成墨菲特那样的护盾（打破后过一会儿回来…</t>
         </is>
       </c>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>妮蔻附加包（league_neeko v0.1.0）
+          <t>妮蔻附加包（league_neeko v0.1.1）
 天生幻魅：脱战 2 秒后整个身体画成最近的友方英雄（站、跑、出招、挨打都用他的图）；放技能、被控（击飞、晕眩、禁锢、嘲讽、恐惧、魅惑、强制位移）、假扮以来挨了她 35% 最大生命的伤害、或…</t>
         </is>
       </c>
@@ -7087,7 +7087,7 @@
 E 送给谁：送给最危险的队友：身边有敌方英雄的队友里，近一秒受到的伤害比例 × 2 + 已损失生命比例最高的；她自己身边有敌人而且更危险时留给自己
 R 什么时候放：同主包；每个人能不能被冲击波打死照样算（按他的魔抗：伤害 × 100 / (100 + 魔抗)），写进日志（v0.1.0 是「2 个敌方英雄或能打死 1 个」，用户：「发条的大招…
 补兵：走上去补刀（v0.2.0）：附近没有敌方英雄时，普攻距离内的小兵先打这一下打得死的、其次血最少的；60k 内的兵线走上去打；塔下要有己方小兵扛塔才去
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 奥莉安娜 E、基兰 E：在打架：她 / 他或射程内的队友 40000 内有敌方英雄（基兰也追射程内生命不到 40% 的）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 瑞兹 R（备好式）：逃命：生命不到 35% 而 60000 内有敌方英雄；去打架：照崔斯特的规则（身边没敌人、远处队友在打）。传到哪里由主包判断</t>
         </is>
       </c>
@@ -7344,7 +7344,7 @@
         <is>
           <t>辛德拉举小兵附加包（league_syndra v0.1.1）
 这个附加包把主包的辛德拉换成 override/ 里的副本（make_override.py 用 tools/kit/build_syndra.py 的 --native 生成：技能 一样，W 施放时在她身上挂 league_syndra_w_grab、在投掷目标身上挂 league_syndra_w_at；她身上有 league_syndra_w_uni…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 辛德拉 R：75000 内的敌方英雄生命不到 60%、被控住，或射程内有两个以上；主包再按法球数和控制决定立刻放还是待命 8 秒（没用上退还冷却）</t>
         </is>
       </c>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>泰隆「刺客之道」翻墙附加包（league_talon_vault v0.1.4）
+          <t>泰隆「刺客之道」翻墙附加包（league_talon_vault v0.1.5）
 什么时候翻：照旧，另外：残血（低于 35%）而身边有敌方英雄，或被围（身边敌方英雄 ≥ 2、比身边友方多、生命低于 70%）时；残血敌方英雄（≤ 60%）躲在墙后、他自己生命 ≥ 40% 时
 往哪翻：翻过墙：撤离时找背向敌人、16000 内的墙翻到另一边（落地后离敌人最远的那处）；追击时朝目标左右 35° 内找墙翻过去，落点要近 15000 以上、不翻进人堆
 冷却：同一个冷却（主包的 league_talon_e_cd），两种翻越不会连着出</t>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 崔斯特 R：只在主包会传送的局面按：他身边 75000 内没有敌方英雄、生命不低于 40%，而且离他 100000–340000 有队友 50000 内贴着敌方英雄（在打架）。之后揭示、引导…</t>
         </is>
       </c>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>维克兹附加包（league_velkoz v0.1.1）
+          <t>维克兹附加包（league_velkoz v0.1.2）
 有机体解构：层数记在每个敌方英雄身上（每层 7 秒，再中一下全部刷新），第 3 层对那个英雄造成真实伤害；每叠一层都「研究」他 7 秒
 Q 等离子裂变：命中点的左右两边各射出一颗分裂弹（垂直于飞行方向，从命中点旁 12000 起飞 55000 远），打中第一个敌人：伤害、减速，英雄还叠层并打开 Q -&gt; W 的窗口
 R 生命形态瓦解射线：只有被他研究过的英雄受到真实伤害，其他敌人魔法伤害；每 3 波叠一层
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
@@ -8044,7 +8044,7 @@
         <is>
           <t>劫读血附加包（league_zed_mark v0.1.3）
 主包 league 保持纯数据。数据读不到生命也读不到伤害，所以主包里劫的两处是替代做法： - 被动「影忍法！灭魂劫」：英雄联盟里是攻击生命低于 50% 的英雄时附加其最大生命的伤害；主包改成「技能刚打中过英雄」后的下一次普攻（league_zed_cw_ready），附加 6% 最大生命真实伤害，10 秒一次。 - 大招「禁奥义！瞬狱影杀阵」：英雄联盟里…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>阿克尚扩展包（league_akshan v0.2.3）
+          <t>阿克尚扩展包（league_akshan v0.2.4）
 无所不用（第 3 下）：每个目标分别数 3 下（英雄联盟）
 恩怨相抵的子弹：按目标已损失生命：最低伤害到 3 倍（少 67% 生命时封顶，英雄联盟）
 恩怨相抵什么时候开火：存的子弹打得死射程里血最少的英雄、或者他快跑出射程，就提前开火
@@ -8377,7 +8377,7 @@
 武器在手里：整身换武器：主手是断魄 / 坠明 / 荧焰 / 折镜时，站着、跑着、挨打、出手的第一刻都画成那把武器在手里（只在游戏 0.6.4 上）
 打空换枪：先进先出的队列（英雄联盟）：打空的那把排到队尾，换上队列最前面的那把；W 换过手以后和固定循环不一样
 残血：另外生命低于 35%、副手是断魄、60000 内有看得见的敌方英雄时直接换上断魄（吸血），每 6 秒最多一次
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 厄斐琉斯 R（备好式，v0.4.0）：90000 内有敌方英雄就按：主包待命 6 秒，正被我方打的敌方英雄身边还有别人、或被控住才放，没用上缩短冷却</t>
         </is>
       </c>
@@ -8681,7 +8681,7 @@
 额外攻速：不变快；每 1% 换成 0.25% 攻击力（+40% 攻速 = +10% 攻击力）
 攻速减益：一样
 低语、第四发、装弹：一样
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
@@ -8870,12 +8870,12 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>卡莉丝塔附加包（league_kalista v0.1.2）
+          <t>卡莉丝塔附加包（league_kalista v0.1.3）
 武术姿态：每次投矛后自己判断往前还是往后：最近的敌方英雄残血（40% 以下），或者它在逃（越跑越远）而且快跑出射程（超过攻击距离 80%），就往前追；其余都往后跳开；身边没有敌方英雄时照主…
 誓约者：开局绑定一名队友（辅助位优先，没有就最近的队友英雄，每条命出生时重新看），大招对誓约者施放
 命运的召唤：把誓约者拉进来保护、定身，然后逐 tick 飞向离她最近的敌方英雄现在的位置（90000 内，没有就两倍范围），到了就在脚下击飞周围敌人
 撕裂：另外按护甲算拔矛伤害，够杀就立刻拔（矛不够 3 根也拔）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 卡莉丝塔 E：主包「矛够了」的标记（league_kalista_e_ok）在、撕裂不在冷却（league_kalista_e_cd）：按下就是撕裂，不会空按</t>
         </is>
       </c>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 克格莫 R：R 好了、射程（130000）内有引擎接受的敌方英雄（主包 R 只打最近被我方打过的）就按，先挑生命比例最低的（大招打残血更痛）。一轮三发、之后锁 20 秒都是主包的数据。不限时…</t>
         </is>
       </c>
@@ -9259,7 +9259,7 @@
           <t>莎弥拉边走边射附加包（league_samira_r v0.1.0）
 R 期间：旋转连射，同时走向 90000 内生命 + 护盾最少的敌方英雄，走到 30000 内站住；被硬控时不走
 枪、伤害、生命偷取、画面：主包（一样）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 莎弥拉 R：R 好了、R 射程（50000）内有敌方英雄就按，目标是最近的那个。S 评价时这一下就放出炼狱扳机，不到 S 就备好 330 tick，期间到了 S 再放
 莎弥拉 E、Q（攒评价）：S 要连着换五种出手打中英雄（枪 / 剑普攻、Q、E 冲刺、落地的 W 旋转），一下打不中 9 秒就掉。R 不按时：60000 内有敌方英雄、她生命不低于 50%、目标身边的敌方…</t>
         </is>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 希维尔 E：60000 内的敌方英雄刚放了技能（20 tick 内技能冷却开始走），或她生命不到 40% 而 40000 内有敌方英雄</t>
         </is>
       </c>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>斯莫德附加包（league_smolder v0.1.2）
+          <t>斯莫德附加包（league_smolder v0.1.3）
 龙之研习的层数：死后保留（层数、计数器、三档全部原样补回）
 三档龙息：灼烧之外，被打中的单位生命不高于最大生命的 6.5% 就处决（真实伤害，击杀算他的）
 扑棱，扑棱，扑棱！：自己的冷却（20 秒），好了就每 3 tick 看一次：撤——生命低于 40% 而 40000 内有敌方英雄、30000 内有敌方英雄、或 40000 内敌方英雄 2 名以上且比…</t>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>泽丽附加包：W 撞墙激光 + 被动偷盾（league_zeri v0.1.2）
+          <t>泽丽附加包：W 撞墙激光 + 被动偷盾（league_zeri v0.1.3）
 - W「强穿激光」的脉冲先打中小兵或野怪时才在那里化为长激光（小兵代替墙）； - 被动「内能迁转」的电击弹打中英雄时给自己一个小护盾（代替偷盾）。</t>
         </is>
       </c>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>巴德「神奇旅程」穿墙门附加包（league_bard v0.6.2）
+          <t>巴德「神奇旅程」穿墙门附加包（league_bard v0.6.3）
 什么时候开门：冷却（16 秒）一好就每 3 tick 看一次：撤——生命低于 45% 而 30000 内有敌方英雄、15000 内有敌方英雄、或 30000 内敌方英雄 2 名以上且比身边友方…
 往哪走：只在墙上开门、穿到墙的另一边（英雄联盟的神奇旅程）：撤——背向身边敌人中心左右 75° 内、60000 内有墙的方向（20000 时他在线上只有 15% 的时间附近有墙，一局开不…
 队友：门边 25000 内的友方英雄一起穿过去（同样的位移；落点在墙里就落在他出口旁，再不行就不带）
@@ -10023,7 +10023,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.1）
+          <t>低血量附加包：布里茨、乐芙兰、丽桑卓（league_lowhp v0.2.2）
 布里茨 法力屏障：生命不高于 30%</t>
         </is>
       </c>
@@ -10151,7 +10151,7 @@
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 迦娜 E 风暴之眼（50000 内）：有危险的队友（生命不高于 50%，或身边 25000 内有 2 个以上敌方英雄）里生命比例最低的；都没危险就给离敌方英雄最近的（正在打的那个）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 迦娜 R：她或身边 40000 内的队友生命不到 35% 而 50000 内有敌方英雄，或两人以上生命不到 60% 而她身边有敌方英雄。对生命最低的那位放（治疗是她身边一圈，对谁放都一样）</t>
         </is>
       </c>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>诺提勒斯钩墙附加包（league_nautilus v0.1.2）
+          <t>诺提勒斯钩墙附加包（league_nautilus v0.1.3）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个附加包里（合集 league_addons 也带着它）。 装上后，诺提勒斯的 Q「疏通航道」：锚沿路线先碰到野区的墙（引擎的碰撞墙，5v5 地图 90 格）时，把他拉到墙边，并返还一半冷却—— 和英雄联盟一样；先碰到敌方英雄时照主包钩人（两人拉向彼此）。</t>
         </is>
       </c>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>波比附加包（league_poppy v0.1.1）
+          <t>波比附加包（league_poppy v0.1.2）
 坚定风采的光环：光环里正在突进的敌方英雄被挡下：击飞 0.5 秒、受魔法伤害，然后缚地并减速 2 秒（每次光环每人一次）
 坚定风采的双抗：生命低于 40% 时翻倍
 英勇冲锋：撞到墙上（地图的墙格、5v5 地图的四边）才再受一次伤害并眩晕；没墙就只推开
@@ -11149,7 +11149,7 @@
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 娑娜 W 回血（60000 内）：损失生命最多的队友
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 娑娜 W：她或 60000 内的队友生命不到 70%，射程内有敌方英雄</t>
         </is>
       </c>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>塔姆附加包（league_tahmkench v0.1.4）
+          <t>塔姆附加包（league_tahmkench v0.1.5）
 培养品味的层数：每个敌方英雄各自记层（最多 3 层，5 秒），鱼标记按那个人自己的层数画
 巨舌鞭笞打 3 层的人：大招冷却好了就留着层数给大招吞，否则眩晕并吃掉层数
 厚实表皮：真的灰色生命：受到伤害的 30% 存起来（最多最大生命的一半），3 秒没挨英雄打就慢慢回成生命；被两名敌方英雄围住、或生命低于 40% 且身边有敌人时，把存的全部加 160 + …
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.23）
+          <t>悠米附加包（league_yuumi v0.1.24）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11531,7 +11531,7 @@
         <is>
           <t>基兰复活附加包（league_zilean_rewind v0.2.0）
 主包 league 保持纯数据。主包里基兰的 R 由 AI 在敌方英雄 60000 内时放出、待命 900 tick（没用上就退还冷却）； 待命期间他每次出手查一次：附近有被控制的友方英雄、或自己被两名以上敌方英雄贴身，才给那个人挂 5 秒的时光符文 （league_zilean_r_rune，带「不死」，生命最低停在 1），到第 299 tick 不管有…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.6）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
 奥莉安娜 E、基兰 E：在打架：她 / 他或射程内的队友 40000 内有敌方英雄（基兰也追射程内生命不到 40% 的）</t>
         </is>
       </c>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.38）
+          <t>俄洛伊附加包（league_illaoi v0.2.39）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.41）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.42）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7019,7 +7019,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>妮蔻附加包（league_neeko v0.1.1）
+          <t>妮蔻附加包（league_neeko v0.1.2）
 天生幻魅：脱战 2 秒后整个身体画成最近的友方英雄（站、跑、出招、挨打都用他的图）；放技能、被控（击飞、晕眩、禁锢、嘲讽、恐惧、魅惑、强制位移）、假扮以来挨了她 35% 最大生命的伤害、或…</t>
         </is>
       </c>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.38）
+          <t>塞拉斯附加包（league_sylas v0.2.39）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.24）
+          <t>悠米附加包（league_yuumi v0.1.25）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11550,1571 +11550,1629 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>远古巨龙</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Elder Dragon</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>tft_elderdragon</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>上单</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>撕咬目标，造成100% 攻击力物理伤害，目标身边的敌人受到35% 攻击力溅射。远古巨龙霸符：被它伤害后生命低于15%的敌方英雄直接被处决。
+（攻击间隔 1.2 秒 · 攻击距离 30000）</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>烈焰吐息：朝穿过目标、敌人最多的直线喷吐龙焰，造成70 + 130% 攻击力物理伤害，每烧过一人伤害-20%（最低40%），并引燃：3秒内每秒受到2.5%最大生命的物理伤害。
+（冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>龙翼风暴：立起身猛拍双翼，身边的敌人受到30 + 60% 攻击力物理伤害、被击退并减速35%（2秒），自己受到的伤害-25%。
+（冷却 10 秒 · 施放距离 25000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>绝伦火热：无敌飞上天空，1.5秒后砸落：大范围敌人受到80 + 80% 攻击力物理伤害、晕眩1.25秒并被引燃；获得30%全能吸血（5秒），立刻喷一次烈焰吐息。
+（冷却 60 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_elderdragon.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
           <t>可酷伯</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Kobuko</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>tft_kobuko</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>上单</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>猫爪掌，造成100% 攻击力物理伤害。第二阶段：每条命第一次生命低于50%时进入狂怒，直到阵亡：攻击速度+40%、生命偷取20%。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>金爪真言：获得70 + 50% 法强的护盾（4秒）；4秒内下一次普攻变为金爪重掌，造成40 + 105% 攻击力 + 2%最大生命物理伤害并晕眩1秒。
 （冷却 9.5 秒 · 施放距离 25000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>猛虎扑：扑向目标，落地时周围的敌人受到40 + 70% 攻击力 + 2%最大生命物理伤害并被击飞0.4秒。
 （冷却 10.5 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>游戏结束！：一跃冲天（期间不可选中、免疫控制），砸落在敌方英雄身上：目标受到70 + 100% 攻击力 + 6%最大生命物理伤害，周围的敌人（含目标）再受到70 + 60% 攻击力 + 3%最大生命物理伤害并被击飞0.8秒。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="3" t="inlineStr">
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_kobuko.md</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>荏妮</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Renni</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>tft_renni</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>上单</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>链锯每次咬3下，每下造成42% 攻击力物理伤害。微光狂热：生命低于40%时注射微光（每30秒一次），4秒内攻速+40%，并回复20%最大生命。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>链锯冲撞：冲向目标，在前方扇形里锯3次，每次造成40 + 60% 攻击力物理伤害并减速30%，持续1.5秒。
 （冷却 9 秒 · 施放距离 40000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>锯刃格挡：竖起链锯格挡：获得100+80% 攻击力护盾，持续2.5秒，期间减伤20%。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>泥奔者重击：把目标挑起举过头顶，造成120 + 190% 攻击力物理伤害并击飞1.1秒，期间回复15%最大生命；再狠狠砸下，对前方周围敌人造成70 + 110% 攻击力物理伤害。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="3" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_renni.md</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>刀疤</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Scar</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>tft_scar</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>上单</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>长矛刺击造成100% 攻击力物理伤害。野火冲刺：每6秒下一击踩滑板冲刺，造成40 + 110% 攻击力+30% 法强伤害，回复上次冲刺以来所受伤害的25%。监察：生命不低于50%时减伤20%，否则10%。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>水坑狙击惊喜：向最近的3名敌人各扔一颗炸弹，造成70 + 80% 法强魔法伤害并晕眩1秒；自己回复60 + 60% 法强生命。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>长矛横扫：长矛横扫前方，造成50 + 80% 攻击力+2% 最大生命物理伤害并击退敌人。
 （冷却 9 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>野火突袭：踩滑板冲向敌人，途中丢下两颗燃烧弹（各40 + 40% 法强魔法伤害）；落地爆炸，周围敌人受到120 + 100% 法强魔法伤害并被击飞0.5秒，之后4秒内减伤40%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_scar.md</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>塞薇卡</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Sevika</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>tft_sevika</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>上单</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>铁拳造成100% 攻击力物理伤害，每第3下钳击造成25 + 150% 攻击力。百变铁手：每次施放技能随机一个改件：火箭、护盾、35%攻速，12%中头奖强化本次技能。
 （攻击间隔 1.1 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>喷火器：喷火1.2秒，对前方扇形造成5次12 + 32% 攻击力物理伤害，期间减伤30%。
 （冷却 8 秒 · 施放距离 32000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>伸缩拳：射出铁拳，造成40 + 120% 攻击力物理伤害并击退；撞到身后的敌人则两人眩晕1.2秒。
 （冷却 10 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>嚼一嚼：冲向目标连咬2口，每口60 + 135% 攻击力物理伤害，眩晕1.1秒并流血；目标生命低于15%时直接咬死，再冲向下一个英雄。
 （冷却 45 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="3" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sevika.md</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>石傲玉</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Shi Oh Yu</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>tft_shiohyu</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>上单</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>左右爪交替挥击，第3下造成20 + 130% 攻击力物理伤害。玉石之肤：生命低于50%时化作玉石，减伤40%（3秒，冷却30秒）。
 （攻击间隔 1.1 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>玉拳连打：冲向目标连打4拳，每拳造成15 + 45% 攻击力物理伤害。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>震地：一拳砸地，周围敌人受到50 + 110% 攻击力物理伤害，被击飞0.75秒并减速35%。
 （冷却 9 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>玉龙形态：减伤35%、免疫控制，接下来3次普攻各造成40 + 175% 攻击力伤害：第1下晕眩1秒；第2下为真实伤害；第3下打出直线冲击波，晕眩沿线敌人。
 （冷却 25 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>2.46</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_shiohyu.md</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>泰拉</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Terra</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>tft_terra</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>上单</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>岩爪一拍，造成100% 攻击力物理伤害。巨岩之躯：受到的伤害永久减少18%。
 （攻击间隔 1.1 秒 · 攻击距离 30000）</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>裂地咬：低头扑咬目标，造成40 + 130% 攻击力 + 50% 护甲物理伤害（=护甲+魔抗），减速30%（1.5秒）。
 （冷却 8 秒 · 施放距离 34000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>龙威咆哮：仰天咆哮，嘲讽周围敌人1.5秒，自己获得80 + 80% 攻击力的岩石护盾（3秒）。
 （冷却 12 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>地震：重踏三次（施放中免疫控制），每踏对周围敌人造成30 + 70% 攻击力 + 32% 护甲物理伤害；之后护甲和魔抗+60（8秒）。
 （冷却 40 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_terra.md</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>绯红印记树怪</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Brambleback</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>tft_brambleback</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>大爪横扫，造成100% 攻击力物理伤害。红霸符：普攻灼烧目标3秒（每秒1.2% 最大生命真实伤害），回复1.5%生命；击杀后扑向下一个敌人，造成60 + 120% 攻击力物理伤害。
 （攻击间隔 1.1 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>荆棘飞扑：跃起扑向目标，造成60 + 150% 攻击力物理伤害并减速30%（1秒）。
 （冷却 7 秒 · 施放距离 55000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>绯红咆哮：人立怒吼：周围敌人减速30%、攻击力降低20%，自己受到的伤害降低25%，持续3秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>猩红之怒：狂暴6秒：攻击力+55%、攻速+35%，无视目标40%护甲。
 （冷却 50 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_brambleback.md</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>远古石甲虫</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Krug</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>tft_krug</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>岩拳砸地，造成100% 攻击力物理伤害。碎岩重生：每条命第一次受到致命伤害时碎成石堆0.75秒，再以小石甲虫站起：生命35%、攻速+30%，嘲讽周围敌人1秒（至少隔60秒）。
 （攻击间隔 1.2 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>岩之摇滚：获得80 + 60% 法强的护盾（4秒），缩成石球滚向目标，造成40 + 140% 攻击力 + 6%最大生命物理伤害并击退。
 （冷却 8 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>坚岩外壳：缩进巨石2.5秒：护甲+40、魔抗+30；周围的敌人被嘲讽0.75秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>远古崩落：一跃而起（不可选中、免疫控制），砸进敌方英雄身边：周围敌人受到70 + 100% 攻击力 + 6%最大生命物理伤害并被击飞0.8秒；随后落石再造成40 + 4%最大生命物理伤害。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_krug.md</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>苍蓝雕纹魔像</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Sentinel</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>tft_sentinel</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>巨拳砸下，造成100% 攻击力物理伤害。蓝霸符：每放一个技能，身边友军的技能剩余冷却立刻降到最多67%。
 （攻击间隔 1.27 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>双拳重砸：双拳砸地，对周围敌人造成85 + 105% 法强 + 4% 最大生命魔法伤害并减速30%（2秒）。
 （冷却 6.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>雕纹石肤：符文亮起，获得120 + 120% 法强护盾（4秒），嘲讽周围敌人1.2秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>蔚蓝冲击波：获得150 + 120% 法强护盾，猛砸地面，朝敌方英雄最多的方向裂开裂隙：击飞、170 + 170% 法强 + 4% 最大生命魔法伤害，破法（下一个技能晚2秒）。
 （冷却 50 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sentinel.md</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>史密奇</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Smeech</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_smeech</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>双爪轮流挥抓，造成100% 攻击力物理伤害。伏击专家：暴击率25%；技能也能暴击，技能暴击造成220%伤害。
 （攻击间隔 0.9 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>废铁黑客：跳向范围内生命最低的敌人，连斩3次，每次造成25 + 70% 攻击力物理伤害；目标阵亡则再跳一次，伤害为70%。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>拆解：双爪撕扯目标，造成45 + 110% 攻击力物理伤害，并使其护甲降低30%，持续4秒。
 （冷却 8 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>废铁狂潮：1.2秒内不受控制、减伤30%，接连跳斩最多5名未被斩过的敌人，每次造成55 + 100% 攻击力物理伤害并获得10%暴击率（5秒）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_smeech.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>赛芬</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Sy'fen</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_syfen</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>翼爪和甩尾交替攻击，造成100% 攻击力物理伤害。幽影低语：他的伤害让敌人缩小4秒（护甲、魔抗-20%）；打缩小的敌人叠怒气，每层+5攻击力，最多5层。
 （攻击间隔 1 秒 · 攻击距离 30000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>噬咬：扑上去咬住目标，造成40 + 160% 攻击力物理伤害，无视33%护甲，回复30 + 30% 攻击力生命。
 （冷却 8 秒 · 施放距离 32000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>翼刃横扫：张开双翼横扫身边，造成40 + 100% 攻击力物理伤害并减速30%（1.5秒）。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>暴走：龙吼后冲向最远的敌方英雄（免疫控制），路上的敌人受到30 + 140% 攻击力物理伤害并晕眩1.25秒，最后猛咬一口造成60 + 235% 攻击力物理伤害，无视33%护甲。
 （冷却 40 秒 · 施放距离 72000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2.52</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_syfen.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>呲呲</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Zippy</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>tft_zippy</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>抬腿一蹬，造成100% 攻击力物理伤害。冒险家之魂：身边每有一个友方英雄，护甲和魔抗+10（最多4个）。
 （攻击间隔 0.97 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>后空翻踢：后空翻踢中目标，造成30 + 140% 攻击力物理伤害并击飞0.67秒。
 （冷却 7 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>翻滚冲锋：缩成羽毛球滚向敌人，路上的敌人受到40 + 80% 攻击力物理伤害；身边友方英雄移速+20%（2.5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>翻滚突袭：获得120 + 100% 攻击力护盾（2秒），跃起砸向生命百分比最高的敌方英雄（免疫控制），造成80 + 220% 攻击力物理伤害，晕眩1.5秒并略微击退。
 （冷却 40 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="3" t="inlineStr">
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_zippy.md</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>诺姆希</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Nomsy</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_nomsy</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>吐出小火团，造成100% 攻击力物理伤害。龙神之躯：生命值低于40%时每秒回复3%最大生命值。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>火球！：抛出大火球，爆炸造成90 + 63% 法强魔法伤害，再弹出2颗小火球打附近的敌人，各造成55%伤害。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>龙息：向前喷出扇形龙息，造成55 + 36% 法强魔法伤害并灼烧2秒，魔抗降低20%（4秒）。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>龙神飞升：飞上天空（减伤50%、免疫控制），降下10颗火球，各造成60 + 35% 法强魔法伤害；落地后攻速+30%、法强+25%（5秒）。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_nomsy.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="3" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>索姆</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Sohm</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>tft_sohm</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>吐出水泡弹，造成100% 攻击力物理伤害。碧波之力：每次施放技能叠一层潮水（6秒，最多5层），每层法强+9%、攻速+9%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>潮涌：朝没开花的敌人冲出一道潮涌，沿途敌人受到95 + 65% 法强魔法伤害，目标头上开出水之花（15秒）；带花的敌人倒下，花跳到附近的敌人。
 （冷却 4 秒 · 施放距离 62000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>海潮护佑：给附近生命比例最低的队友套上95 + 65% 法强的水盾（3秒），攻速+25%。
 （冷却 8 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>潮汐绽放：所有水之花一齐绽放，每朵花周围的敌人受到180 + 90% 法强魔法伤害，花随之散去；没有花时在目标身上绽放。
 （冷却 35 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="3" t="inlineStr">
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sohm.md</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>迭嘉</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>Daeja</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>tft_daeja</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
 （攻击间隔 1.2 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="3" t="inlineStr">
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="3" t="inlineStr">
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>深红锋喙鸟</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>Mama Beak</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>tft_raptor</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>甩出一根锋羽，造成100% 攻击力物理伤害。橙霸符：它的物理伤害使目标护甲-6（3秒，最多5层）。
 （攻击间隔 1.17 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>羽刃扇射：张开翅膀，扇形甩出5根羽刃，每根命中第一个敌人，造成35 + 55% 攻击力物理伤害。
 （冷却 6 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>惊飞跃退：受惊尖叫，往后一跳，之后3秒攻速+70%。
 （冷却 9 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>鸟群之家：召唤4只不可选中的小锋喙鸟（7秒）：它每次普攻，小鸟们一起啄同一目标，各造成18 + 30% 攻击力物理伤害。
 （冷却 45 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="3" t="inlineStr">
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_raptor.md</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="3" t="inlineStr">
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="3" t="inlineStr">
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="3" t="inlineStr">
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L201"/>
+  <autoFilter ref="A1:L202"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13316,6 +13374,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId201"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -2875,11 +2875,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>沃利贝尔附加包（league_volibear v0.2.0）
+          <t>沃利贝尔附加包（league_volibear v0.3.0）
 狂雷渐起的闪电（满 5 层）：打目标和离它最近的 4 个敌人（22000 以内，防御塔不算），每个身上闪一下
 暴怒撕咬的标记：标记记在被咬的那个英雄身上（8 秒）：再咬同一个人才是第二口；第二口回复再加已损失生命的 12%
+天声震落跳谁：跳进人堆：AI 按下 R 时，射程（70000）内要是有落在他身上能砸到更多敌方英雄（他身边 32000 以内）的，改跳他；一样多照 AI 挑的
 天声震落：另外让落点 55000 以内的敌方防御塔 4 秒不能攻击（塔身上缠着电光）
-天声震落后的 12 秒风暴形态：他整个人变成雷电蓝：白毛变浅电蓝、腿变深蓝，符文和冰晶爪子发亮青光，外圈一道电蓝描边；形态结束或阵亡时变回来</t>
+天声震落后的 12 秒风暴形态：他整个人变成雷电蓝：白毛变浅电蓝、腿变深蓝，符文和冰晶爪子发亮青光，外圈一道电蓝描边；形态结束或阵亡时变回来（体型同主包）</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.39）
+          <t>俄洛伊附加包（league_illaoi v0.2.40）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.42）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.43）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>妮蔻附加包（league_neeko v0.1.2）
+          <t>妮蔻附加包（league_neeko v0.1.3）
 天生幻魅：脱战 2 秒后整个身体画成最近的友方英雄（站、跑、出招、挨打都用他的图）；放技能、被控（击飞、晕眩、禁锢、嘲讽、恐惧、魅惑、强制位移）、假扮以来挨了她 35% 最大生命的伤害、或…</t>
         </is>
       </c>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.39）
+          <t>塞拉斯附加包（league_sylas v0.2.40）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.25）
+          <t>悠米附加包（league_yuumi v0.1.26）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -12073,1107 +12073,1165 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
+          <t>暗影狼</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Murkwolf</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>tft_murkwolf</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>打野</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>两个头一起撕咬，造成100% 攻击力物理伤害。灰霸符：暴击率25%，随已损失生命值最多再+30%，技能也能暴击。
+（攻击间隔 0.93 秒 · 攻击距离 23000）</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>撕裂之爪：跃向附近生命值最低的敌人，造成40 + 110% 攻击力物理伤害。接下来3次攻击攻速+60%，额外造成10 + 30% 攻击力物理伤害。
+（冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>狂战士之嚎：仰头长嚎，5秒内吸血20%，伤害提高15%，对生命低于50%的敌人翻倍。
+（冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>狼群攻击：叫来2只小暗影狼扑向目标，造成40 + 60% 攻击力物理伤害。6秒内它每次攻击，小狼咬2口，每口12 + 25% 攻击力物理伤害。
+（冷却 45 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_murkwolf.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
           <t>苍蓝雕纹魔像</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Sentinel</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>tft_sentinel</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>巨拳砸下，造成100% 攻击力物理伤害。蓝霸符：每放一个技能，身边友军的技能剩余冷却立刻降到最多67%。
 （攻击间隔 1.27 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>双拳重砸：双拳砸地，对周围敌人造成85 + 105% 法强 + 4% 最大生命魔法伤害并减速30%（2秒）。
 （冷却 6.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>雕纹石肤：符文亮起，获得120 + 120% 法强护盾（4秒），嘲讽周围敌人1.2秒。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>蔚蓝冲击波：获得150 + 120% 法强护盾，猛砸地面，朝敌方英雄最多的方向裂开裂隙：击飞、170 + 170% 法强 + 4% 最大生命魔法伤害，破法（下一个技能晚2秒）。
 （冷却 50 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sentinel.md</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>史密奇</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Smeech</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>tft_smeech</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>双爪轮流挥抓，造成100% 攻击力物理伤害。伏击专家：暴击率25%；技能也能暴击，技能暴击造成220%伤害。
 （攻击间隔 0.9 秒 · 攻击距离 23000）</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>废铁黑客：跳向范围内生命最低的敌人，连斩3次，每次造成25 + 70% 攻击力物理伤害；目标阵亡则再跳一次，伤害为70%。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>拆解：双爪撕扯目标，造成45 + 110% 攻击力物理伤害，并使其护甲降低30%，持续4秒。
 （冷却 8 秒 · 施放距离 26000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>废铁狂潮：1.2秒内不受控制、减伤30%，接连跳斩最多5名未被斩过的敌人，每次造成55 + 100% 攻击力物理伤害并获得10%暴击率（5秒）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_smeech.md</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>赛芬</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Sy'fen</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>tft_syfen</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>翼爪和甩尾交替攻击，造成100% 攻击力物理伤害。幽影低语：他的伤害让敌人缩小4秒（护甲、魔抗-20%）；打缩小的敌人叠怒气，每层+5攻击力，最多5层。
 （攻击间隔 1 秒 · 攻击距离 30000）</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>噬咬：扑上去咬住目标，造成40 + 160% 攻击力物理伤害，无视33%护甲，回复30 + 30% 攻击力生命。
 （冷却 8 秒 · 施放距离 32000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>翼刃横扫：张开双翼横扫身边，造成40 + 100% 攻击力物理伤害并减速30%（1.5秒）。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>暴走：龙吼后冲向最远的敌方英雄（免疫控制），路上的敌人受到30 + 140% 攻击力物理伤害并晕眩1.25秒，最后猛咬一口造成60 + 235% 攻击力物理伤害，无视33%护甲。
 （冷却 40 秒 · 施放距离 72000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>2.52</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr">
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_syfen.md</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>范德尔</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Vander</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>tft_vander</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。监察：受到的伤害降低10%，生命高于50%时降低20%。
 （攻击间隔 1.07 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>地下猎犬：摆出防御姿态，嘲讽周围的敌人0.75秒，获得40护甲和30魔抗（2.5秒）；下一拳造成40 + 140% 攻击力物理伤害，队里每有一个家人再加40% 攻击力。
 （冷却 10 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>铁拳突进：冲向敌人打出上勾拳，造成50 + 90% 攻击力物理伤害并晕眩0.5秒，身边的敌人受到35%的伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>桥头死守：跳进敌群砸地，周围的敌人受到150 + 150% 攻击力物理伤害并被击飞1秒；之后4秒内受到的伤害降低15%，身边每个敌方英雄再降低8%（最多4个）。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_vander.md</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>蔚奥莱</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Violet</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>tft_violet</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>挥拳造成100% 攻击力物理伤害。搏击手：每次命中额外造成5% 攻击力真实伤害，全能吸血10%；每条命第一次生命低于50%时，2秒内回复15%最大生命。
 （攻击间隔 0.93 秒 · 攻击距离 24000）</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>1-2-3连招：两记刺拳各造成50% 攻击力物理伤害，再一记上勾拳造成40 + 120% 攻击力物理伤害并击飞0.5秒。
 （冷却 8 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>冲拳：冲向敌人一拳打退，造成40 + 100% 攻击力物理伤害。
 （冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>底城怒拳：跳进敌群双拳砸地，周围的敌人受到120 + 130% 攻击力物理伤害并被击飞0.8秒；之后5秒内攻速+40%、吸血+5%，队里每有一个家人攻速再+10%。
 （冷却 50 秒 · 施放距离 50000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="3" t="inlineStr">
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_violet.md</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>呲呲</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Zippy</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>tft_zippy</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>打野</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>抬腿一蹬，造成100% 攻击力物理伤害。冒险家之魂：身边每有一个友方英雄，护甲和魔抗+10（最多4个）。
 （攻击间隔 0.97 秒 · 攻击距离 26000）</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>后空翻踢：后空翻踢中目标，造成30 + 140% 攻击力物理伤害并击飞0.67秒。
 （冷却 7 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>翻滚冲锋：缩成羽毛球滚向敌人，路上的敌人受到40 + 80% 攻击力物理伤害；身边友方英雄移速+20%（2.5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>翻滚突袭：获得120 + 100% 攻击力护盾（2秒），跃起砸向生命百分比最高的敌方英雄（免疫控制），造成80 + 220% 攻击力物理伤害，晕眩1.5秒并略微击退。
 （冷却 40 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_zippy.md</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>拉露恩</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Alune</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>tft_alune</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>把螺旋月环像飞盘一样甩出去，造成100% 攻击力物理伤害，月环飞回她手里，回程路上的敌人受到30% 攻击力物理伤害。月相：每放一次技能月亮长一档，最多3档；大招每档伤害+20%，砸完回到新月。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>月之降临：月光碎片从天而降，落在离她最近的3个敌人身上，每枚造成42 + 32% 法强魔法伤害，并使魔抗降低20%，持续6秒。
 （冷却 4.25 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>月华：月光洒在她和身边的友方英雄身上，攻击速度提高36%，持续5秒。
 （冷却 10 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>月曜降临：敌方英雄脚下浮现月影，0.75秒后满月砸下：165 + 72% 法强魔法伤害×220%由范围内的敌人平分（每人最多180%），中心的敌人眩晕0.83秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_alune.md</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>敖兴</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Ao Shin</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>tft_aoshin</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>吐出球状闪电，造成100% 攻击力物理伤害。风暴龙威：交战3秒后天雷劈中周围所有敌方英雄，造成12%最大生命真实伤害并眩晕0.83秒；随后自身法术强度+30%（6秒，每20秒一次）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>雷息：喷出一道雷息，直线上的敌人受到80 + 50% 法强魔法伤害并被沉默0.67秒。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>腾云：驾云飞离附近的敌方英雄，获得110 + 40% 法强的风暴护盾（3秒）。
 （冷却 8 秒 · 施放距离 42000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>闪电暴雨：召来雷暴：12道闪电接连劈向周围随机的敌方英雄，每道造成55 + 32% 法强魔法伤害并沉默0.3秒。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_aoshin.md</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>诺姆希</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Nomsy</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>tft_nomsy</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>吐出小火团，造成100% 攻击力物理伤害。龙神之躯：生命值低于40%时每秒回复3%最大生命值。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>火球！：抛出大火球，爆炸造成90 + 63% 法强魔法伤害，再弹出2颗小火球打附近的敌人，各造成55%伤害。
 （冷却 4 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>龙息：向前喷出扇形龙息，造成55 + 36% 法强魔法伤害并灼烧2秒，魔抗降低20%（4秒）。
 （冷却 7 秒 · 施放距离 45000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>龙神飞升：飞上天空（减伤50%、免疫控制），降下10颗火球，各造成60 + 35% 法强魔法伤害；落地后攻速+30%、法强+25%（5秒）。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_nomsy.md</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>诺拉</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Norra</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>tft_norra</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>普攻100% 攻击力物理伤害。寄情琐物：每10秒技能落点撒3个琐物4秒，飞向踩到的敌方英雄：30 + 20% 法强魔法伤害并挂线缕；技能命中英雄冷却-20%。奇异旅程：贴身的敌人受40 + 30% 法强魔法伤害，放逐1.5秒后减速80%0.75秒。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>回忆涌现：蓄力后射出回忆魔法弹，自己后退一步：落点周围敌人受到35 + 28% 法强魔法伤害，已有线缕的英雄再受最大生命2%，随后挂上线缕；打中英雄时地上的琐物待爆：敌方英雄靠近就飞向他。
 （冷却 5.5 秒 · 施放距离 90000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>思乡线缕：在目标两侧打开两扇门，0.3秒后线缕穿过：范围内敌人受到35 + 26% 法强魔法伤害并挂上线缕：4秒内体型变大15%（更容易被命中），减速20%2秒。
 （冷却 10 秒 · 施放距离 85000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>传送门欢腾！：在敌方英雄脚下展开大裂隙，每0.5秒一波共4波：两个毛线球沿一条穿过敌方英雄的线从两头对飞，路上敌人各受30 + 15% 法强魔法伤害，每个球碰到的第一个英雄减速80%0.5秒；第4波+40%。
 （冷却 50 秒 · 施放距离 100000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_norra.md</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>爆爆</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Powder</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>tft_powder</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>扔出自制小鞭炮，造成100% 攻击力物理伤害。伏击者：技能炸弹可以暴击（25%几率，伤害翻倍）。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>猴子炸弹：把上了发条的猴子炸弹丢到目标脚下，范围内敌人受到36 + 28% 法强魔法伤害，中心再受一次；被炸到的敌人灼烧3秒，并重伤4秒（受到治疗-40%）。
 （冷却 5.5 秒 · 施放距离 70000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>快跑，爆爆！：敌方英雄靠近时摔下闪光烟雾弹：周围敌人受到45 + 30% 法强魔法伤害并致盲1秒（无法普攻），自己向后跳开。
 （冷却 10 秒 · 施放距离 24000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>海克斯水晶炸弹：把装着海克斯水晶的包丢向敌方英雄，引线烧完0.9秒后蓝光大爆炸：范围内敌人受到170 + 65% 法强魔法伤害并击飞0.75秒。
 （冷却 50 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="3" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_powder.md</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>希尔科</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Silco</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>tft_silco</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>甩出一支微光药剂，造成100% 攻击力物理伤害。统领：每次出生获得120 + 40% 法强护盾（15秒）；每放一次技能法强+10%，最多5层，阵亡清空。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>罐装畸变体：扔出储罐，造成65 + 45% 法强魔法伤害，放出2只畸变体扑向附近的敌人，各咬5口，每口15 + 11% 法强魔法伤害；被咬的人倒下就跳到下一个。
 （冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>微光注射：把微光抛给身边攻击力最高的友方英雄（没有就自己）：攻速+50%、移速+20%，4秒；药效过去扣当前生命的8%。
 （冷却 12 秒 · 施放距离 60000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>炼金狂潮：向敌方英雄扔出巨型储罐，造成180 + 80% 法强魔法伤害，放出4只畸变体，留下4秒毒雾：敌人减速30%，每秒受到6 + 4% 法强魔法伤害。
 （冷却 50 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="3" t="inlineStr">
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_silco.md</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>索姆</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>Sohm</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>tft_sohm</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>中单</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>吐出水泡弹，造成100% 攻击力物理伤害。碧波之力：每次施放技能叠一层潮水（6秒，最多5层），每层法强+9%、攻速+9%。
 （攻击间隔 1.5 秒 · 攻击距离 55000）</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>潮涌：朝没开花的敌人冲出一道潮涌，沿途敌人受到95 + 65% 法强魔法伤害，目标头上开出水之花（15秒）；带花的敌人倒下，花跳到附近的敌人。
 （冷却 4 秒 · 施放距离 62000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>海潮护佑：给附近生命比例最低的队友套上95 + 65% 法强的水盾（3秒），攻速+25%。
 （冷却 8 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>潮汐绽放：所有水之花一齐绽放，每朵花周围的敌人受到180 + 90% 法强魔法伤害，花随之散去；没有花时在目标身上绽放。
 （冷却 35 秒 · 施放距离 70000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="3" t="inlineStr">
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sohm.md</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>迭嘉</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>Daeja</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>tft_daeja</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>推出风弹，造成100% 攻击力物理伤害。三连弹幕：每次普攻再射出3颗小风弹，各造成10 + 15% 法强魔法伤害，魔抗-4（3秒，可叠加）。
 （攻击间隔 1.2 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>罡风轰击：双翼前扫，朝敌人最多的直线轰出穿透的风波，造成110 + 70% 法强魔法伤害。
 （冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>振翼退风：振翅朝身边的敌人扇出一阵风，造成40 + 30% 法强魔法伤害并减速40%（1.5秒），自己借风后跳。
 （冷却 10 秒 · 施放距离 40000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>苍穹罡风：展翅飞起（减伤30%、免疫控制），朝敌人最多的直线连续轰出3道大冲击波，各造成150 + 70% 法强魔法伤害。
 （冷却 45 秒 · 施放距离 75000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="3" t="inlineStr">
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_daeja.md</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="3" t="inlineStr">
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>深红锋喙鸟</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>Mama Beak</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>tft_raptor</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>甩出一根锋羽，造成100% 攻击力物理伤害。橙霸符：它的物理伤害使目标护甲-6（3秒，最多5层）。
 （攻击间隔 1.17 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>羽刃扇射：张开翅膀，扇形甩出5根羽刃，每根命中第一个敌人，造成35 + 55% 攻击力物理伤害。
 （冷却 6 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>惊飞跃退：受惊尖叫，往后一跳，之后3秒攻速+70%。
 （冷却 9 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>鸟群之家：召唤4只不可选中的小锋喙鸟（7秒）：它每次普攻，小鸟们一起啄同一目标，各造成18 + 30% 攻击力物理伤害。
 （冷却 45 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="3" t="inlineStr">
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_raptor.md</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="3" t="inlineStr">
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="3" t="inlineStr">
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="3" t="inlineStr">
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L202"/>
+  <autoFilter ref="A1:L203"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13376,6 +13434,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.39）
+          <t>俄洛伊附加包（league_illaoi v0.2.40）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.42）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.43）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.39）
+          <t>塞拉斯附加包（league_sylas v0.2.40）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.25）
+          <t>悠米附加包（league_yuumi v0.1.26）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -13117,63 +13117,121 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
+          <t>小木灵</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Meepsie</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>tft_meepsie</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>辅助</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>挥出月岩重拳，造成100% 攻击力物理伤害。木灵驾驶员：每一拳额外造成15 + 25% 法强魔法伤害。
+（攻击间隔 1.5 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>月尘震地：一拳砸向前方地面，扇形范围内的敌人受到100 + 70% 法强魔法伤害并减速40%（2秒）。
+（冷却 6 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>治疗木灵：驾驶员一招手，4只小木灵飞向身边生命比例最低的队友（名额有剩时也治疗自己），每0.5秒回复20 + 10% 法强生命，持续3秒。
+（冷却 9 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>宇宙大爆炸：跳向附近敌方英雄最多的地方砸地，周围的敌人受到160 + 90% 法强魔法伤害，离中心每远一格少35%；离落点最近的3个敌方英雄被击飞1.25秒。
+（冷却 35 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_meepsie.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="3" t="inlineStr">
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L202"/>
+  <autoFilter ref="A1:L203"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13376,6 +13434,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.40）
+          <t>俄洛伊附加包（league_illaoi v0.2.41）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.43）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.44）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.40）
+          <t>塞拉斯附加包（league_sylas v0.2.41）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.26）
+          <t>悠米附加包（league_yuumi v0.1.27）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.41）
+          <t>俄洛伊附加包（league_illaoi v0.2.42）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.44）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.45）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.41）
+          <t>塞拉斯附加包（league_sylas v0.2.42）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>佐伊附加包（league_zoe v0.4.0）
+          <t>佐伊附加包（league_zoe v0.5.0）
 催眠气泡的睡眠：一样是官方睡眠，2.25 秒（英雄联盟的时长）；睡着时头上有睡泡，醒了就摘掉，被打醒的放醒来的画面
 飞星的伤害：按真实飞行距离：出手点 20000 以内 100%，到 85000 线性加到 250%
 窃法巧手：另外：敌方英雄放大招时原地掉下一块法术碎片（20 秒，最多 3 块），她走到 18000 以内就捡起来，射 3 颗飞弹（打 70000 内最近的敌方英雄，每颗 45 + 15% …
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.27）
+          <t>悠米附加包（league_yuumi v0.1.28）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -13233,63 +13233,121 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
+          <t>迅捷蟹</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Scuttle Crab</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>tft_scuttlecrab</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>辅助</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>跳一段螃蟹舞，踩中身边所有敌人，造成100% 攻击力物理伤害。绿霸符：附近的友方英雄生命低于40%时回复12%最大生命（每人10秒一次）。
+（攻击间隔 1.33 秒 · 攻击距离 25000）</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>疾行神龛：在脚下放下神龛（4秒），水花使周围敌人受到80 + 60% 法强魔法伤害并减速40%；神龛里的友方英雄移速+30%、攻速+25%。
+（冷却 7 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>蟹壳护盾：缩进壳里，获得120 + 60% 法强护盾（2秒）。护盾打光或到时间时蟹壳碎裂：周围敌人受到80 + 60% 法强魔法伤害、眩晕0.5秒并减速40%。
+（冷却 6 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>你挖得动吗？：钻入地下2.5秒：受到的伤害降低50%、免疫控制，持续回复250 + 80% 法强生命；然后钻出地面，周围敌人受到160 + 60% 攻击力物理伤害并被击飞1.5秒。
+（冷却 25 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_scuttlecrab.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="3" t="inlineStr">
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L204"/>
+  <autoFilter ref="A1:L205"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13494,6 +13552,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId204"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.42）
+          <t>俄洛伊附加包（league_illaoi v0.2.43）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.45）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.46）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>妮蔻附加包（league_neeko v0.1.3）
+          <t>妮蔻附加包（league_neeko v0.1.4）
 天生幻魅：脱战 2 秒后整个身体画成最近的友方英雄（站、跑、出招、挨打都用他的图）；放技能、被控（击飞、晕眩、禁锢、嘲讽、恐惧、魅惑、强制位移）、假扮以来挨了她 35% 最大生命的伤害、或…</t>
         </is>
       </c>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.42）
+          <t>塞拉斯附加包（league_sylas v0.2.43）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.28）
+          <t>悠米附加包（league_yuumi v0.1.29）
 附身多久：不限时，队友死了才跳下来
 附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -12943,411 +12943,469 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
+          <t>魔沼蛙</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Gromp</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>tft_gromp</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>吐出毒口水，造成100% 攻击力物理伤害和40% 法强魔法伤害。紫霸符：战斗中每4秒法术加成+8，最多8层。
+（攻击间隔 1.2 秒 · 攻击距离 60000）</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>打嗝泡泡：打出一个毒泡泡，碰到第一个敌人造成110 + 80% 法强魔法伤害并炸开，周围敌人3秒内受到80 + 60% 法强魔法伤害。
+（冷却 5 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>黏液沼泽：往敌人脚下吐一滩黏液，持续4秒，站在里面的敌人减速55%，每秒受到24 + 16% 法强魔法伤害。
+（冷却 8 秒 · 施放距离 60000 · 施放：地点 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>毒沼大嗝：肚子鼓起变大5秒（受到伤害-20%），向前打出大嗝，造成170 + 80% 法强魔法伤害并减速35%，毒雾留在地上4秒，每秒36 + 21% 法强魔法伤害。
+（冷却 40 秒 · 施放距离 60000 · 施放：地点 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_gromp.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
           <t>麦迪</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>Maddie</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>tft_maddie</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>步枪射击，造成100% 攻击力物理伤害。狙神：目标离得越远，她造成的伤害越高，最多+25%；被通缉的敌人阵亡时她领一份赏金：攻速+15%，最多4份。
 （攻击间隔 1.1 秒 · 攻击距离 68000）</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>连拨击锤：半蹲朝范围内最远的敌人连开6枪（先打英雄），每枪打中路上第一个敌人，造成10 + 40% 攻击力物理伤害。
 （冷却 9 秒 · 施放距离 80000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近当前生命最高的敌方英雄8秒：它受到的伤害+15%。
 （冷却 15 秒 · 施放距离 90000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>执法狙杀：瞄准后向生命比例最低的敌方英雄射出一发穿透子弹，路上每个敌人受到220 + 140% 攻击力物理伤害，按其已损失生命比例最多再加60%。
 （冷却 50 秒 · 施放距离 200000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="3" t="inlineStr">
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_maddie.md</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>深红锋喙鸟</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>Mama Beak</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>tft_raptor</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>甩出一根锋羽，造成100% 攻击力物理伤害。橙霸符：它的物理伤害使目标护甲-6（3秒，最多5层）。
 （攻击间隔 1.17 秒 · 攻击距离 60000）</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>羽刃扇射：张开翅膀，扇形甩出5根羽刃，每根命中第一个敌人，造成35 + 55% 攻击力物理伤害。
 （冷却 6 秒 · 施放距离 60000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>惊飞跃退：受惊尖叫，往后一跳，之后3秒攻速+70%。
 （冷却 9 秒 · 施放距离 35000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>鸟群之家：召唤4只不可选中的小锋喙鸟（7秒）：它每次普攻，小鸟们一起啄同一目标，各造成18 + 30% 攻击力物理伤害。
 （冷却 45 秒 · 施放距离 65000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="3" t="inlineStr">
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_raptor.md</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="3" t="inlineStr">
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="3" t="inlineStr">
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>小木灵</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>Meepsie</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>tft_meepsie</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>挥出月岩重拳，造成100% 攻击力物理伤害。木灵驾驶员：每一拳额外造成15 + 25% 法强魔法伤害。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>月尘震地：一拳砸向前方地面，扇形范围内的敌人受到100 + 70% 法强魔法伤害并减速40%（2秒）。
 （冷却 6 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>治疗木灵：驾驶员一招手，4只小木灵飞向身边生命比例最低的队友（名额有剩时也治疗自己），每0.5秒回复20 + 10% 法强生命，持续3秒。
 （冷却 9 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>宇宙大爆炸：跳向附近敌方英雄最多的地方砸地，周围的敌人受到160 + 90% 法强魔法伤害，离中心每远一格少35%；离落点最近的3个敌方英雄被击飞1.25秒。
 （冷却 35 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr">
         <is>
           <t>2.88</t>
         </is>
       </c>
-      <c r="K203" s="2" t="inlineStr"/>
-      <c r="L203" s="3" t="inlineStr">
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_meepsie.md</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>迅捷蟹</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>Scuttle Crab</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>tft_scuttlecrab</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>跳一段螃蟹舞，踩中身边所有敌人，造成100% 攻击力物理伤害。绿霸符：附近的友方英雄生命低于40%时回复12%最大生命（每人10秒一次）。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>疾行神龛：在脚下放下神龛（4秒），水花使周围敌人受到80 + 60% 法强魔法伤害并减速40%；神龛里的友方英雄移速+30%、攻速+25%。
 （冷却 7 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>蟹壳护盾：缩进壳里，获得120 + 60% 法强护盾（2秒）。护盾打光或到时间时蟹壳碎裂：周围敌人受到80 + 60% 法强魔法伤害、眩晕0.5秒并减速40%。
 （冷却 6 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>你挖得动吗？：钻入地下2.5秒：受到的伤害降低50%、免疫控制，持续回复250 + 80% 法强生命；然后钻出地面，周围敌人受到160 + 60% 攻击力物理伤害并被击飞1.5秒。
 （冷却 25 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr">
         <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="3" t="inlineStr">
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_scuttlecrab.md</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="3" t="inlineStr">
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L205"/>
+  <autoFilter ref="A1:L206"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13553,6 +13611,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId205"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -8871,8 +8871,8 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>卡莉丝塔附加包（league_kalista v0.1.3）
-武术姿态：每次投矛后自己判断往前还是往后：最近的敌方英雄残血（40% 以下），或者它在逃（越跑越远）而且快跑出射程（超过攻击距离 80%），就往前追；其余都往后跳开；身边没有敌方英雄时照主…
+          <t>卡莉丝塔附加包（league_kalista v0.2.0）
+武术姿态：每次投矛后自己判断往哪跳：最近的敌方英雄残血（40% 以下），或者它在逃（越跑越远）而且快跑出射程（超过攻击距离 80%），就往前追；贴到射程 60% 以内或正冲过来，就往后拉开…
 誓约者：开局绑定一名队友（辅助位优先，没有就最近的队友英雄，每条命出生时重新看），大招对誓约者施放
 命运的召唤：把誓约者拉进来保护、定身，然后逐 tick 飞向离她最近的敌方英雄现在的位置（90000 内，没有就两倍范围），到了就在脚下击飞周围敌人
 撕裂：另外按护甲算拔矛伤害，够杀就立刻拔（矛不够 3 根也拔）

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.46）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.47）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -11033,7 +11033,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -3462,7 +3462,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -2370,7 +2370,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -5308,7 +5308,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -2040,7 +2040,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>奥恩附加包（league_ornn v0.1.3）
+          <t>奥恩附加包（league_ornn v0.2.0）
 熔岩柱：真的地形：立在裂隙的尽头 4 秒，立起时把站在上面的单位推开，之后谁都走不进去（两边的英雄、小兵、野怪，他自己也算）
 E 的地震：撞上柱子或墙才地震：撞上目标的那一刻柱子够近（30000 加上柱子和他的半径），或冲撞方向 14000 内是墙（卡蜜尔附加包的墙格、地图的四边）；撞上的柱子随之碎掉
 易碎：记在每个英雄身上：只有带着易碎的英雄被他普攻打中才引爆（最大生命 8% 的真实伤害、击飞、从他身边击退）
@@ -11463,9 +11463,9 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.1.29）
+          <t>悠米附加包（league_yuumi v0.2.0）
 附身多久：不限时，队友死了才跳下来
-附身时能不能出招：能：Q、R、再给他一次旺盛精力，都从他头上放
+附身时能不能出招：能：Q、R、再给他一次旺盛精力（护盾 130 + 60% 法强 3 秒、攻速 +20%、移速 +10%），都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
 附身时队友回血：每秒 45 + 15% 法强，一直回
 猫的博爱：普攻或摸鱼飞弹命中英雄（附身时她不普攻）</t>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -11463,8 +11463,8 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.2.0）
-附身多久：不限时，队友死了才跳下来
+          <t>悠米附加包（league_yuumi v0.2.1）
+附身多久：不限时，队友死了才跳下来；骑着时看局势换人：宿主闲着就跳去打架的队友，去救快死的队友，跟着中单 / 下路
 附身时能不能出招：能：Q、R、再给他一次旺盛精力（护盾 130 + 60% 法强 3 秒、攻速 +20%、移速 +10%），都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
 附身时队友回血：每秒 45 + 15% 法强，一直回

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -693,7 +693,7 @@
         <is>
           <t>青钢影钩墙附加包（league_camille_wall v0.4.9）
 主包 league 保持纯数据、全平台可用；钩墙要读地图的墙，只能用原生代码，所以放在这个单独的附加包里。 装上后，青钢影的 E「钩索」钩墙、地图四边和防御塔，不再钩小兵、野怪；英雄、树林、草丛也不钩（墙就在树林里）。
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 卡蜜尔 E：E 好了、60000 内有敌方英雄就按，目标是最近的那个（钩墙附加包的 E 射程是 85000，取小的）。钩索、钩墙、冲向敌人照旧由主包 / 钩墙附加包决定</t>
         </is>
       </c>
@@ -756,7 +756,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>科加斯附加包（league_chogath v0.1.3）
+          <t>科加斯附加包（league_chogath v0.1.4）
 盛宴的层数：死后原样补回，层数一局里只增不减
 什么时候放盛宴：读射程内敌方英雄的生命、护盾、免死和受到伤害的增减，一口吃得死才放（几个时吃生命 + 护盾最少的，AI 没想放也放）；吃不死时 AI 想放就改成普攻那个人</t>
         </is>
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>蒙多附加包（league_drmundo v0.1.6）
+          <t>蒙多附加包（league_drmundo v0.1.7）
 想去哪就去哪：控制落下的那个 tick 就清掉（只认硬控：击飞、眩晕、定身、嘲讽、恐惧、魅惑、强制位移），扣当前生命的 7%，丢药罐；生命不满 85%、身边没有敌方英雄时走回去捡药罐（该放大招…
 病毒屠刀打英雄：按目标当前生命的 20% 算魔法伤害（至少是 Q 的基础伤害）
 大力行医：按他的已损生命最多再翻一倍；攻击力随额外生命（装备给的）涨 2.5%
@@ -1212,9 +1212,9 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>格温被动附加包（league_gwen v0.1.1）
+          <t>格温被动附加包（league_gwen v0.1.2）
 主包 league 保持纯数据。数据里能读目标最大生命值的只有真实伤害，读不到法强，所以主包格温的被动「千穿百孔」对英雄造成 1% 最大生命值的真实伤害（用户：「这个可以改rust」）。这个附加包用原生代码做成英雄联盟的样子： - 百分比最大生命值魔法伤害：原生效果 league_gwen:cuts 代替主包里那段真实伤害。被动每次打到敌方英雄（普攻、E …
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>艾瑞莉娅附加包：Q「利刃冲击」真正的刷新 + 跳兵线（league_irelia v0.1.2）
+          <t>艾瑞莉娅附加包：Q「利刃冲击」真正的刷新 + 跳兵线（league_irelia v0.1.3）
 - E「比翼双刃」、R「先锋之刃」打中英雄时，在她自己身上挂一面旗子 mk 代替印记，下一次 Q 施放时附近有敌方英雄就算「打到了带印记的」； - Q 打死目标靠 league_jinx 的击杀触发器（一个 3 tick 的持续效果在目标活着时拿掉旗子）近似。</t>
         </is>
       </c>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>杰斯附加包（league_jayce v0.1.1）
+          <t>杰斯附加包（league_jayce v0.1.2）
 炮形态的样子：整个身体都是炮：待机、跑步、受击播 c_idle / c_run / c_hit（只在游戏 0.6.4 上，别的版本退回左边那样）；阵亡还是锤子的倒地
 雷霆一击往哪推：打中的敌方英雄推向他这边：8 万内有他的友方英雄就推向它们的中心，没有就推向离目标最近的己方塔；这个方向 35000 内碰到墙就左右最多偏 60°，都不行（或者没有友方和塔）才笔…
 加速电炮打谁：射程内、线上没有别的英雄挡着（电炮停在第一个英雄身上）的敌方英雄：这一炮打得死的先（生命 + 护盾不超过估算的伤害，按护甲打折），再是受了伤的里生命比例最低的，都满血就挑最远的</t>
@@ -1594,7 +1594,7 @@
         <is>
           <t>凯尔升阶附加包：按真实等级升阶、死后不掉（league_kayle v0.2.0）
 这个附加包把主包的凯尔换成 override/ 里的副本（make_override.py 生成），和主包有两处不同：
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>奥恩附加包（league_ornn v0.2.0）
+          <t>奥恩附加包（league_ornn v0.2.1）
 熔岩柱：真的地形：立在裂隙的尽头 4 秒，立起时把站在上面的单位推开，之后谁都走不进去（两边的英雄、小兵、野怪，他自己也算）
 E 的地震：撞上柱子或墙才地震：撞上目标的那一刻柱子够近（30000 加上柱子和他的半径），或冲撞方向 14000 内是墙（卡蜜尔附加包的墙格、地图的四边）；撞上的柱子随之碎掉
 易碎：记在每个英雄身上：只有带着易碎的英雄被他普攻打中才引爆（最大生命 8% 的真实伤害、击飞、从他身边击退）
@@ -2107,7 +2107,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>奎因附加包（league_quinn v0.2.0）
+          <t>奎因附加包（league_quinn v0.3.0）
 深入敌后：照英雄联盟骑着跑：骑上华洛 6 秒，移速 +80%，她照常走位；骑着时下一次普攻、技能 1 或技能 2 会先施放鹰翼天翔，6 秒到了也会自动落地施放
 旋翔掠杀：踢完往冲过来的方向翻回去约一个攻击距离（4000 x 12 tick，被控就停；用户 2026-10-22：「奎因E完人不会拉开距离」）
 骑乘的样子：整身换形态：骑着的 6 秒里站着、走着、挨打都是骑在华洛背上（r_idle / r_run / r_hit）</t>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>提莫蘑菇附加包（league_teemo_shrooms v0.2.1）
+          <t>提莫蘑菇附加包（league_teemo_shrooms v0.2.2）
 蘑菇在地上多久：3 分钟（10800 tick），提莫阵亡也在；最多 9 个，再多收掉最早的
 扔、布好、踩发距离 8000、毒云 30000 内中毒 4 秒共 100 + 48% 法强、减速 40% 2 秒、画面：一样
 往哪扔：打架时一样；不打架时往身边最近的草丛里种（0.2.0：R 留一次充能给打架，没埋过的草丛、不在自家基地）</t>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>厄加特附加包（league_urgot v0.2.1）
+          <t>厄加特附加包（league_urgot v0.2.2）
 回响烈焰：六条腿各朝一个方向（每条 60°）、各自冷却：子弹落在哪边，就由朝那边的两条腿里冷却好的那条喷（英雄联盟：普攻落在哪条腿的扇形里就是哪条）；每条腿冷却是主包的 2 倍，朝着目标的…
 超越死亡的恐惧：只处决生命低于 25% 的（英雄联盟的处决线）：拴满时读目标当前生命，低于 25% 才拽回来处决；血多的只吃钻头的伤害和减速
 鄙弃：一定甩到他身后、朝他冲过来的那一边：出手时记下起跳的位置，抓住 0.25 秒后 3 tick 内把目标挪到他身后 15000 处（英雄联盟：从头顶甩到背后，拖回自己这边）（用户 …</t>
@@ -2812,7 +2812,7 @@
         <is>
           <t>弗拉基米尔残血血池附加包（league_vladimir_pool v0.2.0）
 主包 league 保持纯数据。数据读不到当前生命，主包里弗拉基米尔的 W「血红之池」是自动的：他身上一直跑着一个每 3 tick 看一次的轮询， 看到 league_vladimir_w_go 就化成血池（2 秒不可选取、脚下敌人减速吸血、20 秒冷却）；w_go 由普攻里的危险信号加上—— 两名以上敌方英雄贴身，或连续两次检查都挨了打。用户选了「危险信…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 弗拉基米尔 R（v0.4.0）：60000 内最近被我方打过的敌方英雄生命不到一半，或他身边 26000（血云半径）内有两个以上敌方英雄；生命比例最低的在前</t>
         </is>
       </c>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>伊莉丝附加包（league_elise v0.1.1）
+          <t>伊莉丝附加包（league_elise v0.1.2）
 蜘蛛形态的样子：整个身体都是蜘蛛：待机、跑步、受击、阵亡播 c_idle / c_run / c_hit / c_dead（只在游戏 0.6.4 上，别的版本退回左边那样）；复活是人形
 结茧打谁：线上没有小兵、野怪、别的英雄挡着的英雄：被控住的先（必中），再挑最近的；都被挡着才挑最近的英雄
 盘丝落到谁身上：生命比例最低的英雄（一样低就近的）
@@ -3456,7 +3456,7 @@
         <is>
           <t>斩杀附加包：伊芙琳、阿卡丽、锐雯（league_executes v0.2.0）
 伊芙琳 R：150 + 75% 法强，对生命不高于 30% 的目标 ×2.4
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 费德提克 R：他生命 ≥ 40%；80000 内的敌方英雄脚下 45000 内有两个以上（挑人最多的一处，一样多挑残血），或只有一个但生命不到 40%；那里不在敌方塔下；那里 60000 内的…</t>
         </is>
       </c>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>盲僧 W 位移附加包（league_leesin_hop v0.1.11）
+          <t>盲僧 W 位移附加包（league_leesin_hop v0.1.12）
 主包 league 保持纯数据。主包的李青不能「摸眼」：R 身后没人时直接冲过目标落到他身后回旋踢，W 并进了 E、不冲刺。 英雄联盟手游里李青的 W 不用插眼就能冲到一个点，这个附加包照这个做（不画眼）： - 回旋踢（照高手的打法，v0.1.6）：R 时目标身后没有别的敌方英雄（有人就照旧正面踢进人堆），第 7 tick 先定往哪踢—— 踢回自己队伍那边…</t>
         </is>
       </c>
@@ -5302,7 +5302,7 @@
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
 附身后的招式：按那个英雄的类别换成五套招式之一：近战（重斩、震地减速、冲锋眩晕）、射手（远程射击、穿透射击、三连射）、法师（法球、溅射爆发、定身）、辅助（远程射击、治疗周围友方英雄、减速周围敌…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -5748,9 +5748,9 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>艾尼维亚附加包（league_anivia v0.1.4）
+          <t>艾尼维亚附加包（league_anivia v0.1.5）
 寒霜涅槃：受到致命伤害时不倒下，变成冰蛋 egg_t tick（6 秒）：生命回满当作蛋的生命，禁普攻、禁技能，双抗降低；蛋被打碎才阵亡（击杀算打碎蛋的人），撑过去就带着蛋剩下的生命孵化。…
-寒冰屏障（Q 晕到英雄时立墙）：真的墙：5 秒里任何单位（两边的英雄、小兵、野怪，她自己也算）的中心一进墙就放回上一 tick 的位置；立墙时站在墙上的被推到她那一侧（墙在被晕的人身后，和主包一样）
+寒冰屏障（Q 晕到英雄时立墙）：真的墙：5 秒里任何单位（两边的英雄、小兵、野怪，她自己也算）的中心一进墙：走路的贴着墙滑（这一步顺着墙的那一份照走，进墙的那一份只走到墙面），冲刺的放回上一 tick 的位置；…
 霜寒刺骨翻倍：目标身上有冰冻标记（被寒冰闪耀穿过或引爆、被成形的风暴打中后 3 秒，数据挂在每个目标身上，头顶一枚雪花）就翻倍，按每个目标判断</t>
         </is>
       </c>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>奥瑞利安·索尔附加包（league_aurelionsol v0.2.0）
+          <t>奥瑞利安·索尔附加包（league_aurelionsol v0.2.1）
 星海焕然（星尘）：活着时记下每一层，死亡清掉后原样补回（最多 d_max 层，范围的档位跟着回来）
 星芒凝汇（黑洞中心）：同样的伤害，另外英雄生命低于 e_low% + 每层星尘 e_low_d%（只算前 e_low_n 层：默认 5% + 1%/层，最多 20%）就直接处决</t>
         </is>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>阿兹尔附加包（league_azir v0.1.8）
+          <t>阿兹尔附加包（league_azir v0.1.9）
 太阳圆盘（并入被动，英雄联盟的「恕瑞玛的传承」）：开局记下我方每座塔；每局一次，某座塔倒了、阿兹尔走到废墟 d_near（60000）内、废墟 d_range（45000）内有敌人时，圆盘从沙里升起，立 d_life tick（…
 禁军之墙的禁军：按阿兹尔到大招目标的方向朝左或朝右（反推时他已经绕到目标身后，禁军就朝回冲）；伤害还是数据那道墙的。墙停下后再立 3 秒，敌方英雄走不过去；墙打中的敌人被带到墙停下的地方外面（正…
 沙兵（用户：「沙兵没攻击动作 你想办法补吧 不让codex了 还有不面向敌人」）：从侧面画：升起，之后每 ss_stand tick（4）盖一次站姿，朝 60 像素内最近的敌人（先英雄，敌人正好在它上下方时不转）；刺过以后下一次改放刺击（ss_stab tic…
@@ -6382,7 +6382,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>黑默丁格附加包（league_heimerdinger v0.2.1）
+          <t>黑默丁格附加包（league_heimerdinger v0.2.2）
 炮台的样子：侧面、炮口朝目标那边（用户：「炮台改成侧面朝敌人」）：英雄联盟模型的侧面，PPU 1.75（用户：「灵活利用PPU 炮也可以调的清晰」，PPU 3 时又「炮太高清了 降低点像素」…
 炮台出手：炮弹（t_shot）、充能光束（t_beam_line）、巨型炮台的等离子弹（x_shot）从侧面炮台的炮口飞向目标，飞到才扣血
 打谁：同样的顺序，每档里打最近的
@@ -6636,7 +6636,7 @@
           <t>卡特琳娜附加包（league_katarina v0.1.1）
 瞬步：另外瞬步一好就自己判断：射程内哪把匕首旁有敌方英雄就跳过去（那里生命比例最低的英雄优先），落地捡刀旋斩、冷却缩短，接着跳下一把——匕首循环；生命低于 30% 而身边有敌方英雄时，…
 贪婪：她参与的每一次英雄击杀（击杀或助攻）都刷新，几个人同时阵亡各算一次
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …
 卡特琳娜 R：她生命 ≥ 30%、自己不在敌方塔下（目标残血除外）；25000 内的敌方英雄，身边 50000 内有两个以上，或目标生命不到一半</t>
         </is>
@@ -7088,7 +7088,7 @@
 E 送给谁：送给最危险的队友：身边有敌方英雄的队友里，近一秒受到的伤害比例 × 2 + 已损失生命比例最高的；她自己身边有敌人而且更危险时留给自己
 R 什么时候放：同主包；每个人能不能被冲击波打死照样算（按他的魔抗：伤害 × 100 / (100 + 魔抗)），写进日志（v0.1.0 是「2 个敌方英雄或能打死 1 个」，用户：「发条的大招…
 补兵：走上去补刀（v0.2.0）：附近没有敌方英雄时，普攻距离内的小兵先打这一下打得死的、其次血最少的；60k 内的兵线走上去打；塔下要有己方小兵扛塔才去
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 奥莉安娜 E、基兰 E：在打架：她 / 他或射程内的队友 40000 内有敌方英雄（基兰也追射程内生命不到 40% 的）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 瑞兹 R（备好式）：逃命：生命不到 35% 而 60000 内有敌方英雄；去打架：照崔斯特的规则（身边没敌人、远处队友在打）。传到哪里由主包判断</t>
         </is>
       </c>
@@ -7345,7 +7345,7 @@
         <is>
           <t>辛德拉举小兵附加包（league_syndra v0.1.1）
 这个附加包把主包的辛德拉换成 override/ 里的副本（make_override.py 用 tools/kit/build_syndra.py 的 --native 生成：技能 一样，W 施放时在她身上挂 league_syndra_w_grab、在投掷目标身上挂 league_syndra_w_at；她身上有 league_syndra_w_uni…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 辛德拉 R：75000 内的敌方英雄生命不到 60%、被控住，或射程内有两个以上；主包再按法球数和控制决定立刻放还是待命 8 秒（没用上退还冷却）</t>
         </is>
       </c>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 崔斯特 R：只在主包会传送的局面按：他身边 75000 内没有敌方英雄、生命不低于 40%，而且离他 100000–340000 有队友 50000 内贴着敌方英雄（在打架）。之后揭示、引导…</t>
         </is>
       </c>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
@@ -7978,9 +7978,9 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>永恩 R 附加包（league_yone_r v0.1.1）
-落在哪里：直线上离他最远的那个被斩中的英雄身后 6000（一个都没斩中就照主包，落在 90000 内最近的敌方英雄身后）
-拉人：落地后把斩中的英雄拉向他（每 tick 2000，每个最多 16000，停在他身前 6000）
+          <t>永恩 R 附加包（league_yone_r v0.1.2）
+落在哪里：直线上离他最远的那个被斩中的英雄身后、他身体外面（两人里大的身体半径 + 1000；一个都没斩中就照主包，落在 90000 内最近的敌方英雄身后）
+拉人：落地后把斩中的英雄拉向他（每 tick 2000，每个最多 16000，停在他身前 12000）
 伤害、击飞、画面、Q3 连 R：一样</t>
         </is>
       </c>
@@ -8045,7 +8045,7 @@
         <is>
           <t>劫读血附加包（league_zed_mark v0.1.3）
 主包 league 保持纯数据。数据读不到生命也读不到伤害，所以主包里劫的两处是替代做法： - 被动「影忍法！灭魂劫」：英雄联盟里是攻击生命低于 50% 的英雄时附加其最大生命的伤害；主包改成「技能刚打中过英雄」后的下一次普攻（league_zed_cw_ready），附加 6% 最大生命真实伤害，10 秒一次。 - 大招「禁奥义！瞬狱影杀阵」：英雄联盟里…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 劫 W、格温 E、佛耶戈 E、卡特琳娜 W（冲上去的）：他生命 ≥ 40%；射程内（劫 55000、格温 45000、佛耶戈 46000、卡特琳娜 55000，引擎只接最近被我方打过的）的敌方英雄，不在敌方塔下（75000 内；生命 …</t>
         </is>
       </c>
@@ -8378,7 +8378,7 @@
 武器在手里：整身换武器：主手是断魄 / 坠明 / 荧焰 / 折镜时，站着、跑着、挨打、出手的第一刻都画成那把武器在手里（只在游戏 0.6.4 上）
 打空换枪：先进先出的队列（英雄联盟）：打空的那把排到队尾，换上队列最前面的那把；W 换过手以后和固定循环不一样
 残血：另外生命低于 35%、副手是断魄、60000 内有看得见的敌方英雄时直接换上断魄（吸血），每 6 秒最多一次
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 厄斐琉斯 R（备好式，v0.4.0）：90000 内有敌方英雄就按：主包待命 6 秒，正被我方打的敌方英雄身边还有别人、或被控住才放，没用上缩短冷却</t>
         </is>
       </c>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>凯特琳附加包（league_caitlyn v0.1.0）
+          <t>凯特琳附加包（league_caitlyn v0.1.1）
 经典引擎模拟（下路对 4 个原版射手、3 套阵容、两边、8 个种子）：她前 5 分钟击杀差 +0.38（金克丝 +1.29、艾希 +0.95、 厄运小姐 +0.90），10 分钟 +1.65，前期伤害只有别的射手的六七成。加攻击、加 Q 伤害、加爆头、出手加快、Q 只能对英雄放等 9 个数值方案，前期最多 +0.6 左右，能拉高前期的也让后期太强。跟踪一局…</t>
         </is>
       </c>
@@ -8682,7 +8682,7 @@
 额外攻速：不变快；每 1% 换成 0.25% 攻击力（+40% 攻速 = +10% 攻击力）
 攻速减益：一样
 低语、第四发、装弹：一样
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 泽拉斯 R、烬 R（站着引导）：自己身边 45000 内没有敌方英雄、生命 ≥ 40%；射程内（泽拉斯取 160000、烬取 140000）生命不到一半的，或我方有人 40000 内贴着的敌方英雄，挑生命比例最…</t>
         </is>
       </c>
@@ -8876,7 +8876,7 @@
 誓约者：开局绑定一名队友（辅助位优先，没有就最近的队友英雄，每条命出生时重新看），大招对誓约者施放
 命运的召唤：把誓约者拉进来保护、定身，然后逐 tick 飞向离她最近的敌方英雄现在的位置（90000 内，没有就两倍范围），到了就在脚下击飞周围敌人
 撕裂：另外按护甲算拔矛伤害，够杀就立刻拔（矛不够 3 根也拔）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 卡莉丝塔 E：主包「矛够了」的标记（league_kalista_e_ok）在、撕裂不在冷却（league_kalista_e_cd）：按下就是撕裂，不会空按</t>
         </is>
       </c>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 克格莫 R：R 好了、射程（130000）内有引擎接受的敌方英雄（主包 R 只打最近被我方打过的）就按，先挑生命比例最低的（大招打残血更痛）。一轮三发、之后锁 20 秒都是主包的数据。不限时…</t>
         </is>
       </c>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>梅尔附加包（league_mel v0.1.3）
+          <t>梅尔附加包（league_mel v0.1.4）
 主包 league 保持纯数据。用户选了「做附加包」，又要求「有连招要做连招」。主包的数据做不到英雄联盟里梅尔的两件事——夺命残影的处决（数据读不到生命，也数不了目标身上的层数）和灵魂折镜的反弹（没有效果能挡住或拐弯一个弹体）——所以放在这个附加包里用原生代码做，外加连招： - 夺命残影的处决：英雄联盟里梅尔每次打中都叠一层残影，残影的伤害够了，下一次打中…</t>
         </is>
       </c>
@@ -9260,7 +9260,7 @@
           <t>莎弥拉边走边射附加包（league_samira_r v0.1.0）
 R 期间：旋转连射，同时走向 90000 内生命 + 护盾最少的敌方英雄，走到 30000 内站住；被硬控时不走
 枪、伤害、生命偷取、画面：主包（一样）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 莎弥拉 R：R 好了、R 射程（50000）内有敌方英雄就按，目标是最近的那个。S 评价时这一下就放出炼狱扳机，不到 S 就备好 330 tick，期间到了 S 再放
 莎弥拉 E、Q（攒评价）：S 要连着换五种出手打中英雄（枪 / 剑普攻、Q、E 冲刺、落地的 W 旋转），一下打不中 9 秒就掉。R 不按时：60000 内有敌方英雄、她生命不低于 50%、目标身边的敌方…</t>
         </is>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 希维尔 E：60000 内的敌方英雄刚放了技能（20 tick 内技能冷却开始走），或她生命不到 40% 而 40000 内有敌方英雄</t>
         </is>
       </c>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>韦鲁斯枯萎附加包（league_varus_blight v0.1.0）
+          <t>韦鲁斯枯萎附加包（league_varus_blight v0.1.1）
 枯萎记在哪里：每个敌方英雄自己身上（各最多 3 层，6 秒）
 引爆：按被打中的那个人身上的层数，数字一样
 引爆返还冷却：每层把 Q、E 的剩余冷却减 13%，不压 R
@@ -9644,8 +9644,9 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>薇恩圣银弩箭附加包（league_vayne_bolts v0.1.1）
-主包 league 保持纯数据。数据分不清一次攻击打中的是谁，所以主包里圣银弩箭的两层记在薇恩自己身上：她轮流打两个人也会凑满 3 下，在第三个被打中的人身上爆。这个附加包用原生代码做成英雄联盟的样子：同一个目标连续挨 3 下才爆。</t>
+          <t>薇恩附加包：圣银弩箭、恶魔审判撞墙（league_vayne_bolts v0.2.0）
+圣银弩箭：同一个目标连续挨 3 下才爆
+恶魔审判：被推到墙上（地图的墙格、5v5 地图的四边）才再受 30 + 35% 攻击力的伤害并眩晕 1 秒；没撞墙只击退</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -9837,7 +9838,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>泽丽附加包：W 撞墙激光 + 被动偷盾（league_zeri v0.1.3）
+          <t>泽丽附加包：W 撞墙激光 + 被动偷盾（league_zeri v0.1.4）
 - W「强穿激光」的脉冲先打中小兵或野怪时才在那里化为长激光（小兵代替墙）； - 被动「内能迁转」的电击弹打中英雄时给自己一个小护盾（代替偷盾）。</t>
         </is>
       </c>
@@ -10152,7 +10153,7 @@
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 迦娜 E 风暴之眼（50000 内）：有危险的队友（生命不高于 50%，或身边 25000 内有 2 个以上敌方英雄）里生命比例最低的；都没危险就给离敌方英雄最近的（正在打的那个）
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 迦娜 R：她或身边 40000 内的队友生命不到 35% 而 50000 内有敌方英雄，或两人以上生命不到 60% 而她身边有敌方英雄。对生命最低的那位放（治疗是她身边一圈，对谁放都一样）</t>
         </is>
       </c>
@@ -10215,7 +10216,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+          <t>游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 凯尔、卡尔玛、伊芙琳、奥莉安娜的 R（备好式）：身边有敌方英雄就按（凯尔 50000、卡尔玛 70000、伊芙琳 45000、奥莉安娜 60000）：这几个 R 格只是「备好」，主包在之后几秒里自己判断时机放出，没用上退还冷却…</t>
         </is>
       </c>
@@ -10399,7 +10400,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>茂凯附加包（league_maokai v0.1.0）
+          <t>茂凯附加包（league_maokai v0.1.1）
 吸元秘术回血：按等级回复最大生命的 4.5%–12%（英雄联盟）
 吸元秘术就绪：他的技能命中敌人后，或被敌方英雄的技能打中后（近似：打他的敌方英雄的技能、技能 2 或大招在 1.5 秒内刚进入冷却，就算技能打中——原生被动收到伤害时分不出普攻和技能）
 草丛里的树苗：读地图的草丛格子；立在草丛里的树苗爆炸半径更大（34000）、伤害 ×1.6、减速 45%（英雄联盟草丛里的树苗更强）</t>
@@ -11150,7 +11151,7 @@
         <is>
           <t>辅助挑人附加包：迦娜、娑娜、璐璐（league_support_pick v0.1.0）
 娑娜 W 回血（60000 内）：损失生命最多的队友
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 娑娜 W：她或 60000 内的队友生命不到 70%，射程内有敌方英雄</t>
         </is>
       </c>
@@ -11463,7 +11464,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.2.1）
+          <t>悠米附加包（league_yuumi v0.2.2）
 附身多久：不限时，队友死了才跳下来；骑着时看局势换人：宿主闲着就跳去打架的队友，去救快死的队友，跟着中单 / 下路
 附身时能不能出招：能：Q、R、再给他一次旺盛精力（护盾 130 + 60% 法强 3 秒、攻速 +20%、移速 +10%），都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -11532,7 +11533,7 @@
         <is>
           <t>基兰复活附加包（league_zilean_rewind v0.2.0）
 主包 league 保持纯数据。主包里基兰的 R 由 AI 在敌方英雄 60000 内时放出、待命 900 tick（没用上就退还冷却）； 待命期间他每次出手查一次：附近有被控制的友方英雄、或自己被两名以上敌方英雄贴身，才给那个人挂 5 秒的时光符文 （league_zilean_r_rune，带「不死」，生命最低停在 1），到第 299 tick 不管有…
-游戏 AI 不按的技能替它按（league_ult_press v0.5.7）
+游戏 AI 不按的技能替它按（league_ult_press v0.5.8）
 奥莉安娜 E、基兰 E：在打架：她 / 他或射程内的队友 40000 内有敌方英雄（基兰也追射程内生命不到 40% 的）</t>
         </is>
       </c>

--- a/docs/heroes.xlsx
+++ b/docs/heroes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="英雄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'英雄'!$A$1:$L$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>俄洛伊附加包（league_illaoi v0.2.43）
+          <t>俄洛伊附加包（league_illaoi v0.2.44）
 触手长在哪：按被动自己的冷却长（1 级 p_cd_1、18 级 p_cd_18，英雄联盟 20 – 10 秒，不再跟着普攻长），长在她附近最近的墙边（p_reach 内，没墙就在她身边 t_…
 触手抽谁：平时不动（英雄联盟）：严酷训诫打中的人（够得着的每条依次抽一下）、灵魂被扯出来的英雄和躯壳（每 t_per tick）；Q 并进被动：她打中敌人时够得着的触手抽一下（q_cd 一…
 灵魂分担伤害：只有她打他的每一下（普攻和技能，on_attack）多算 e_echo%，和英雄联盟打灵魂传到本体一样只算她的
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.47）
+          <t>佛耶戈「君命已决」附加包（league_viego_soul v0.2.48）
 什么时候附身：读每个敌方英雄的死亡：他 3 秒内打过的英雄一死就算他的功劳，每个都算
 灵魂在哪：尸体那里留下灵魂 8 秒，35000 以内直接附身，90000 以内他冲过去附身（照英雄联盟要去拿那个灵魂）
 附身后的样子：整个身体变成被附身的那个英雄：站、跑、出招、挨打都是那个英雄的图（只在游戏 0.6.4 上，别的版本退回左边那样）
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>妮蔻附加包（league_neeko v0.1.4）
+          <t>妮蔻附加包（league_neeko v0.1.5）
 天生幻魅：脱战 2 秒后整个身体画成最近的友方英雄（站、跑、出招、挨打都用他的图）；放技能、被控（击飞、晕眩、禁锢、嘲讽、恐惧、魅惑、强制位移）、假扮以来挨了她 35% 最大生命的伤害、或…</t>
         </is>
       </c>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>塞拉斯附加包（league_sylas v0.2.43）
+          <t>塞拉斯附加包（league_sylas v0.2.44）
 主包 league 保持纯数据。用户选了「做，含按类别偷大招+连招」，又要求「有连招要做连招」。主包的数据复制不了别的英雄的大招，也读不到当前生命，所以这两件事放在这个附加包里用原生代码做，外加连招： - 其人之道：偷到谁就放谁的大招（0.2.0，用户：「塞拉斯偷到谁就放谁的真大招」「只用管LOL的」）：偷到本包的英雄联盟英雄（src/stealable.…</t>
         </is>
       </c>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>悠米附加包（league_yuumi v0.2.1）
+          <t>悠米附加包（league_yuumi v0.2.3）
 附身多久：不限时，队友死了才跳下来；骑着时看局势换人：宿主闲着就跳去打架的队友，去救快死的队友，跟着中单 / 下路
 附身时能不能出招：能：Q、R、再给他一次旺盛精力（护盾 130 + 60% 法强 3 秒、攻速 +20%、移速 +10%），都从他头上放
 附身时谁能打到她：平时谁都打不到（一段一段地放逐）；出招的那一小段受到的伤害 -100%、免控
@@ -13117,295 +13117,353 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
+          <t>苍蓝哨戒</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Pebbles</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>tft_sentry</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>蓝核射出碎光弹，造成100% 攻击力物理伤害和45% 法强魔法伤害。青霸符：蔚蓝激光每引导1秒，大招冷却-1秒。
+（攻击间隔 1.2 秒 · 攻击距离 60000）</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>蔚蓝激光：对目标引导激光2.5秒（可以边飘边照），共造成460 + 250% 法强魔法伤害，每0.25秒魔抗-4（可叠加，持续2秒）。目标离开射程或自己被控时中断。
+（冷却 6 秒 · 施放距离 65000 · 施放：指定目标 · 敌人（不含防御塔））</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>裂石跃迁：两块石头猛地分开再合拢，周围敌人受到80 + 45% 法强魔法伤害并减速40%（1.5秒），自己向后闪开。
+（冷却 10 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>棱镜扫射：两块石头张开，蓝核射出光柱扫过前方扇形，造成320 + 160% 法强魔法伤害，魔抗-25（3秒）。
+（冷却 35 秒 · 施放距离 70000 · 施放：地点 · 敌方英雄）</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_sentry.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
           <t>艾达丝</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>Idas</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>tft_idas</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>挥爪造成100% 攻击力物理伤害。护卫之誓：生命值低于50%时，她和最近的一名友军各获得她最大生命值18%的护盾（5秒），每30秒一次。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>黄金龙息：向前喷出扇形金色龙息，造成110 + 70% 法强魔法伤害，护甲降低35%（4秒）。
 （冷却 5 秒 · 施放距离 35000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>龙威振翅：振翅一吼：附近的敌人眩晕0.75秒并减速50%（2秒）；她和附近友军获得50 + 30% 法强护盾（3秒）。
 （冷却 9 秒 · 施放距离 55000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>黄金龙鳞：双翼裹身2秒，受到的伤害降低60%；然后回复200 + 60% 法强生命值，附近友军获得150 + 50% 法强护盾（5秒），护盾在时攻速+30%。
 （冷却 25 秒 · 施放距离 70000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="3" t="inlineStr">
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_idas.md</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>洛里斯</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>Loris</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>tft_loris</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>举盾猛砸，造成100% 攻击力物理伤害。神盾使：每条命第一次生命低于75%和25%时，各获得最大生命12%的护盾（4秒）。
 （攻击间隔 1.4 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>皮城争斗：获得70 + 50% 法强的护盾（4秒），举盾冲锋，撞到的敌人受到110 + 70% 法强魔法伤害并晕眩1.5秒。
 （冷却 7 秒 · 施放距离 42000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>盾卫：冲到附近生命比例最低的友方英雄身边，两人各获得70 + 45% 法强的护盾（4秒），期间替他承受30%的伤害。
 （冷却 10 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>钢铁防线：把巨盾砸进地里，周围的敌人受到220 + 80% 法强魔法伤害、被击飞1秒并嘲讽2秒；自己受到的伤害降低50%（4秒）。
 （冷却 50 秒 · 施放距离 30000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K203" s="2" t="inlineStr"/>
-      <c r="L203" s="3" t="inlineStr">
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_loris.md</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>小木灵</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>Meepsie</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>tft_meepsie</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>挥出月岩重拳，造成100% 攻击力物理伤害。木灵驾驶员：每一拳额外造成15 + 25% 法强魔法伤害。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>月尘震地：一拳砸向前方地面，扇形范围内的敌人受到100 + 70% 法强魔法伤害并减速40%（2秒）。
 （冷却 6 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>治疗木灵：驾驶员一招手，4只小木灵飞向身边生命比例最低的队友（名额有剩时也治疗自己），每0.5秒回复20 + 10% 法强生命，持续3秒。
 （冷却 9 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>宇宙大爆炸：跳向附近敌方英雄最多的地方砸地，周围的敌人受到160 + 90% 法强魔法伤害，离中心每远一格少35%；离落点最近的3个敌方英雄被击飞1.25秒。
 （冷却 35 秒 · 施放距离 45000 · 施放：指定目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr">
         <is>
           <t>2.88</t>
         </is>
       </c>
-      <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="3" t="inlineStr">
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_meepsie.md</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>迅捷蟹</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>Scuttle Crab</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>tft_scuttlecrab</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>跳一段螃蟹舞，踩中身边所有敌人，造成100% 攻击力物理伤害。绿霸符：附近的友方英雄生命低于40%时回复12%最大生命（每人10秒一次）。
 （攻击间隔 1.33 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>疾行神龛：在脚下放下神龛（4秒），水花使周围敌人受到80 + 60% 法强魔法伤害并减速40%；神龛里的友方英雄移速+30%、攻速+25%。
 （冷却 7 秒 · 施放距离 60000 · 施放：无目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>蟹壳护盾：缩进壳里，获得120 + 60% 法强护盾（2秒）。护盾打光或到时间时蟹壳碎裂：周围敌人受到80 + 60% 法强魔法伤害、眩晕0.5秒并减速40%。
 （冷却 6 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>你挖得动吗？：钻入地下2.5秒：受到的伤害降低50%、免疫控制，持续回复250 + 80% 法强生命；然后钻出地面，周围敌人受到160 + 60% 攻击力物理伤害并被击飞1.5秒。
 （冷却 25 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr">
         <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="3" t="inlineStr">
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_scuttlecrab.md</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>斯特卜</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>Steb</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
         <is>
           <t>tft_steb</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>双警棍轮流打击，造成100% 攻击力物理伤害。战地医疗：自己受到治疗时，最近的2名友方英雄也回复该治疗量的25%。
 （攻击间隔 1.5 秒 · 攻击距离 25000）</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>战地医疗：给自己打一针，回复120 + 60% 法强生命，再重击目标造成170 + 120% 法强魔法伤害并眩晕0.75秒。
 （冷却 5.5 秒 · 施放距离 30000 · 施放：指定目标 · 敌人（不含防御塔））</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>通缉令：通缉附近生命最高的敌方英雄5秒：它受到的伤害提高25%；它在通缉中阵亡时，自己和附近友方攻速提高30%（5秒）。
 （冷却 10 秒 · 施放距离 60000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>医疗背包：打开医疗背包：自己和周围友方英雄获得120 + 50% 法强的护盾（4秒），自己减伤30%；之后每0.5秒为周围友方回复25 + 12% 法强生命，共6次。
 （冷却 40 秒 · 施放距离 50000 · 施放：无目标 · 敌方英雄）</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr">
+      <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="3" t="inlineStr">
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="3" t="inlineStr">
         <is>
           <t>https://github.com/BoDUD/TFM2-League-Heroes/blob/main/docs/heroes/tft_steb.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L206"/>
+  <autoFilter ref="A1:L207"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -13612,6 +13670,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId206"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
